--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/10 22:56:10</t>
+          <t>2026/06/10 23:56:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:06:10</t>
+          <t>167:06:10</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026/06/10 22:49:56</t>
+          <t>2026/06/10 23:49:59</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>03:58:20</t>
+          <t>04:58:23</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026/06/10 21:57:22</t>
+          <t>2026/06/10 23:57:22</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L167" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/11 22:56:10</t>
+          <t>2026/06/11 23:56:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026/06/11 22:57:22</t>
+          <t>2026/06/11 23:57:27</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>53:48:44</t>
+          <t>54:48:49</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/06/11 22:52:36</t>
+          <t>2026/06/11 23:52:36</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>04:03:30</t>
+          <t>05:03:30</t>
         </is>
       </c>
       <c r="L161" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/06/12 22:56:08</t>
+          <t>2026/06/12 23:56:08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>165:59:59</t>
+          <t>166:59:59</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/06/12 22:57:22</t>
+          <t>2026/06/12 23:57:21</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>77:48:44</t>
+          <t>78:48:43</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/06/12 22:46:50</t>
+          <t>2026/06/12 23:46:40</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>29:57:47</t>
+          <t>30:57:37</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/06/12 22:49:34</t>
+          <t>2026/06/12 23:49:34</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>01:04:15</t>
+          <t>02:04:15</t>
         </is>
       </c>
       <c r="L154" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/06/13 22:57:37</t>
+          <t>2026/06/13 23:57:21</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>101:48:59</t>
+          <t>102:48:43</t>
         </is>
       </c>
       <c r="L108" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/06/15 22:57:33</t>
+          <t>2026/06/15 23:57:53</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>149:48:55</t>
+          <t>150:49:15</t>
         </is>
       </c>
       <c r="L86" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/06/17 22:57:24</t>
+          <t>2026/06/17 23:56:58</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>166:50:48</t>
+          <t>167:50:22</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/06/17 22:56:10</t>
+          <t>2026/06/17 23:56:10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/06/17 21:53:19</t>
+          <t>2026/06/17 23:53:19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>04:11:14</t>
+          <t>06:11:14</t>
         </is>
       </c>
       <c r="L148" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N153"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7966,11 +7966,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SLP20250627045</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,165 +7979,165 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/06/15 16:57:33</t>
+          <t>2026/06/15 14:07:26</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-34.579669, -70.961426</t>
+          <t>-33.38846, -70.617173</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-34.57967, -70.96143</t>
+          <t>-33.38846, -70.61717</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/06/16 01:37:04</t>
+          <t>2026/06/15 18:13:36</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-34.579474, -70.961408</t>
+          <t>-33.388382, -70.617199</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-34.57947, -70.96141</t>
+          <t>-33.38838, -70.61720</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>08:39:31</t>
+          <t>04:06:10</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SLP20250425120</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/06/15 16:58:46</t>
+          <t>2026/06/15 14:19:46</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-32.7975933, -70.887045</t>
+          <t>-33.388383, -70.617094</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88705</t>
+          <t>-33.38838, -70.61709</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/06/15 18:12:44</t>
+          <t>2026/06/15 18:32:49</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-32.7833433, -70.854065</t>
+          <t>-33.388513, -70.617131</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-32.78334, -70.85407</t>
+          <t>-33.38851, -70.61713</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>01:13:58</t>
+          <t>04:13:03</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>4.01</v>
+        <v>0.02</v>
       </c>
       <c r="M131" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="N131" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/06/15 17:40:35</t>
+          <t>2026/06/15 16:57:33</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-33.36033, -70.8051983</t>
+          <t>-34.579669, -70.961426</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-33.36033, -70.80520</t>
+          <t>-34.57967, -70.96143</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/06/15 19:12:40</t>
+          <t>2026/06/16 01:37:04</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-33.0873083, -71.3622833</t>
+          <t>-34.579474, -70.961408</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36228</t>
+          <t>-34.57947, -70.96141</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>01:32:05</t>
+          <t>08:39:31</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>112.63</v>
+        <v>0.02</v>
       </c>
       <c r="M132" t="n">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="N132" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,57 +8156,57 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/06/15 18:12:59</t>
+          <t>2026/06/15 16:58:46</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-32.7834316, -70.8542516</t>
+          <t>-32.7975933, -70.887045</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-32.78343, -70.85425</t>
+          <t>-32.79759, -70.88705</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/06/15 18:27:41</t>
+          <t>2026/06/15 18:12:44</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-32.79773, -70.8874249</t>
+          <t>-32.7833433, -70.854065</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-32.79773, -70.88742</t>
+          <t>-32.78334, -70.85407</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>00:14:42</t>
+          <t>01:13:58</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.71</v>
+        <v>4.01</v>
       </c>
       <c r="M133" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="N133" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8215,57 +8215,57 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/06/15 18:27:59</t>
+          <t>2026/06/15 17:40:35</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870866</t>
+          <t>-33.36033, -70.8051983</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88709</t>
+          <t>-33.36033, -70.80520</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/06/15 19:50:54</t>
+          <t>2026/06/15 19:12:40</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-32.7976599, -70.8873633</t>
+          <t>-33.0873083, -71.3622833</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-32.79766, -70.88736</t>
+          <t>-33.08731, -71.36228</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>01:22:55</t>
+          <t>01:32:05</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>12.97</v>
+        <v>112.63</v>
       </c>
       <c r="M134" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="N134" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8274,47 +8274,47 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/06/15 19:13:55</t>
+          <t>2026/06/15 18:12:59</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-33.0872216, -71.3622716</t>
+          <t>-32.7834316, -70.8542516</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36227</t>
+          <t>-32.78343, -70.85425</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/06/16 08:53:03</t>
+          <t>2026/06/15 18:27:41</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-33.0873283, -71.3622833</t>
+          <t>-32.79773, -70.8874249</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36228</t>
+          <t>-32.79773, -70.88742</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>13:39:08</t>
+          <t>00:14:42</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0.02</v>
+        <v>3.71</v>
       </c>
       <c r="M135" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="N135" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8333,53 +8333,53 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/06/15 19:51:11</t>
+          <t>2026/06/15 18:27:59</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-32.797595, -70.8870983</t>
+          <t>-32.797605, -70.8870866</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88710</t>
+          <t>-32.79760, -70.88709</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/06/16 08:20:52</t>
+          <t>2026/06/15 19:50:54</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-33.6327316, -70.8686649</t>
+          <t>-32.7976599, -70.8873633</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-33.63273, -70.86866</t>
+          <t>-32.79766, -70.88736</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>12:29:41</t>
+          <t>01:22:55</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>154.64</v>
+        <v>12.97</v>
       </c>
       <c r="M136" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250627045</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -8387,62 +8387,62 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026/06/16 14:24:41</t>
+          <t>2026/06/15 19:11:20</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-34.346895, -71.125647</t>
+          <t>-33.38901, -70.617349</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-34.34690, -71.12565</t>
+          <t>-33.38901, -70.61735</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/06/16 14:49:17</t>
+          <t>2026/06/16 04:49:52</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-34.346909, -71.125536</t>
+          <t>-33.38851, -70.617518</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>-34.34691, -71.12554</t>
+          <t>-33.38851, -70.61752</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>00:24:36</t>
+          <t>09:38:32</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="M137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8451,165 +8451,165 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026/06/16 14:49:31</t>
+          <t>2026/06/15 19:13:55</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-34.346926, -71.125537</t>
+          <t>-33.0872216, -71.3622716</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-34.34693, -71.12554</t>
+          <t>-33.08722, -71.36227</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/06/16 15:15:53</t>
+          <t>2026/06/16 08:53:03</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-34.347368, -71.125768</t>
+          <t>-33.0873283, -71.3622833</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>-34.34737, -71.12577</t>
+          <t>-33.08733, -71.36228</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>00:26:22</t>
+          <t>13:39:08</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="M138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N138" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250425120</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026/06/16 15:16:53</t>
+          <t>2026/06/15 19:31:24</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-34.347169, -71.125764</t>
+          <t>-33.388753, -70.617397</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-34.34717, -71.12576</t>
+          <t>-33.38875, -70.61740</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026/06/16 16:47:57</t>
+          <t>2026/06/16 02:19:45</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-34.346, -71.125769</t>
+          <t>-33.388201, -70.61719</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12577</t>
+          <t>-33.38820, -70.61719</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>01:31:04</t>
+          <t>06:48:21</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.76</v>
+        <v>0.06</v>
       </c>
       <c r="M139" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026/06/16 16:30:10</t>
+          <t>2026/06/15 19:51:11</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-34.205426, -70.677296</t>
+          <t>-32.797595, -70.8870983</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-34.20543, -70.67730</t>
+          <t>-32.79760, -70.88710</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/06/17 23:27:45</t>
+          <t>2026/06/16 08:20:52</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>-34.205436, -70.677309</t>
+          <t>-33.6327316, -70.8686649</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67731</t>
+          <t>-33.63273, -70.86866</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>30:57:35</t>
+          <t>12:29:41</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>154.64</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="141">
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8628,41 +8628,41 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026/06/16 16:48:53</t>
+          <t>2026/06/16 14:24:41</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-34.346001, -71.125795</t>
+          <t>-34.346895, -71.125647</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12579</t>
+          <t>-34.34690, -71.12565</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/06/17 09:45:58</t>
+          <t>2026/06/16 14:49:17</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>-34.34638, -71.125155</t>
+          <t>-34.346909, -71.125536</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>-34.34638, -71.12516</t>
+          <t>-34.34691, -71.12554</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>16:57:05</t>
+          <t>00:24:36</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="M141" t="n">
         <v>4</v>
@@ -8674,11 +8674,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8687,57 +8687,57 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026/06/16 16:51:18</t>
+          <t>2026/06/16 14:49:31</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-33.3595416, -70.8088316</t>
+          <t>-34.346926, -71.125537</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-33.35954, -70.80883</t>
+          <t>-34.34693, -71.12554</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/06/16 17:13:18</t>
+          <t>2026/06/16 15:15:53</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>-33.359995, -70.807095</t>
+          <t>-34.347368, -71.125768</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80710</t>
+          <t>-34.34737, -71.12577</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>00:22:00</t>
+          <t>00:26:22</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="M142" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N142" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8746,116 +8746,116 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026/06/16 17:13:19</t>
+          <t>2026/06/16 15:16:53</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-33.359995, -70.807095</t>
+          <t>-34.347169, -71.125764</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80710</t>
+          <t>-34.34717, -71.12576</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/06/16 19:02:32</t>
+          <t>2026/06/16 16:47:57</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>-32.7431433, -70.7330466</t>
+          <t>-34.346, -71.125769</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>-32.74314, -70.73305</t>
+          <t>-34.34600, -71.12577</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>01:49:13</t>
+          <t>01:31:04</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>90.31999999999999</v>
+        <v>1.76</v>
       </c>
       <c r="M143" t="n">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="N143" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026/06/16 19:02:42</t>
+          <t>2026/06/16 16:30:10</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-32.7432649, -70.7327716</t>
+          <t>-34.205426, -70.677296</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-32.74326, -70.73277</t>
+          <t>-34.20543, -70.67730</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026/06/16 19:19:22</t>
+          <t>2026/06/17 23:27:45</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>-32.7431533, -70.7296483</t>
+          <t>-34.205436, -70.677309</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>-32.74315, -70.72965</t>
+          <t>-34.20544, -70.67731</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>00:16:40</t>
+          <t>30:57:35</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -8864,293 +8864,293 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026/06/16 19:20:37</t>
+          <t>2026/06/16 16:48:53</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-32.74312, -70.72972</t>
+          <t>-34.346001, -71.125795</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-32.74312, -70.72972</t>
+          <t>-34.34600, -71.12579</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/06/17 08:22:56</t>
+          <t>2026/06/17 09:45:58</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-33.3599599, -70.8071483</t>
+          <t>-34.34638, -71.125155</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80715</t>
+          <t>-34.34638, -71.12516</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>13:02:19</t>
+          <t>16:57:05</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>90.22</v>
+        <v>0.22</v>
       </c>
       <c r="M145" t="n">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="N145" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026/06/17 15:17:42</t>
+          <t>2026/06/16 16:51:18</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-34.57966, -70.961408</t>
+          <t>-33.3595416, -70.8088316</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96141</t>
+          <t>-33.35954, -70.80883</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/06/17 23:19:18</t>
+          <t>2026/06/16 17:13:18</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>-34.57966, -70.961408</t>
+          <t>-33.359995, -70.807095</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96141</t>
+          <t>-33.35999, -70.80710</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>08:01:36</t>
+          <t>00:22:00</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026/06/17 16:36:14</t>
+          <t>2026/06/16 17:13:19</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>-34.345978, -71.125749</t>
+          <t>-33.359995, -70.807095</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12575</t>
+          <t>-33.35999, -70.80710</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/06/17 23:37:59</t>
+          <t>2026/06/16 19:02:32</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>-34.345978, -71.125749</t>
+          <t>-32.7431433, -70.7330466</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12575</t>
+          <t>-32.74314, -70.73305</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>07:01:45</t>
+          <t>01:49:13</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026/06/17 17:42:05</t>
+          <t>2026/06/16 19:02:42</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-33.0873166, -71.36232</t>
+          <t>-32.7432649, -70.7327716</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36232</t>
+          <t>-32.74326, -70.73277</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/06/17 23:53:19</t>
+          <t>2026/06/16 19:19:22</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>-33.0872466, -71.36224</t>
+          <t>-32.7431533, -70.7296483</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>-33.08725, -71.36224</t>
+          <t>-32.74315, -70.72965</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>06:11:14</t>
+          <t>00:16:40</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026/06/17 18:35:03</t>
+          <t>2026/06/16 19:20:37</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870916</t>
+          <t>-32.74312, -70.72972</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88709</t>
+          <t>-32.74312, -70.72972</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/06/17 23:12:37</t>
+          <t>2026/06/17 08:22:56</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870916</t>
+          <t>-33.3599599, -70.8071483</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88709</t>
+          <t>-33.35996, -70.80715</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>04:37:34</t>
+          <t>13:02:19</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>90.22</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9159,37 +9159,37 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026/06/17 19:42:38</t>
+          <t>2026/06/17 15:17:42</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-32.74302, -70.7297716</t>
+          <t>-34.57966, -70.961408</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-32.74302, -70.72977</t>
+          <t>-34.57966, -70.96141</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/06/17 23:42:44</t>
+          <t>2026/06/17 23:19:18</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>-32.74302, -70.7297716</t>
+          <t>-34.57966, -70.961408</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>-32.74302, -70.72977</t>
+          <t>-34.57966, -70.96141</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>04:00:06</t>
+          <t>08:01:36</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -9205,11 +9205,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9218,37 +9218,37 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026/06/17 19:44:02</t>
+          <t>2026/06/17 16:36:14</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-33.47617, -70.6984266</t>
+          <t>-34.345978, -71.125749</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69843</t>
+          <t>-34.34598, -71.12575</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026/06/17 23:44:12</t>
+          <t>2026/06/17 23:37:59</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>-33.47617, -70.6984266</t>
+          <t>-34.345978, -71.125749</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69843</t>
+          <t>-34.34598, -71.12575</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>04:00:10</t>
+          <t>07:01:45</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -9264,11 +9264,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9277,41 +9277,41 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026/06/17 21:24:40</t>
+          <t>2026/06/17 17:42:05</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-33.4370583, -70.6293866</t>
+          <t>-33.0873166, -71.36232</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-33.43706, -70.62939</t>
+          <t>-33.08732, -71.36232</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/06/17 23:26:45</t>
+          <t>2026/06/17 23:53:19</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>-33.4370583, -70.6293866</t>
+          <t>-33.0872466, -71.36224</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>-33.43706, -70.62939</t>
+          <t>-33.08725, -71.36224</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>02:02:05</t>
+          <t>06:11:14</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -9323,11 +9323,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9336,37 +9336,37 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026/06/17 22:16:58</t>
+          <t>2026/06/17 18:35:03</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-32.841647, -70.93681</t>
+          <t>-32.7976083, -70.8870916</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-32.84165, -70.93681</t>
+          <t>-32.79761, -70.88709</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/06/17 23:20:00</t>
+          <t>2026/06/17 23:12:37</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-32.841647, -70.93681</t>
+          <t>-32.7976083, -70.8870916</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>-32.84165, -70.93681</t>
+          <t>-32.79761, -70.88709</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>01:03:02</t>
+          <t>04:37:34</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -9376,6 +9376,242 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>13</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026/06/17 19:42:38</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-32.74302, -70.7297716</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-32.74302, -70.72977</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026/06/17 23:42:44</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-32.74302, -70.7297716</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-32.74302, -70.72977</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>04:00:06</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>9</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026/06/17 19:44:02</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-33.47617, -70.6984266</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-33.47617, -70.69843</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026/06/17 23:44:12</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-33.47617, -70.6984266</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-33.47617, -70.69843</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>04:00:10</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>11</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026/06/17 21:24:40</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-33.4370583, -70.6293866</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-33.43706, -70.62939</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026/06/17 23:26:45</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-33.4370583, -70.6293866</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-33.43706, -70.62939</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>02:02:05</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>8</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026/06/17 22:16:58</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-32.841647, -70.93681</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-32.84165, -70.93681</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026/06/17 23:20:00</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-32.841647, -70.93681</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-32.84165, -70.93681</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>01:03:02</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9390,7 +9626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9689,38 +9925,76 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250425120</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>656.04</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>SLP20250627045</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>656.04</v>
+      </c>
+      <c r="C18" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B19" t="n">
         <v>907.61</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C19" t="n">
         <v>51</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E19" t="n">
         <v>143</v>
       </c>
     </row>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/19 22:53:32</t>
+          <t>2026/06/19 23:53:32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:57:24</t>
+          <t>166:57:24</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/06/19 22:57:45</t>
+          <t>2026/06/19 23:57:37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>165:58:37</t>
+          <t>166:58:29</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/06/19 22:34:42</t>
+          <t>2026/06/19 23:34:40</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>29:37:41</t>
+          <t>30:37:39</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/06/19 22:52:29</t>
+          <t>2026/06/19 23:52:29</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>07:01:01</t>
+          <t>08:01:01</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/06/19 21:53:59</t>
+          <t>2026/06/19 23:53:59</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026/06/19 22:59:21</t>
+          <t>2026/06/19 23:59:20</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>01:57:30</t>
+          <t>02:57:29</t>
         </is>
       </c>
       <c r="L167" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/06/22 22:56:10</t>
+          <t>2026/06/22 23:56:10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/22 22:57:39</t>
+          <t>2026/06/22 23:57:15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:00:07</t>
+          <t>166:59:43</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/06/22 22:45:44</t>
+          <t>2026/06/22 23:45:43</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>08:01:04</t>
+          <t>09:01:03</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026/06/22 22:49:05</t>
+          <t>2026/06/22 23:49:05</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>06:01:37</t>
+          <t>07:01:37</t>
         </is>
       </c>
       <c r="L168" t="n">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026/06/22 22:37:26</t>
+          <t>2026/06/22 23:37:26</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>05:03:21</t>
+          <t>06:03:21</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/06/22 21:54:15</t>
+          <t>2026/06/22 23:54:15</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/06/22 22:41:17</t>
+          <t>2026/06/22 23:41:17</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>01:57:29</t>
+          <t>02:57:29</t>
         </is>
       </c>
       <c r="L175" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/06/23 22:56:12</t>
+          <t>2026/06/23 23:56:12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/23 22:57:21</t>
+          <t>2026/06/23 23:57:21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:58:13</t>
+          <t>166:58:13</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/23 22:31:38</t>
+          <t>2026/06/23 23:31:38</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>164:00:00</t>
+          <t>165:00:00</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/06/23 21:59:44</t>
+          <t>2026/06/23 23:59:44</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>02:00:17</t>
+          <t>04:00:17</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/06/23 22:42:56</t>
+          <t>2026/06/23 23:42:57</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>01:57:35</t>
+          <t>02:57:36</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -10885,26 +10885,26 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026/06/23 23:28:28</t>
+          <t>2026/06/23 23:57:08</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>-32.845465, -70.6048249</t>
+          <t>-32.84549, -70.6047049</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>-32.84546, -70.60482</t>
+          <t>-32.84549, -70.60470</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>00:46:38</t>
+          <t>01:15:18</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/06/24 22:31:21</t>
+          <t>2026/06/24 23:31:38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>165:59:43</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/06/24 22:56:12</t>
+          <t>2026/06/24 23:56:12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>166:00:02</t>
+          <t>167:00:02</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/06/24 22:57:21</t>
+          <t>2026/06/24 23:57:37</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>165:59:58</t>
+          <t>167:00:14</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026/06/24 22:40:54</t>
+          <t>2026/06/24 23:40:54</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>09:04:34</t>
+          <t>10:04:34</t>
         </is>
       </c>
       <c r="L168" t="n">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026/06/24 21:54:20</t>
+          <t>2026/06/24 23:54:20</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>08:01:43</t>
+          <t>10:01:43</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026/06/24 21:44:27</t>
+          <t>2026/06/24 23:44:27</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>06:10:39</t>
+          <t>08:10:39</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026/06/24 22:43:50</t>
+          <t>2026/06/24 23:43:50</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>06:01:31</t>
+          <t>07:01:31</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/06/24 22:45:55</t>
+          <t>2026/06/24 23:45:55</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>06:01:00</t>
+          <t>07:01:00</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/06/24 22:34:19</t>
+          <t>2026/06/24 23:34:19</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>04:03:04</t>
+          <t>05:03:04</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/06/24 21:49:21</t>
+          <t>2026/06/24 23:49:21</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/06/24 21:51:19</t>
+          <t>2026/06/24 23:51:19</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -11028,6 +11028,65 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>13</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026/06/24 21:39:56</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-32.838389, -70.955509</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-32.83839, -70.95551</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2026/06/24 23:38:30</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-32.838389, -70.955509</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-32.83839, -70.95551</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>01:58:34</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11098,13 +11157,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1317.27</v>
+        <v>1317.21</v>
       </c>
       <c r="C3" t="n">
         <v>61</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>141</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N182"/>
+  <dimension ref="A1:N183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/06/25 22:53:35</t>
+          <t>2026/06/25 23:53:35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>166:00:03</t>
+          <t>167:00:03</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/25 22:57:15</t>
+          <t>2026/06/25 23:57:40</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:58:03</t>
+          <t>166:58:28</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -10354,22 +10354,22 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/06/25 22:48:10</t>
+          <t>2026/06/25 23:48:10</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>-33.36004, -70.807126</t>
+          <t>-33.36003, -70.807123</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80713</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>06:01:00</t>
+          <t>07:01:00</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026/06/25 21:40:26</t>
+          <t>2026/06/25 23:40:26</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>02:11:51</t>
+          <t>04:11:51</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -11003,26 +11003,26 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/06/25 21:51:01</t>
+          <t>2026/06/25 21:50:46</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>-32.7430566, -70.729785</t>
+          <t>-32.7430883, -70.7297366</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>-32.74306, -70.72979</t>
+          <t>-32.74309, -70.72974</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>00:33:58</t>
+          <t>00:33:43</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="M181" t="n">
         <v>15</v>
@@ -11087,6 +11087,65 @@
         <v>0</v>
       </c>
       <c r="N182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>20</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026/06/25 21:51:01</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-32.7430566, -70.729785</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-32.74306, -70.72979</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2026/06/25 23:51:01</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-32.7430566, -70.729785</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-32.74306, -70.72979</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11195,13 +11254,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1012.33</v>
+        <v>1012.32</v>
       </c>
       <c r="C5" t="n">
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>139</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/06/26 22:53:35</t>
+          <t>2026/06/26 23:53:35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>166:00:03</t>
+          <t>167:00:03</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/06/26 21:57:14</t>
+          <t>2026/06/26 23:57:17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>164:59:53</t>
+          <t>166:59:56</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/06/26 22:40:42</t>
+          <t>2026/06/26 23:40:42</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>67:00:33</t>
+          <t>68:00:33</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/06/26 22:13:05</t>
+          <t>2026/06/26 23:13:24</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>53:30:46</t>
+          <t>54:31:05</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/06/26 21:18:29</t>
+          <t>2026/06/26 23:18:29</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>05:41:02</t>
+          <t>07:41:02</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026/06/26 22:14:15</t>
+          <t>2026/06/26 23:13:51</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>05:00:26</t>
+          <t>06:00:02</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/06/26 21:34:24</t>
+          <t>2026/06/26 23:34:24</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026/06/26 21:51:17</t>
+          <t>2026/06/26 23:51:17</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -10798,11 +10798,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -10811,46 +10811,164 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026/06/26 21:53:47</t>
+          <t>2026/06/26 21:13:03</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-32.743075, -70.7297933</t>
+          <t>-33.4761283, -70.6985433</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>-32.74307, -70.72979</t>
+          <t>-33.47613, -70.69854</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/06/26 22:01:41</t>
+          <t>2026/06/26 23:13:33</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>-32.7430083, -70.7298233</t>
+          <t>-33.4761283, -70.6985433</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>-32.74301, -70.72982</t>
+          <t>-33.47613, -70.69854</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>00:07:54</t>
+          <t>02:00:30</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
         <v>0</v>
       </c>
       <c r="N178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>13</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026/06/26 21:53:47</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-32.743075, -70.7297933</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-32.74307, -70.72979</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2026/06/26 22:01:41</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-32.7430083, -70.7298233</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-32.74301, -70.72982</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>00:07:54</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>9</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026/06/26 22:31:15</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-33.399197, -70.795128</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-33.39920, -70.79513</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2026/06/26 23:35:15</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-33.399197, -70.795128</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-33.39920, -70.79513</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>01:04:00</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10921,10 +11039,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>818.65</v>
+        <v>819.58</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -11130,13 +11248,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1564.21</v>
+        <v>1564.18</v>
       </c>
       <c r="C14" t="n">
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>131</v>
@@ -11244,13 +11362,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>635.54</v>
+        <v>635.47</v>
       </c>
       <c r="C20" t="n">
         <v>57</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>147</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/06/27 22:53:35</t>
+          <t>2026/06/27 23:53:35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>166:00:03</t>
+          <t>167:00:03</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/27 22:57:46</t>
+          <t>2026/06/27 23:57:45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>165:58:39</t>
+          <t>166:58:38</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/06/27 22:40:42</t>
+          <t>2026/06/27 23:40:42</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>91:00:33</t>
+          <t>92:00:33</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/06/27 21:54:08</t>
+          <t>2026/06/27 23:54:08</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/06/27 22:48:54</t>
+          <t>2026/06/27 23:48:54</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>01:02:59</t>
+          <t>02:02:59</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -11028,6 +11028,65 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>8</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026/06/27 21:48:29</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-32.780847, -70.98129</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-32.78085, -70.98129</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2026/06/27 23:45:58</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-32.780847, -70.98129</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-32.78085, -70.98129</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>01:57:29</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11104,7 +11163,7 @@
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>140</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N185"/>
+  <dimension ref="A1:N186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/06/28 22:56:10</t>
+          <t>2026/06/28 23:56:10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/28 22:57:45</t>
+          <t>2026/06/28 23:57:47</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>166:00:08</t>
+          <t>167:00:10</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -11211,11 +11211,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11224,37 +11224,37 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026/06/28 21:51:51</t>
+          <t>2026/06/28 21:51:21</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-32.841725, -70.93688</t>
+          <t>-33.4362983, -70.6294</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>-32.84172, -70.93688</t>
+          <t>-33.43630, -70.62940</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026/06/28 22:54:50</t>
+          <t>2026/06/28 23:51:21</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>-32.841725, -70.93688</t>
+          <t>-33.4362983, -70.6294</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>-32.84172, -70.93688</t>
+          <t>-33.43630, -70.62940</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>01:02:59</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -11264,6 +11264,65 @@
         <v>0</v>
       </c>
       <c r="N185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>7</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026/06/28 21:51:51</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-32.841725, -70.93688</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-32.84172, -70.93688</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2026/06/28 23:54:50</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-32.841725, -70.93688</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-32.84172, -70.93688</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>02:02:59</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11568,7 +11627,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>144</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/06/29 22:56:10</t>
+          <t>2026/06/29 23:56:10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/06/29 22:57:38</t>
+          <t>2026/06/29 23:57:15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>165:58:27</t>
+          <t>166:58:04</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/06/29 21:44:31</t>
+          <t>2026/06/29 23:44:31</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>99:36:24</t>
+          <t>101:36:24</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/06/29 22:46:40</t>
+          <t>2026/06/29 23:46:16</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>77:32:51</t>
+          <t>78:32:27</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026/06/29 22:47:44</t>
+          <t>2026/06/29 23:47:47</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>01:02:55</t>
+          <t>02:02:58</t>
         </is>
       </c>
       <c r="L184" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/30 22:56:08</t>
+          <t>2026/06/30 23:56:08</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>165:59:56</t>
+          <t>166:59:56</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/06/30 22:57:21</t>
+          <t>2026/06/30 23:57:17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>165:59:44</t>
+          <t>166:59:40</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026/06/30 21:44:31</t>
+          <t>2026/06/30 23:44:31</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>123:36:24</t>
+          <t>125:36:24</t>
         </is>
       </c>
       <c r="L144" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/01 22:56:08</t>
+          <t>2026/07/01 23:56:08</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:59:56</t>
+          <t>166:59:56</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/01 22:57:22</t>
+          <t>2026/07/01 23:57:41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:58:15</t>
+          <t>166:58:34</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/01 21:44:31</t>
+          <t>2026/07/01 23:44:31</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>147:36:24</t>
+          <t>149:36:24</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/07/01 22:40:46</t>
+          <t>2026/07/01 23:40:46</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>44:01:19</t>
+          <t>45:01:19</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/07/01 22:46:14</t>
+          <t>2026/07/01 23:46:14</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>34:51:17</t>
+          <t>35:51:17</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/07/01 22:42:50</t>
+          <t>2026/07/01 23:42:50</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>29:13:16</t>
+          <t>30:13:16</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/07/01 21:48:02</t>
+          <t>2026/07/01 23:48:02</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>03:06:51</t>
+          <t>05:06:51</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/07/01 21:50:56</t>
+          <t>2026/07/01 23:50:56</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L159" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1063,7 +1063,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SLP20250425120</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1181,7 +1181,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2597,7 +2597,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3482,7 +3482,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3600,7 +3600,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3718,7 +3718,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -6078,7 +6078,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -6137,7 +6137,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -9264,7 +9264,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -10298,7 +10298,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SLP20250425120</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -10317,7 +10317,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SLP20250627045</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="B18" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/02 22:01:38</t>
+          <t>2026/07/02 23:01:16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>166:00:17</t>
+          <t>166:59:55</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/02 21:44:31</t>
+          <t>2026/07/02 23:44:31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>165:36:22</t>
+          <t>167:36:22</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/02 22:13:15</t>
+          <t>2026/07/02 23:13:36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>165:59:52</t>
+          <t>167:00:13</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/02 21:56:12</t>
+          <t>2026/07/02 23:56:12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>165:02:37</t>
+          <t>167:02:37</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/02 21:57:15</t>
+          <t>2026/07/02 23:57:21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>164:59:38</t>
+          <t>166:59:44</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/02 22:41:12</t>
+          <t>2026/07/02 23:41:12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>68:01:45</t>
+          <t>69:01:45</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/02 22:11:24</t>
+          <t>2026/07/02 23:11:22</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>52:41:50</t>
+          <t>53:41:48</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/07/02 21:53:23</t>
+          <t>2026/07/02 23:53:17</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>06:15:11</t>
+          <t>08:15:05</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/02 22:04:58</t>
+          <t>2026/07/02 23:04:58</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>04:03:05</t>
+          <t>05:03:05</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/02 21:08:56</t>
+          <t>2026/07/02 23:08:56</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>02:00:43</t>
+          <t>04:00:43</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/02 21:48:16</t>
+          <t>2026/07/02 23:48:17</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>01:57:29</t>
+          <t>03:57:30</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8728,6 +8728,65 @@
       </c>
       <c r="N142" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026/07/02 21:57:31</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-33.4760816, -70.6985116</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-33.47608, -70.69851</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026/07/02 23:57:43</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-33.4760816, -70.6985116</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-33.47608, -70.69851</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>02:00:12</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9006,13 +9065,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1025.93</v>
+        <v>1025.91</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>131</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/06/26 04:00:00   Hasta : 2026/07/03 03:59:59</t>
+          <t>Desde : 2026/06/27 04:00:00   Hasta : 2026/07/04 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,58 +540,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/06/26 00:01:21</t>
+          <t>2026/06/27 00:00:49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.345977, -71.125867</t>
+          <t>-32.788962, -70.95912</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12587</t>
+          <t>-32.78896, -70.95912</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/02 23:01:16</t>
+          <t>2026/06/27 00:16:02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-34.345999, -71.125878</t>
+          <t>-32.838378, -70.956093</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12588</t>
+          <t>-32.83838, -70.95609</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>166:59:55</t>
+          <t>00:15:13</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.03</v>
+        <v>11.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,41 +604,41 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/06/26 00:08:09</t>
+          <t>2026/06/27 00:01:39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.3665816, -70.6957783</t>
+          <t>-34.345961, -71.125867</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69578</t>
+          <t>-34.34596, -71.12587</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/02 23:44:31</t>
+          <t>2026/07/03 22:01:26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.3665816, -70.6957783</t>
+          <t>-34.345999, -71.125878</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69578</t>
+          <t>-34.34600, -71.12588</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>167:36:22</t>
+          <t>165:59:47</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,53 +663,53 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/06/26 00:12:02</t>
+          <t>2026/06/27 00:01:41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.205416, -70.677299</t>
+          <t>-32.7430083, -70.7298233</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67730</t>
+          <t>-32.74301, -70.72982</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/06/26 15:57:18</t>
+          <t>2026/06/28 14:14:55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.204327, -70.678795</t>
+          <t>-32.74311, -70.7297249</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.20433, -70.67879</t>
+          <t>-32.74311, -70.72972</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15:45:16</t>
+          <t>38:13:14</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.23</v>
+        <v>0.98</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/06/26 00:13:23</t>
+          <t>2026/06/27 00:08:09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.360005, -70.807064</t>
+          <t>-33.3665816, -70.6957783</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80706</t>
+          <t>-33.36658, -70.69578</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/02 23:13:36</t>
+          <t>2026/07/03 11:48:11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.360009, -70.807069</t>
+          <t>-33.3673166, -70.6955883</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80707</t>
+          <t>-33.36732, -70.69559</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>167:00:13</t>
+          <t>155:40:02</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.04</v>
+        <v>36.77</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,53 +781,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/06/26 00:15:51</t>
+          <t>2026/06/27 00:10:12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-32.838389, -70.955493</t>
+          <t>-33.399197, -70.795128</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-32.83839, -70.95549</t>
+          <t>-33.39920, -70.79513</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/06/26 09:56:27</t>
+          <t>2026/06/27 01:05:18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.367257, -70.69596</t>
+          <t>-32.841699, -70.936905</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.36726, -70.69596</t>
+          <t>-32.84170, -70.93690</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>09:40:36</t>
+          <t>00:55:06</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>77.87</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N8" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/06/26 00:18:04</t>
+          <t>2026/06/27 00:13:10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-34.579663, -70.961401</t>
+          <t>-33.360005, -70.807064</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96140</t>
+          <t>-33.36001, -70.80706</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/06/26 01:36:37</t>
+          <t>2026/07/03 22:13:14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-34.579852, -70.96131</t>
+          <t>-33.360042, -70.80706</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96131</t>
+          <t>-33.36004, -70.80706</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>01:18:33</t>
+          <t>166:00:04</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -899,57 +899,57 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/06/26 00:22:31</t>
+          <t>2026/06/27 00:14:16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.482159, -70.764902</t>
+          <t>-33.360057, -70.807151</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.48216, -70.76490</t>
+          <t>-33.36006, -70.80715</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/06/26 08:58:57</t>
+          <t>2026/06/30 11:39:26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.359824, -70.806738</t>
+          <t>-33.360734, -70.809006</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.35982, -70.80674</t>
+          <t>-33.36073, -70.80901</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>08:36:26</t>
+          <t>83:25:10</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>22.71</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -958,53 +958,53 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/06/26 00:23:37</t>
+          <t>2026/06/27 00:16:50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.876448, -71.127238</t>
+          <t>-32.838367, -70.955489</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.87645, -71.12724</t>
+          <t>-32.83837, -70.95549</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/06/26 10:53:15</t>
+          <t>2026/06/27 13:49:01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.876323, -71.127333</t>
+          <t>-32.840002, -70.961183</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.87632, -71.12733</t>
+          <t>-32.84000, -70.96118</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10:29:38</t>
+          <t>13:32:11</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/06/26 00:24:43</t>
+          <t>2026/06/27 00:31:21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-32.79758, -70.8870983</t>
+          <t>-33.899792, -71.429506</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88710</t>
+          <t>-33.89979, -71.42951</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/06/26 10:02:45</t>
+          <t>2026/07/01 08:15:25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-32.7538566, -70.72979</t>
+          <t>-33.899941, -71.429577</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.75386, -70.72979</t>
+          <t>-33.89994, -71.42958</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09:38:02</t>
+          <t>103:44:04</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>27.8</v>
+        <v>0.09</v>
       </c>
       <c r="M12" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,58 +1071,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/06/26 00:31:25</t>
+          <t>2026/06/27 00:31:56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.899792, -71.429506</t>
+          <t>-34.205399, -70.67729</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.89979, -71.42951</t>
+          <t>-34.20540, -70.67729</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/01 08:15:25</t>
+          <t>2026/06/30 16:59:54</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.899941, -71.429577</t>
+          <t>-34.205234, -70.680382</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.89994, -71.42958</t>
+          <t>-34.20523, -70.68038</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>127:44:00</t>
+          <t>88:27:58</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,58 +1130,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/06/26 00:39:50</t>
+          <t>2026/06/27 00:34:56</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.366517, -70.696602</t>
+          <t>-34.579852, -70.96131</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36652, -70.69660</t>
+          <t>-34.57985, -70.96131</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/06/28 01:41:03</t>
+          <t>2026/06/27 01:37:22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.368129, -70.696085</t>
+          <t>-34.579844, -70.961378</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36813, -70.69608</t>
+          <t>-34.57984, -70.96138</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>49:01:13</t>
+          <t>01:02:26</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/06/26 00:48:10</t>
+          <t>2026/06/27 00:38:42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.36003, -70.807123</t>
+          <t>-33.367472, -70.696453</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-33.36747, -70.69645</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/06/26 09:58:04</t>
+          <t>2026/06/28 01:41:03</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.360494, -70.80905</t>
+          <t>-33.368129, -70.696085</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36049, -70.80905</t>
+          <t>-33.36813, -70.69608</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>09:09:54</t>
+          <t>25:02:21</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.32</v>
+        <v>0.08</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/06/26 00:48:52</t>
+          <t>2026/06/27 00:45:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.4761049, -70.6985</t>
+          <t>-37.79751, -73.4010766</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69850</t>
+          <t>-37.79751, -73.40108</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/26 08:26:10</t>
+          <t>2026/06/27 17:20:46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.476255, -70.6983316</t>
+          <t>-37.2067683, -73.210845</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69833</t>
+          <t>-37.20677, -73.21085</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>07:37:18</t>
+          <t>16:34:53</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.03</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,53 +1312,53 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/06/26 00:53:35</t>
+          <t>2026/06/27 00:48:55</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.876382, -71.127239</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.87638, -71.12724</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/02 23:56:12</t>
+          <t>2026/06/29 01:25:19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.876375, -71.127119</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.87638, -71.12712</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>167:02:37</t>
+          <t>48:36:24</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,41 +1371,41 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/06/26 00:57:37</t>
+          <t>2026/06/27 00:53:35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-34.042641, -70.681766</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-34.04264, -70.68177</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/02 23:57:21</t>
+          <t>2026/07/03 21:56:12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-34.042661, -70.681754</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68175</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>166:59:44</t>
+          <t>165:02:37</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/06/26 01:09:38</t>
+          <t>2026/06/27 00:57:37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.0872283, -71.3622499</t>
+          <t>-34.042641, -70.681766</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.08723, -71.36225</t>
+          <t>-34.04264, -70.68177</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/06/26 08:51:04</t>
+          <t>2026/07/03 21:57:29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.087295, -71.3622916</t>
+          <t>-34.04266, -70.681752</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36229</t>
+          <t>-34.04266, -70.68175</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07:41:26</t>
+          <t>164:59:52</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/06/26 01:24:24</t>
+          <t>2026/06/27 01:05:21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-32.8792433, -70.6088016</t>
+          <t>-32.841678, -70.936878</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60880</t>
+          <t>-32.84168, -70.93688</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/06/26 08:30:57</t>
+          <t>2026/06/27 10:25:30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.9301216, -70.7161466</t>
+          <t>-32.848304, -70.924562</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.93012, -70.71615</t>
+          <t>-32.84830, -70.92456</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>07:06:33</t>
+          <t>09:20:09</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>143.4</v>
+        <v>2.48</v>
       </c>
       <c r="M20" t="n">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="N20" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/06/26 01:40:26</t>
+          <t>2026/06/27 01:13:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-37.7975383, -73.4010416</t>
+          <t>-33.4761283, -70.6985433</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-37.79754, -73.40104</t>
+          <t>-33.47613, -70.69854</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/26 12:37:16</t>
+          <t>2026/06/27 10:06:28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-37.7759566, -73.3821316</t>
+          <t>-33.36231, -70.67015</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-37.77596, -73.38213</t>
+          <t>-33.36231, -70.67015</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10:56:50</t>
+          <t>08:52:55</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.42</v>
+        <v>18.77</v>
       </c>
       <c r="M21" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,116 +1607,116 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/06/26 01:51:01</t>
+          <t>2026/06/27 01:18:29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-32.7430566, -70.729785</t>
+          <t>-33.0872383, -71.36227</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-32.74306, -70.72979</t>
+          <t>-33.08724, -71.36227</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/06/26 08:18:56</t>
+          <t>2026/06/27 10:05:33</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.3599683, -70.806995</t>
+          <t>-33.0873016, -71.3623633</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80700</t>
+          <t>-33.08730, -71.36236</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06:27:55</t>
+          <t>08:47:04</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>89.79000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/06/26 02:34:09</t>
+          <t>2026/06/27 01:34:24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-34.579852, -70.96131</t>
+          <t>-32.7976133, -70.8870716</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96131</t>
+          <t>-32.79761, -70.88707</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/06/27 01:37:22</t>
+          <t>2026/06/27 09:33:41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-34.579844, -70.961378</t>
+          <t>-32.6229216, -70.7180833</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-34.57984, -70.96138</t>
+          <t>-32.62292, -70.71808</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23:03:13</t>
+          <t>07:59:17</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.01</v>
+        <v>41.67</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/06/26 08:19:05</t>
+          <t>2026/06/27 01:51:17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.3599033, -70.8071633</t>
+          <t>-32.8792133, -70.608785</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80716</t>
+          <t>-32.87921, -70.60878</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/06/26 09:51:35</t>
+          <t>2026/06/27 09:57:19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.360305, -70.8090283</t>
+          <t>-32.8520266, -70.6067616</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.36030, -70.80903</t>
+          <t>-32.85203, -70.60676</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>01:32:30</t>
+          <t>08:06:02</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.22</v>
+        <v>4.18</v>
       </c>
       <c r="M24" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1779,58 +1779,58 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/06/26 08:26:19</t>
+          <t>2026/06/27 02:34:38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.4763033, -70.6983733</t>
+          <t>-34.579844, -70.961378</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.47630, -70.69837</t>
+          <t>-34.57984, -70.96138</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/06/26 09:36:32</t>
+          <t>2026/06/29 01:37:19</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.3623233, -70.67015</t>
+          <t>-34.579894, -70.961485</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.36232, -70.67015</t>
+          <t>-34.57989, -70.96148</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01:10:13</t>
+          <t>47:02:41</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21.7</v>
+        <v>0.08</v>
       </c>
       <c r="M25" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1843,53 +1843,53 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/06/26 08:31:32</t>
+          <t>2026/06/27 09:34:56</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.9317099, -70.71546</t>
+          <t>-32.6253016, -70.7184416</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.93171, -70.71546</t>
+          <t>-32.62530, -70.71844</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/06/26 09:04:50</t>
+          <t>2026/06/27 10:10:25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-34.26604, -70.8104766</t>
+          <t>-32.5634483, -70.694755</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-34.26604, -70.81048</t>
+          <t>-32.56345, -70.69476</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>00:33:18</t>
+          <t>00:35:29</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>40.99</v>
+        <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="N26" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1902,53 +1902,53 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/06/26 08:52:19</t>
+          <t>2026/06/27 09:57:44</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.0873083, -71.3622933</t>
+          <t>-32.8521949, -70.6077133</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36229</t>
+          <t>-32.85219, -70.60771</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/06/26 10:44:01</t>
+          <t>2026/06/27 10:07:41</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.3637883, -70.78537</t>
+          <t>-32.8547316, -70.6037666</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.36379, -70.78537</t>
+          <t>-32.85473, -70.60377</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01:51:42</t>
+          <t>00:09:57</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>111.69</v>
+        <v>0.65</v>
       </c>
       <c r="M27" t="n">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="N27" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/06/26 08:59:23</t>
+          <t>2026/06/27 10:06:18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.359958, -70.807116</t>
+          <t>-33.0871949, -71.36224</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80712</t>
+          <t>-33.08719, -71.36224</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/06/26 09:53:36</t>
+          <t>2026/06/30 09:33:52</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.360362, -70.809004</t>
+          <t>-33.04526, -71.41807</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.36036, -70.80900</t>
+          <t>-33.04526, -71.41807</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:54:13</t>
+          <t>71:27:34</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.19</v>
+        <v>11.25</v>
       </c>
       <c r="M28" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,53 +2020,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/06/26 09:05:12</t>
+          <t>2026/06/27 10:07:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-34.2661516, -70.8105366</t>
+          <t>-33.362065, -70.6701616</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-34.26615, -70.81054</t>
+          <t>-33.36207, -70.67016</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/06/26 10:28:13</t>
+          <t>2026/06/27 10:21:12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.5791333, -70.9614083</t>
+          <t>-33.3533383, -70.6704066</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.57913, -70.96141</t>
+          <t>-33.35334, -70.67041</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01:23:01</t>
+          <t>00:14:12</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>39.99</v>
+        <v>1.08</v>
       </c>
       <c r="M29" t="n">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2079,53 +2079,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/06/26 09:36:53</t>
+          <t>2026/06/27 10:08:56</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-33.3621049, -70.6701833</t>
+          <t>-32.852205, -70.6077133</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67018</t>
+          <t>-32.85220, -70.60771</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/06/26 10:36:21</t>
+          <t>2026/06/27 11:17:39</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-33.3657233, -70.67031</t>
+          <t>-32.8364866, -70.5945683</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-33.36572, -70.67031</t>
+          <t>-32.83649, -70.59457</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:59:28</t>
+          <t>01:08:43</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.91</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="N30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2138,53 +2138,53 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/06/26 09:51:52</t>
+          <t>2026/06/27 10:11:40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-33.3607566, -70.80896</t>
+          <t>-32.5634049, -70.695095</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-33.36076, -70.80896</t>
+          <t>-32.56340, -70.69509</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/06/26 10:15:18</t>
+          <t>2026/06/27 17:37:13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-33.3601849, -70.80904</t>
+          <t>-32.797685, -70.8873916</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-33.36018, -70.80904</t>
+          <t>-32.79769, -70.88739</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:23:26</t>
+          <t>07:25:33</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.62</v>
+        <v>40.7</v>
       </c>
       <c r="M31" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2197,44 +2197,44 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/06/26 09:54:36</t>
+          <t>2026/06/27 10:21:54</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.360734, -70.809029</t>
+          <t>-33.3533966, -70.669735</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.36073, -70.80903</t>
+          <t>-33.35340, -70.66974</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/06/26 12:46:18</t>
+          <t>2026/06/27 10:43:51</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.350699, -70.805758</t>
+          <t>-33.3623266, -70.670125</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.35070, -70.80576</t>
+          <t>-33.36233, -70.67012</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>02:51:42</t>
+          <t>00:21:57</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.66</v>
+        <v>3.17</v>
       </c>
       <c r="M32" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N32" t="n">
         <v>15</v>
@@ -2243,11 +2243,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/06/26 09:56:38</t>
+          <t>2026/06/27 10:26:12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-33.367265, -70.695965</t>
+          <t>-32.848095, -70.925136</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-33.36727, -70.69597</t>
+          <t>-32.84810, -70.92514</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/06/26 14:53:30</t>
+          <t>2026/06/27 11:10:27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-33.364886, -70.677353</t>
+          <t>-32.83858, -70.953996</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-33.36489, -70.67735</t>
+          <t>-32.83858, -70.95400</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>04:56:52</t>
+          <t>00:44:15</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>6.85</v>
       </c>
       <c r="M33" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/06/26 09:58:24</t>
+          <t>2026/06/27 10:44:15</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-33.360572, -70.809053</t>
+          <t>-33.362145, -70.6701483</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-33.36057, -70.80905</t>
+          <t>-33.36214, -70.67015</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/06/26 10:18:58</t>
+          <t>2026/06/27 13:04:17</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-33.361196, -70.809027</t>
+          <t>-33.4516283, -70.633405</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-33.36120, -70.80903</t>
+          <t>-33.45163, -70.63340</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>00:20:34</t>
+          <t>02:20:02</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.1</v>
+        <v>17.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,53 +2374,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/06/26 10:03:16</t>
+          <t>2026/06/27 11:10:48</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.75351, -70.730845</t>
+          <t>-32.8388, -70.954135</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.75351, -70.73085</t>
+          <t>-32.83880, -70.95413</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/06/26 10:33:41</t>
+          <t>2026/06/27 11:55:33</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.8166133, -70.6912283</t>
+          <t>-32.840116, -70.950532</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.81661, -70.69123</t>
+          <t>-32.84012, -70.95053</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:30:25</t>
+          <t>00:44:45</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>9.619999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="M35" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="N35" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/06/26 10:15:33</t>
+          <t>2026/06/27 11:17:49</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.3606333, -70.8089749</t>
+          <t>-32.836485, -70.5946266</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.36063, -70.80897</t>
+          <t>-32.83649, -70.59463</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/06/26 11:38:54</t>
+          <t>2026/06/27 11:35:11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.3599583, -70.8069966</t>
+          <t>-32.8289833, -70.59968</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80700</t>
+          <t>-32.82898, -70.59968</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>01:23:21</t>
+          <t>00:17:22</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>2.09</v>
       </c>
       <c r="M36" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/06/26 10:19:58</t>
+          <t>2026/06/27 11:36:26</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.361594, -70.809035</t>
+          <t>-32.8303366, -70.600205</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.36159, -70.80903</t>
+          <t>-32.83034, -70.60021</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/06/26 11:21:49</t>
+          <t>2026/06/27 12:21:45</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.360766, -70.808953</t>
+          <t>-32.8525433, -70.6055483</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.36077, -70.80895</t>
+          <t>-32.85254, -70.60555</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>01:01:51</t>
+          <t>00:45:19</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.12</v>
+        <v>5.13</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/06/26 10:29:28</t>
+          <t>2026/06/27 11:55:54</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-34.5791533, -70.9614316</t>
+          <t>-32.840112, -70.950526</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-34.57915, -70.96143</t>
+          <t>-32.84011, -70.95053</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/06/26 11:21:56</t>
+          <t>2026/06/27 12:22:51</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-34.87726, -71.1261916</t>
+          <t>-32.84386, -70.936934</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-34.87726, -71.12619</t>
+          <t>-32.84386, -70.93693</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:52:28</t>
+          <t>00:26:57</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>42.32</v>
+        <v>2.77</v>
       </c>
       <c r="M38" t="n">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="N38" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/06/26 10:34:56</t>
+          <t>2026/06/27 12:23:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-32.820035, -70.6897083</t>
+          <t>-32.8521766, -70.607525</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-32.82003, -70.68971</t>
+          <t>-32.85218, -70.60752</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/06/26 11:02:57</t>
+          <t>2026/06/27 12:47:12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-32.8825033, -70.6119566</t>
+          <t>-32.85219, -70.6075033</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-32.88250, -70.61196</t>
+          <t>-32.85219, -70.60750</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:28:01</t>
+          <t>00:24:12</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>16.25</v>
+        <v>0.65</v>
       </c>
       <c r="M39" t="n">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="N39" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/06/26 10:37:01</t>
+          <t>2026/06/27 12:23:45</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-33.3655649, -70.67031</t>
+          <t>-32.841922, -70.936833</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-33.36556, -70.67031</t>
+          <t>-32.84192, -70.93683</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/06/26 10:46:37</t>
+          <t>2026/06/27 14:43:51</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-33.3623733, -70.6701266</t>
+          <t>-32.840239, -70.960661</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-33.36237, -70.67013</t>
+          <t>-32.84024, -70.96066</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:09:36</t>
+          <t>02:20:06</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.4</v>
+        <v>2.64</v>
       </c>
       <c r="M40" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/06/26 10:45:16</t>
+          <t>2026/06/27 12:48:27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.3637116, -70.7854783</t>
+          <t>-32.8521866, -70.6075366</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.36371, -70.78548</t>
+          <t>-32.85219, -70.60754</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/06/26 10:59:03</t>
+          <t>2026/06/27 13:23:52</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.3601833, -70.8090216</t>
+          <t>-32.844175, -70.599195</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.36018, -70.80902</t>
+          <t>-32.84417, -70.59919</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:13:47</t>
+          <t>00:35:25</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.38</v>
+        <v>11.1</v>
       </c>
       <c r="M41" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="N41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/06/26 10:47:02</t>
+          <t>2026/06/27 13:05:32</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-33.3620883, -70.6701233</t>
+          <t>-33.45008, -70.63392</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67012</t>
+          <t>-33.45008, -70.63392</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/06/26 11:43:42</t>
+          <t>2026/06/27 13:53:25</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-33.3895149, -70.6738883</t>
+          <t>-33.4472583, -70.6322033</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-33.38951, -70.67389</t>
+          <t>-33.44726, -70.63220</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:56:40</t>
+          <t>00:47:53</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.99</v>
+        <v>0.46</v>
       </c>
       <c r="M42" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N42" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/06/26 10:54:15</t>
+          <t>2026/06/27 13:25:07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-34.876221, -71.127472</t>
+          <t>-32.8442583, -70.5993883</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-34.87622, -71.12747</t>
+          <t>-32.84426, -70.59939</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/06/26 11:12:15</t>
+          <t>2026/06/27 13:45:50</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-34.876673, -71.127589</t>
+          <t>-32.8791933, -70.608955</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-34.87667, -71.12759</t>
+          <t>-32.87919, -70.60895</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:18:00</t>
+          <t>00:20:43</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.13</v>
+        <v>5.88</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/06/26 11:00:18</t>
+          <t>2026/06/27 13:46:19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.3608083, -70.809045</t>
+          <t>-32.8790566, -70.6093983</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.36081, -70.80904</t>
+          <t>-32.87906, -70.60940</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/06/26 12:25:51</t>
+          <t>2026/06/27 14:51:03</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.360555, -70.8091433</t>
+          <t>-32.8791966, -70.608935</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.36055, -70.80914</t>
+          <t>-32.87920, -70.60894</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01:25:33</t>
+          <t>01:04:44</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.28</v>
+        <v>6.2</v>
       </c>
       <c r="M44" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/06/26 11:04:12</t>
+          <t>2026/06/27 13:49:26</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-32.8831816, -70.6123833</t>
+          <t>-32.840002, -70.961183</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-32.88318, -70.61238</t>
+          <t>-32.84000, -70.96118</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/06/26 12:06:26</t>
+          <t>2026/06/27 14:06:55</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-32.7576983, -70.7027899</t>
+          <t>-32.840463, -70.95988</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-32.75770, -70.70279</t>
+          <t>-32.84046, -70.95988</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>01:02:14</t>
+          <t>00:17:29</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>25.38</v>
+        <v>0.14</v>
       </c>
       <c r="M45" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="N45" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,53 +3023,53 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/06/26 11:13:15</t>
+          <t>2026/06/27 13:54:40</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-34.876714, -71.127592</t>
+          <t>-33.4451933, -70.632835</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-34.87671, -71.12759</t>
+          <t>-33.44519, -70.63284</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/06/26 12:12:04</t>
+          <t>2026/06/27 14:32:42</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-34.876241, -71.127603</t>
+          <t>-33.3895216, -70.6738533</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-34.87624, -71.12760</t>
+          <t>-33.38952, -70.67385</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:58:49</t>
+          <t>00:38:02</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.46</v>
+        <v>12.37</v>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3077,62 +3077,62 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/06/26 11:22:02</t>
+          <t>2026/06/27 14:07:50</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.360728, -70.808967</t>
+          <t>-32.840464, -70.959878</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.36073, -70.80897</t>
+          <t>-32.84046, -70.95988</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/06/26 11:59:38</t>
+          <t>2026/06/27 14:41:54</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.360795, -70.808967</t>
+          <t>-32.838385, -70.955506</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.36080, -70.80897</t>
+          <t>-32.83839, -70.95551</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:37:36</t>
+          <t>00:34:04</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.02</v>
+        <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,53 +3141,53 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/06/26 11:23:11</t>
+          <t>2026/06/27 14:33:13</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-34.87913, -71.1277316</t>
+          <t>-33.3893333, -70.6740066</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-34.87913, -71.12773</t>
+          <t>-33.38933, -70.67401</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/06/26 14:17:25</t>
+          <t>2026/06/27 15:12:42</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-32.8653099, -70.63864</t>
+          <t>-33.36706, -70.6796766</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-32.86531, -70.63864</t>
+          <t>-33.36706, -70.67968</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>02:54:14</t>
+          <t>00:39:29</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>245.55</v>
+        <v>3.45</v>
       </c>
       <c r="M48" t="n">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="N48" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/06/26 11:39:01</t>
+          <t>2026/06/27 14:42:15</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-33.3600016, -70.8071233</t>
+          <t>-32.838384, -70.955512</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80712</t>
+          <t>-32.83838, -70.95551</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/06/26 11:55:49</t>
+          <t>2026/06/27 15:25:06</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-33.360955, -70.80907</t>
+          <t>-32.791624, -70.912643</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-33.36095, -70.80907</t>
+          <t>-32.79162, -70.91264</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:16:48</t>
+          <t>00:42:51</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.9</v>
+        <v>18.52</v>
       </c>
       <c r="M49" t="n">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="N49" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/06/26 11:44:04</t>
+          <t>2026/06/27 14:44:51</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.3893433, -70.6740133</t>
+          <t>-32.840319, -70.960333</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.38934, -70.67401</t>
+          <t>-32.84032, -70.96033</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/06/26 13:59:39</t>
+          <t>2026/06/27 15:14:57</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-34.8763533, -71.127295</t>
+          <t>-32.841743, -70.936878</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-34.87635, -71.12730</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>02:15:35</t>
+          <t>00:30:06</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>185.46</v>
+        <v>2.75</v>
       </c>
       <c r="M50" t="n">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="N50" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/06/26 11:55:56</t>
+          <t>2026/06/27 14:51:31</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-33.3609449, -70.8091183</t>
+          <t>-32.8790633, -70.6093749</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-33.36094, -70.80912</t>
+          <t>-32.87906, -70.60937</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/06/26 12:42:20</t>
+          <t>2026/06/27 18:01:38</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.3600166, -70.8071666</t>
+          <t>-32.8826616, -70.6107166</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80717</t>
+          <t>-32.88266, -70.61072</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>00:46:24</t>
+          <t>03:10:07</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="M51" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/06/26 11:59:58</t>
+          <t>2026/06/27 15:13:57</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.360756, -70.808975</t>
+          <t>-33.3651883, -70.679935</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.36076, -70.80898</t>
+          <t>-33.36519, -70.67994</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/06/26 13:15:38</t>
+          <t>2026/06/27 15:31:46</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.359992, -70.807052</t>
+          <t>-33.3513016, -70.6718799</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80705</t>
+          <t>-33.35130, -70.67188</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>01:15:40</t>
+          <t>00:17:49</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.28</v>
+        <v>3.03</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,57 +3436,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/06/26 12:07:41</t>
+          <t>2026/06/27 15:15:49</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-32.7577316, -70.70258</t>
+          <t>-32.84174, -70.936879</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-32.75773, -70.70258</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/06/26 12:57:34</t>
+          <t>2026/06/27 20:40:09</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-32.7582, -70.729785</t>
+          <t>-32.83962, -70.949828</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-32.75820, -70.72979</t>
+          <t>-32.83962, -70.94983</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:49:53</t>
+          <t>05:24:20</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.96</v>
+        <v>3.16</v>
       </c>
       <c r="M53" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="N53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/06/26 12:12:31</t>
+          <t>2026/06/27 15:25:19</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-34.876373, -71.127631</t>
+          <t>-32.791656, -70.912644</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-34.87637, -71.12763</t>
+          <t>-32.79166, -70.91264</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/06/26 13:56:15</t>
+          <t>2026/06/27 19:23:58</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-34.876401, -71.127258</t>
+          <t>-32.838375, -70.955515</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-34.87640, -71.12726</t>
+          <t>-32.83837, -70.95552</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>01:43:44</t>
+          <t>03:58:39</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.02</v>
+        <v>20.26</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/06/26 12:26:01</t>
+          <t>2026/06/27 15:31:58</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.3607316, -70.8091716</t>
+          <t>-33.351275, -70.6716433</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.36073, -70.80917</t>
+          <t>-33.35128, -70.67164</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/06/26 13:10:32</t>
+          <t>2026/06/27 15:44:45</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.36168, -70.80909</t>
+          <t>-33.3623299, -70.67012</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.36168, -70.80909</t>
+          <t>-33.36233, -70.67012</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:44:31</t>
+          <t>00:12:47</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.11</v>
+        <v>2.93</v>
       </c>
       <c r="M55" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,57 +3613,57 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/06/26 12:37:24</t>
+          <t>2026/06/27 15:45:17</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-37.7759583, -73.3820866</t>
+          <t>-33.3620616, -70.6701116</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-37.77596, -73.38209</t>
+          <t>-33.36206, -70.67011</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/06/26 13:45:54</t>
+          <t>2026/06/27 19:52:55</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-37.797005, -73.400775</t>
+          <t>-33.476245, -70.6983966</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-37.79700, -73.40077</t>
+          <t>-33.47624, -70.69840</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>01:08:30</t>
+          <t>04:07:38</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.48</v>
+        <v>18.19</v>
       </c>
       <c r="M56" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,53 +3672,53 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/06/26 12:42:37</t>
+          <t>2026/06/27 17:21:50</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.3600533, -70.80717</t>
+          <t>-37.1956749, -73.2035466</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80717</t>
+          <t>-37.19567, -73.20355</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/06/26 12:54:17</t>
+          <t>2026/06/27 18:34:15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.3598633, -70.8071</t>
+          <t>-36.9039566, -73.028235</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.35986, -70.80710</t>
+          <t>-36.90396, -73.02823</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:11:40</t>
+          <t>01:12:25</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.5600000000000001</v>
+        <v>61.44</v>
       </c>
       <c r="M57" t="n">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="N57" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/06/26 12:46:38</t>
+          <t>2026/06/27 17:37:36</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-33.350803, -70.805755</t>
+          <t>-32.7975933, -70.8870683</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-33.35080, -70.80576</t>
+          <t>-32.79759, -70.88707</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/06/26 12:54:15</t>
+          <t>2026/06/28 10:02:13</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-33.360335, -70.805338</t>
+          <t>-32.835125, -70.6046299</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-33.36033, -70.80534</t>
+          <t>-32.83512, -70.60463</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:07:37</t>
+          <t>16:24:37</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.44</v>
+        <v>32.97</v>
       </c>
       <c r="M58" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="N58" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/06/26 12:54:20</t>
+          <t>2026/06/27 18:02:53</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.359855, -70.807095</t>
+          <t>-32.8849033, -70.6103083</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.35986, -70.80710</t>
+          <t>-32.88490, -70.61031</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/06/26 15:29:19</t>
+          <t>2026/06/27 18:30:25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.3598866, -70.8070666</t>
+          <t>-32.8430116, -70.59892</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.35989, -70.80707</t>
+          <t>-32.84301, -70.59892</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>02:34:59</t>
+          <t>00:27:32</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.01</v>
+        <v>6.74</v>
       </c>
       <c r="M59" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/06/26 12:54:54</t>
+          <t>2026/06/27 18:31:40</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-33.3599, -70.806836</t>
+          <t>-32.84306, -70.598865</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80684</t>
+          <t>-32.84306, -70.59887</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/06/26 15:30:24</t>
+          <t>2026/06/27 18:54:52</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-33.359134, -70.80887</t>
+          <t>-32.8481666, -70.5919649</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-33.35913, -70.80887</t>
+          <t>-32.84817, -70.59196</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>02:35:30</t>
+          <t>00:23:12</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.36</v>
+        <v>2.01</v>
       </c>
       <c r="M60" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="N60" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/06/26 12:58:49</t>
+          <t>2026/06/27 18:35:14</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-32.7553766, -70.7287033</t>
+          <t>-36.9038983, -73.0298766</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-32.75538, -70.72870</t>
+          <t>-36.90390, -73.02988</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/06/26 13:51:49</t>
+          <t>2026/06/28 13:39:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.7977583, -70.8874333</t>
+          <t>-36.8459166, -73.0518549</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.79776, -70.88743</t>
+          <t>-36.84592, -73.05185</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:53:00</t>
+          <t>19:03:46</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>26.42</v>
+        <v>6.81</v>
       </c>
       <c r="M61" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N61" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/06/26 13:12:29</t>
+          <t>2026/06/27 18:56:07</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-33.3618283, -70.8092233</t>
+          <t>-32.84827, -70.5920433</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-33.36183, -70.80922</t>
+          <t>-32.84827, -70.59204</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/06/26 13:29:16</t>
+          <t>2026/06/27 19:15:38</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-33.3603116, -70.8089866</t>
+          <t>-32.8791983, -70.608915</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-33.36031, -70.80899</t>
+          <t>-32.87920, -70.60891</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:16:47</t>
+          <t>00:19:31</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.19</v>
+        <v>7.4</v>
       </c>
       <c r="M62" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="N62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,53 +4026,53 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/06/26 13:16:05</t>
+          <t>2026/06/27 19:16:20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-33.360063, -70.807123</t>
+          <t>-32.8790583, -70.6093816</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-33.36006, -70.80712</t>
+          <t>-32.87906, -70.60938</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/06/26 16:16:22</t>
+          <t>2026/06/28 11:00:25</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-33.360057, -70.807151</t>
+          <t>-32.8663783, -70.6238599</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-33.36006, -70.80715</t>
+          <t>-32.86638, -70.62386</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>03:00:17</t>
+          <t>15:44:05</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.01</v>
+        <v>3.87</v>
       </c>
       <c r="M63" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="N63" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/06/26 13:30:31</t>
+          <t>2026/06/27 19:24:26</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.3595383, -70.8090083</t>
+          <t>-32.838372, -70.955529</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.35954, -70.80901</t>
+          <t>-32.83837, -70.95553</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/06/26 13:38:00</t>
+          <t>2026/06/27 21:07:34</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.3601266, -70.8068849</t>
+          <t>-32.785696, -70.960382</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.36013, -70.80688</t>
+          <t>-32.78570, -70.96038</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:07:29</t>
+          <t>01:43:08</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.26</v>
+        <v>14.9</v>
       </c>
       <c r="M64" t="n">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="N64" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/06/26 13:38:05</t>
+          <t>2026/06/27 19:54:08</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.360075, -70.8068416</t>
+          <t>-33.4761199, -70.6985283</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80684</t>
+          <t>-33.47612, -70.69853</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/06/26 15:36:12</t>
+          <t>2026/06/28 08:07:43</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.08735, -71.3622599</t>
+          <t>-33.4761916, -70.6984216</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36226</t>
+          <t>-33.47619, -70.69842</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01:58:07</t>
+          <t>12:13:35</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>112.89</v>
+        <v>0.02</v>
       </c>
       <c r="M65" t="n">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="N65" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,57 +4203,57 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/06/26 13:46:58</t>
+          <t>2026/06/27 20:41:00</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-37.797525, -73.4010183</t>
+          <t>-32.840071, -70.950259</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-37.79753, -73.40102</t>
+          <t>-32.84007, -70.95026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/06/26 16:17:53</t>
+          <t>2026/06/27 20:54:21</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-38.3416883, -73.4949883</t>
+          <t>-32.840052, -70.95025</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-38.34169, -73.49499</t>
+          <t>-32.84005, -70.95025</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>02:30:55</t>
+          <t>00:13:21</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>67.5</v>
+        <v>1.31</v>
       </c>
       <c r="M66" t="n">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="N66" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,116 +4262,116 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/06/26 13:52:05</t>
+          <t>2026/06/27 20:55:21</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-32.7976233, -70.8870916</t>
+          <t>-32.840061, -70.95026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88709</t>
+          <t>-32.84006, -70.95026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/06/26 17:09:11</t>
+          <t>2026/06/27 21:05:21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-32.7857883, -70.8316066</t>
+          <t>-32.838616, -70.954015</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-32.78579, -70.83161</t>
+          <t>-32.83862, -70.95401</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>03:17:06</t>
+          <t>00:10:00</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.61</v>
+        <v>0.84</v>
       </c>
       <c r="M67" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="N67" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/06/26 13:57:01</t>
+          <t>2026/06/27 21:05:36</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.876434, -71.127229</t>
+          <t>-32.838715, -70.954078</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12723</t>
+          <t>-32.83872, -70.95408</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/06/29 01:25:19</t>
+          <t>2026/06/27 21:45:39</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-34.876375, -71.127119</t>
+          <t>-32.841841, -70.936899</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-34.87638, -71.12712</t>
+          <t>-32.84184, -70.93690</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>59:28:18</t>
+          <t>00:40:03</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.03</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,57 +4380,57 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/06/26 14:00:07</t>
+          <t>2026/06/27 21:08:02</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.8759516, -71.1274916</t>
+          <t>-32.785385, -70.960451</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.87595, -71.12749</t>
+          <t>-32.78538, -70.96045</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/06/26 14:20:00</t>
+          <t>2026/06/27 21:48:08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.8751633, -71.1283866</t>
+          <t>-32.780869, -70.981334</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.87516, -71.12839</t>
+          <t>-32.78087, -70.98133</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:19:53</t>
+          <t>00:40:06</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.17</v>
+        <v>3.05</v>
       </c>
       <c r="M69" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="N69" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,57 +4439,57 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/06/26 14:18:40</t>
+          <t>2026/06/27 21:45:55</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-32.8643533, -70.6411583</t>
+          <t>-32.841804, -70.936878</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-32.86435, -70.64116</t>
+          <t>-32.84180, -70.93688</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/06/26 14:35:57</t>
+          <t>2026/06/28 10:55:29</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-32.8675966, -70.62318</t>
+          <t>-32.83853, -70.953887</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-32.86760, -70.62318</t>
+          <t>-32.83853, -70.95389</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:17:17</t>
+          <t>13:09:34</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.93</v>
+        <v>2.29</v>
       </c>
       <c r="M70" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="N70" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/06/26 14:20:05</t>
+          <t>2026/06/27 21:48:29</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.8751633, -71.1285</t>
+          <t>-32.780847, -70.98129</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.87516, -71.12850</t>
+          <t>-32.78085, -70.98129</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/06/26 15:33:27</t>
+          <t>2026/06/28 01:41:15</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-34.8751983, -71.1283616</t>
+          <t>-32.785697, -70.960385</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-34.87520, -71.12836</t>
+          <t>-32.78570, -70.96039</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>01:13:22</t>
+          <t>03:52:46</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.01</v>
+        <v>3.11</v>
       </c>
       <c r="M71" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="N71" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/06/26 14:36:34</t>
+          <t>2026/06/28 02:40:11</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-32.86622, -70.6239799</t>
+          <t>-33.368129, -70.696085</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-32.86622, -70.62398</t>
+          <t>-33.36813, -70.69608</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/06/26 15:00:52</t>
+          <t>2026/06/30 01:41:05</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-32.8791266, -70.6092616</t>
+          <t>-33.367112, -70.696652</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-32.87913, -70.60926</t>
+          <t>-33.36711, -70.69665</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:24:18</t>
+          <t>47:00:54</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4.02</v>
+        <v>0.12</v>
       </c>
       <c r="M72" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,116 +4616,116 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/06/26 14:54:21</t>
+          <t>2026/06/29 14:00:24</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-33.364875, -70.676849</t>
+          <t>-32.7975833, -70.8870766</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-33.36487, -70.67685</t>
+          <t>-32.79758, -70.88708</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/06/26 15:58:18</t>
+          <t>2026/06/30 09:05:06</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.367313, -70.695542</t>
+          <t>-33.3672816, -70.696575</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.36731, -70.69554</t>
+          <t>-33.36728, -70.69657</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>01:03:57</t>
+          <t>19:04:42</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.56</v>
+        <v>100.14</v>
       </c>
       <c r="M73" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="N73" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/06/26 15:01:16</t>
+          <t>2026/06/30 10:05:46</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-32.879225, -70.6087683</t>
+          <t>-32.840279, -70.964577</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60877</t>
+          <t>-32.84028, -70.96458</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/06/26 15:26:17</t>
+          <t>2026/06/30 10:56:45</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-32.8429533, -70.6028383</t>
+          <t>-32.840287, -70.964573</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-32.84295, -70.60284</t>
+          <t>-32.84029, -70.96457</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:25:01</t>
+          <t>00:50:59</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>5.89</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="N74" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,116 +4734,116 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/06/26 15:27:32</t>
+          <t>2026/06/30 10:28:39</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-32.8427, -70.6036016</t>
+          <t>-33.0448016, -71.4202366</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-32.84270, -70.60360</t>
+          <t>-33.04480, -71.42024</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/06/26 16:00:08</t>
+          <t>2026/06/30 10:58:00</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-32.8792033, -70.60894</t>
+          <t>-33.0873283, -71.362295</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60894</t>
+          <t>-33.08733, -71.36230</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:32:36</t>
+          <t>00:29:21</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>8.48</v>
+        <v>10.54</v>
       </c>
       <c r="M75" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N75" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/06/26 15:29:33</t>
+          <t>2026/06/30 10:57:04</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.3600183, -70.8071383</t>
+          <t>-32.840354, -70.964574</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80714</t>
+          <t>-32.84035, -70.96457</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/06/26 17:37:36</t>
+          <t>2026/06/30 12:37:02</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-32.7432316, -70.7329316</t>
+          <t>-32.840478, -70.964481</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-32.74323, -70.73293</t>
+          <t>-32.84048, -70.96448</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>02:08:03</t>
+          <t>01:39:58</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>89.81</v>
+        <v>0.05</v>
       </c>
       <c r="M76" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,106 +4852,106 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/06/26 15:31:28</t>
+          <t>2026/06/30 10:59:15</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.360421, -70.809071</t>
+          <t>-33.0873166, -71.3623183</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.36042, -70.80907</t>
+          <t>-33.08732, -71.36232</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/06/26 15:54:15</t>
+          <t>2026/06/30 14:38:33</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.360048, -70.807097</t>
+          <t>-33.0978099, -71.3298233</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80710</t>
+          <t>-33.09781, -71.32982</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:22:47</t>
+          <t>03:39:18</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.21</v>
+        <v>4.18</v>
       </c>
       <c r="M77" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N77" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/06/26 15:34:42</t>
+          <t>2026/06/30 11:54:57</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-34.8764566, -71.1271483</t>
+          <t>-33.360036, -70.807118</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-34.87646, -71.12715</t>
+          <t>-33.36004, -70.80712</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/06/26 18:12:03</t>
+          <t>2026/07/02 14:40:46</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.3623033, -70.6701366</t>
+          <t>-33.359985, -70.807068</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.36230, -70.67014</t>
+          <t>-33.35999, -70.80707</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>02:37:21</t>
+          <t>50:45:49</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>188.71</v>
+        <v>0.03</v>
       </c>
       <c r="M78" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,57 +4970,57 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/06/26 15:37:27</t>
+          <t>2026/06/30 14:38:52</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.087335, -71.3622983</t>
+          <t>-33.0976766, -71.3297416</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36230</t>
+          <t>-33.09768, -71.32974</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/06/27 10:05:33</t>
+          <t>2026/06/30 16:56:22</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.0873016, -71.3623633</t>
+          <t>-33.0868266, -71.361695</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36236</t>
+          <t>-33.08683, -71.36169</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18:28:06</t>
+          <t>02:17:30</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.3</v>
+        <v>4.13</v>
       </c>
       <c r="M79" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="N79" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/06/26 15:55:12</t>
+          <t>2026/06/30 16:57:11</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-33.36007, -70.807112</t>
+          <t>-33.0873449, -71.3622499</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80711</t>
+          <t>-33.08734, -71.36225</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/06/26 16:37:42</t>
+          <t>2026/06/30 17:24:32</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.474046, -70.739572</t>
+          <t>-33.0444533, -71.3743799</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.47405, -70.73957</t>
+          <t>-33.04445, -71.37438</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:42:30</t>
+          <t>00:27:21</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>20.29</v>
+        <v>6.63</v>
       </c>
       <c r="M80" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="N80" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,116 +5088,116 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/06/26 15:57:31</t>
+          <t>2026/06/30 17:25:47</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-34.204304, -70.678835</t>
+          <t>-33.0453866, -71.3743666</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-34.20430, -70.67884</t>
+          <t>-33.04539, -71.37437</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/06/26 16:31:24</t>
+          <t>2026/06/30 17:43:45</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-34.205284, -70.677492</t>
+          <t>-33.0583616, -71.3730366</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-34.20528, -70.67749</t>
+          <t>-33.05836, -71.37304</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:33:53</t>
+          <t>00:17:58</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="M81" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/06/26 15:59:02</t>
+          <t>2026/06/30 17:29:34</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-33.367284, -70.695898</t>
+          <t>-34.205411, -70.677278</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69590</t>
+          <t>-34.20541, -70.67728</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/06/26 17:17:31</t>
+          <t>2026/07/03 22:11:17</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-32.838346, -70.955586</t>
+          <t>-34.205464, -70.677346</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-32.83835, -70.95559</t>
+          <t>-34.20546, -70.67735</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>01:18:29</t>
+          <t>76:41:43</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>77.01000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="M82" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/06/26 16:00:40</t>
+          <t>2026/06/30 17:45:00</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-32.8791166, -70.6093483</t>
+          <t>-33.0582999, -71.3728383</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-32.87912, -70.60935</t>
+          <t>-33.05830, -71.37284</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/06/26 19:09:57</t>
+          <t>2026/06/30 18:03:42</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-32.88006, -70.6035416</t>
+          <t>-33.0873483, -71.3622933</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-32.88006, -70.60354</t>
+          <t>-33.08735, -71.36229</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>03:09:17</t>
+          <t>00:18:42</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.59</v>
+        <v>4.46</v>
       </c>
       <c r="M83" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="N83" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/06/26 16:18:40</t>
+          <t>2026/06/30 18:00:06</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-38.3433699, -73.4938983</t>
+          <t>-32.7853849, -70.8316733</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-38.34337, -73.49390</t>
+          <t>-32.78538, -70.83167</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/06/26 17:03:13</t>
+          <t>2026/06/30 18:15:43</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-38.3433283, -73.5009216</t>
+          <t>-32.7977249, -70.8874233</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-38.34333, -73.50092</t>
+          <t>-32.79772, -70.88742</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:44:33</t>
+          <t>00:15:37</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.17</v>
+        <v>7.39</v>
       </c>
       <c r="M84" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="N84" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/06/26 16:31:58</t>
+          <t>2026/06/30 18:04:57</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-34.205407, -70.677286</t>
+          <t>-33.0872683, -71.3622716</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67729</t>
+          <t>-33.08727, -71.36227</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/06/30 16:59:54</t>
+          <t>2026/07/01 09:04:41</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-34.205234, -70.680382</t>
+          <t>-33.0873116, -71.3623033</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-34.20523, -70.68038</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>96:27:56</t>
+          <t>14:59:44</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="M85" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/06/26 16:38:36</t>
+          <t>2026/06/30 18:16:32</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.473794, -70.740116</t>
+          <t>-32.7976249, -70.8871316</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.47379, -70.74012</t>
+          <t>-32.79762, -70.88713</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/06/26 17:48:15</t>
+          <t>2026/07/01 08:29:06</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.482118, -70.765264</t>
+          <t>-33.367225, -70.6965716</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.48212, -70.76526</t>
+          <t>-33.36722, -70.69657</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>01:09:39</t>
+          <t>14:12:34</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.85</v>
+        <v>92.52</v>
       </c>
       <c r="M86" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="N86" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/06/26 17:03:49</t>
+          <t>2026/06/30 19:32:56</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-38.3419266, -73.5017033</t>
+          <t>-33.389315, -70.6740216</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-38.34193, -73.50170</t>
+          <t>-33.38932, -70.67402</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/06/26 18:43:55</t>
+          <t>2026/06/30 20:28:10</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-37.7969683, -73.4007616</t>
+          <t>-33.4762483, -70.6982899</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-37.79697, -73.40076</t>
+          <t>-33.47625, -70.69829</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01:40:06</t>
+          <t>00:55:14</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>69.98999999999999</v>
+        <v>13.58</v>
       </c>
       <c r="M87" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="N87" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,116 +5501,116 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/06/26 17:09:22</t>
+          <t>2026/06/30 20:29:25</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-32.78552, -70.8316366</t>
+          <t>-33.4761, -70.6985283</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-32.78552, -70.83164</t>
+          <t>-33.47610, -70.69853</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/06/26 17:18:56</t>
+          <t>2026/07/01 09:24:18</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-32.7675333, -70.8303733</t>
+          <t>-33.4761566, -70.698465</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-32.76753, -70.83037</t>
+          <t>-33.47616, -70.69846</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:09:34</t>
+          <t>12:54:53</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.36</v>
+        <v>0.01</v>
       </c>
       <c r="M88" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="N88" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026/07/01 09:52:27</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-33.3679799, -70.7269766</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-33.36798, -70.72698</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026/07/01 10:10:34</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-33.3686783, -70.7259816</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-33.36868, -70.72598</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>00:18:07</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M89" t="n">
+        <v>9</v>
+      </c>
+      <c r="N89" t="n">
         <v>7</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2026/06/26 17:13:49</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-33.360057, -70.807151</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-33.36006, -70.80715</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2026/06/30 11:39:26</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-33.360734, -70.809006</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-33.36073, -70.80901</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>90:25:37</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M89" t="n">
-        <v>4</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/06/26 17:17:44</t>
+          <t>2026/07/01 10:11:49</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-32.838347, -70.955531</t>
+          <t>-33.3685633, -70.7261283</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-32.83835, -70.95553</t>
+          <t>-33.36856, -70.72613</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/06/26 18:29:01</t>
+          <t>2026/07/01 10:47:32</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-32.841359, -70.955513</t>
+          <t>-33.3599716, -70.8071033</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-32.84136, -70.95551</t>
+          <t>-33.35997, -70.80710</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>01:11:17</t>
+          <t>00:35:43</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.78</v>
+        <v>10.85</v>
       </c>
       <c r="M90" t="n">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="N90" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/06/26 17:20:11</t>
+          <t>2026/07/01 10:47:44</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-32.76759, -70.8301649</t>
+          <t>-33.3600133, -70.8071849</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-32.76759, -70.83016</t>
+          <t>-33.36001, -70.80718</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/06/26 17:34:05</t>
+          <t>2026/07/01 12:15:18</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-32.7977183, -70.8874249</t>
+          <t>-33.5031949, -71.2568966</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88742</t>
+          <t>-33.50319, -71.25690</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:13:54</t>
+          <t>01:27:34</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>6.51</v>
+        <v>64.69</v>
       </c>
       <c r="M91" t="n">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="N91" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,47 +5737,47 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/06/26 17:34:24</t>
+          <t>2026/07/01 12:16:33</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.8870716</t>
+          <t>-33.506265, -71.2518333</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88707</t>
+          <t>-33.50626, -71.25183</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/06/27 09:33:41</t>
+          <t>2026/07/01 13:20:12</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-32.6229216, -70.7180833</t>
+          <t>-33.4559049, -71.3000066</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-32.62292, -70.71808</t>
+          <t>-33.45590, -71.30001</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>15:59:17</t>
+          <t>01:03:39</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>41.67</v>
+        <v>7.56</v>
       </c>
       <c r="M92" t="n">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="N92" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/06/26 17:38:03</t>
+          <t>2026/07/01 13:20:34</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-32.74332, -70.7327116</t>
+          <t>-33.4562116, -71.300045</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-32.74332, -70.73271</t>
+          <t>-33.45621, -71.30004</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/06/26 17:53:36</t>
+          <t>2026/07/01 18:22:09</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-32.745745, -70.7284716</t>
+          <t>-32.9641266, -70.6888516</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-32.74574, -70.72847</t>
+          <t>-32.96413, -70.68885</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:15:33</t>
+          <t>05:01:35</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.49</v>
+        <v>123.71</v>
       </c>
       <c r="M93" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="N93" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/06/26 17:48:33</t>
+          <t>2026/07/01 14:54:21</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.482181, -70.764877</t>
+          <t>-33.366535, -70.696175</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76488</t>
+          <t>-33.36653, -70.69617</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/06/26 22:30:18</t>
+          <t>2026/07/01 16:36:18</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.39985, -70.795284</t>
+          <t>-33.3665766, -70.696145</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.39985, -70.79528</t>
+          <t>-33.36658, -70.69615</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>04:41:45</t>
+          <t>01:41:57</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>20.66</v>
+        <v>0.04</v>
       </c>
       <c r="M94" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="N94" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/06/26 17:53:47</t>
+          <t>2026/07/01 16:17:48</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-32.7458983, -70.7285133</t>
+          <t>-33.35124, -70.6716316</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-32.74590, -70.72851</t>
+          <t>-33.35124, -70.67163</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/06/26 18:06:32</t>
+          <t>2026/07/01 16:33:09</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-32.7432633, -70.7329133</t>
+          <t>-33.3623016, -70.6701366</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-32.74326, -70.73291</t>
+          <t>-33.36230, -70.67014</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:12:45</t>
+          <t>00:15:21</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.51</v>
+        <v>2.91</v>
       </c>
       <c r="M95" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="N95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,44 +5973,44 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/06/26 18:06:52</t>
+          <t>2026/07/01 16:34:16</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-32.743335, -70.73272</t>
+          <t>-33.3621083, -70.6701349</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-32.74334, -70.73272</t>
+          <t>-33.36211, -70.67013</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/06/26 20:22:21</t>
+          <t>2026/07/01 18:13:15</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-32.7432533, -70.7328566</t>
+          <t>-33.3895166, -70.6738466</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-32.74325, -70.73286</t>
+          <t>-33.38952, -70.67385</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>02:15:29</t>
+          <t>01:38:59</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.55</v>
+        <v>4.04</v>
       </c>
       <c r="M96" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="N96" t="n">
         <v>13</v>
@@ -6019,11 +6019,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/06/26 18:12:32</t>
+          <t>2026/07/01 16:37:24</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-33.3620916, -70.67014</t>
+          <t>-33.3665449, -70.6961266</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67014</t>
+          <t>-33.36654, -70.69613</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/06/26 19:56:14</t>
+          <t>2026/07/01 18:37:01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-33.4762783, -70.69835</t>
+          <t>-33.4292333, -70.62603</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69835</t>
+          <t>-33.42923, -70.62603</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>01:43:42</t>
+          <t>01:59:37</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>18.1</v>
+        <v>18.18</v>
       </c>
       <c r="M97" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="N97" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,57 +6091,57 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/06/26 18:29:35</t>
+          <t>2026/07/01 18:13:40</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-32.841353, -70.955568</t>
+          <t>-33.389315, -70.6739966</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-32.84135, -70.95557</t>
+          <t>-33.38932, -70.67400</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/06/26 19:02:19</t>
+          <t>2026/07/01 18:55:19</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.780665, -70.967703</t>
+          <t>-33.3623416, -70.6701316</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.78066, -70.96770</t>
+          <t>-33.36234, -70.67013</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:32:44</t>
+          <t>00:41:39</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>10.51</v>
+        <v>3.57</v>
       </c>
       <c r="M98" t="n">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="N98" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/06/26 18:45:10</t>
+          <t>2026/07/01 18:23:24</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-37.7973733, -73.4009716</t>
+          <t>-32.9638666, -70.6887733</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-37.79737, -73.40097</t>
+          <t>-32.96387, -70.68877</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/06/27 17:20:46</t>
+          <t>2026/07/01 19:04:24</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-37.2067683, -73.210845</t>
+          <t>-32.74321, -70.7329233</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-37.20677, -73.21085</t>
+          <t>-32.74321, -70.73292</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>22:35:36</t>
+          <t>00:41:00</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>75.98</v>
+        <v>26.93</v>
       </c>
       <c r="M99" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="N99" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,44 +6209,44 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/06/26 19:02:46</t>
+          <t>2026/07/01 18:38:16</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.780653, -70.967714</t>
+          <t>-33.429875, -70.6266516</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.78065, -70.96771</t>
+          <t>-33.42988, -70.62665</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/06/26 20:31:51</t>
+          <t>2026/07/01 19:12:43</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.776206, -70.965091</t>
+          <t>-33.4658483, -70.59143</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.77621, -70.96509</t>
+          <t>-33.46585, -70.59143</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>01:29:05</t>
+          <t>00:34:27</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.03</v>
+        <v>7.39</v>
       </c>
       <c r="M100" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="N100" t="n">
         <v>18</v>
@@ -6255,11 +6255,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,116 +6268,116 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/06/26 19:11:12</t>
+          <t>2026/07/01 18:56:17</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-32.8752533, -70.6031866</t>
+          <t>-33.3621316, -70.67014</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-32.87525, -70.60319</t>
+          <t>-33.36213, -70.67014</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/06/26 19:27:07</t>
+          <t>2026/07/01 19:49:48</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-32.8664, -70.6238783</t>
+          <t>-33.4761366, -70.6985283</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-32.86640, -70.62388</t>
+          <t>-33.47614, -70.69853</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:15:55</t>
+          <t>00:53:31</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.93</v>
+        <v>18.19</v>
       </c>
       <c r="M101" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="N101" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C102" t="n">
+        <v>8</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026/07/01 19:04:34</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-32.7433216, -70.7327416</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-32.74332, -70.73274</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026/07/01 19:26:08</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-32.7431749, -70.7296599</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-32.74317, -70.72966</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>00:21:34</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M102" t="n">
         <v>12</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2026/06/26 19:28:22</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-32.8661333, -70.6240466</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-32.86613, -70.62405</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2026/06/26 19:50:57</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-32.8792166, -70.6088699</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-32.87922, -70.60887</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>00:22:35</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="M102" t="n">
-        <v>50</v>
-      </c>
       <c r="N102" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/06/26 19:51:17</t>
+          <t>2026/07/01 19:09:05</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.608785</t>
+          <t>-32.83838, -70.955483</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60878</t>
+          <t>-32.83838, -70.95548</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/06/27 09:57:19</t>
+          <t>2026/07/02 09:35:22</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.8520266, -70.6067616</t>
+          <t>-32.83736, -70.967134</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.85203, -70.60676</t>
+          <t>-32.83736, -70.96713</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>14:06:02</t>
+          <t>14:26:17</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>4.18</v>
+        <v>3.15</v>
       </c>
       <c r="M103" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="N103" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,47 +6445,47 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/06/26 19:56:20</t>
+          <t>2026/07/01 19:13:06</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-33.47632, -70.6983833</t>
+          <t>-33.466, -70.59085</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69838</t>
+          <t>-33.46600, -70.59085</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/06/26 21:11:48</t>
+          <t>2026/07/01 21:09:14</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.4762799, -70.6983316</t>
+          <t>-33.4358966, -70.630045</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69833</t>
+          <t>-33.43590, -70.63004</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>01:15:28</t>
+          <t>01:56:08</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>52.19</v>
+        <v>8.27</v>
       </c>
       <c r="M104" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="N104" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/06/26 20:22:31</t>
+          <t>2026/07/01 19:26:31</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.74333, -70.7327283</t>
+          <t>-32.7430433, -70.7297616</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.74333, -70.73273</t>
+          <t>-32.74304, -70.72976</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/06/26 21:52:36</t>
+          <t>2026/07/02 08:14:22</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.74317, -70.7296833</t>
+          <t>-33.4821016, -70.7654016</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72968</t>
+          <t>-33.48210, -70.76540</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>01:30:05</t>
+          <t>12:47:51</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.12</v>
+        <v>95.72</v>
       </c>
       <c r="M105" t="n">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="N105" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/06/26 20:32:01</t>
+          <t>2026/07/01 19:50:56</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.776326, -70.965305</t>
+          <t>-33.4761066, -70.6985333</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.77633, -70.96531</t>
+          <t>-33.47611, -70.69853</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/06/26 20:39:31</t>
+          <t>2026/07/02 08:43:30</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-32.780692, -70.967683</t>
+          <t>-33.47627, -70.698345</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-32.78069, -70.96768</t>
+          <t>-33.47627, -70.69835</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>00:07:30</t>
+          <t>12:52:34</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.65</v>
+        <v>0.03</v>
       </c>
       <c r="M106" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="N106" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/06/26 20:39:59</t>
+          <t>2026/07/01 21:10:29</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.780667, -70.967708</t>
+          <t>-33.4364533, -70.6295916</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.78067, -70.96771</t>
+          <t>-33.43645, -70.62959</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/06/26 22:06:51</t>
+          <t>2026/07/02 12:50:54</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.780718, -70.967693</t>
+          <t>-33.3673183, -70.6960249</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.78072, -70.96769</t>
+          <t>-33.36732, -70.69602</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>01:26:52</t>
+          <t>15:40:25</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.95</v>
+        <v>13.73</v>
       </c>
       <c r="M107" t="n">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="N107" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,57 +6681,57 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/06/26 21:13:03</t>
+          <t>2026/07/01 21:10:55</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-33.4761283, -70.6985433</t>
+          <t>-32.7975766, -70.8870866</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-33.47613, -70.69854</t>
+          <t>-32.79758, -70.88709</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/06/27 10:06:28</t>
+          <t>2026/07/02 07:49:14</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67015</t>
+          <t>-32.8517066, -70.6845583</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67015</t>
+          <t>-32.85171, -70.68456</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>12:53:25</t>
+          <t>10:38:19</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>18.77</v>
+        <v>29.01</v>
       </c>
       <c r="M108" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="N108" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,53 +6740,53 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/06/26 21:53:47</t>
+          <t>2026/07/02 14:03:25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-32.743075, -70.7297933</t>
+          <t>-34.20837, -70.6774733</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-32.74307, -70.72979</t>
+          <t>-34.20837, -70.67747</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/06/28 14:14:55</t>
+          <t>2026/07/02 14:34:28</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-32.74311, -70.7297249</t>
+          <t>-34.2054716, -70.679015</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-32.74311, -70.72972</t>
+          <t>-34.20547, -70.67902</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>40:21:08</t>
+          <t>00:31:03</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="M109" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N109" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6799,57 +6799,57 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/06/26 22:07:11</t>
+          <t>2026/07/02 14:34:42</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-32.78071, -70.967697</t>
+          <t>-34.205505, -70.6783</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-32.78071, -70.96770</t>
+          <t>-34.20551, -70.67830</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/06/26 23:46:03</t>
+          <t>2026/07/02 15:07:31</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-32.782421, -70.962345</t>
+          <t>-34.205605, -70.6770266</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-32.78242, -70.96234</t>
+          <t>-34.20560, -70.67703</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>01:38:52</t>
+          <t>00:32:49</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.71</v>
+        <v>0.16</v>
       </c>
       <c r="M110" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="N110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,57 +6858,57 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/06/26 22:31:15</t>
+          <t>2026/07/02 15:08:46</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.399197, -70.795128</t>
+          <t>-34.20555, -70.6775616</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.39920, -70.79513</t>
+          <t>-34.20555, -70.67756</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/06/27 01:05:18</t>
+          <t>2026/07/02 18:26:46</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-32.841699, -70.936905</t>
+          <t>-32.7977149, -70.8874383</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-32.84170, -70.93690</t>
+          <t>-32.79771, -70.88744</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>02:34:03</t>
+          <t>03:18:00</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>90.76000000000001</v>
+        <v>196.44</v>
       </c>
       <c r="M111" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="N111" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,470 +6917,470 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/06/26 23:46:43</t>
+          <t>2026/07/02 15:30:04</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-32.782298, -70.961861</t>
+          <t>-33.3603466, -70.8100116</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-32.78230, -70.96186</t>
+          <t>-33.36035, -70.81001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/06/27 00:16:02</t>
+          <t>2026/07/02 15:59:47</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-32.838378, -70.956093</t>
+          <t>-33.3592333, -70.8099633</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95609</t>
+          <t>-33.35923, -70.80996</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:29:19</t>
+          <t>00:29:43</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>12.65</v>
+        <v>0.26</v>
       </c>
       <c r="M112" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="N112" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/06/27 21:45:55</t>
+          <t>2026/07/02 15:38:12</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-32.841804, -70.936878</t>
+          <t>-33.359985, -70.807068</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-32.84180, -70.93688</t>
+          <t>-33.35999, -70.80707</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/06/28 10:55:29</t>
+          <t>2026/07/03 15:48:05</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-32.83853, -70.953887</t>
+          <t>-33.359771, -70.807271</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-32.83853, -70.95389</t>
+          <t>-33.35977, -70.80727</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>13:09:34</t>
+          <t>24:09:53</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.29</v>
+        <v>0.06</v>
       </c>
       <c r="M113" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/06/29 02:23:08</t>
+          <t>2026/07/02 16:00:01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-34.876375, -71.127119</t>
+          <t>-33.35928, -70.8097799</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-34.87638, -71.12712</t>
+          <t>-33.35928, -70.80978</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/01 08:16:05</t>
+          <t>2026/07/02 16:19:50</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-34.876391, -71.127306</t>
+          <t>-33.3612449, -70.8117633</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-34.87639, -71.12731</t>
+          <t>-33.36124, -70.81176</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>53:52:57</t>
+          <t>00:19:49</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="M114" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/06/30 02:39:27</t>
+          <t>2026/07/02 16:19:55</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.367112, -70.696652</t>
+          <t>-33.3612433, -70.8117233</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.36711, -70.69665</t>
+          <t>-33.36124, -70.81172</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/02 23:41:12</t>
+          <t>2026/07/02 18:28:33</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.367536, -70.696538</t>
+          <t>-32.7568816, -70.7350316</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.36754, -70.69654</t>
+          <t>-32.75688, -70.73503</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>69:01:45</t>
+          <t>02:08:38</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0.05</v>
+        <v>114.06</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/06/30 10:05:46</t>
+          <t>2026/07/02 18:27:40</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-32.840279, -70.964577</t>
+          <t>-32.7975916, -70.88712</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-32.84028, -70.96458</t>
+          <t>-32.79759, -70.88712</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/06/30 10:56:45</t>
+          <t>2026/07/03 08:37:23</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-32.840287, -70.964573</t>
+          <t>-32.7568733, -70.7339866</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-32.84029, -70.96457</t>
+          <t>-32.75687, -70.73399</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>00:50:59</t>
+          <t>14:09:43</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>17.39</v>
       </c>
       <c r="M116" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/06/30 10:57:04</t>
+          <t>2026/07/02 18:29:48</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.840354, -70.964574</t>
+          <t>-32.7569433, -70.7346383</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.84035, -70.96457</t>
+          <t>-32.75694, -70.73464</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/06/30 12:37:02</t>
+          <t>2026/07/02 18:45:19</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-32.840478, -70.964481</t>
+          <t>-32.74318, -70.7331016</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-32.84048, -70.96448</t>
+          <t>-32.74318, -70.73310</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>01:39:58</t>
+          <t>00:15:31</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="M117" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/06/30 11:54:57</t>
+          <t>2026/07/02 18:45:31</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-33.360036, -70.807118</t>
+          <t>-32.74332, -70.732715</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-32.74332, -70.73271</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/02 14:40:46</t>
+          <t>2026/07/02 19:06:58</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-33.359985, -70.807068</t>
+          <t>-32.7431666, -70.7296599</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80707</t>
+          <t>-32.74317, -70.72966</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>50:45:49</t>
+          <t>00:21:27</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="M118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/06/30 17:29:34</t>
+          <t>2026/07/02 19:08:13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-34.205411, -70.677278</t>
+          <t>-32.7430483, -70.7297816</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67728</t>
+          <t>-32.74305, -70.72978</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/02 23:11:22</t>
+          <t>2026/07/03 09:06:28</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-34.205464, -70.677346</t>
+          <t>-33.3599466, -70.8069483</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-34.20546, -70.67735</t>
+          <t>-33.35995, -70.80695</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>53:41:48</t>
+          <t>13:58:15</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.03</v>
+        <v>90.03</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7389,57 +7389,57 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/06/30 20:29:25</t>
+          <t>2026/07/02 19:25:25</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.4761, -70.6985283</t>
+          <t>-32.8351466, -70.5981016</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69853</t>
+          <t>-32.83515, -70.59810</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/01 09:24:18</t>
+          <t>2026/07/02 19:35:35</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.4761566, -70.698465</t>
+          <t>-32.829985, -70.5961166</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69846</t>
+          <t>-32.82999, -70.59612</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>12:54:53</t>
+          <t>00:10:10</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="M120" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N120" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,57 +7448,57 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/01 16:17:48</t>
+          <t>2026/07/02 19:35:58</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-33.35124, -70.6716316</t>
+          <t>-32.8296933, -70.59693</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-33.35124, -70.67163</t>
+          <t>-32.82969, -70.59693</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/01 16:33:09</t>
+          <t>2026/07/02 19:52:58</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-33.3623016, -70.6701366</t>
+          <t>-32.8438816, -70.5976683</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-33.36230, -70.67014</t>
+          <t>-32.84388, -70.59767</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:15:21</t>
+          <t>00:17:00</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.91</v>
+        <v>2.38</v>
       </c>
       <c r="M121" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="N121" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,57 +7507,57 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/07/01 16:34:16</t>
+          <t>2026/07/02 19:54:13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-33.3621083, -70.6701349</t>
+          <t>-32.84522, -70.5986183</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-33.36211, -70.67013</t>
+          <t>-32.84522, -70.59862</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/01 18:13:15</t>
+          <t>2026/07/02 20:18:57</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-33.3895166, -70.6738466</t>
+          <t>-32.8358783, -70.5712266</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-33.38952, -70.67385</t>
+          <t>-32.83588, -70.57123</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>01:38:59</t>
+          <t>00:24:44</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>4.04</v>
+        <v>3.68</v>
       </c>
       <c r="M122" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N122" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,57 +7566,57 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/01 18:13:40</t>
+          <t>2026/07/02 20:19:46</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-33.389315, -70.6739966</t>
+          <t>-32.8345466, -70.5704883</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67400</t>
+          <t>-32.83455, -70.57049</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/01 18:55:19</t>
+          <t>2026/07/02 21:03:15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-33.3623416, -70.6701316</t>
+          <t>-32.8452433, -70.5986616</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-33.36234, -70.67013</t>
+          <t>-32.84524, -70.59866</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>00:41:39</t>
+          <t>00:43:29</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.57</v>
+        <v>4.85</v>
       </c>
       <c r="M123" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="N123" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,57 +7625,57 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/01 18:56:17</t>
+          <t>2026/07/02 21:04:30</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-33.3621316, -70.67014</t>
+          <t>-32.8452483, -70.5986783</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-33.36213, -70.67014</t>
+          <t>-32.84525, -70.59868</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/01 19:49:48</t>
+          <t>2026/07/02 21:41:37</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-33.4761366, -70.6985283</t>
+          <t>-32.8345933, -70.5706366</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-33.47614, -70.69853</t>
+          <t>-32.83459, -70.57064</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>00:53:31</t>
+          <t>00:37:07</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>18.19</v>
+        <v>3.95</v>
       </c>
       <c r="M124" t="n">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="N124" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,57 +7684,57 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/01 19:13:06</t>
+          <t>2026/07/02 21:42:52</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.466, -70.59085</t>
+          <t>-32.8345683, -70.5706116</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.46600, -70.59085</t>
+          <t>-32.83457, -70.57061</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/01 21:09:14</t>
+          <t>2026/07/02 22:16:43</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.4358966, -70.630045</t>
+          <t>-32.8793333, -70.6089049</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.43590, -70.63004</t>
+          <t>-32.87933, -70.60890</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>01:56:08</t>
+          <t>00:33:51</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>8.27</v>
+        <v>9.69</v>
       </c>
       <c r="M125" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N125" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,106 +7743,106 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/01 19:50:56</t>
+          <t>2026/07/02 22:17:58</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.4761066, -70.6985333</t>
+          <t>-32.879225, -70.6087949</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69853</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/02 08:43:30</t>
+          <t>2026/07/03 12:56:31</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.47627, -70.698345</t>
+          <t>-32.8319416, -70.5967766</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69835</t>
+          <t>-32.83194, -70.59678</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>12:52:34</t>
+          <t>14:38:33</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.03</v>
+        <v>7.74</v>
       </c>
       <c r="M126" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="N126" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/07/01 21:03:17</t>
+          <t>2026/07/03 11:49:26</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-32.879205, -70.60883</t>
+          <t>-33.3672966, -70.6958899</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60883</t>
+          <t>-33.36730, -70.69589</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/02 10:10:43</t>
+          <t>2026/07/03 21:49:36</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-33.3363116, -70.7193983</t>
+          <t>-33.3672966, -70.6958899</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-33.33631, -70.71940</t>
+          <t>-33.36730, -70.69589</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>13:07:26</t>
+          <t>10:00:10</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>65.22</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7861,57 +7861,57 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/07/01 21:10:29</t>
+          <t>2026/07/03 14:17:56</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-33.4364533, -70.6295916</t>
+          <t>-33.3595616, -70.8090049</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-33.43645, -70.62959</t>
+          <t>-33.35956, -70.80900</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/02 12:50:54</t>
+          <t>2026/07/03 14:28:37</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-33.3673183, -70.6960249</t>
+          <t>-33.3601516, -70.807085</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-33.36732, -70.69602</t>
+          <t>-33.36015, -70.80709</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>15:40:25</t>
+          <t>00:10:41</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>13.73</v>
+        <v>0.29</v>
       </c>
       <c r="M128" t="n">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="N128" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,57 +7920,57 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/07/02 15:08:46</t>
+          <t>2026/07/03 14:29:52</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-34.20555, -70.6775616</t>
+          <t>-33.3600166, -70.8069183</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67756</t>
+          <t>-33.36002, -70.80692</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/02 18:26:46</t>
+          <t>2026/07/03 15:13:44</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.8874383</t>
+          <t>-33.3665599, -70.6955966</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88744</t>
+          <t>-33.36656, -70.69560</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>03:18:00</t>
+          <t>00:43:52</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>196.44</v>
+        <v>13.92</v>
       </c>
       <c r="M129" t="n">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="N129" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,112 +7979,112 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/07/02 15:38:12</t>
+          <t>2026/07/03 15:00:11</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-33.359985, -70.807068</t>
+          <t>-32.840477, -70.964531</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80707</t>
+          <t>-32.84048, -70.96453</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/07/02 23:53:17</t>
+          <t>2026/07/03 15:16:03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-33.360125, -70.807178</t>
+          <t>-32.840579, -70.964609</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80718</t>
+          <t>-32.84058, -70.96461</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>08:15:05</t>
+          <t>00:15:52</t>
         </is>
       </c>
       <c r="L130" t="n">
         <v>0.02</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/07/02 18:01:53</t>
+          <t>2026/07/03 15:14:18</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-33.482164, -70.764922</t>
+          <t>-33.3665483, -70.695875</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-33.48216, -70.76492</t>
+          <t>-33.36655, -70.69588</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/02 23:04:58</t>
+          <t>2026/07/03 16:17:44</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-33.482164, -70.764922</t>
+          <t>-33.4159316, -70.6119666</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-33.48216, -70.76492</t>
+          <t>-33.41593, -70.61197</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>05:03:05</t>
+          <t>01:03:26</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -8092,62 +8092,62 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/07/02 18:27:40</t>
+          <t>2026/07/03 16:18:59</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-32.7975916, -70.88712</t>
+          <t>-33.41755, -70.61364</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88712</t>
+          <t>-33.41755, -70.61364</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/02 22:28:40</t>
+          <t>2026/07/03 16:31:06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-32.7975916, -70.88712</t>
+          <t>-33.4362766, -70.6296133</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88712</t>
+          <t>-33.43628, -70.62961</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>04:01:00</t>
+          <t>00:12:07</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,41 +8156,41 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/07/02 18:42:01</t>
+          <t>2026/07/03 16:32:01</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-33.0872783, -71.3623383</t>
+          <t>-33.437295, -70.6293983</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36234</t>
+          <t>-33.43729, -70.62940</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/02 22:36:13</t>
+          <t>2026/07/03 22:32:01</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-33.0872383, -71.362265</t>
+          <t>-33.437295, -70.6293983</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-33.08724, -71.36226</t>
+          <t>-33.43729, -70.62940</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>03:54:12</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -8202,11 +8202,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8215,37 +8215,37 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/07/02 19:08:13</t>
+          <t>2026/07/03 17:55:58</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-32.7430483, -70.7297816</t>
+          <t>-32.8791833, -70.6087016</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-32.74305, -70.72978</t>
+          <t>-32.87918, -70.60870</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/02 23:08:56</t>
+          <t>2026/07/03 21:38:36</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-32.7430483, -70.7297816</t>
+          <t>-32.8791883, -70.608695</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-32.74305, -70.72978</t>
+          <t>-32.87919, -70.60869</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>04:00:43</t>
+          <t>03:42:38</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -8261,129 +8261,129 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/07/02 19:25:25</t>
+          <t>2026/07/03 18:20:17</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-32.8351466, -70.5981016</t>
+          <t>-32.7976183, -70.887105</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-32.83515, -70.59810</t>
+          <t>-32.79762, -70.88711</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/07/02 19:35:35</t>
+          <t>2026/07/03 22:20:17</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-32.829985, -70.5961166</t>
+          <t>-32.7976183, -70.887105</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-32.82999, -70.59612</t>
+          <t>-32.79762, -70.88711</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>00:10:10</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/07/02 19:35:58</t>
+          <t>2026/07/03 19:45:56</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-32.8296933, -70.59693</t>
+          <t>-32.7431983, -70.7296233</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-32.82969, -70.59693</t>
+          <t>-32.74320, -70.72962</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/07/02 19:52:58</t>
+          <t>2026/07/03 21:46:58</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-32.8438816, -70.5976683</t>
+          <t>-32.7430383, -70.7297633</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-32.84388, -70.59767</t>
+          <t>-32.74304, -70.72976</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>00:17:00</t>
+          <t>02:01:02</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.38</v>
+        <v>0.02</v>
       </c>
       <c r="M136" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8392,37 +8392,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026/07/02 19:50:47</t>
+          <t>2026/07/03 22:00:28</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-32.838375, -70.955489</t>
+          <t>-32.841732, -70.936767</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95549</t>
+          <t>-32.84173, -70.93677</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/02 23:48:17</t>
+          <t>2026/07/03 22:06:43</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-32.838375, -70.955489</t>
+          <t>-32.841732, -70.936767</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95549</t>
+          <t>-32.84173, -70.93677</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>03:57:30</t>
+          <t>00:06:15</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8432,360 +8432,6 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>17</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026/07/02 19:54:13</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-32.84522, -70.5986183</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-32.84522, -70.59862</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2026/07/02 20:18:57</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-32.8358783, -70.5712266</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-32.83588, -70.57123</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>00:24:44</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="M138" t="n">
-        <v>46</v>
-      </c>
-      <c r="N138" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>18</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026/07/02 20:19:46</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-32.8345466, -70.5704883</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-32.83455, -70.57049</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>2026/07/02 21:03:15</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-32.8452433, -70.5986616</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-32.84524, -70.59866</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>00:43:29</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="M139" t="n">
-        <v>55</v>
-      </c>
-      <c r="N139" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>6</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026/07/02 20:34:49</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.6288783</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.62888</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2026/07/02 22:35:17</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.6288783</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.62888</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>02:00:28</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>19</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026/07/02 21:04:30</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-32.8452483, -70.5986783</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-32.84525, -70.59868</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>2026/07/02 21:41:37</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-32.8345933, -70.5706366</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-32.83459, -70.57064</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>00:37:07</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="M141" t="n">
-        <v>43</v>
-      </c>
-      <c r="N141" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>20</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026/07/02 21:42:52</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-32.8345683, -70.5706116</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-32.83457, -70.57061</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2026/07/02 22:21:27</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-32.879225, -70.6087949</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>-32.87922, -70.60879</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>00:38:35</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="M142" t="n">
-        <v>57</v>
-      </c>
-      <c r="N142" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>9</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026/07/02 21:57:31</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-33.4760816, -70.6985116</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-33.47608, -70.69851</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2026/07/02 23:57:43</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-33.4760816, -70.6985116</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-33.47608, -70.69851</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>02:00:12</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8837,10 +8483,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1305.26</v>
+        <v>1434.99</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8856,10 +8502,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>742.59</v>
+        <v>662.99</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -8875,13 +8521,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>437.2</v>
+        <v>298.51</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>129</v>
@@ -8894,10 +8540,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>835.9299999999999</v>
+        <v>831.21</v>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -8913,10 +8559,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.56</v>
+        <v>0.93</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -8932,13 +8578,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -9027,16 +8673,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -9065,16 +8711,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1025.91</v>
+        <v>940.05</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
@@ -9084,10 +8730,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>952.23</v>
+        <v>872.85</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -9103,16 +8749,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>36.77</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17">
@@ -9141,16 +8787,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.45</v>
+        <v>0.62</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -9160,16 +8806,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1117.81</v>
+        <v>592.33</v>
       </c>
       <c r="C19" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
@@ -9179,10 +8825,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>774.67</v>
+        <v>859.55</v>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/03 22:01:26</t>
+          <t>2026/07/03 23:01:37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>165:59:47</t>
+          <t>166:59:58</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/03 22:13:14</t>
+          <t>2026/07/03 23:13:24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>166:00:04</t>
+          <t>167:00:14</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/03 21:56:12</t>
+          <t>2026/07/03 23:56:12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:02:37</t>
+          <t>167:02:37</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/03 21:57:29</t>
+          <t>2026/07/03 23:57:27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>164:59:52</t>
+          <t>166:59:50</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/07/03 22:11:17</t>
+          <t>2026/07/03 23:11:36</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>76:41:43</t>
+          <t>77:42:02</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/03 21:49:36</t>
+          <t>2026/07/03 23:49:36</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>10:00:10</t>
+          <t>12:00:10</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/03 21:38:36</t>
+          <t>2026/07/03 23:38:36</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>03:42:38</t>
+          <t>05:42:38</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/07/03 21:46:58</t>
+          <t>2026/07/03 23:46:58</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>02:01:02</t>
+          <t>04:01:02</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/03 22:06:43</t>
+          <t>2026/07/03 23:06:40</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>00:06:15</t>
+          <t>01:06:12</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>662.99</v>
+        <v>663.73</v>
       </c>
       <c r="C3" t="n">
         <v>51</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/06/27 04:00:00   Hasta : 2026/07/04 03:59:59</t>
+          <t>Desde : 2026/06/28 04:00:00   Hasta : 2026/07/05 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,58 +540,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/06/27 00:00:49</t>
+          <t>2026/06/28 00:01:16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.788962, -70.95912</t>
+          <t>-34.345961, -71.125867</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-32.78896, -70.95912</t>
+          <t>-34.34596, -71.12587</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/06/27 00:16:02</t>
+          <t>2026/07/04 22:01:37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-32.838378, -70.956093</t>
+          <t>-34.346035, -71.125894</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95609</t>
+          <t>-34.34604, -71.12589</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>00:15:13</t>
+          <t>166:00:21</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11.65</v>
+        <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,58 +599,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/06/27 00:01:39</t>
+          <t>2026/06/28 00:01:41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.345961, -71.125867</t>
+          <t>-32.7430083, -70.7298233</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12587</t>
+          <t>-32.74301, -70.72982</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/03 23:01:37</t>
+          <t>2026/06/28 14:14:55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.345999, -71.125878</t>
+          <t>-32.74311, -70.7297249</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12588</t>
+          <t>-32.74311, -70.72972</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>166:59:58</t>
+          <t>14:13:14</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.02</v>
+        <v>0.98</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,47 +663,47 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/06/27 00:01:41</t>
+          <t>2026/06/28 00:05:34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-32.7430083, -70.7298233</t>
+          <t>-32.8790583, -70.6093816</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-32.74301, -70.72982</t>
+          <t>-32.87906, -70.60938</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/06/28 14:14:55</t>
+          <t>2026/06/28 11:00:25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-32.74311, -70.7297249</t>
+          <t>-32.8663783, -70.6238599</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.74311, -70.72972</t>
+          <t>-32.86638, -70.62386</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>38:13:14</t>
+          <t>10:54:51</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.98</v>
+        <v>3.87</v>
       </c>
       <c r="M6" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/06/27 00:08:09</t>
+          <t>2026/06/28 00:08:09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>155:40:02</t>
+          <t>131:40:02</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -776,58 +776,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/06/27 00:10:12</t>
+          <t>2026/06/28 00:13:16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.399197, -70.795128</t>
+          <t>-33.360039, -70.807034</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.39920, -70.79513</t>
+          <t>-33.36004, -70.80703</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/06/27 01:05:18</t>
+          <t>2026/07/04 22:13:16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-32.841699, -70.936905</t>
+          <t>-33.360042, -70.80706</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.84170, -70.93690</t>
+          <t>-33.36004, -70.80706</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>00:55:06</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>90.76000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/06/27 00:13:10</t>
+          <t>2026/06/28 00:13:50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.360005, -70.807064</t>
+          <t>-33.360057, -70.807151</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80706</t>
+          <t>-33.36006, -70.80715</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/03 23:13:24</t>
+          <t>2026/06/30 11:39:26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.360042, -70.80706</t>
+          <t>-33.360734, -70.809006</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80706</t>
+          <t>-33.36073, -70.80901</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>167:00:14</t>
+          <t>59:25:36</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,62 +894,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/06/27 00:14:16</t>
+          <t>2026/06/28 00:31:47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.360057, -70.807151</t>
+          <t>-33.899863, -71.429125</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.36006, -70.80715</t>
+          <t>-33.89986, -71.42912</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/06/30 11:39:26</t>
+          <t>2026/07/01 08:15:25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.360734, -70.809006</t>
+          <t>-33.899941, -71.429577</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.36073, -70.80901</t>
+          <t>-33.89994, -71.42958</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>83:25:10</t>
+          <t>79:43:38</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -958,53 +958,53 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/06/27 00:16:50</t>
+          <t>2026/06/28 00:31:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-32.838367, -70.955489</t>
+          <t>-34.205399, -70.67729</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95549</t>
+          <t>-34.20540, -70.67729</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/06/27 13:49:01</t>
+          <t>2026/06/30 16:59:54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-32.840002, -70.961183</t>
+          <t>-34.205234, -70.680382</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.84000, -70.96118</t>
+          <t>-34.20523, -70.68038</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13:32:11</t>
+          <t>64:28:01</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.87</v>
+        <v>0.46</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,41 +1017,41 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/06/27 00:31:21</t>
+          <t>2026/06/28 00:34:42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-33.899792, -71.429506</t>
+          <t>-34.579844, -70.961378</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-33.89979, -71.42951</t>
+          <t>-34.57984, -70.96138</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/01 08:15:25</t>
+          <t>2026/06/29 01:37:19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.899941, -71.429577</t>
+          <t>-34.579894, -70.961485</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.89994, -71.42958</t>
+          <t>-34.57989, -70.96148</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>103:44:04</t>
+          <t>25:02:37</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
@@ -1063,7 +1063,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,58 +1071,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/06/27 00:31:56</t>
+          <t>2026/06/28 00:38:35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.205399, -70.67729</t>
+          <t>-33.367472, -70.696453</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67729</t>
+          <t>-33.36747, -70.69645</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/06/30 16:59:54</t>
+          <t>2026/06/28 01:41:03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.205234, -70.680382</t>
+          <t>-33.368129, -70.696085</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.20523, -70.68038</t>
+          <t>-33.36813, -70.69608</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>88:27:58</t>
+          <t>01:02:28</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/06/27 00:34:56</t>
+          <t>2026/06/28 00:45:56</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-34.579852, -70.96131</t>
+          <t>-34.876438, -71.127209</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96131</t>
+          <t>-34.87644, -71.12721</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/06/27 01:37:22</t>
+          <t>2026/06/29 01:25:19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-34.579844, -70.961378</t>
+          <t>-34.876375, -71.127119</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-34.57984, -70.96138</t>
+          <t>-34.87638, -71.12712</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>01:02:26</t>
+          <t>24:39:23</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>0.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/06/27 00:38:42</t>
+          <t>2026/06/28 00:46:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.367472, -70.696453</t>
+          <t>-32.780847, -70.98129</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36747, -70.69645</t>
+          <t>-32.78085, -70.98129</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/06/28 01:41:03</t>
+          <t>2026/06/28 01:41:15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.368129, -70.696085</t>
+          <t>-32.785697, -70.960385</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36813, -70.69608</t>
+          <t>-32.78570, -70.96039</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25:02:21</t>
+          <t>00:55:15</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/06/27 00:45:53</t>
+          <t>2026/06/28 00:48:54</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-37.79751, -73.4010766</t>
+          <t>-32.841804, -70.936878</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-37.79751, -73.40108</t>
+          <t>-32.84180, -70.93688</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/27 17:20:46</t>
+          <t>2026/06/28 10:55:29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-37.2067683, -73.210845</t>
+          <t>-32.83853, -70.953887</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-37.20677, -73.21085</t>
+          <t>-32.83853, -70.95389</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>16:34:53</t>
+          <t>10:06:35</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>75.95999999999999</v>
+        <v>2.29</v>
       </c>
       <c r="M16" t="n">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,52 +1307,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/06/27 00:48:55</t>
+          <t>2026/06/28 00:51:36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.876382, -71.127239</t>
+          <t>-36.9038983, -73.0297049</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.87638, -71.12724</t>
+          <t>-36.90390, -73.02970</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/06/29 01:25:19</t>
+          <t>2026/06/28 13:39:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-34.876375, -71.127119</t>
+          <t>-36.8459166, -73.0518549</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.87638, -71.12712</t>
+          <t>-36.84592, -73.05185</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>48:36:24</t>
+          <t>12:47:24</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.02</v>
+        <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/06/27 00:53:35</t>
+          <t>2026/06/28 00:53:35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/03 23:56:12</t>
+          <t>2026/07/04 22:56:09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>167:02:37</t>
+          <t>166:02:34</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/06/27 00:57:37</t>
+          <t>2026/06/28 00:58:08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-34.042641, -70.681766</t>
+          <t>-34.042665, -70.681745</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-34.04264, -70.68177</t>
+          <t>-34.04266, -70.68175</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/03 23:57:27</t>
+          <t>2026/07/04 21:57:38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,11 +1460,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>166:59:50</t>
+          <t>164:59:30</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1476,11 +1476,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/06/27 01:05:21</t>
+          <t>2026/06/28 01:06:59</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-32.841678, -70.936878</t>
+          <t>-33.0871366, -71.3621566</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-32.84168, -70.93688</t>
+          <t>-33.08714, -71.36216</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/06/27 10:25:30</t>
+          <t>2026/06/30 09:33:52</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-32.848304, -70.924562</t>
+          <t>-33.04526, -71.41807</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.84830, -70.92456</t>
+          <t>-33.04526, -71.41807</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>09:20:09</t>
+          <t>56:26:53</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.48</v>
+        <v>11.24</v>
       </c>
       <c r="M20" t="n">
+        <v>118</v>
+      </c>
+      <c r="N20" t="n">
         <v>32</v>
-      </c>
-      <c r="N20" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,44 +1548,44 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/06/27 01:13:33</t>
+          <t>2026/06/28 01:37:36</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-33.4761283, -70.6985433</t>
+          <t>-32.7975933, -70.8870683</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-33.47613, -70.69854</t>
+          <t>-32.79759, -70.88707</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/27 10:06:28</t>
+          <t>2026/06/28 10:02:13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67015</t>
+          <t>-32.835125, -70.6046299</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67015</t>
+          <t>-32.83512, -70.60463</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08:52:55</t>
+          <t>08:24:37</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>18.77</v>
+        <v>32.97</v>
       </c>
       <c r="M21" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="N21" t="n">
         <v>44</v>
@@ -1594,11 +1594,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1607,53 +1607,53 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/06/27 01:18:29</t>
+          <t>2026/06/28 01:41:45</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-33.0872383, -71.36227</t>
+          <t>-32.785359, -70.960425</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-33.08724, -71.36227</t>
+          <t>-32.78536, -70.96043</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/06/27 10:05:33</t>
+          <t>2026/06/28 13:45:07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.0873016, -71.3623633</t>
+          <t>-32.791566, -70.912456</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36236</t>
+          <t>-32.79157, -70.91246</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>08:47:04</t>
+          <t>12:03:22</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>7.63</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1666,57 +1666,57 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/06/27 01:34:24</t>
+          <t>2026/06/28 01:54:08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.8870716</t>
+          <t>-33.4761199, -70.6985283</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88707</t>
+          <t>-33.47612, -70.69853</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/06/27 09:33:41</t>
+          <t>2026/06/28 08:07:43</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-32.6229216, -70.7180833</t>
+          <t>-33.4761916, -70.6984216</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-32.62292, -70.71808</t>
+          <t>-33.47619, -70.69842</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>07:59:17</t>
+          <t>06:13:35</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>41.67</v>
+        <v>0.02</v>
       </c>
       <c r="M23" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/06/27 01:51:17</t>
+          <t>2026/06/28 02:40:11</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.608785</t>
+          <t>-33.368129, -70.696085</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60878</t>
+          <t>-33.36813, -70.69608</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/06/27 09:57:19</t>
+          <t>2026/06/30 01:41:05</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-32.8520266, -70.6067616</t>
+          <t>-33.367112, -70.696652</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-32.85203, -70.60676</t>
+          <t>-33.36711, -70.69665</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08:06:02</t>
+          <t>47:00:54</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.18</v>
+        <v>0.12</v>
       </c>
       <c r="M24" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1779,62 +1779,62 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/06/27 02:34:38</t>
+          <t>2026/06/28 08:08:58</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-34.579844, -70.961378</t>
+          <t>-33.4763233, -70.69837</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-34.57984, -70.96138</t>
+          <t>-33.47632, -70.69837</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/06/29 01:37:19</t>
+          <t>2026/06/28 08:36:46</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.579894, -70.961485</t>
+          <t>-33.3997016, -70.7920883</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.57989, -70.96148</t>
+          <t>-33.39970, -70.79209</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>47:02:41</t>
+          <t>00:27:48</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.08</v>
+        <v>18.69</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/06/27 09:34:56</t>
+          <t>2026/06/28 08:38:01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-32.6253016, -70.7184416</t>
+          <t>-33.39722, -70.7921483</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-32.62530, -70.71844</t>
+          <t>-33.39722, -70.79215</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/06/27 10:10:25</t>
+          <t>2026/06/28 09:29:41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-32.5634483, -70.694755</t>
+          <t>-33.3895033, -70.6738583</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-32.56345, -70.69476</t>
+          <t>-33.38950, -70.67386</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>00:35:29</t>
+          <t>00:51:40</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>21.18</v>
       </c>
       <c r="M26" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N26" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,53 +1902,53 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/06/27 09:57:44</t>
+          <t>2026/06/28 09:30:24</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-32.8521949, -70.6077133</t>
+          <t>-33.3892816, -70.67405</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.85219, -70.60771</t>
+          <t>-33.38928, -70.67405</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/06/27 10:07:41</t>
+          <t>2026/06/28 10:33:10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-32.8547316, -70.6037666</t>
+          <t>-33.4762366, -70.6982866</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-32.85473, -70.60377</t>
+          <t>-33.47624, -70.69829</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:09:57</t>
+          <t>01:02:46</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.65</v>
+        <v>13.55</v>
       </c>
       <c r="M27" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="N27" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1961,47 +1961,47 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/06/27 10:06:18</t>
+          <t>2026/06/28 10:02:48</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.0871949, -71.36224</t>
+          <t>-32.8352783, -70.6044299</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.08719, -71.36224</t>
+          <t>-32.83528, -70.60443</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/06/30 09:33:52</t>
+          <t>2026/06/28 13:16:25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.04526, -71.41807</t>
+          <t>-32.8830583, -70.6125433</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.04526, -71.41807</t>
+          <t>-32.88306, -70.61254</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>71:27:34</t>
+          <t>03:13:37</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>11.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="N28" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,57 +2020,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/06/27 10:07:00</t>
+          <t>2026/06/28 10:34:25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-33.362065, -70.6701616</t>
+          <t>-33.4760666, -70.6985233</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-33.36207, -70.67016</t>
+          <t>-33.47607, -70.69852</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/06/27 10:21:12</t>
+          <t>2026/06/29 20:00:07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-33.3533383, -70.6704066</t>
+          <t>-33.3895183, -70.6738483</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-33.35334, -70.67041</t>
+          <t>-33.38952, -70.67385</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:14:12</t>
+          <t>33:25:42</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.08</v>
+        <v>15.4</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,57 +2079,57 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/06/27 10:08:56</t>
+          <t>2026/06/28 10:55:47</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-32.852205, -70.6077133</t>
+          <t>-32.838731, -70.954033</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-32.85220, -70.60771</t>
+          <t>-32.83873, -70.95403</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/06/27 11:17:39</t>
+          <t>2026/06/28 11:52:17</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-32.8364866, -70.5945683</t>
+          <t>-32.84283, -70.936869</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.83649, -70.59457</t>
+          <t>-32.84283, -70.93687</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>01:08:43</t>
+          <t>00:56:30</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="N30" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,53 +2138,53 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/06/27 10:11:40</t>
+          <t>2026/06/28 11:01:40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-32.5634049, -70.695095</t>
+          <t>-32.8661383, -70.6240233</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-32.56340, -70.69509</t>
+          <t>-32.86614, -70.62402</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/06/27 17:37:13</t>
+          <t>2026/06/28 11:22:45</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-32.797685, -70.8873916</t>
+          <t>-32.8723833, -70.6029383</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.79769, -70.88739</t>
+          <t>-32.87238, -70.60294</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>07:25:33</t>
+          <t>00:21:05</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>40.7</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="N31" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/06/27 10:21:54</t>
+          <t>2026/06/28 11:24:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.3533966, -70.669735</t>
+          <t>-32.8754433, -70.6031666</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.35340, -70.66974</t>
+          <t>-32.87544, -70.60317</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/06/27 10:43:51</t>
+          <t>2026/06/28 11:35:53</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.3623266, -70.670125</t>
+          <t>-32.87919, -70.6089266</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.36233, -70.67012</t>
+          <t>-32.87919, -70.60893</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:21:57</t>
+          <t>00:11:53</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.17</v>
+        <v>1.04</v>
       </c>
       <c r="M32" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="N32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/06/27 10:26:12</t>
+          <t>2026/06/28 11:36:36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.848095, -70.925136</t>
+          <t>-32.8790466, -70.6093933</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.84810, -70.92514</t>
+          <t>-32.87905, -70.60939</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/06/27 11:10:27</t>
+          <t>2026/06/28 19:03:31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-32.83858, -70.953996</t>
+          <t>-32.8791316, -70.6092916</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.83858, -70.95400</t>
+          <t>-32.87913, -70.60929</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:44:15</t>
+          <t>07:26:55</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.85</v>
+        <v>0.01</v>
       </c>
       <c r="M33" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/06/27 10:44:15</t>
+          <t>2026/06/28 11:53:17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-33.362145, -70.6701483</t>
+          <t>-32.841833, -70.936834</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-33.36214, -70.67015</t>
+          <t>-32.84183, -70.93683</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/06/27 13:04:17</t>
+          <t>2026/06/28 16:43:56</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-33.4516283, -70.633405</t>
+          <t>-32.839208, -70.949417</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-33.45163, -70.63340</t>
+          <t>-32.83921, -70.94942</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>02:20:02</t>
+          <t>04:50:39</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>17.95</v>
+        <v>1.81</v>
       </c>
       <c r="M34" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="N34" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,57 +2374,57 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/06/27 11:10:48</t>
+          <t>2026/06/28 13:17:40</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.8388, -70.954135</t>
+          <t>-32.8829683, -70.612425</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.83880, -70.95413</t>
+          <t>-32.88297, -70.61243</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/06/27 11:55:33</t>
+          <t>2026/06/28 14:17:30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.840116, -70.950532</t>
+          <t>-32.7976399, -70.8871449</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.84012, -70.95053</t>
+          <t>-32.79764, -70.88714</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:44:45</t>
+          <t>00:59:50</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.67</v>
+        <v>41.43</v>
       </c>
       <c r="M35" t="n">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="N35" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/06/27 11:17:49</t>
+          <t>2026/06/28 13:40:15</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.836485, -70.5946266</t>
+          <t>-36.8464016, -73.0517766</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-32.83649, -70.59463</t>
+          <t>-36.84640, -73.05178</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/06/27 11:35:11</t>
+          <t>2026/06/28 14:28:59</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-32.8289833, -70.59968</t>
+          <t>-36.9039616, -73.0282216</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-32.82898, -70.59968</t>
+          <t>-36.90396, -73.02822</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:17:22</t>
+          <t>00:48:44</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.09</v>
+        <v>6.94</v>
       </c>
       <c r="M36" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="N36" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/06/27 11:36:26</t>
+          <t>2026/06/28 13:45:10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-32.8303366, -70.600205</t>
+          <t>-32.791579, -70.912464</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-32.83034, -70.60021</t>
+          <t>-32.79158, -70.91246</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/06/27 12:21:45</t>
+          <t>2026/06/28 19:01:05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-32.8525433, -70.6055483</t>
+          <t>-32.785691, -70.96037</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-32.85254, -70.60555</t>
+          <t>-32.78569, -70.96037</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:45:19</t>
+          <t>05:15:55</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.13</v>
+        <v>7.61</v>
       </c>
       <c r="M37" t="n">
+        <v>53</v>
+      </c>
+      <c r="N37" t="n">
         <v>30</v>
-      </c>
-      <c r="N37" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/06/27 11:55:54</t>
+          <t>2026/06/28 14:15:11</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-32.840112, -70.950526</t>
+          <t>-32.74303, -70.7297999</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-32.84011, -70.95053</t>
+          <t>-32.74303, -70.72980</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/06/27 12:22:51</t>
+          <t>2026/07/01 07:51:22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-32.84386, -70.936934</t>
+          <t>-33.35998, -70.806935</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-32.84386, -70.93693</t>
+          <t>-33.35998, -70.80693</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:26:57</t>
+          <t>65:36:11</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.77</v>
+        <v>89.81</v>
       </c>
       <c r="M38" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/06/27 12:23:00</t>
+          <t>2026/06/28 14:17:48</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-32.8521766, -70.607525</t>
+          <t>-32.7976283, -70.8870716</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-32.85218, -70.60752</t>
+          <t>-32.79763, -70.88707</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/06/27 12:47:12</t>
+          <t>2026/06/29 08:14:08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-32.85219, -70.6075033</t>
+          <t>-32.7976533, -70.8874083</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-32.85219, -70.60750</t>
+          <t>-32.79765, -70.88741</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:24:12</t>
+          <t>17:56:20</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.65</v>
+        <v>19.86</v>
       </c>
       <c r="M39" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/06/27 12:23:45</t>
+          <t>2026/06/28 14:29:35</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-32.841922, -70.936833</t>
+          <t>-36.9039266, -73.0296516</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-32.84192, -70.93683</t>
+          <t>-36.90393, -73.02965</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/06/27 14:43:51</t>
+          <t>2026/06/28 21:51:07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-32.840239, -70.960661</t>
+          <t>-33.4362766, -70.6294433</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-32.84024, -70.96066</t>
+          <t>-33.43628, -70.62944</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>02:20:06</t>
+          <t>07:21:32</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.64</v>
+        <v>510.12</v>
       </c>
       <c r="M40" t="n">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="N40" t="n">
-        <v>18</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,53 +2728,53 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/06/27 12:48:27</t>
+          <t>2026/06/28 16:44:54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-32.8521866, -70.6075366</t>
+          <t>-32.839819, -70.949986</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-32.85219, -70.60754</t>
+          <t>-32.83982, -70.94999</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/06/27 13:23:52</t>
+          <t>2026/06/28 16:59:47</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-32.844175, -70.599195</t>
+          <t>-32.847954, -70.925078</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-32.84417, -70.59919</t>
+          <t>-32.84795, -70.92508</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:35:25</t>
+          <t>00:14:53</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>11.1</v>
+        <v>3.51</v>
       </c>
       <c r="M41" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="N41" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/06/27 13:05:32</t>
+          <t>2026/06/28 17:00:08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-33.45008, -70.63392</t>
+          <t>-32.84784, -70.925064</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-33.45008, -70.63392</t>
+          <t>-32.84784, -70.92506</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/06/27 13:53:25</t>
+          <t>2026/06/28 20:34:14</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-33.4472583, -70.6322033</t>
+          <t>-32.841937, -70.936854</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-33.44726, -70.63220</t>
+          <t>-32.84194, -70.93685</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:47:53</t>
+          <t>03:34:06</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.46</v>
+        <v>3.63</v>
       </c>
       <c r="M42" t="n">
+        <v>38</v>
+      </c>
+      <c r="N42" t="n">
         <v>17</v>
-      </c>
-      <c r="N42" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,47 +2846,47 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/06/27 13:25:07</t>
+          <t>2026/06/28 19:02:01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-32.8442583, -70.5993883</t>
+          <t>-32.78549, -70.960404</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-32.84426, -70.59939</t>
+          <t>-32.78549, -70.96040</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/06/27 13:45:50</t>
+          <t>2026/06/28 21:27:15</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.608955</t>
+          <t>-32.838362, -70.955502</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60895</t>
+          <t>-32.83836, -70.95550</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:20:43</t>
+          <t>02:25:14</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.88</v>
+        <v>12.17</v>
       </c>
       <c r="M43" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="N43" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/06/27 13:46:19</t>
+          <t>2026/06/28 19:04:46</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-32.8790566, -70.6093983</t>
+          <t>-32.879205, -70.6088333</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-32.87906, -70.60940</t>
+          <t>-32.87920, -70.60883</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/06/27 14:51:03</t>
+          <t>2026/06/30 09:21:51</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-32.8791966, -70.608935</t>
+          <t>-32.8554583, -70.6255983</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60894</t>
+          <t>-32.85546, -70.62560</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01:04:44</t>
+          <t>38:17:05</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6.2</v>
+        <v>5.26</v>
       </c>
       <c r="M44" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/06/27 13:49:26</t>
+          <t>2026/06/28 20:35:14</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-32.840002, -70.961183</t>
+          <t>-32.841795, -70.93679</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-32.84000, -70.96118</t>
+          <t>-32.84179, -70.93679</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/06/27 14:06:55</t>
+          <t>2026/06/28 20:56:02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-32.840463, -70.95988</t>
+          <t>-32.838505, -70.953947</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-32.84046, -70.95988</t>
+          <t>-32.83850, -70.95395</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:17:29</t>
+          <t>00:20:48</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.14</v>
+        <v>2.27</v>
       </c>
       <c r="M45" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,47 +3023,47 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/06/27 13:54:40</t>
+          <t>2026/06/28 20:56:14</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-33.4451933, -70.632835</t>
+          <t>-32.83871, -70.954071</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-33.44519, -70.63284</t>
+          <t>-32.83871, -70.95407</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/06/27 14:32:42</t>
+          <t>2026/06/28 21:51:35</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-33.3895216, -70.6738533</t>
+          <t>-32.84175, -70.936885</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-33.38952, -70.67385</t>
+          <t>-32.84175, -70.93689</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:38:02</t>
+          <t>00:55:21</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>12.37</v>
+        <v>2.26</v>
       </c>
       <c r="M46" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="N46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/06/27 14:07:50</t>
+          <t>2026/06/28 21:27:50</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-32.840464, -70.959878</t>
+          <t>-32.838362, -70.955502</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-32.84046, -70.95988</t>
+          <t>-32.83836, -70.95550</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/06/27 14:41:54</t>
+          <t>2026/06/29 11:42:44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-32.838385, -70.955506</t>
+          <t>-32.841711, -70.954081</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-32.83839, -70.95551</t>
+          <t>-32.84171, -70.95408</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:34:04</t>
+          <t>14:14:54</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M47" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,57 +3141,57 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/06/27 14:33:13</t>
+          <t>2026/06/28 21:51:21</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.3893333, -70.6740066</t>
+          <t>-33.4362983, -70.6294</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.38933, -70.67401</t>
+          <t>-33.43630, -70.62940</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/06/27 15:12:42</t>
+          <t>2026/06/29 10:10:14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.36706, -70.6796766</t>
+          <t>-33.3665466, -70.6957333</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.36706, -70.67968</t>
+          <t>-33.36655, -70.69573</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:39:29</t>
+          <t>12:18:53</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.45</v>
+        <v>13.34</v>
       </c>
       <c r="M48" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="N48" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/06/27 14:42:15</t>
+          <t>2026/06/28 21:51:51</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.838384, -70.955512</t>
+          <t>-32.841725, -70.93688</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95551</t>
+          <t>-32.84172, -70.93688</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/06/27 15:25:06</t>
+          <t>2026/06/29 11:05:29</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.791624, -70.912643</t>
+          <t>-32.841556, -70.959284</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.79162, -70.91264</t>
+          <t>-32.84156, -70.95928</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:42:51</t>
+          <t>13:13:38</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>18.52</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="N49" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/06/27 14:44:51</t>
+          <t>2026/06/29 14:00:24</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-32.840319, -70.960333</t>
+          <t>-32.7975833, -70.8870766</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-32.84032, -70.96033</t>
+          <t>-32.79758, -70.88708</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/06/27 15:14:57</t>
+          <t>2026/06/30 09:05:06</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-32.841743, -70.936878</t>
+          <t>-33.3672816, -70.696575</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-32.84174, -70.93688</t>
+          <t>-33.36728, -70.69657</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:30:06</t>
+          <t>19:04:42</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.75</v>
+        <v>100.14</v>
       </c>
       <c r="M50" t="n">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="N50" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/06/27 14:51:31</t>
+          <t>2026/06/29 16:40:09</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-32.8790633, -70.6093749</t>
+          <t>-32.790901, -70.975998</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-32.87906, -70.60937</t>
+          <t>-32.79090, -70.97600</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/06/27 18:01:38</t>
+          <t>2026/06/29 20:25:50</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-32.8826616, -70.6107166</t>
+          <t>-32.838377, -70.9561</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-32.88266, -70.61072</t>
+          <t>-32.83838, -70.95610</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>03:10:07</t>
+          <t>03:45:41</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.63</v>
+        <v>12.75</v>
       </c>
       <c r="M51" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="N51" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,47 +3377,47 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/06/27 15:13:57</t>
+          <t>2026/06/29 20:26:42</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.3651883, -70.679935</t>
+          <t>-32.838376, -70.955488</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.36519, -70.67994</t>
+          <t>-32.83838, -70.95549</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/06/27 15:31:46</t>
+          <t>2026/06/30 10:05:36</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.3513016, -70.6718799</t>
+          <t>-32.840312, -70.964487</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.35130, -70.67188</t>
+          <t>-32.84031, -70.96449</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:17:49</t>
+          <t>13:38:54</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.03</v>
+        <v>1.57</v>
       </c>
       <c r="M52" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="N52" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,47 +3436,47 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/06/27 15:15:49</t>
+          <t>2026/06/29 21:44:49</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-32.84174, -70.936879</t>
+          <t>-32.841646, -70.936791</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-32.84174, -70.93688</t>
+          <t>-32.84165, -70.93679</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/06/27 20:40:09</t>
+          <t>2026/06/30 09:23:43</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-32.83962, -70.949828</t>
+          <t>-33.482129, -70.765257</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-32.83962, -70.94983</t>
+          <t>-33.48213, -70.76526</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>05:24:20</t>
+          <t>11:38:54</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.16</v>
+        <v>100.91</v>
       </c>
       <c r="M53" t="n">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
@@ -3486,66 +3486,66 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/06/27 15:25:19</t>
+          <t>2026/06/30 10:05:46</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-32.791656, -70.912644</t>
+          <t>-32.840279, -70.964577</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-32.79166, -70.91264</t>
+          <t>-32.84028, -70.96458</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/06/27 19:23:58</t>
+          <t>2026/06/30 10:56:45</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-32.838375, -70.955515</t>
+          <t>-32.840287, -70.964573</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95552</t>
+          <t>-32.84029, -70.96457</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>03:58:39</t>
+          <t>00:50:59</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>20.26</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/06/27 15:31:58</t>
+          <t>2026/06/30 10:09:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.351275, -70.6716433</t>
+          <t>-33.043545, -71.4165783</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.35128, -70.67164</t>
+          <t>-33.04355, -71.41658</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/06/27 15:44:45</t>
+          <t>2026/06/30 10:28:28</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.3623299, -70.67012</t>
+          <t>-33.0447666, -71.420215</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.36233, -70.67012</t>
+          <t>-33.04477, -71.42021</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:12:47</t>
+          <t>00:19:28</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.93</v>
+        <v>0.84</v>
       </c>
       <c r="M55" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="N55" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,53 +3613,53 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/06/27 15:45:17</t>
+          <t>2026/06/30 10:28:39</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-33.3620616, -70.6701116</t>
+          <t>-33.0448016, -71.4202366</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-33.36206, -70.67011</t>
+          <t>-33.04480, -71.42024</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/06/27 19:52:55</t>
+          <t>2026/06/30 10:58:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-33.476245, -70.6983966</t>
+          <t>-33.0873283, -71.362295</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69840</t>
+          <t>-33.08733, -71.36230</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>04:07:38</t>
+          <t>00:29:21</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>18.19</v>
+        <v>10.54</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="N56" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3667,58 +3667,58 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/06/27 17:21:50</t>
+          <t>2026/06/30 10:57:04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-37.1956749, -73.2035466</t>
+          <t>-32.840354, -70.964574</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-37.19567, -73.20355</t>
+          <t>-32.84035, -70.96457</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/06/27 18:34:15</t>
+          <t>2026/06/30 12:37:02</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-36.9039566, -73.028235</t>
+          <t>-32.840478, -70.964481</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-36.90396, -73.02823</t>
+          <t>-32.84048, -70.96448</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01:12:25</t>
+          <t>01:39:58</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>61.44</v>
+        <v>0.05</v>
       </c>
       <c r="M57" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3731,47 +3731,47 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/06/27 17:37:36</t>
+          <t>2026/06/30 10:59:15</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.7975933, -70.8870683</t>
+          <t>-33.0873166, -71.3623183</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88707</t>
+          <t>-33.08732, -71.36232</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/06/28 10:02:13</t>
+          <t>2026/06/30 14:38:33</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.835125, -70.6046299</t>
+          <t>-33.0978099, -71.3298233</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.83512, -70.60463</t>
+          <t>-33.09781, -71.32982</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>16:24:37</t>
+          <t>03:39:18</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>32.97</v>
+        <v>4.18</v>
       </c>
       <c r="M58" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="N58" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -3781,125 +3781,125 @@
         </is>
       </c>
       <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026/06/30 11:07:23</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-32.8832883, -70.6113416</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-32.88329, -70.61134</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026/06/30 12:47:23</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-32.8824116, -70.6113149</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-32.88241, -70.61131</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>01:40:00</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20</v>
+      </c>
+      <c r="N59" t="n">
         <v>11</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026/06/27 18:02:53</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-32.8849033, -70.6103083</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-32.88490, -70.61031</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026/06/27 18:30:25</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-32.8430116, -70.59892</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-32.84301, -70.59892</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>00:27:32</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="M59" t="n">
-        <v>44</v>
-      </c>
-      <c r="N59" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/06/27 18:31:40</t>
+          <t>2026/06/30 11:54:57</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-32.84306, -70.598865</t>
+          <t>-33.360036, -70.807118</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-32.84306, -70.59887</t>
+          <t>-33.36004, -70.80712</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/06/27 18:54:52</t>
+          <t>2026/07/02 14:40:46</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-32.8481666, -70.5919649</t>
+          <t>-33.359985, -70.807068</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-32.84817, -70.59196</t>
+          <t>-33.35999, -70.80707</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:23:12</t>
+          <t>50:45:49</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.01</v>
+        <v>0.03</v>
       </c>
       <c r="M60" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,47 +3908,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/06/27 18:35:14</t>
+          <t>2026/06/30 12:48:38</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-36.9038983, -73.0298766</t>
+          <t>-32.8832433, -70.6113333</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-36.90390, -73.02988</t>
+          <t>-32.88324, -70.61133</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/06/28 13:39:00</t>
+          <t>2026/06/30 13:17:42</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-36.8459166, -73.0518549</t>
+          <t>-32.8790866, -70.6093316</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-36.84592, -73.05185</t>
+          <t>-32.87909, -70.60933</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>19:03:46</t>
+          <t>00:29:04</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6.81</v>
+        <v>1.48</v>
       </c>
       <c r="M61" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="N61" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/06/27 18:56:07</t>
+          <t>2026/06/30 13:18:57</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-32.84827, -70.5920433</t>
+          <t>-32.8792016, -70.6088499</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-32.84827, -70.59204</t>
+          <t>-32.87920, -70.60885</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/06/27 19:15:38</t>
+          <t>2026/06/30 13:53:46</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-32.8791983, -70.608915</t>
+          <t>-32.8296016, -70.6116533</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60891</t>
+          <t>-32.82960, -70.61165</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:19:31</t>
+          <t>00:34:49</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>7.4</v>
+        <v>8.76</v>
       </c>
       <c r="M62" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="N62" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,57 +4026,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/06/27 19:16:20</t>
+          <t>2026/06/30 13:42:35</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-32.8790583, -70.6093816</t>
+          <t>-33.4763033, -70.6983916</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-32.87906, -70.60938</t>
+          <t>-33.47630, -70.69839</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/06/28 11:00:25</t>
+          <t>2026/06/30 14:21:26</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-32.8663783, -70.6238599</t>
+          <t>-33.3893383, -70.6740283</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-32.86638, -70.62386</t>
+          <t>-33.38934, -70.67403</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15:44:05</t>
+          <t>00:38:51</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.87</v>
+        <v>14.95</v>
       </c>
       <c r="M63" t="n">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="N63" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,47 +4085,47 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/06/27 19:24:26</t>
+          <t>2026/06/30 13:53:51</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-32.838372, -70.955529</t>
+          <t>-32.8295516, -70.61164</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95553</t>
+          <t>-32.82955, -70.61164</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/06/27 21:07:34</t>
+          <t>2026/06/30 14:39:32</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-32.785696, -70.960382</t>
+          <t>-32.87918, -70.6089183</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-32.78570, -70.96038</t>
+          <t>-32.87918, -70.60892</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>01:43:08</t>
+          <t>00:45:41</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>14.9</v>
+        <v>9.5</v>
       </c>
       <c r="M64" t="n">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="N64" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/06/27 19:54:08</t>
+          <t>2026/06/30 14:21:38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.4761199, -70.6985283</t>
+          <t>-33.38934, -70.674035</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69853</t>
+          <t>-33.38934, -70.67404</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/06/28 08:07:43</t>
+          <t>2026/06/30 15:17:53</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.4761916, -70.6984216</t>
+          <t>-33.36235, -70.67012</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69842</t>
+          <t>-33.36235, -70.67012</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>12:13:35</t>
+          <t>00:56:15</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.02</v>
+        <v>14.27</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="N65" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,44 +4203,44 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/06/27 20:41:00</t>
+          <t>2026/06/30 14:38:52</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-32.840071, -70.950259</t>
+          <t>-33.0976766, -71.3297416</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-32.84007, -70.95026</t>
+          <t>-33.09768, -71.32974</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/06/27 20:54:21</t>
+          <t>2026/06/30 16:56:22</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-32.840052, -70.95025</t>
+          <t>-33.0868266, -71.361695</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-32.84005, -70.95025</t>
+          <t>-33.08683, -71.36169</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>00:13:21</t>
+          <t>02:17:30</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.31</v>
+        <v>4.13</v>
       </c>
       <c r="M66" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N66" t="n">
         <v>17</v>
@@ -4249,7 +4249,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4262,57 +4262,57 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/06/27 20:55:21</t>
+          <t>2026/06/30 14:39:53</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-32.840061, -70.95026</t>
+          <t>-32.8790299, -70.6093833</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-32.84006, -70.95026</t>
+          <t>-32.87903, -70.60938</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/06/27 21:05:21</t>
+          <t>2026/06/30 18:19:01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-32.838616, -70.954015</t>
+          <t>-32.87913, -70.6093416</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-32.83862, -70.95401</t>
+          <t>-32.87913, -70.60934</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>00:10:00</t>
+          <t>03:39:08</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.84</v>
+        <v>0.01</v>
       </c>
       <c r="M67" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/06/27 21:05:36</t>
+          <t>2026/06/30 15:18:15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-32.838715, -70.954078</t>
+          <t>-33.362185, -70.6700933</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-32.83872, -70.95408</t>
+          <t>-33.36218, -70.67009</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/06/27 21:45:39</t>
+          <t>2026/06/30 16:28:47</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-32.841841, -70.936899</t>
+          <t>-33.4500183, -70.663415</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-32.84184, -70.93690</t>
+          <t>-33.45002, -70.66342</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:40:03</t>
+          <t>01:10:32</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>23.98</v>
       </c>
       <c r="M68" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="N68" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,57 +4380,57 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/06/27 21:08:02</t>
+          <t>2026/06/30 15:37:00</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-32.785385, -70.960451</t>
+          <t>-33.482162, -70.764856</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-32.78538, -70.96045</t>
+          <t>-33.48216, -70.76486</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/06/27 21:48:08</t>
+          <t>2026/06/30 16:59:08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-32.780869, -70.981334</t>
+          <t>-33.482132, -70.765251</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-32.78087, -70.98133</t>
+          <t>-33.48213, -70.76525</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:40:06</t>
+          <t>01:22:08</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.05</v>
+        <v>4.87</v>
       </c>
       <c r="M69" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N69" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,44 +4439,44 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/06/27 21:45:55</t>
+          <t>2026/06/30 16:30:02</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-32.841804, -70.936878</t>
+          <t>-33.4504183, -70.6650516</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-32.84180, -70.93688</t>
+          <t>-33.45042, -70.66505</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/06/28 10:55:29</t>
+          <t>2026/06/30 17:08:23</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-32.83853, -70.953887</t>
+          <t>-33.476265, -70.6983316</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-32.83853, -70.95389</t>
+          <t>-33.47626, -70.69833</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>13:09:34</t>
+          <t>00:38:21</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.29</v>
+        <v>5.56</v>
       </c>
       <c r="M70" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N70" t="n">
         <v>20</v>
@@ -4485,11 +4485,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/06/27 21:48:29</t>
+          <t>2026/06/30 16:57:11</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-32.780847, -70.98129</t>
+          <t>-33.0873449, -71.3622499</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-32.78085, -70.98129</t>
+          <t>-33.08734, -71.36225</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/06/28 01:41:15</t>
+          <t>2026/06/30 17:24:32</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-32.785697, -70.960385</t>
+          <t>-33.0444533, -71.3743799</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-32.78570, -70.96039</t>
+          <t>-33.04445, -71.37438</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>03:52:46</t>
+          <t>00:27:21</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.11</v>
+        <v>6.63</v>
       </c>
       <c r="M71" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/06/28 02:40:11</t>
+          <t>2026/06/30 17:00:08</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.368129, -70.696085</t>
+          <t>-33.482181, -70.764876</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.36813, -70.69608</t>
+          <t>-33.48218, -70.76488</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/06/30 01:41:05</t>
+          <t>2026/07/01 08:55:47</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.367112, -70.696652</t>
+          <t>-33.359983, -70.807052</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.36711, -70.69665</t>
+          <t>-33.35998, -70.80705</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>47:00:54</t>
+          <t>15:55:39</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.12</v>
+        <v>19.57</v>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,234 +4616,234 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/06/29 14:00:24</t>
+          <t>2026/06/30 17:08:32</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-32.7975833, -70.8870766</t>
+          <t>-33.4763216, -70.6983716</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88708</t>
+          <t>-33.47632, -70.69837</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/06/30 09:05:06</t>
+          <t>2026/06/30 17:45:45</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.696575</t>
+          <t>-33.3623483, -70.6701433</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69657</t>
+          <t>-33.36235, -70.67014</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>19:04:42</t>
+          <t>00:37:13</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>100.14</v>
+        <v>18.64</v>
       </c>
       <c r="M73" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N73" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/06/30 10:05:46</t>
+          <t>2026/06/30 17:25:47</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-32.840279, -70.964577</t>
+          <t>-33.0453866, -71.3743666</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-32.84028, -70.96458</t>
+          <t>-33.04539, -71.37437</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/06/30 10:56:45</t>
+          <t>2026/06/30 17:43:45</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-32.840287, -70.964573</t>
+          <t>-33.0583616, -71.3730366</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-32.84029, -70.96457</t>
+          <t>-33.05836, -71.37304</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:50:59</t>
+          <t>00:17:58</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M74" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/06/30 10:28:39</t>
+          <t>2026/06/30 17:29:34</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.0448016, -71.4202366</t>
+          <t>-34.205411, -70.677278</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.04480, -71.42024</t>
+          <t>-34.20541, -70.67728</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/06/30 10:58:00</t>
+          <t>2026/07/04 22:11:47</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.0873283, -71.362295</t>
+          <t>-34.205306, -70.677463</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36230</t>
+          <t>-34.20531, -70.67746</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:29:21</t>
+          <t>100:42:13</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>10.54</v>
+        <v>0.05</v>
       </c>
       <c r="M75" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/06/30 10:57:04</t>
+          <t>2026/06/30 17:45:00</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-32.840354, -70.964574</t>
+          <t>-33.0582999, -71.3728383</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-32.84035, -70.96457</t>
+          <t>-33.05830, -71.37284</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/06/30 12:37:02</t>
+          <t>2026/06/30 18:03:42</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-32.840478, -70.964481</t>
+          <t>-33.0873483, -71.3622933</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-32.84048, -70.96448</t>
+          <t>-33.08735, -71.36229</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01:39:58</t>
+          <t>00:18:42</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.05</v>
+        <v>4.46</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,106 +4852,106 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/06/30 10:59:15</t>
+          <t>2026/06/30 17:46:05</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.0873166, -71.3623183</t>
+          <t>-33.362135, -70.6701833</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36232</t>
+          <t>-33.36214, -70.67018</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/06/30 14:38:33</t>
+          <t>2026/06/30 19:31:53</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.0978099, -71.3298233</t>
+          <t>-33.38949, -70.67389</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.09781, -71.32982</t>
+          <t>-33.38949, -70.67389</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>03:39:18</t>
+          <t>01:45:48</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="M77" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/06/30 11:54:57</t>
+          <t>2026/06/30 18:00:06</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.360036, -70.807118</t>
+          <t>-32.7853849, -70.8316733</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-32.78538, -70.83167</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/07/02 14:40:46</t>
+          <t>2026/06/30 18:15:43</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.359985, -70.807068</t>
+          <t>-32.7977249, -70.8874233</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80707</t>
+          <t>-32.79772, -70.88742</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>50:45:49</t>
+          <t>00:15:37</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.03</v>
+        <v>7.39</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,57 +4970,57 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/06/30 14:38:52</t>
+          <t>2026/06/30 18:04:57</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.0976766, -71.3297416</t>
+          <t>-33.0872683, -71.3622716</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.09768, -71.32974</t>
+          <t>-33.08727, -71.36227</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/06/30 16:56:22</t>
+          <t>2026/07/01 09:04:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.0868266, -71.361695</t>
+          <t>-33.0873116, -71.3623033</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.08683, -71.36169</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>02:17:30</t>
+          <t>14:59:44</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.13</v>
+        <v>0.02</v>
       </c>
       <c r="M79" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="N79" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/06/30 16:57:11</t>
+          <t>2026/06/30 18:16:32</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-33.0873449, -71.3622499</t>
+          <t>-32.7976249, -70.8871316</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36225</t>
+          <t>-32.79762, -70.88713</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/06/30 17:24:32</t>
+          <t>2026/07/01 08:29:06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.0444533, -71.3743799</t>
+          <t>-33.367225, -70.6965716</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.04445, -71.37438</t>
+          <t>-33.36722, -70.69657</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:27:21</t>
+          <t>14:12:34</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>6.63</v>
+        <v>92.52</v>
       </c>
       <c r="M80" t="n">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="N80" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,116 +5088,116 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/06/30 17:25:47</t>
+          <t>2026/06/30 18:19:38</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.0453866, -71.3743666</t>
+          <t>-32.8792399, -70.608805</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.04539, -71.37437</t>
+          <t>-32.87924, -70.60881</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/06/30 17:43:45</t>
+          <t>2026/07/01 09:18:54</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.0583616, -71.3730366</t>
+          <t>-32.8677716, -70.6224</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.05836, -71.37304</t>
+          <t>-32.86777, -70.62240</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:17:58</t>
+          <t>14:59:16</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.5</v>
+        <v>3.51</v>
       </c>
       <c r="M81" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="N81" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/06/30 17:29:34</t>
+          <t>2026/06/30 19:32:56</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-34.205411, -70.677278</t>
+          <t>-33.389315, -70.6740216</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67728</t>
+          <t>-33.38932, -70.67402</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/07/03 23:11:36</t>
+          <t>2026/06/30 20:28:10</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-34.205464, -70.677346</t>
+          <t>-33.4762483, -70.6982899</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-34.20546, -70.67735</t>
+          <t>-33.47625, -70.69829</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>77:42:02</t>
+          <t>00:55:14</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.03</v>
+        <v>13.58</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/06/30 17:45:00</t>
+          <t>2026/06/30 20:29:25</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.0582999, -71.3728383</t>
+          <t>-33.4761, -70.6985283</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.05830, -71.37284</t>
+          <t>-33.47610, -70.69853</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/06/30 18:03:42</t>
+          <t>2026/07/01 09:24:18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.0873483, -71.3622933</t>
+          <t>-33.4761566, -70.698465</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36229</t>
+          <t>-33.47616, -70.69846</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>00:18:42</t>
+          <t>12:54:53</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.46</v>
+        <v>0.01</v>
       </c>
       <c r="M83" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="N83" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/06/30 18:00:06</t>
+          <t>2026/07/01 10:11:49</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-32.7853849, -70.8316733</t>
+          <t>-33.3685633, -70.7261283</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-32.78538, -70.83167</t>
+          <t>-33.36856, -70.72613</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/06/30 18:15:43</t>
+          <t>2026/07/01 10:47:32</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-32.7977249, -70.8874233</t>
+          <t>-33.3599716, -70.8071033</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88742</t>
+          <t>-33.35997, -70.80710</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:15:37</t>
+          <t>00:35:43</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>7.39</v>
+        <v>10.85</v>
       </c>
       <c r="M84" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="N84" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/06/30 18:04:57</t>
+          <t>2026/07/01 10:47:44</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-33.0872683, -71.3622716</t>
+          <t>-33.3600133, -70.8071849</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36227</t>
+          <t>-33.36001, -70.80718</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/07/01 09:04:41</t>
+          <t>2026/07/01 12:15:18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.0873116, -71.3623033</t>
+          <t>-33.5031949, -71.2568966</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36230</t>
+          <t>-33.50319, -71.25690</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>14:59:44</t>
+          <t>01:27:34</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.02</v>
+        <v>64.69</v>
       </c>
       <c r="M85" t="n">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="N85" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/06/30 18:16:32</t>
+          <t>2026/07/01 12:16:33</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871316</t>
+          <t>-33.506265, -71.2518333</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88713</t>
+          <t>-33.50626, -71.25183</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/01 08:29:06</t>
+          <t>2026/07/01 13:20:12</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.367225, -70.6965716</t>
+          <t>-33.4559049, -71.3000066</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.36722, -70.69657</t>
+          <t>-33.45590, -71.30001</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>14:12:34</t>
+          <t>01:03:39</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>92.52</v>
+        <v>7.56</v>
       </c>
       <c r="M86" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="N86" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,47 +5442,47 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/06/30 19:32:56</t>
+          <t>2026/07/01 13:20:34</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.389315, -70.6740216</t>
+          <t>-33.4562116, -71.300045</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67402</t>
+          <t>-33.45621, -71.30004</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/06/30 20:28:10</t>
+          <t>2026/07/01 18:22:09</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.4762483, -70.6982899</t>
+          <t>-32.9641266, -70.6888516</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69829</t>
+          <t>-32.96413, -70.68885</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>00:55:14</t>
+          <t>05:01:35</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>13.58</v>
+        <v>123.71</v>
       </c>
       <c r="M87" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="N87" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/06/30 20:29:25</t>
+          <t>2026/07/01 16:17:48</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.4761, -70.6985283</t>
+          <t>-33.35124, -70.6716316</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69853</t>
+          <t>-33.35124, -70.67163</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/01 09:24:18</t>
+          <t>2026/07/01 16:33:09</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.4761566, -70.698465</t>
+          <t>-33.3623016, -70.6701366</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69846</t>
+          <t>-33.36230, -70.67014</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>12:54:53</t>
+          <t>00:15:21</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.01</v>
+        <v>2.91</v>
       </c>
       <c r="M88" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,57 +5560,57 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/01 09:52:27</t>
+          <t>2026/07/01 16:34:16</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-33.3679799, -70.7269766</t>
+          <t>-33.3621083, -70.6701349</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-33.36798, -70.72698</t>
+          <t>-33.36211, -70.67013</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/01 10:10:34</t>
+          <t>2026/07/01 18:13:15</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-33.3686783, -70.7259816</t>
+          <t>-33.3895166, -70.6738466</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-33.36868, -70.72598</t>
+          <t>-33.38952, -70.67385</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:18:07</t>
+          <t>01:38:59</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.14</v>
+        <v>4.04</v>
       </c>
       <c r="M89" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/07/01 10:11:49</t>
+          <t>2026/07/01 16:37:24</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.3685633, -70.7261283</t>
+          <t>-33.3665449, -70.6961266</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.36856, -70.72613</t>
+          <t>-33.36654, -70.69613</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/07/01 10:47:32</t>
+          <t>2026/07/01 18:37:01</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.3599716, -70.8071033</t>
+          <t>-33.4292333, -70.62603</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80710</t>
+          <t>-33.42923, -70.62603</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>00:35:43</t>
+          <t>01:59:37</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>10.85</v>
+        <v>18.18</v>
       </c>
       <c r="M90" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="N90" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/07/01 10:47:44</t>
+          <t>2026/07/01 17:07:00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-33.3600133, -70.8071849</t>
+          <t>-32.8355983, -70.5980033</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80718</t>
+          <t>-32.83560, -70.59800</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/07/01 12:15:18</t>
+          <t>2026/07/01 17:33:51</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.5031949, -71.2568966</t>
+          <t>-32.83001, -70.59606</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.50319, -71.25690</t>
+          <t>-32.83001, -70.59606</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>01:27:34</t>
+          <t>00:26:51</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>64.69</v>
+        <v>0.66</v>
       </c>
       <c r="M91" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="N91" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,57 +5737,57 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/07/01 12:16:33</t>
+          <t>2026/07/01 17:34:20</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-33.506265, -71.2518333</t>
+          <t>-32.8297266, -70.5967333</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-33.50626, -71.25183</t>
+          <t>-32.82973, -70.59673</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/07/01 13:20:12</t>
+          <t>2026/07/01 21:02:02</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-33.4559049, -71.3000066</t>
+          <t>-32.87944, -70.6088683</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-33.45590, -71.30001</t>
+          <t>-32.87944, -70.60887</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>01:03:39</t>
+          <t>03:27:42</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>7.56</v>
+        <v>23.77</v>
       </c>
       <c r="M92" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N92" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/01 13:20:34</t>
+          <t>2026/07/01 18:13:40</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.4562116, -71.300045</t>
+          <t>-33.389315, -70.6739966</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.45621, -71.30004</t>
+          <t>-33.38932, -70.67400</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/01 18:22:09</t>
+          <t>2026/07/01 18:55:19</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-32.9641266, -70.6888516</t>
+          <t>-33.3623416, -70.6701316</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-32.96413, -70.68885</t>
+          <t>-33.36234, -70.67013</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>05:01:35</t>
+          <t>00:41:39</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>123.71</v>
+        <v>3.57</v>
       </c>
       <c r="M93" t="n">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="N93" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/01 14:54:21</t>
+          <t>2026/07/01 18:23:24</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.366535, -70.696175</t>
+          <t>-32.9638666, -70.6887733</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.36653, -70.69617</t>
+          <t>-32.96387, -70.68877</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/01 16:36:18</t>
+          <t>2026/07/01 19:04:24</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.3665766, -70.696145</t>
+          <t>-32.74321, -70.7329233</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69615</t>
+          <t>-32.74321, -70.73292</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>01:41:57</t>
+          <t>00:41:00</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.04</v>
+        <v>26.93</v>
       </c>
       <c r="M94" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="N94" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/01 16:17:48</t>
+          <t>2026/07/01 18:36:10</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-33.35124, -70.6716316</t>
+          <t>-32.840309, -70.960003</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-33.35124, -70.67163</t>
+          <t>-32.84031, -70.96000</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/01 16:33:09</t>
+          <t>2026/07/01 18:52:38</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-33.3623016, -70.6701366</t>
+          <t>-32.840673, -70.959203</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-33.36230, -70.67014</t>
+          <t>-32.84067, -70.95920</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:15:21</t>
+          <t>00:16:28</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.91</v>
+        <v>0.29</v>
       </c>
       <c r="M95" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="N95" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/01 16:34:16</t>
+          <t>2026/07/01 18:38:16</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-33.3621083, -70.6701349</t>
+          <t>-33.429875, -70.6266516</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-33.36211, -70.67013</t>
+          <t>-33.42988, -70.62665</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/01 18:13:15</t>
+          <t>2026/07/01 19:12:43</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-33.3895166, -70.6738466</t>
+          <t>-33.4658483, -70.59143</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-33.38952, -70.67385</t>
+          <t>-33.46585, -70.59143</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>01:38:59</t>
+          <t>00:34:27</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.04</v>
+        <v>7.39</v>
       </c>
       <c r="M96" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N96" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,47 +6032,47 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/07/01 16:37:24</t>
+          <t>2026/07/01 18:52:50</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-33.3665449, -70.6961266</t>
+          <t>-32.840977, -70.959267</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-33.36654, -70.69613</t>
+          <t>-32.84098, -70.95927</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/07/01 18:37:01</t>
+          <t>2026/07/01 19:08:06</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-33.4292333, -70.62603</t>
+          <t>-32.838368, -70.956176</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-33.42923, -70.62603</t>
+          <t>-32.83837, -70.95618</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>01:59:37</t>
+          <t>00:15:16</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>18.18</v>
+        <v>1.02</v>
       </c>
       <c r="M97" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N97" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,47 +6091,47 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/01 18:13:40</t>
+          <t>2026/07/01 18:56:17</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.389315, -70.6739966</t>
+          <t>-33.3621316, -70.67014</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67400</t>
+          <t>-33.36213, -70.67014</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/01 18:55:19</t>
+          <t>2026/07/01 19:49:48</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-33.3623416, -70.6701316</t>
+          <t>-33.4761366, -70.6985283</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-33.36234, -70.67013</t>
+          <t>-33.47614, -70.69853</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:41:39</t>
+          <t>00:53:31</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.57</v>
+        <v>18.19</v>
       </c>
       <c r="M98" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="N98" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/01 18:23:24</t>
+          <t>2026/07/01 19:04:34</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.9638666, -70.6887733</t>
+          <t>-32.7433216, -70.7327416</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.96387, -70.68877</t>
+          <t>-32.74332, -70.73274</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/01 19:04:24</t>
+          <t>2026/07/01 19:26:08</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-32.74321, -70.7329233</t>
+          <t>-32.7431749, -70.7296599</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-32.74321, -70.73292</t>
+          <t>-32.74317, -70.72966</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:41:00</t>
+          <t>00:21:34</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>26.93</v>
+        <v>0.37</v>
       </c>
       <c r="M99" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="N99" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,44 +6209,44 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/01 18:38:16</t>
+          <t>2026/07/01 19:09:05</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-33.429875, -70.6266516</t>
+          <t>-32.83838, -70.955483</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-33.42988, -70.62665</t>
+          <t>-32.83838, -70.95548</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/01 19:12:43</t>
+          <t>2026/07/02 09:35:22</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-33.4658483, -70.59143</t>
+          <t>-32.83736, -70.967134</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-33.46585, -70.59143</t>
+          <t>-32.83736, -70.96713</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:34:27</t>
+          <t>14:26:17</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>7.39</v>
+        <v>3.15</v>
       </c>
       <c r="M100" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N100" t="n">
         <v>18</v>
@@ -6255,11 +6255,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,47 +6268,47 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/01 18:56:17</t>
+          <t>2026/07/01 19:13:06</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.3621316, -70.67014</t>
+          <t>-33.466, -70.59085</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.36213, -70.67014</t>
+          <t>-33.46600, -70.59085</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/01 19:49:48</t>
+          <t>2026/07/01 21:09:14</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.4761366, -70.6985283</t>
+          <t>-33.4358966, -70.630045</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.47614, -70.69853</t>
+          <t>-33.43590, -70.63004</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:53:31</t>
+          <t>01:56:08</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>18.19</v>
+        <v>8.27</v>
       </c>
       <c r="M101" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="N101" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102">
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/01 19:04:34</t>
+          <t>2026/07/01 19:26:31</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.7433216, -70.7327416</t>
+          <t>-32.7430433, -70.7297616</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.74332, -70.73274</t>
+          <t>-32.74304, -70.72976</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/01 19:26:08</t>
+          <t>2026/07/02 08:14:22</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.7431749, -70.7296599</t>
+          <t>-33.4821016, -70.7654016</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72966</t>
+          <t>-33.48210, -70.76540</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:21:34</t>
+          <t>12:47:51</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0.37</v>
+        <v>95.72</v>
       </c>
       <c r="M102" t="n">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="N102" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/01 19:09:05</t>
+          <t>2026/07/01 19:50:56</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.83838, -70.955483</t>
+          <t>-33.4761066, -70.6985333</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95548</t>
+          <t>-33.47611, -70.69853</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/02 09:35:22</t>
+          <t>2026/07/02 08:43:30</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.83736, -70.967134</t>
+          <t>-33.47627, -70.698345</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.83736, -70.96713</t>
+          <t>-33.47627, -70.69835</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>14:26:17</t>
+          <t>12:52:34</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.15</v>
+        <v>0.03</v>
       </c>
       <c r="M103" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="N103" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/01 19:13:06</t>
+          <t>2026/07/01 21:03:17</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-33.466, -70.59085</t>
+          <t>-32.879205, -70.60883</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-33.46600, -70.59085</t>
+          <t>-32.87920, -70.60883</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/01 21:09:14</t>
+          <t>2026/07/02 10:10:43</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.4358966, -70.630045</t>
+          <t>-33.3363116, -70.7193983</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.43590, -70.63004</t>
+          <t>-33.33631, -70.71940</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>01:56:08</t>
+          <t>13:07:26</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>8.27</v>
+        <v>65.22</v>
       </c>
       <c r="M104" t="n">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="N104" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/01 19:26:31</t>
+          <t>2026/07/01 21:10:29</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.7430433, -70.7297616</t>
+          <t>-33.4364533, -70.6295916</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.74304, -70.72976</t>
+          <t>-33.43645, -70.62959</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/02 08:14:22</t>
+          <t>2026/07/02 12:50:54</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.4821016, -70.7654016</t>
+          <t>-33.3673183, -70.6960249</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.48210, -70.76540</t>
+          <t>-33.36732, -70.69602</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12:47:51</t>
+          <t>15:40:25</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>95.72</v>
+        <v>13.73</v>
       </c>
       <c r="M105" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="N105" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/01 19:50:56</t>
+          <t>2026/07/01 21:10:55</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-33.4761066, -70.6985333</t>
+          <t>-32.7975766, -70.8870866</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69853</t>
+          <t>-32.79758, -70.88709</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/02 08:43:30</t>
+          <t>2026/07/02 07:49:14</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.47627, -70.698345</t>
+          <t>-32.8517066, -70.6845583</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69835</t>
+          <t>-32.85171, -70.68456</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>12:52:34</t>
+          <t>10:38:19</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.03</v>
+        <v>29.01</v>
       </c>
       <c r="M106" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="N106" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,47 +6622,47 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/01 21:10:29</t>
+          <t>2026/07/02 14:03:25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-33.4364533, -70.6295916</t>
+          <t>-34.20837, -70.6774733</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-33.43645, -70.62959</t>
+          <t>-34.20837, -70.67747</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/02 12:50:54</t>
+          <t>2026/07/02 14:34:28</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-33.3673183, -70.6960249</t>
+          <t>-34.2054716, -70.679015</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-33.36732, -70.69602</t>
+          <t>-34.20547, -70.67902</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>15:40:25</t>
+          <t>00:31:03</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>13.73</v>
+        <v>1.12</v>
       </c>
       <c r="M107" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="N107" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,47 +6681,47 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/01 21:10:55</t>
+          <t>2026/07/02 14:34:42</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-32.7975766, -70.8870866</t>
+          <t>-34.205505, -70.6783</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88709</t>
+          <t>-34.20551, -70.67830</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/02 07:49:14</t>
+          <t>2026/07/02 15:07:31</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-32.8517066, -70.6845583</t>
+          <t>-34.205605, -70.6770266</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-32.85171, -70.68456</t>
+          <t>-34.20560, -70.67703</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>10:38:19</t>
+          <t>00:32:49</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>29.01</v>
+        <v>0.16</v>
       </c>
       <c r="M108" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="N108" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,53 +6740,53 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/02 14:03:25</t>
+          <t>2026/07/02 15:08:46</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-34.20837, -70.6774733</t>
+          <t>-34.20555, -70.6775616</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-34.20837, -70.67747</t>
+          <t>-34.20555, -70.67756</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/02 14:34:28</t>
+          <t>2026/07/02 18:26:46</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-34.2054716, -70.679015</t>
+          <t>-32.7977149, -70.8874383</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67902</t>
+          <t>-32.79771, -70.88744</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:31:03</t>
+          <t>03:18:00</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.12</v>
+        <v>196.44</v>
       </c>
       <c r="M109" t="n">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="N109" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6799,106 +6799,106 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/02 14:34:42</t>
+          <t>2026/07/02 15:30:04</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.205505, -70.6783</t>
+          <t>-33.3603466, -70.8100116</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67830</t>
+          <t>-33.36035, -70.81001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/02 15:07:31</t>
+          <t>2026/07/02 15:59:47</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.205605, -70.6770266</t>
+          <t>-33.3592333, -70.8099633</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.20560, -70.67703</t>
+          <t>-33.35923, -70.80996</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:32:49</t>
+          <t>00:29:43</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="M110" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/02 15:08:46</t>
+          <t>2026/07/02 15:38:12</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.20555, -70.6775616</t>
+          <t>-33.359985, -70.807068</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67756</t>
+          <t>-33.35999, -70.80707</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/02 18:26:46</t>
+          <t>2026/07/03 15:48:05</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.8874383</t>
+          <t>-33.359771, -70.807271</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88744</t>
+          <t>-33.35977, -70.80727</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>03:18:00</t>
+          <t>24:09:53</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>196.44</v>
+        <v>0.06</v>
       </c>
       <c r="M111" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,116 +6917,116 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/02 15:30:04</t>
+          <t>2026/07/02 16:00:01</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-33.3603466, -70.8100116</t>
+          <t>-33.35928, -70.8097799</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-33.36035, -70.81001</t>
+          <t>-33.35928, -70.80978</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/02 15:59:47</t>
+          <t>2026/07/02 16:19:50</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-33.3592333, -70.8099633</t>
+          <t>-33.3612449, -70.8117633</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-33.35923, -70.80996</t>
+          <t>-33.36124, -70.81176</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:29:43</t>
+          <t>00:19:49</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="M112" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/07/02 15:38:12</t>
+          <t>2026/07/02 16:19:55</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.359985, -70.807068</t>
+          <t>-33.3612433, -70.8117233</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80707</t>
+          <t>-33.36124, -70.81172</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/03 15:48:05</t>
+          <t>2026/07/02 18:28:33</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.359771, -70.807271</t>
+          <t>-32.7568816, -70.7350316</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.35977, -70.80727</t>
+          <t>-32.75688, -70.73503</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>24:09:53</t>
+          <t>02:08:38</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.06</v>
+        <v>114.06</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,47 +7035,47 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/02 16:00:01</t>
+          <t>2026/07/02 18:27:40</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.35928, -70.8097799</t>
+          <t>-32.7975916, -70.88712</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.35928, -70.80978</t>
+          <t>-32.79759, -70.88712</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/02 16:19:50</t>
+          <t>2026/07/03 08:37:23</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.3612449, -70.8117633</t>
+          <t>-32.7568733, -70.7339866</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.36124, -70.81176</t>
+          <t>-32.75687, -70.73399</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:19:49</t>
+          <t>14:09:43</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.34</v>
+        <v>17.39</v>
       </c>
       <c r="M114" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="N114" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/02 16:19:55</t>
+          <t>2026/07/02 18:29:48</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.3612433, -70.8117233</t>
+          <t>-32.7569433, -70.7346383</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.36124, -70.81172</t>
+          <t>-32.75694, -70.73464</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/02 18:28:33</t>
+          <t>2026/07/02 18:45:19</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-32.7568816, -70.7350316</t>
+          <t>-32.74318, -70.7331016</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-32.75688, -70.73503</t>
+          <t>-32.74318, -70.73310</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>02:08:38</t>
+          <t>00:15:31</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>114.06</v>
+        <v>1.8</v>
       </c>
       <c r="M115" t="n">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="N115" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,47 +7153,47 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/02 18:27:40</t>
+          <t>2026/07/02 18:45:31</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-32.7975916, -70.88712</t>
+          <t>-32.74332, -70.732715</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88712</t>
+          <t>-32.74332, -70.73271</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/03 08:37:23</t>
+          <t>2026/07/02 19:06:58</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-32.7568733, -70.7339866</t>
+          <t>-32.7431666, -70.7296599</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-32.75687, -70.73399</t>
+          <t>-32.74317, -70.72966</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>14:09:43</t>
+          <t>00:21:27</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>17.39</v>
+        <v>0.37</v>
       </c>
       <c r="M116" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="N116" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,116 +7212,116 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/02 18:29:48</t>
+          <t>2026/07/02 19:08:13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.7569433, -70.7346383</t>
+          <t>-32.7430483, -70.7297816</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.75694, -70.73464</t>
+          <t>-32.74305, -70.72978</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/02 18:45:19</t>
+          <t>2026/07/03 09:06:28</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-32.74318, -70.7331016</t>
+          <t>-33.3599466, -70.8069483</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-32.74318, -70.73310</t>
+          <t>-33.35995, -70.80695</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:15:31</t>
+          <t>13:58:15</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.8</v>
+        <v>90.03</v>
       </c>
       <c r="M117" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="N117" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C118" t="n">
+        <v>15</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026/07/02 19:25:25</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-32.8351466, -70.5981016</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-32.83515, -70.59810</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026/07/02 19:35:35</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-32.829985, -70.5961166</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-32.82999, -70.59612</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>00:10:10</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M118" t="n">
+        <v>19</v>
+      </c>
+      <c r="N118" t="n">
         <v>14</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2026/07/02 18:45:31</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-32.74332, -70.732715</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-32.74332, -70.73271</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>2026/07/02 19:06:58</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-32.7431666, -70.7296599</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>-32.74317, -70.72966</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>00:21:27</t>
-        </is>
-      </c>
-      <c r="L118" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="M118" t="n">
-        <v>10</v>
-      </c>
-      <c r="N118" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,47 +7330,47 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/02 19:08:13</t>
+          <t>2026/07/02 19:35:58</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-32.7430483, -70.7297816</t>
+          <t>-32.8296933, -70.59693</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-32.74305, -70.72978</t>
+          <t>-32.82969, -70.59693</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/03 09:06:28</t>
+          <t>2026/07/02 19:52:58</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.3599466, -70.8069483</t>
+          <t>-32.8438816, -70.5976683</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80695</t>
+          <t>-32.84388, -70.59767</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>13:58:15</t>
+          <t>00:17:00</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>90.03</v>
+        <v>2.38</v>
       </c>
       <c r="M119" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="N119" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7389,47 +7389,47 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/02 19:25:25</t>
+          <t>2026/07/02 19:54:13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-32.8351466, -70.5981016</t>
+          <t>-32.84522, -70.5986183</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-32.83515, -70.59810</t>
+          <t>-32.84522, -70.59862</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/02 19:35:35</t>
+          <t>2026/07/02 20:18:57</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-32.829985, -70.5961166</t>
+          <t>-32.8358783, -70.5712266</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-32.82999, -70.59612</t>
+          <t>-32.83588, -70.57123</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>00:10:10</t>
+          <t>00:24:44</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.61</v>
+        <v>3.68</v>
       </c>
       <c r="M120" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="N120" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121">
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,47 +7448,47 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/02 19:35:58</t>
+          <t>2026/07/02 20:19:46</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-32.8296933, -70.59693</t>
+          <t>-32.8345466, -70.5704883</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-32.82969, -70.59693</t>
+          <t>-32.83455, -70.57049</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/02 19:52:58</t>
+          <t>2026/07/02 21:03:15</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-32.8438816, -70.5976683</t>
+          <t>-32.8452433, -70.5986616</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-32.84388, -70.59767</t>
+          <t>-32.84524, -70.59866</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:17:00</t>
+          <t>00:43:29</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.38</v>
+        <v>4.85</v>
       </c>
       <c r="M121" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N121" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122">
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,44 +7507,44 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/07/02 19:54:13</t>
+          <t>2026/07/02 21:04:30</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.84522, -70.5986183</t>
+          <t>-32.8452483, -70.5986783</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.84522, -70.59862</t>
+          <t>-32.84525, -70.59868</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/02 20:18:57</t>
+          <t>2026/07/02 21:41:37</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.8358783, -70.5712266</t>
+          <t>-32.8345933, -70.5706366</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.83588, -70.57123</t>
+          <t>-32.83459, -70.57064</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:24:44</t>
+          <t>00:37:07</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="M122" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N122" t="n">
         <v>21</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,47 +7566,47 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/02 20:19:46</t>
+          <t>2026/07/02 21:42:52</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.8345466, -70.5704883</t>
+          <t>-32.8345683, -70.5706116</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.83455, -70.57049</t>
+          <t>-32.83457, -70.57061</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/02 21:03:15</t>
+          <t>2026/07/02 22:16:43</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.8452433, -70.5986616</t>
+          <t>-32.8793333, -70.6089049</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.84524, -70.59866</t>
+          <t>-32.87933, -70.60890</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>00:43:29</t>
+          <t>00:33:51</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>4.85</v>
+        <v>9.69</v>
       </c>
       <c r="M123" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124">
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,44 +7625,44 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/02 21:04:30</t>
+          <t>2026/07/02 22:17:58</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.8452483, -70.5986783</t>
+          <t>-32.879225, -70.6087949</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.84525, -70.59868</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/02 21:41:37</t>
+          <t>2026/07/03 12:56:31</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.8345933, -70.5706366</t>
+          <t>-32.8319416, -70.5967766</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.83459, -70.57064</t>
+          <t>-32.83194, -70.59678</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>00:37:07</t>
+          <t>14:38:33</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.95</v>
+        <v>7.74</v>
       </c>
       <c r="M124" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="N124" t="n">
         <v>21</v>
@@ -7671,70 +7671,70 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/02 21:42:52</t>
+          <t>2026/07/03 11:49:26</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-32.8345683, -70.5706116</t>
+          <t>-33.3672966, -70.6958899</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-32.83457, -70.57061</t>
+          <t>-33.36730, -70.69589</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/02 22:16:43</t>
+          <t>2026/07/04 22:41:12</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-32.8793333, -70.6089049</t>
+          <t>-33.3672966, -70.6958899</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-32.87933, -70.60890</t>
+          <t>-33.36730, -70.69589</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>00:33:51</t>
+          <t>34:51:46</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>9.69</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,165 +7743,165 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/02 22:17:58</t>
+          <t>2026/07/03 14:17:56</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-32.879225, -70.6087949</t>
+          <t>-33.3595616, -70.8090049</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-33.35956, -70.80900</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/03 12:56:31</t>
+          <t>2026/07/03 14:28:37</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-32.8319416, -70.5967766</t>
+          <t>-33.3601516, -70.807085</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-32.83194, -70.59678</t>
+          <t>-33.36015, -70.80709</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>14:38:33</t>
+          <t>00:10:41</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>7.74</v>
+        <v>0.29</v>
       </c>
       <c r="M126" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="N126" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/07/03 11:49:26</t>
+          <t>2026/07/03 14:29:52</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-33.3672966, -70.6958899</t>
+          <t>-33.3600166, -70.8069183</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69589</t>
+          <t>-33.36002, -70.80692</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/03 23:49:36</t>
+          <t>2026/07/03 15:13:44</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-33.3672966, -70.6958899</t>
+          <t>-33.3665599, -70.6955966</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69589</t>
+          <t>-33.36656, -70.69560</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>12:00:10</t>
+          <t>00:43:52</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>13.92</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/07/03 14:17:56</t>
+          <t>2026/07/03 15:00:11</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-33.3595616, -70.8090049</t>
+          <t>-32.840477, -70.964531</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-33.35956, -70.80900</t>
+          <t>-32.84048, -70.96453</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/03 14:28:37</t>
+          <t>2026/07/03 15:16:03</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-33.3601516, -70.807085</t>
+          <t>-32.840579, -70.964609</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80709</t>
+          <t>-32.84058, -70.96461</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>00:10:41</t>
+          <t>00:15:52</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0.29</v>
+        <v>0.02</v>
       </c>
       <c r="M128" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,106 +7920,106 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/07/03 14:29:52</t>
+          <t>2026/07/03 15:14:18</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-33.3600166, -70.8069183</t>
+          <t>-33.3665483, -70.695875</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80692</t>
+          <t>-33.36655, -70.69588</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/03 15:13:44</t>
+          <t>2026/07/03 16:17:44</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-33.3665599, -70.6955966</t>
+          <t>-33.4159316, -70.6119666</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-33.36656, -70.69560</t>
+          <t>-33.41593, -70.61197</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>00:43:52</t>
+          <t>01:03:26</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>13.92</v>
+        <v>12.12</v>
       </c>
       <c r="M129" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="N129" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/07/03 15:00:11</t>
+          <t>2026/07/03 16:18:59</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-32.840477, -70.964531</t>
+          <t>-33.41755, -70.61364</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-32.84048, -70.96453</t>
+          <t>-33.41755, -70.61364</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/07/03 15:16:03</t>
+          <t>2026/07/03 16:31:06</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-32.840579, -70.964609</t>
+          <t>-33.4362766, -70.6296133</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-32.84058, -70.96461</t>
+          <t>-33.43628, -70.62961</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>00:15:52</t>
+          <t>00:12:07</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0.02</v>
+        <v>2.76</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="N130" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131">
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8038,116 +8038,116 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/07/03 15:14:18</t>
+          <t>2026/07/03 16:32:01</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-33.3665483, -70.695875</t>
+          <t>-33.437295, -70.6293983</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-33.36655, -70.69588</t>
+          <t>-33.43729, -70.62940</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/03 16:17:44</t>
+          <t>2026/07/04 15:45:53</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-33.4159316, -70.6119666</t>
+          <t>-33.3841349, -70.621735</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-33.41593, -70.61197</t>
+          <t>-33.38413, -70.62174</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>01:03:26</t>
+          <t>23:13:52</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>12.12</v>
+        <v>12.52</v>
       </c>
       <c r="M131" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N131" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/07/03 16:18:59</t>
+          <t>2026/07/04 12:42:53</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-33.41755, -70.61364</t>
+          <t>-32.743075, -70.7297533</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-33.41755, -70.61364</t>
+          <t>-32.74307, -70.72975</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/03 16:31:06</t>
+          <t>2026/07/04 12:49:08</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-33.4362766, -70.6296133</t>
+          <t>-32.74303, -70.7298016</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62961</t>
+          <t>-32.74303, -70.72980</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>00:12:07</t>
+          <t>00:06:15</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.76</v>
+        <v>0.01</v>
       </c>
       <c r="M132" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,37 +8156,37 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/07/03 16:32:01</t>
+          <t>2026/07/04 12:49:23</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-33.437295, -70.6293983</t>
+          <t>-32.7430266, -70.7298083</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-33.43729, -70.62940</t>
+          <t>-32.74303, -70.72981</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/03 22:32:01</t>
+          <t>2026/07/04 22:49:23</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-33.437295, -70.6293983</t>
+          <t>-32.7430266, -70.7298083</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-33.43729, -70.62940</t>
+          <t>-32.74303, -70.72981</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -8202,11 +8202,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8215,47 +8215,47 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/07/03 17:55:58</t>
+          <t>2026/07/04 14:46:55</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-32.8791833, -70.6087016</t>
+          <t>-33.0872766, -71.3623033</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60870</t>
+          <t>-33.08728, -71.36230</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/03 23:38:36</t>
+          <t>2026/07/04 20:51:57</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-32.8791883, -70.608695</t>
+          <t>-33.0872983, -71.3623833</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60869</t>
+          <t>-33.08730, -71.36238</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>05:42:38</t>
+          <t>06:05:02</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8274,37 +8274,37 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/07/03 18:20:17</t>
+          <t>2026/07/04 17:23:45</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-32.7976183, -70.887105</t>
+          <t>-32.7976233, -70.8871516</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88711</t>
+          <t>-32.79762, -70.88715</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/07/03 22:20:17</t>
+          <t>2026/07/04 21:25:06</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-32.7976183, -70.887105</t>
+          <t>-32.7976133, -70.887105</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88711</t>
+          <t>-32.79761, -70.88711</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>04:01:21</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -8320,7 +8320,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -8333,41 +8333,41 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/07/03 19:45:56</t>
+          <t>2026/07/04 18:00:43</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-32.7431983, -70.7296233</t>
+          <t>-33.4760866, -70.6985016</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-32.74320, -70.72962</t>
+          <t>-33.47609, -70.69850</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/07/03 23:46:58</t>
+          <t>2026/07/04 22:00:43</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-32.7430383, -70.7297633</t>
+          <t>-33.4760866, -70.6985016</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-32.74304, -70.72976</t>
+          <t>-33.47609, -70.69850</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>04:01:02</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -8379,11 +8379,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8392,37 +8392,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026/07/03 22:00:28</t>
+          <t>2026/07/04 18:01:58</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-32.841732, -70.936767</t>
+          <t>-32.87922, -70.608745</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-32.84173, -70.93677</t>
+          <t>-32.87922, -70.60874</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/03 23:06:40</t>
+          <t>2026/07/04 22:01:58</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-32.841732, -70.936767</t>
+          <t>-32.87922, -70.608745</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>-32.84173, -70.93677</t>
+          <t>-32.87922, -70.60874</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>01:06:12</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8432,6 +8432,183 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026/07/04 20:25:26</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-33.4363883, -70.6291633</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-33.43639, -70.62916</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026/07/04 22:25:33</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-33.4363883, -70.6291633</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-33.43639, -70.62916</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>02:00:07</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>5</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026/07/04 20:52:25</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-33.0872366, -71.3622716</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-33.08724, -71.36227</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026/07/04 22:52:25</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-33.0872366, -71.3622716</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-33.08724, -71.36227</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>8</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026/07/04 21:35:55</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-32.841836, -70.936884</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-32.84184, -70.93688</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026/07/04 22:38:58</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-32.841836, -70.936884</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-32.84184, -70.93688</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>01:03:03</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8483,10 +8660,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1434.99</v>
+        <v>1565.81</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8502,10 +8679,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>663.73</v>
+        <v>749.15</v>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -8521,13 +8698,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>298.51</v>
+        <v>313.86</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>129</v>
@@ -8540,13 +8717,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>831.21</v>
+        <v>1045.89</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>126</v>
@@ -8584,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -8641,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -8711,13 +8888,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>940.05</v>
+        <v>929.22</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>122</v>
@@ -8730,10 +8907,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>872.85</v>
+        <v>773.34</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -8806,10 +8983,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>592.33</v>
+        <v>567.87</v>
       </c>
       <c r="C19" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -8825,10 +9002,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>859.55</v>
+        <v>769.6900000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/04 22:01:37</t>
+          <t>2026/07/04 23:01:21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>166:00:21</t>
+          <t>167:00:05</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/04 22:13:16</t>
+          <t>2026/07/04 23:13:36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:20</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/04 22:56:09</t>
+          <t>2026/07/04 23:56:09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>166:02:34</t>
+          <t>167:02:34</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/04 21:57:38</t>
+          <t>2026/07/04 23:57:21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>164:59:30</t>
+          <t>166:59:13</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/04 22:11:47</t>
+          <t>2026/07/04 23:11:32</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>100:42:13</t>
+          <t>101:41:58</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/07/04 21:25:06</t>
+          <t>2026/07/04 23:25:06</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>04:01:21</t>
+          <t>06:01:21</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/07/04 22:38:58</t>
+          <t>2026/07/04 23:38:58</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>01:03:03</t>
+          <t>02:03:03</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -8609,6 +8609,65 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>10</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026/07/04 21:52:40</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-32.780851, -70.981255</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-32.78085, -70.98126</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026/07/04 23:50:10</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-32.780851, -70.981255</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-32.78085, -70.98126</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>01:57:30</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8685,7 +8744,7 @@
         <v>53</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>141</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/06/28 04:00:00   Hasta : 2026/07/05 03:59:59</t>
+          <t>Desde : 2026/06/29 04:00:00   Hasta : 2026/07/06 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/06/28 00:01:16</t>
+          <t>2026/06/29 00:01:44</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.345961, -71.125867</t>
+          <t>-34.345991, -71.125811</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12587</t>
+          <t>-34.34599, -71.12581</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/04 23:01:21</t>
+          <t>2026/07/05 23:01:38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,11 +575,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>167:00:05</t>
+          <t>166:59:54</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,53 +604,53 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/06/28 00:01:41</t>
+          <t>2026/06/29 00:11:15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-32.7430083, -70.7298233</t>
+          <t>-34.20543, -70.67739</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-32.74301, -70.72982</t>
+          <t>-34.20543, -70.67739</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/06/28 14:14:55</t>
+          <t>2026/06/30 16:59:54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-32.74311, -70.7297249</t>
+          <t>-34.205234, -70.680382</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.74311, -70.72972</t>
+          <t>-34.20523, -70.68038</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14:13:14</t>
+          <t>40:48:39</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -658,58 +658,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/06/28 00:05:34</t>
+          <t>2026/06/29 00:13:25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-32.8790583, -70.6093816</t>
+          <t>-33.360039, -70.807034</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-32.87906, -70.60938</t>
+          <t>-33.36004, -70.80703</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/06/28 11:00:25</t>
+          <t>2026/07/05 23:13:23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-32.8663783, -70.6238599</t>
+          <t>-33.360001, -70.807037</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.86638, -70.62386</t>
+          <t>-33.36000, -70.80704</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10:54:51</t>
+          <t>166:59:58</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.87</v>
+        <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -722,53 +722,53 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/06/28 00:08:09</t>
+          <t>2026/06/29 00:14:01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.3665816, -70.6957783</t>
+          <t>-33.360057, -70.807151</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69578</t>
+          <t>-33.36006, -70.80715</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/03 11:48:11</t>
+          <t>2026/06/30 11:39:26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.3673166, -70.6955883</t>
+          <t>-33.360734, -70.809006</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.36732, -70.69559</t>
+          <t>-33.36073, -70.80901</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>131:40:02</t>
+          <t>35:25:25</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>36.77</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -776,58 +776,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/06/28 00:13:16</t>
+          <t>2026/06/29 00:15:11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.360039, -70.807034</t>
+          <t>-32.74303, -70.7297999</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80703</t>
+          <t>-32.74303, -70.72980</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/04 23:13:36</t>
+          <t>2026/07/01 07:51:22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.360042, -70.80706</t>
+          <t>-33.35998, -70.806935</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80706</t>
+          <t>-33.35998, -70.80693</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>167:00:20</t>
+          <t>55:36:11</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.04</v>
+        <v>89.81</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/06/28 00:13:50</t>
+          <t>2026/06/29 00:17:48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.360057, -70.807151</t>
+          <t>-32.7976283, -70.8870716</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.36006, -70.80715</t>
+          <t>-32.79763, -70.88707</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/06/30 11:39:26</t>
+          <t>2026/06/29 08:14:08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.360734, -70.809006</t>
+          <t>-32.7976533, -70.8874083</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.36073, -70.80901</t>
+          <t>-32.79765, -70.88741</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>59:25:36</t>
+          <t>07:56:20</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>19.86</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/06/28 00:31:47</t>
+          <t>2026/06/29 00:25:20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.899863, -71.429125</t>
+          <t>-32.838362, -70.955502</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.89986, -71.42912</t>
+          <t>-32.83836, -70.95550</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/01 08:15:25</t>
+          <t>2026/06/29 11:42:44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.899941, -71.429577</t>
+          <t>-32.841711, -70.954081</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.89994, -71.42958</t>
+          <t>-32.84171, -70.95408</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>79:43:38</t>
+          <t>11:17:24</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.06</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,52 +953,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/06/28 00:31:53</t>
+          <t>2026/06/29 00:31:38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.205399, -70.67729</t>
+          <t>-33.899863, -71.429125</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67729</t>
+          <t>-33.89986, -71.42912</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/06/30 16:59:54</t>
+          <t>2026/07/01 08:15:25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.205234, -70.680382</t>
+          <t>-33.899941, -71.429577</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.20523, -70.68038</t>
+          <t>-33.89994, -71.42958</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>64:28:01</t>
+          <t>55:43:47</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.46</v>
+        <v>0.06</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/06/28 00:34:42</t>
+          <t>2026/06/29 00:34:40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-34.579844, -70.961378</t>
+          <t>-34.579515, -70.961388</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-34.57984, -70.96138</t>
+          <t>-34.57952, -70.96139</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1047,11 +1047,11 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25:02:37</t>
+          <t>01:02:39</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
@@ -1063,7 +1063,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,58 +1071,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/06/28 00:38:35</t>
+          <t>2026/06/29 00:34:52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.367472, -70.696453</t>
+          <t>-33.4760666, -70.6985233</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.36747, -70.69645</t>
+          <t>-33.47607, -70.69852</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/06/28 01:41:03</t>
+          <t>2026/06/29 20:00:07</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.368129, -70.696085</t>
+          <t>-33.3895183, -70.6738483</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.36813, -70.69608</t>
+          <t>-33.38952, -70.67385</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01:02:28</t>
+          <t>19:25:15</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.08</v>
+        <v>15.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,58 +1130,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/06/28 00:45:56</t>
+          <t>2026/06/29 00:40:45</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-34.876438, -71.127209</t>
+          <t>-33.368129, -70.696085</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-34.87644, -71.12721</t>
+          <t>-33.36813, -70.69608</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/06/29 01:25:19</t>
+          <t>2026/06/30 01:41:05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-34.876375, -71.127119</t>
+          <t>-33.367112, -70.696652</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-34.87638, -71.12712</t>
+          <t>-33.36711, -70.69665</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24:39:23</t>
+          <t>25:00:20</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,52 +1189,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/06/28 00:46:00</t>
+          <t>2026/06/29 00:45:58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-32.780847, -70.98129</t>
+          <t>-34.876438, -71.127209</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-32.78085, -70.98129</t>
+          <t>-34.87644, -71.12721</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/06/28 01:41:15</t>
+          <t>2026/06/29 01:25:19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-32.785697, -70.960385</t>
+          <t>-34.876375, -71.127119</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.78570, -70.96039</t>
+          <t>-34.87638, -71.12712</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>00:55:15</t>
+          <t>00:39:21</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>0.01</v>
       </c>
       <c r="M15" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/06/28 00:48:54</t>
+          <t>2026/06/29 00:54:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-32.841804, -70.936878</t>
+          <t>-32.841725, -70.93688</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-32.84180, -70.93688</t>
+          <t>-32.84172, -70.93688</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/06/28 10:55:29</t>
+          <t>2026/06/29 11:05:29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-32.83853, -70.953887</t>
+          <t>-32.841556, -70.959284</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-32.83853, -70.95389</t>
+          <t>-32.84156, -70.95928</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10:06:35</t>
+          <t>10:10:36</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,58 +1307,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/06/28 00:51:36</t>
+          <t>2026/06/29 00:56:10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-36.9038983, -73.0297049</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-36.90390, -73.02970</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/06/28 13:39:00</t>
+          <t>2026/07/05 22:56:09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-36.8459166, -73.0518549</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-36.84592, -73.05185</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12:47:24</t>
+          <t>165:59:59</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,37 +1371,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/06/28 00:53:35</t>
+          <t>2026/06/29 00:59:08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.042665, -70.681745</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.04266, -70.68175</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/04 23:56:09</t>
+          <t>2026/07/05 22:57:39</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.04266, -70.681752</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.04266, -70.68175</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>167:02:34</t>
+          <t>165:58:31</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1417,7 +1417,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,58 +1425,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/06/28 00:58:08</t>
+          <t>2026/06/29 01:06:59</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-34.042665, -70.681745</t>
+          <t>-33.0871366, -71.3621566</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68175</t>
+          <t>-33.08714, -71.36216</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/04 23:57:21</t>
+          <t>2026/06/30 09:33:52</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-34.04266, -70.681752</t>
+          <t>-33.04526, -71.41807</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68175</t>
+          <t>-33.04526, -71.41807</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>166:59:13</t>
+          <t>32:26:53</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>11.24</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/06/28 01:06:59</t>
+          <t>2026/06/29 01:15:47</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.0871366, -71.3621566</t>
+          <t>-32.8792283, -70.6088166</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.08714, -71.36216</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/06/30 09:33:52</t>
+          <t>2026/06/30 09:21:51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.04526, -71.41807</t>
+          <t>-32.8554583, -70.6255983</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.04526, -71.41807</t>
+          <t>-32.85546, -70.62560</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>56:26:53</t>
+          <t>32:06:04</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.24</v>
+        <v>5.26</v>
       </c>
       <c r="M20" t="n">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="N20" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,57 +1548,57 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/06/28 01:37:36</t>
+          <t>2026/06/29 01:44:31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-32.7975933, -70.8870683</t>
+          <t>-33.3665816, -70.6957783</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88707</t>
+          <t>-33.36658, -70.69578</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/06/28 10:02:13</t>
+          <t>2026/07/03 11:48:11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-32.835125, -70.6046299</t>
+          <t>-33.3673166, -70.6955883</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.83512, -70.60463</t>
+          <t>-33.36732, -70.69559</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08:24:37</t>
+          <t>106:03:40</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>32.97</v>
+        <v>36.77</v>
       </c>
       <c r="M21" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="N21" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1607,112 +1607,112 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/06/28 01:41:45</t>
+          <t>2026/06/29 01:51:21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-32.785359, -70.960425</t>
+          <t>-33.4362983, -70.6294</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-32.78536, -70.96043</t>
+          <t>-33.43630, -70.62940</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/06/28 13:45:07</t>
+          <t>2026/06/29 10:10:14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-32.791566, -70.912456</t>
+          <t>-33.3665466, -70.6957333</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.79157, -70.91246</t>
+          <t>-33.36655, -70.69573</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>12:03:22</t>
+          <t>08:18:53</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.63</v>
+        <v>13.34</v>
       </c>
       <c r="M22" t="n">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="N22" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/06/28 01:54:08</t>
+          <t>2026/06/29 02:23:08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.4761199, -70.6985283</t>
+          <t>-34.876375, -71.127119</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69853</t>
+          <t>-34.87638, -71.12712</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/06/28 08:07:43</t>
+          <t>2026/07/01 08:16:05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.4761916, -70.6984216</t>
+          <t>-34.876391, -71.127306</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69842</t>
+          <t>-34.87639, -71.12731</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>06:13:35</t>
+          <t>53:52:57</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1720,58 +1720,58 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/06/28 02:40:11</t>
+          <t>2026/06/29 02:35:08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.368129, -70.696085</t>
+          <t>-34.579894, -70.961485</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-33.36813, -70.69608</t>
+          <t>-34.57989, -70.96148</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/06/30 01:41:05</t>
+          <t>2026/06/30 01:36:57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.367112, -70.696652</t>
+          <t>-34.579711, -70.961383</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.36711, -70.69665</t>
+          <t>-34.57971, -70.96138</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>47:00:54</t>
+          <t>23:01:49</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/06/28 08:08:58</t>
+          <t>2026/06/29 08:14:21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.4763233, -70.69837</t>
+          <t>-32.7975766, -70.8871033</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69837</t>
+          <t>-32.79758, -70.88710</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/06/28 08:36:46</t>
+          <t>2026/06/29 10:52:02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.3997016, -70.7920883</t>
+          <t>-32.7957083, -70.820085</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.39970, -70.79209</t>
+          <t>-32.79571, -70.82009</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>00:27:48</t>
+          <t>02:37:41</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.69</v>
+        <v>9.74</v>
       </c>
       <c r="M25" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="N25" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/06/28 08:38:01</t>
+          <t>2026/06/29 10:10:25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.39722, -70.7921483</t>
+          <t>-33.3665683, -70.6957399</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.39722, -70.79215</t>
+          <t>-33.36657, -70.69574</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/06/28 09:29:41</t>
+          <t>2026/06/29 17:20:26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.3895033, -70.6738583</t>
+          <t>-33.4360616, -70.6299533</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.38950, -70.67386</t>
+          <t>-33.43606, -70.62995</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>00:51:40</t>
+          <t>07:10:01</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>21.18</v>
+        <v>13.58</v>
       </c>
       <c r="M26" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N26" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,47 +1902,47 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/06/28 09:30:24</t>
+          <t>2026/06/29 10:52:06</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.3892816, -70.67405</t>
+          <t>-32.795725, -70.8200833</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.38928, -70.67405</t>
+          <t>-32.79572, -70.82008</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/06/28 10:33:10</t>
+          <t>2026/06/29 10:57:29</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.4762366, -70.6982866</t>
+          <t>-32.795725, -70.82015</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69829</t>
+          <t>-32.79572, -70.82015</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01:02:46</t>
+          <t>00:05:23</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>13.55</v>
+        <v>0.05</v>
       </c>
       <c r="M27" t="n">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="N27" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/06/28 10:02:48</t>
+          <t>2026/06/29 10:57:35</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.8352783, -70.6044299</t>
+          <t>-32.7958066, -70.8200916</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.83528, -70.60443</t>
+          <t>-32.79581, -70.82009</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/06/28 13:16:25</t>
+          <t>2026/06/29 13:04:02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.8830583, -70.6125433</t>
+          <t>-32.79773, -70.8874133</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.88306, -70.61254</t>
+          <t>-32.79773, -70.88741</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03:13:37</t>
+          <t>02:06:27</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.529999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="N28" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,47 +2020,47 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/06/28 10:34:25</t>
+          <t>2026/06/29 11:06:23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-33.4760666, -70.6985233</t>
+          <t>-32.841837, -70.95827</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-33.47607, -70.69852</t>
+          <t>-32.84184, -70.95827</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/06/29 20:00:07</t>
+          <t>2026/06/29 11:28:20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-33.3895183, -70.6738483</t>
+          <t>-32.838559, -70.953959</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-33.38952, -70.67385</t>
+          <t>-32.83856, -70.95396</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>33:25:42</t>
+          <t>00:21:57</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>15.4</v>
+        <v>0.89</v>
       </c>
       <c r="M29" t="n">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,57 +2079,57 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/06/28 10:55:47</t>
+          <t>2026/06/29 11:29:05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-32.838731, -70.954033</t>
+          <t>-32.838807, -70.954103</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-32.83873, -70.95403</t>
+          <t>-32.83881, -70.95410</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/06/28 11:52:17</t>
+          <t>2026/06/29 11:38:20</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-32.84283, -70.936869</t>
+          <t>-32.84091, -70.957519</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.84283, -70.93687</t>
+          <t>-32.84091, -70.95752</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:56:30</t>
+          <t>00:09:15</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>0.47</v>
       </c>
       <c r="M30" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="N30" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/06/28 11:01:40</t>
+          <t>2026/06/29 11:39:20</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-32.8661383, -70.6240233</t>
+          <t>-32.840656, -70.958645</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-32.86614, -70.62402</t>
+          <t>-32.84066, -70.95865</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/06/28 11:22:45</t>
+          <t>2026/06/29 12:00:59</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-32.8723833, -70.6029383</t>
+          <t>-32.843904, -70.936953</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.87238, -70.60294</t>
+          <t>-32.84390, -70.93695</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:21:05</t>
+          <t>00:21:39</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="M31" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="N31" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/06/28 11:24:00</t>
+          <t>2026/06/29 11:43:17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-32.8754433, -70.6031666</t>
+          <t>-32.84171, -70.954052</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-32.87544, -70.60317</t>
+          <t>-32.84171, -70.95405</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/06/28 11:35:53</t>
+          <t>2026/06/29 12:07:01</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-32.87919, -70.6089266</t>
+          <t>-32.840325, -70.95904</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60893</t>
+          <t>-32.84032, -70.95904</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:11:53</t>
+          <t>00:23:44</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.04</v>
+        <v>0.51</v>
       </c>
       <c r="M32" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,53 +2256,53 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/06/28 11:36:36</t>
+          <t>2026/06/29 12:01:56</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.8790466, -70.6093933</t>
+          <t>-32.841963, -70.936835</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.87905, -70.60939</t>
+          <t>-32.84196, -70.93684</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/06/28 19:03:31</t>
+          <t>2026/06/29 16:23:35</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-32.8791316, -70.6092916</t>
+          <t>-32.841948, -70.936818</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.87913, -70.60929</t>
+          <t>-32.84195, -70.93682</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>07:26:55</t>
+          <t>04:21:39</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.01</v>
+        <v>5.7</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/06/28 11:53:17</t>
+          <t>2026/06/29 12:07:28</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.841833, -70.936834</t>
+          <t>-32.840357, -70.959035</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.84183, -70.93683</t>
+          <t>-32.84036, -70.95904</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/06/28 16:43:56</t>
+          <t>2026/06/29 12:52:02</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.839208, -70.949417</t>
+          <t>-32.839729, -70.954579</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.83921, -70.94942</t>
+          <t>-32.83973, -70.95458</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>04:50:39</t>
+          <t>00:44:34</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.81</v>
+        <v>0.54</v>
       </c>
       <c r="M34" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,57 +2374,57 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/06/28 13:17:40</t>
+          <t>2026/06/29 12:52:36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.8829683, -70.612425</t>
+          <t>-32.838769, -70.954098</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.88297, -70.61243</t>
+          <t>-32.83877, -70.95410</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/06/28 14:17:30</t>
+          <t>2026/06/29 13:16:08</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.7976399, -70.8871449</t>
+          <t>-32.838376, -70.956088</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.79764, -70.88714</t>
+          <t>-32.83838, -70.95609</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:59:50</t>
+          <t>00:23:32</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>41.43</v>
+        <v>0.43</v>
       </c>
       <c r="M35" t="n">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="N35" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,47 +2433,47 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/06/28 13:40:15</t>
+          <t>2026/06/29 13:04:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-36.8464016, -73.0517766</t>
+          <t>-32.7976166, -70.8870666</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-36.84640, -73.05178</t>
+          <t>-32.79762, -70.88707</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/06/28 14:28:59</t>
+          <t>2026/06/29 13:59:43</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-36.9039616, -73.0282216</t>
+          <t>-32.7976933, -70.8873666</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-36.90396, -73.02822</t>
+          <t>-32.79769, -70.88737</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:48:44</t>
+          <t>00:55:00</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.94</v>
+        <v>19.64</v>
       </c>
       <c r="M36" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N36" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/06/28 13:45:10</t>
+          <t>2026/06/29 13:17:08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-32.791579, -70.912464</t>
+          <t>-32.838383, -70.955475</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-32.79158, -70.91246</t>
+          <t>-32.83838, -70.95548</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/06/28 19:01:05</t>
+          <t>2026/06/29 14:58:23</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-32.785691, -70.96037</t>
+          <t>-32.838384, -70.956177</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-32.78569, -70.96037</t>
+          <t>-32.83838, -70.95618</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>05:15:55</t>
+          <t>01:41:15</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.61</v>
+        <v>2.09</v>
       </c>
       <c r="M37" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="N37" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/06/28 14:15:11</t>
+          <t>2026/06/29 14:00:24</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-32.74303, -70.7297999</t>
+          <t>-32.7975833, -70.8870766</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72980</t>
+          <t>-32.79758, -70.88708</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/07/01 07:51:22</t>
+          <t>2026/06/30 09:05:06</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.35998, -70.806935</t>
+          <t>-33.3672816, -70.696575</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80693</t>
+          <t>-33.36728, -70.69657</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>65:36:11</t>
+          <t>19:04:42</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>89.81</v>
+        <v>100.14</v>
       </c>
       <c r="M38" t="n">
         <v>108</v>
       </c>
       <c r="N38" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/06/28 14:17:48</t>
+          <t>2026/06/29 14:59:06</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-32.7976283, -70.8870716</t>
+          <t>-32.838392, -70.95548</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-32.79763, -70.88707</t>
+          <t>-32.83839, -70.95548</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/06/29 08:14:08</t>
+          <t>2026/06/29 16:39:52</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-32.7976533, -70.8874083</t>
+          <t>-32.790935, -70.976063</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-32.79765, -70.88741</t>
+          <t>-32.79093, -70.97606</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>17:56:20</t>
+          <t>01:40:46</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19.86</v>
+        <v>12.74</v>
       </c>
       <c r="M39" t="n">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="N39" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/06/28 14:29:35</t>
+          <t>2026/06/29 16:24:23</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-36.9039266, -73.0296516</t>
+          <t>-32.841823, -70.936828</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-36.90393, -73.02965</t>
+          <t>-32.84182, -70.93683</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/06/28 21:51:07</t>
+          <t>2026/06/29 17:37:56</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-33.4362766, -70.6294433</t>
+          <t>-32.841791, -70.936887</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62944</t>
+          <t>-32.84179, -70.93689</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>07:21:32</t>
+          <t>01:13:33</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>510.12</v>
+        <v>5.67</v>
       </c>
       <c r="M40" t="n">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="N40" t="n">
-        <v>109</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/06/28 16:44:54</t>
+          <t>2026/06/29 16:40:09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-32.839819, -70.949986</t>
+          <t>-32.790901, -70.975998</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-32.83982, -70.94999</t>
+          <t>-32.79090, -70.97600</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/06/28 16:59:47</t>
+          <t>2026/06/29 20:25:50</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-32.847954, -70.925078</t>
+          <t>-32.838377, -70.9561</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-32.84795, -70.92508</t>
+          <t>-32.83838, -70.95610</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:14:53</t>
+          <t>03:45:41</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.51</v>
+        <v>12.75</v>
       </c>
       <c r="M41" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="N41" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/06/28 17:00:08</t>
+          <t>2026/06/29 17:20:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-32.84784, -70.925064</t>
+          <t>-33.4362549, -70.6294316</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-32.84784, -70.92506</t>
+          <t>-33.43625, -70.62943</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/06/28 20:34:14</t>
+          <t>2026/06/30 10:00:03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-32.841937, -70.936854</t>
+          <t>-33.3661566, -70.6955316</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-32.84194, -70.93685</t>
+          <t>-33.36616, -70.69553</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>03:34:06</t>
+          <t>16:39:10</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.63</v>
+        <v>13.22</v>
       </c>
       <c r="M42" t="n">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="N42" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/06/28 19:02:01</t>
+          <t>2026/06/29 17:38:08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-32.78549, -70.960404</t>
+          <t>-32.841766, -70.936884</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-32.78549, -70.96040</t>
+          <t>-32.84177, -70.93688</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/06/28 21:27:15</t>
+          <t>2026/06/29 20:25:38</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-32.838362, -70.955502</t>
+          <t>-32.838756, -70.954083</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95550</t>
+          <t>-32.83876, -70.95408</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02:25:14</t>
+          <t>02:47:30</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>12.17</v>
+        <v>2.28</v>
       </c>
       <c r="M43" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="N43" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,47 +2905,47 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/06/28 19:04:46</t>
+          <t>2026/06/29 20:00:47</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-32.879205, -70.6088333</t>
+          <t>-33.3893183, -70.6740566</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60883</t>
+          <t>-33.38932, -70.67406</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/06/30 09:21:51</t>
+          <t>2026/06/29 21:30:44</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-32.8554583, -70.6255983</t>
+          <t>-33.4762749, -70.6983333</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-32.85546, -70.62560</t>
+          <t>-33.47627, -70.69833</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>38:17:05</t>
+          <t>01:29:57</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.26</v>
+        <v>13.58</v>
       </c>
       <c r="M44" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="N44" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/06/28 20:35:14</t>
+          <t>2026/06/29 20:26:19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-32.841795, -70.93679</t>
+          <t>-32.838768, -70.954088</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-32.84179, -70.93679</t>
+          <t>-32.83877, -70.95409</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/06/28 20:56:02</t>
+          <t>2026/06/29 21:28:53</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-32.838505, -70.953947</t>
+          <t>-32.83699, -70.967114</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-32.83850, -70.95395</t>
+          <t>-32.83699, -70.96711</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:20:48</t>
+          <t>01:02:34</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.27</v>
+        <v>4.04</v>
       </c>
       <c r="M45" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="N45" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/06/28 20:56:14</t>
+          <t>2026/06/29 20:26:42</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-32.83871, -70.954071</t>
+          <t>-32.838376, -70.955488</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-32.83871, -70.95407</t>
+          <t>-32.83838, -70.95549</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/06/28 21:51:35</t>
+          <t>2026/06/30 10:05:36</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-32.84175, -70.936885</t>
+          <t>-32.840312, -70.964487</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-32.84175, -70.93689</t>
+          <t>-32.84031, -70.96449</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:55:21</t>
+          <t>13:38:54</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="N46" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/06/28 21:27:50</t>
+          <t>2026/06/29 21:29:08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-32.838362, -70.955502</t>
+          <t>-32.836961, -70.96723</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95550</t>
+          <t>-32.83696, -70.96723</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/06/29 11:42:44</t>
+          <t>2026/06/29 21:44:29</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-32.841711, -70.954081</t>
+          <t>-32.841762, -70.936846</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-32.84171, -70.95408</t>
+          <t>-32.84176, -70.93685</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14:14:54</t>
+          <t>00:15:21</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.19</v>
+        <v>3.54</v>
       </c>
       <c r="M47" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="N47" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,47 +3141,47 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/06/28 21:51:21</t>
+          <t>2026/06/29 21:30:50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.4362983, -70.6294</t>
+          <t>-33.4762966, -70.6983666</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.43630, -70.62940</t>
+          <t>-33.47630, -70.69837</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/06/29 10:10:14</t>
+          <t>2026/06/29 21:56:48</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.3665466, -70.6957333</t>
+          <t>-33.3895133, -70.6738416</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.36655, -70.69573</t>
+          <t>-33.38951, -70.67384</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12:18:53</t>
+          <t>00:25:58</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>13.34</v>
+        <v>15.42</v>
       </c>
       <c r="M48" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="N48" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/06/28 21:51:51</t>
+          <t>2026/06/29 21:44:49</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.841725, -70.93688</t>
+          <t>-32.841646, -70.936791</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.84172, -70.93688</t>
+          <t>-32.84165, -70.93679</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/06/29 11:05:29</t>
+          <t>2026/06/30 09:23:43</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.841556, -70.959284</t>
+          <t>-33.482129, -70.765257</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.84156, -70.95928</t>
+          <t>-33.48213, -70.76526</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>13:13:38</t>
+          <t>11:38:54</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>100.91</v>
       </c>
       <c r="M49" t="n">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="N49" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/06/29 14:00:24</t>
+          <t>2026/06/29 21:57:31</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-32.7975833, -70.8870766</t>
+          <t>-33.3892866, -70.6740033</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88708</t>
+          <t>-33.38929, -70.67400</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/06/30 09:05:06</t>
+          <t>2026/06/29 22:50:09</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.696575</t>
+          <t>-33.4762083, -70.6984266</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69657</t>
+          <t>-33.47621, -70.69843</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19:04:42</t>
+          <t>00:52:38</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>100.14</v>
+        <v>13.53</v>
       </c>
       <c r="M50" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="N50" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,116 +3318,116 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/06/29 16:40:09</t>
+          <t>2026/06/29 22:51:24</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-32.790901, -70.975998</t>
+          <t>-33.4761316, -70.6985133</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-32.79090, -70.97600</t>
+          <t>-33.47613, -70.69851</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/06/29 20:25:50</t>
+          <t>2026/06/30 10:05:57</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-32.838377, -70.9561</t>
+          <t>-33.389525, -70.6739083</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95610</t>
+          <t>-33.38952, -70.67391</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>03:45:41</t>
+          <t>11:14:33</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>12.75</v>
+        <v>14.94</v>
       </c>
       <c r="M51" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="N51" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/06/29 20:26:42</t>
+          <t>2026/06/30 02:39:27</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-32.838376, -70.955488</t>
+          <t>-33.367112, -70.696652</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95549</t>
+          <t>-33.36711, -70.69665</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/06/30 10:05:36</t>
+          <t>2026/07/04 02:41:38</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-32.840312, -70.964487</t>
+          <t>-33.367244, -70.696732</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-32.84031, -70.96449</t>
+          <t>-33.36724, -70.69673</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13:38:54</t>
+          <t>96:02:11</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.57</v>
+        <v>0.09</v>
       </c>
       <c r="M52" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,47 +3436,47 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/06/29 21:44:49</t>
+          <t>2026/06/30 09:34:11</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-32.841646, -70.936791</t>
+          <t>-32.866165, -70.6240133</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-32.84165, -70.93679</t>
+          <t>-32.86617, -70.62401</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/06/30 09:23:43</t>
+          <t>2026/06/30 10:13:42</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.482129, -70.765257</t>
+          <t>-32.8824616, -70.6113033</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.48213, -70.76526</t>
+          <t>-32.88246, -70.61130</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>11:38:54</t>
+          <t>00:39:31</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>100.91</v>
+        <v>4.73</v>
       </c>
       <c r="M53" t="n">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="N53" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -3600,7 +3600,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3613,112 +3613,112 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/06/30 10:28:39</t>
+          <t>2026/06/30 10:14:22</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-33.0448016, -71.4202366</t>
+          <t>-32.8832383, -70.6113449</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-33.04480, -71.42024</t>
+          <t>-32.88324, -70.61134</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/06/30 10:58:00</t>
+          <t>2026/06/30 10:31:09</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-33.0873283, -71.362295</t>
+          <t>-32.8792133, -70.60893</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36230</t>
+          <t>-32.87921, -70.60893</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:29:21</t>
+          <t>00:16:47</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>10.54</v>
+        <v>0.84</v>
       </c>
       <c r="M56" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="N56" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/06/30 10:57:04</t>
+          <t>2026/06/30 10:28:39</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-32.840354, -70.964574</t>
+          <t>-33.0448016, -71.4202366</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-32.84035, -70.96457</t>
+          <t>-33.04480, -71.42024</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/06/30 12:37:02</t>
+          <t>2026/06/30 10:58:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-32.840478, -70.964481</t>
+          <t>-33.0873283, -71.362295</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-32.84048, -70.96448</t>
+          <t>-33.08733, -71.36230</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01:39:58</t>
+          <t>00:29:21</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.05</v>
+        <v>10.54</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3731,47 +3731,47 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/06/30 10:59:15</t>
+          <t>2026/06/30 10:32:24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-33.0873166, -71.3623183</t>
+          <t>-32.8792383, -70.608825</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36232</t>
+          <t>-32.87924, -70.60882</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/06/30 14:38:33</t>
+          <t>2026/06/30 10:43:27</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-33.0978099, -71.3298233</t>
+          <t>-32.8824133, -70.61128</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-33.09781, -71.32982</t>
+          <t>-32.88241, -70.61128</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>03:39:18</t>
+          <t>00:11:03</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.18</v>
+        <v>0.75</v>
       </c>
       <c r="M58" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="N58" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,53 +3790,53 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/06/30 11:07:23</t>
+          <t>2026/06/30 10:43:58</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-32.8832883, -70.6113416</t>
+          <t>-32.8832483, -70.6113166</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-32.88329, -70.61134</t>
+          <t>-32.88325, -70.61132</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/06/30 12:47:23</t>
+          <t>2026/06/30 11:06:51</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-32.8824116, -70.6113149</t>
+          <t>-32.8824266, -70.6112916</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-32.88241, -70.61131</t>
+          <t>-32.88243, -70.61129</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>01:40:00</t>
+          <t>00:22:53</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>0.43</v>
       </c>
       <c r="M59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3849,41 +3849,41 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/06/30 11:54:57</t>
+          <t>2026/06/30 10:57:04</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-33.360036, -70.807118</t>
+          <t>-32.840354, -70.964574</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-32.84035, -70.96457</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/07/02 14:40:46</t>
+          <t>2026/06/30 12:37:02</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-33.359985, -70.807068</t>
+          <t>-32.840478, -70.964481</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80707</t>
+          <t>-32.84048, -70.96448</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>50:45:49</t>
+          <t>01:39:58</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
@@ -3895,11 +3895,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,47 +3908,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/06/30 12:48:38</t>
+          <t>2026/06/30 10:59:15</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-32.8832433, -70.6113333</t>
+          <t>-33.0873166, -71.3623183</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-32.88324, -70.61133</t>
+          <t>-33.08732, -71.36232</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/06/30 13:17:42</t>
+          <t>2026/06/30 14:38:33</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.8790866, -70.6093316</t>
+          <t>-33.0978099, -71.3298233</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.87909, -70.60933</t>
+          <t>-33.09781, -71.32982</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:29:04</t>
+          <t>03:39:18</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.48</v>
+        <v>4.18</v>
       </c>
       <c r="M61" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="N61" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,106 +3967,106 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/06/30 13:18:57</t>
+          <t>2026/06/30 11:07:23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-32.8792016, -70.6088499</t>
+          <t>-32.8832883, -70.6113416</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60885</t>
+          <t>-32.88329, -70.61134</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/06/30 13:53:46</t>
+          <t>2026/06/30 12:47:23</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-32.8296016, -70.6116533</t>
+          <t>-32.8824116, -70.6113149</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-32.82960, -70.61165</t>
+          <t>-32.88241, -70.61131</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:34:49</t>
+          <t>01:40:00</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>8.76</v>
+        <v>0.43</v>
       </c>
       <c r="M62" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="N62" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/06/30 13:42:35</t>
+          <t>2026/06/30 11:54:57</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-33.4763033, -70.6983916</t>
+          <t>-33.360036, -70.807118</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-33.47630, -70.69839</t>
+          <t>-33.36004, -70.80712</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/06/30 14:21:26</t>
+          <t>2026/07/02 14:40:46</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-33.3893383, -70.6740283</t>
+          <t>-33.359985, -70.807068</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-33.38934, -70.67403</t>
+          <t>-33.35999, -70.80707</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:38:51</t>
+          <t>50:45:49</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>14.95</v>
+        <v>0.03</v>
       </c>
       <c r="M63" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/06/30 13:53:51</t>
+          <t>2026/06/30 12:48:38</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-32.8295516, -70.61164</t>
+          <t>-32.8832433, -70.6113333</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-32.82955, -70.61164</t>
+          <t>-32.88324, -70.61133</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/06/30 14:39:32</t>
+          <t>2026/06/30 13:17:42</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-32.87918, -70.6089183</t>
+          <t>-32.8790866, -70.6093316</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60892</t>
+          <t>-32.87909, -70.60933</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:45:41</t>
+          <t>00:29:04</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>9.5</v>
+        <v>1.48</v>
       </c>
       <c r="M64" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="N64" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,41 +4144,41 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/06/30 14:21:38</t>
+          <t>2026/06/30 13:18:57</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.38934, -70.674035</t>
+          <t>-32.8792016, -70.6088499</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.38934, -70.67404</t>
+          <t>-32.87920, -70.60885</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/06/30 15:17:53</t>
+          <t>2026/06/30 13:53:46</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.36235, -70.67012</t>
+          <t>-32.8296016, -70.6116533</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.36235, -70.67012</t>
+          <t>-32.82960, -70.61165</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:56:15</t>
+          <t>00:34:49</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>14.27</v>
+        <v>8.76</v>
       </c>
       <c r="M65" t="n">
         <v>47</v>
@@ -4190,11 +4190,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,47 +4203,47 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/06/30 14:38:52</t>
+          <t>2026/06/30 13:42:35</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-33.0976766, -71.3297416</t>
+          <t>-33.4763033, -70.6983916</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-33.09768, -71.32974</t>
+          <t>-33.47630, -70.69839</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/06/30 16:56:22</t>
+          <t>2026/06/30 14:21:26</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-33.0868266, -71.361695</t>
+          <t>-33.3893383, -70.6740283</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-33.08683, -71.36169</t>
+          <t>-33.38934, -70.67403</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>02:17:30</t>
+          <t>00:38:51</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.13</v>
+        <v>14.95</v>
       </c>
       <c r="M66" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="N66" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,47 +4262,47 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/06/30 14:39:53</t>
+          <t>2026/06/30 13:53:51</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-32.8790299, -70.6093833</t>
+          <t>-32.8295516, -70.61164</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-32.87903, -70.60938</t>
+          <t>-32.82955, -70.61164</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/06/30 18:19:01</t>
+          <t>2026/06/30 14:39:32</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-32.87913, -70.6093416</t>
+          <t>-32.87918, -70.6089183</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-32.87913, -70.60934</t>
+          <t>-32.87918, -70.60892</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>03:39:08</t>
+          <t>00:45:41</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.01</v>
+        <v>9.5</v>
       </c>
       <c r="M67" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="N67" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/06/30 15:18:15</t>
+          <t>2026/06/30 14:21:38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-33.362185, -70.6700933</t>
+          <t>-33.38934, -70.674035</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-33.36218, -70.67009</t>
+          <t>-33.38934, -70.67404</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/06/30 16:28:47</t>
+          <t>2026/06/30 15:17:53</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-33.4500183, -70.663415</t>
+          <t>-33.36235, -70.67012</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-33.45002, -70.66342</t>
+          <t>-33.36235, -70.67012</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>01:10:32</t>
+          <t>00:56:15</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>23.98</v>
+        <v>14.27</v>
       </c>
       <c r="M68" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="N68" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,57 +4380,57 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/06/30 15:37:00</t>
+          <t>2026/06/30 14:38:52</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-33.482162, -70.764856</t>
+          <t>-33.0976766, -71.3297416</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-33.48216, -70.76486</t>
+          <t>-33.09768, -71.32974</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/06/30 16:59:08</t>
+          <t>2026/06/30 16:56:22</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-33.482132, -70.765251</t>
+          <t>-33.0868266, -71.361695</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-33.48213, -70.76525</t>
+          <t>-33.08683, -71.36169</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>01:22:08</t>
+          <t>02:17:30</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.87</v>
+        <v>4.13</v>
       </c>
       <c r="M69" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,57 +4439,57 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/06/30 16:30:02</t>
+          <t>2026/06/30 14:39:53</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-33.4504183, -70.6650516</t>
+          <t>-32.8790299, -70.6093833</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-33.45042, -70.66505</t>
+          <t>-32.87903, -70.60938</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/06/30 17:08:23</t>
+          <t>2026/06/30 18:19:01</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-33.476265, -70.6983316</t>
+          <t>-32.87913, -70.6093416</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69833</t>
+          <t>-32.87913, -70.60934</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:38:21</t>
+          <t>03:39:08</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.56</v>
+        <v>0.01</v>
       </c>
       <c r="M70" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/06/30 16:57:11</t>
+          <t>2026/06/30 15:18:15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-33.0873449, -71.3622499</t>
+          <t>-33.362185, -70.6700933</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36225</t>
+          <t>-33.36218, -70.67009</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/06/30 17:24:32</t>
+          <t>2026/06/30 16:28:47</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.0444533, -71.3743799</t>
+          <t>-33.4500183, -70.663415</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.04445, -71.37438</t>
+          <t>-33.45002, -70.66342</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:27:21</t>
+          <t>01:10:32</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>6.63</v>
+        <v>23.98</v>
       </c>
       <c r="M71" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="N71" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/06/30 17:00:08</t>
+          <t>2026/06/30 16:30:02</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.482181, -70.764876</t>
+          <t>-33.4504183, -70.6650516</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76488</t>
+          <t>-33.45042, -70.66505</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/07/01 08:55:47</t>
+          <t>2026/06/30 17:08:23</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.359983, -70.807052</t>
+          <t>-33.476265, -70.6983316</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80705</t>
+          <t>-33.47626, -70.69833</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>15:55:39</t>
+          <t>00:38:21</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>19.57</v>
+        <v>5.56</v>
       </c>
       <c r="M72" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="N72" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/06/30 17:08:32</t>
+          <t>2026/06/30 16:57:11</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-33.4763216, -70.6983716</t>
+          <t>-33.0873449, -71.3622499</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69837</t>
+          <t>-33.08734, -71.36225</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/06/30 17:45:45</t>
+          <t>2026/06/30 17:24:32</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.3623483, -70.6701433</t>
+          <t>-33.0444533, -71.3743799</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.36235, -70.67014</t>
+          <t>-33.04445, -71.37438</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:37:13</t>
+          <t>00:27:21</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>18.64</v>
+        <v>6.63</v>
       </c>
       <c r="M73" t="n">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="N73" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,106 +4675,106 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/06/30 17:25:47</t>
+          <t>2026/06/30 17:00:08</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.0453866, -71.3743666</t>
+          <t>-33.482181, -70.764876</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.04539, -71.37437</t>
+          <t>-33.48218, -70.76488</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/06/30 17:43:45</t>
+          <t>2026/07/01 08:55:47</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.0583616, -71.3730366</t>
+          <t>-33.359983, -70.807052</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.05836, -71.37304</t>
+          <t>-33.35998, -70.80705</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:17:58</t>
+          <t>15:55:39</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.5</v>
+        <v>19.57</v>
       </c>
       <c r="M74" t="n">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="N74" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/06/30 17:29:34</t>
+          <t>2026/06/30 17:08:32</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-34.205411, -70.677278</t>
+          <t>-33.4763216, -70.6983716</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67728</t>
+          <t>-33.47632, -70.69837</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/04 23:11:32</t>
+          <t>2026/06/30 17:45:45</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-34.205306, -70.677463</t>
+          <t>-33.3623483, -70.6701433</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-34.20531, -70.67746</t>
+          <t>-33.36235, -70.67014</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>101:41:58</t>
+          <t>00:37:13</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.05</v>
+        <v>18.64</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76">
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,116 +4793,116 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/06/30 17:45:00</t>
+          <t>2026/06/30 17:25:47</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.0582999, -71.3728383</t>
+          <t>-33.0453866, -71.3743666</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.05830, -71.37284</t>
+          <t>-33.04539, -71.37437</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/06/30 18:03:42</t>
+          <t>2026/06/30 17:43:45</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.0873483, -71.3622933</t>
+          <t>-33.0583616, -71.3730366</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36229</t>
+          <t>-33.05836, -71.37304</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>00:18:42</t>
+          <t>00:17:58</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>4.46</v>
+        <v>1.5</v>
       </c>
       <c r="M76" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="N76" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/06/30 17:46:05</t>
+          <t>2026/06/30 17:29:34</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.362135, -70.6701833</t>
+          <t>-34.205411, -70.677278</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.36214, -70.67018</t>
+          <t>-34.20541, -70.67728</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/06/30 19:31:53</t>
+          <t>2026/07/05 23:11:30</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.38949, -70.67389</t>
+          <t>-34.205306, -70.677463</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.38949, -70.67389</t>
+          <t>-34.20531, -70.67746</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>01:45:48</t>
+          <t>125:41:56</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4.03</v>
+        <v>0.05</v>
       </c>
       <c r="M77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/06/30 18:00:06</t>
+          <t>2026/06/30 17:45:00</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-32.7853849, -70.8316733</t>
+          <t>-33.0582999, -71.3728383</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-32.78538, -70.83167</t>
+          <t>-33.05830, -71.37284</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/06/30 18:15:43</t>
+          <t>2026/06/30 18:03:42</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-32.7977249, -70.8874233</t>
+          <t>-33.0873483, -71.3622933</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88742</t>
+          <t>-33.08735, -71.36229</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:15:37</t>
+          <t>00:18:42</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>7.39</v>
+        <v>4.46</v>
       </c>
       <c r="M78" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N78" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,116 +4970,116 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/06/30 18:04:57</t>
+          <t>2026/06/30 17:46:05</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.0872683, -71.3622716</t>
+          <t>-33.362135, -70.6701833</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36227</t>
+          <t>-33.36214, -70.67018</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/07/01 09:04:41</t>
+          <t>2026/06/30 19:31:53</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.0873116, -71.3623033</t>
+          <t>-33.38949, -70.67389</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36230</t>
+          <t>-33.38949, -70.67389</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>14:59:44</t>
+          <t>01:45:48</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.02</v>
+        <v>4.03</v>
       </c>
       <c r="M79" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026/06/30 18:04:57</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-33.0872683, -71.3622716</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-33.08727, -71.36227</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026/07/01 09:04:41</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-33.0873116, -71.3623033</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-33.08731, -71.36230</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>14:59:44</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M80" t="n">
+        <v>8</v>
+      </c>
+      <c r="N80" t="n">
         <v>7</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026/06/30 18:16:32</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-32.7976249, -70.8871316</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-32.79762, -70.88713</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2026/07/01 08:29:06</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-33.367225, -70.6965716</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-33.36722, -70.69657</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>14:12:34</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>92.52</v>
-      </c>
-      <c r="M80" t="n">
-        <v>130</v>
-      </c>
-      <c r="N80" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,57 +5088,57 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/06/30 18:19:38</t>
+          <t>2026/06/30 18:16:32</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-32.8792399, -70.608805</t>
+          <t>-32.7976249, -70.8871316</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60881</t>
+          <t>-32.79762, -70.88713</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/07/01 09:18:54</t>
+          <t>2026/07/01 08:29:06</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-32.8677716, -70.6224</t>
+          <t>-33.367225, -70.6965716</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-32.86777, -70.62240</t>
+          <t>-33.36722, -70.69657</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>14:59:16</t>
+          <t>14:12:34</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.51</v>
+        <v>92.52</v>
       </c>
       <c r="M81" t="n">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="N81" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,47 +5147,47 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/06/30 19:32:56</t>
+          <t>2026/06/30 18:19:38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-33.389315, -70.6740216</t>
+          <t>-32.8792399, -70.608805</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67402</t>
+          <t>-32.87924, -70.60881</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/06/30 20:28:10</t>
+          <t>2026/07/01 09:18:54</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-33.4762483, -70.6982899</t>
+          <t>-32.8677716, -70.6224</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69829</t>
+          <t>-32.86777, -70.62240</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:55:14</t>
+          <t>14:59:16</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>13.58</v>
+        <v>3.51</v>
       </c>
       <c r="M82" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="N82" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/06/30 20:29:25</t>
+          <t>2026/06/30 19:32:56</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.4761, -70.6985283</t>
+          <t>-33.389315, -70.6740216</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69853</t>
+          <t>-33.38932, -70.67402</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/07/01 09:24:18</t>
+          <t>2026/06/30 20:28:10</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.4761566, -70.698465</t>
+          <t>-33.4762483, -70.6982899</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69846</t>
+          <t>-33.47625, -70.69829</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>12:54:53</t>
+          <t>00:55:14</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.01</v>
+        <v>13.58</v>
       </c>
       <c r="M83" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="N83" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,47 +5265,47 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/07/01 10:11:49</t>
+          <t>2026/06/30 20:29:25</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.3685633, -70.7261283</t>
+          <t>-33.4761, -70.6985283</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.36856, -70.72613</t>
+          <t>-33.47610, -70.69853</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/07/01 10:47:32</t>
+          <t>2026/07/01 09:24:18</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.3599716, -70.8071033</t>
+          <t>-33.4761566, -70.698465</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80710</t>
+          <t>-33.47616, -70.69846</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:35:43</t>
+          <t>12:54:53</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>10.85</v>
+        <v>0.01</v>
       </c>
       <c r="M84" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="N84" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,47 +5324,47 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/07/01 10:47:44</t>
+          <t>2026/07/01 09:52:27</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-33.3600133, -70.8071849</t>
+          <t>-33.3679799, -70.7269766</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80718</t>
+          <t>-33.36798, -70.72698</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/07/01 12:15:18</t>
+          <t>2026/07/01 10:10:34</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.5031949, -71.2568966</t>
+          <t>-33.3686783, -70.7259816</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.50319, -71.25690</t>
+          <t>-33.36868, -70.72598</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>01:27:34</t>
+          <t>00:18:07</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>64.69</v>
+        <v>0.14</v>
       </c>
       <c r="M85" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="N85" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,47 +5383,47 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/07/01 12:16:33</t>
+          <t>2026/07/01 10:11:49</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.506265, -71.2518333</t>
+          <t>-33.3685633, -70.7261283</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.50626, -71.25183</t>
+          <t>-33.36856, -70.72613</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/01 13:20:12</t>
+          <t>2026/07/01 10:47:32</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.4559049, -71.3000066</t>
+          <t>-33.3599716, -70.8071033</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.45590, -71.30001</t>
+          <t>-33.35997, -70.80710</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>01:03:39</t>
+          <t>00:35:43</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.56</v>
+        <v>10.85</v>
       </c>
       <c r="M86" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="N86" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/07/01 13:20:34</t>
+          <t>2026/07/01 10:47:44</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.4562116, -71.300045</t>
+          <t>-33.3600133, -70.8071849</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.45621, -71.30004</t>
+          <t>-33.36001, -70.80718</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/07/01 18:22:09</t>
+          <t>2026/07/01 12:15:18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-32.9641266, -70.6888516</t>
+          <t>-33.5031949, -71.2568966</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-32.96413, -70.68885</t>
+          <t>-33.50319, -71.25690</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>05:01:35</t>
+          <t>01:27:34</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>123.71</v>
+        <v>64.69</v>
       </c>
       <c r="M87" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="N87" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/07/01 16:17:48</t>
+          <t>2026/07/01 12:16:33</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.35124, -70.6716316</t>
+          <t>-33.506265, -71.2518333</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.35124, -70.67163</t>
+          <t>-33.50626, -71.25183</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/01 16:33:09</t>
+          <t>2026/07/01 13:20:12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.3623016, -70.6701366</t>
+          <t>-33.4559049, -71.3000066</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.36230, -70.67014</t>
+          <t>-33.45590, -71.30001</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:15:21</t>
+          <t>01:03:39</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.91</v>
+        <v>7.56</v>
       </c>
       <c r="M88" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N88" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,47 +5560,47 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/01 16:34:16</t>
+          <t>2026/07/01 13:20:34</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-33.3621083, -70.6701349</t>
+          <t>-33.4562116, -71.300045</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-33.36211, -70.67013</t>
+          <t>-33.45621, -71.30004</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/01 18:13:15</t>
+          <t>2026/07/01 18:22:09</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-33.3895166, -70.6738466</t>
+          <t>-32.9641266, -70.6888516</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-33.38952, -70.67385</t>
+          <t>-32.96413, -70.68885</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>01:38:59</t>
+          <t>05:01:35</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>4.04</v>
+        <v>123.71</v>
       </c>
       <c r="M89" t="n">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="N89" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/07/01 16:37:24</t>
+          <t>2026/07/01 14:54:21</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.3665449, -70.6961266</t>
+          <t>-33.366535, -70.696175</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.36654, -70.69613</t>
+          <t>-33.36653, -70.69617</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/07/01 18:37:01</t>
+          <t>2026/07/01 16:36:18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.4292333, -70.62603</t>
+          <t>-33.3665766, -70.696145</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.42923, -70.62603</t>
+          <t>-33.36658, -70.69615</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>01:59:37</t>
+          <t>01:41:57</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>18.18</v>
+        <v>0.04</v>
       </c>
       <c r="M90" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="N90" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,116 +5678,116 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/07/01 17:07:00</t>
+          <t>2026/07/01 16:17:48</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-32.8355983, -70.5980033</t>
+          <t>-33.35124, -70.6716316</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-32.83560, -70.59800</t>
+          <t>-33.35124, -70.67163</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/07/01 17:33:51</t>
+          <t>2026/07/01 16:33:09</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-32.83001, -70.59606</t>
+          <t>-33.3623016, -70.6701366</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-32.83001, -70.59606</t>
+          <t>-33.36230, -70.67014</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:26:51</t>
+          <t>00:15:21</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.66</v>
+        <v>2.91</v>
       </c>
       <c r="M91" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>15</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026/07/01 16:34:16</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-33.3621083, -70.6701349</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-33.36211, -70.67013</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026/07/01 18:13:15</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-33.3895166, -70.6738466</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-33.38952, -70.67385</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>01:38:59</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="M92" t="n">
+        <v>58</v>
+      </c>
+      <c r="N92" t="n">
         <v>13</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2026/07/01 17:34:20</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-32.8297266, -70.5967333</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-32.82973, -70.59673</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2026/07/01 21:02:02</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-32.87944, -70.6088683</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-32.87944, -70.60887</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>03:27:42</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="M92" t="n">
-        <v>55</v>
-      </c>
-      <c r="N92" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/01 18:13:40</t>
+          <t>2026/07/01 16:37:24</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.389315, -70.6739966</t>
+          <t>-33.3665449, -70.6961266</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67400</t>
+          <t>-33.36654, -70.69613</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/01 18:55:19</t>
+          <t>2026/07/01 18:37:01</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.3623416, -70.6701316</t>
+          <t>-33.4292333, -70.62603</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.36234, -70.67013</t>
+          <t>-33.42923, -70.62603</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:41:39</t>
+          <t>01:59:37</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.57</v>
+        <v>18.18</v>
       </c>
       <c r="M93" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="N93" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/01 18:23:24</t>
+          <t>2026/07/01 17:07:00</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-32.9638666, -70.6887733</t>
+          <t>-32.8355983, -70.5980033</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-32.96387, -70.68877</t>
+          <t>-32.83560, -70.59800</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/01 19:04:24</t>
+          <t>2026/07/01 17:33:51</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-32.74321, -70.7329233</t>
+          <t>-32.83001, -70.59606</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-32.74321, -70.73292</t>
+          <t>-32.83001, -70.59606</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>00:41:00</t>
+          <t>00:26:51</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>26.93</v>
+        <v>0.66</v>
       </c>
       <c r="M94" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="N94" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/01 18:36:10</t>
+          <t>2026/07/01 17:34:20</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-32.840309, -70.960003</t>
+          <t>-32.8297266, -70.5967333</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-32.84031, -70.96000</t>
+          <t>-32.82973, -70.59673</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/01 18:52:38</t>
+          <t>2026/07/01 21:02:02</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-32.840673, -70.959203</t>
+          <t>-32.87944, -70.6088683</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-32.84067, -70.95920</t>
+          <t>-32.87944, -70.60887</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:16:28</t>
+          <t>03:27:42</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.29</v>
+        <v>23.77</v>
       </c>
       <c r="M95" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="N95" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/01 18:38:16</t>
+          <t>2026/07/01 18:13:40</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-33.429875, -70.6266516</t>
+          <t>-33.389315, -70.6739966</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-33.42988, -70.62665</t>
+          <t>-33.38932, -70.67400</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/01 19:12:43</t>
+          <t>2026/07/01 18:55:19</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-33.4658483, -70.59143</t>
+          <t>-33.3623416, -70.6701316</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-33.46585, -70.59143</t>
+          <t>-33.36234, -70.67013</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:34:27</t>
+          <t>00:41:39</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>7.39</v>
+        <v>3.57</v>
       </c>
       <c r="M96" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N96" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/07/01 18:52:50</t>
+          <t>2026/07/01 18:23:24</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-32.840977, -70.959267</t>
+          <t>-32.9638666, -70.6887733</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-32.84098, -70.95927</t>
+          <t>-32.96387, -70.68877</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/07/01 19:08:06</t>
+          <t>2026/07/01 19:04:24</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-32.838368, -70.956176</t>
+          <t>-32.74321, -70.7329233</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95618</t>
+          <t>-32.74321, -70.73292</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:15:16</t>
+          <t>00:41:00</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.02</v>
+        <v>26.93</v>
       </c>
       <c r="M97" t="n">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="N97" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,57 +6091,57 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/01 18:56:17</t>
+          <t>2026/07/01 18:38:16</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.3621316, -70.67014</t>
+          <t>-33.429875, -70.6266516</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.36213, -70.67014</t>
+          <t>-33.42988, -70.62665</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/01 19:49:48</t>
+          <t>2026/07/01 19:12:43</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-33.4761366, -70.6985283</t>
+          <t>-33.4658483, -70.59143</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-33.47614, -70.69853</t>
+          <t>-33.46585, -70.59143</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:53:31</t>
+          <t>00:34:27</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>18.19</v>
+        <v>7.39</v>
       </c>
       <c r="M98" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="N98" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/01 19:04:34</t>
+          <t>2026/07/01 18:52:50</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.7433216, -70.7327416</t>
+          <t>-32.840977, -70.959267</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.74332, -70.73274</t>
+          <t>-32.84098, -70.95927</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/01 19:26:08</t>
+          <t>2026/07/01 19:08:06</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-32.7431749, -70.7296599</t>
+          <t>-32.838368, -70.956176</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72966</t>
+          <t>-32.83837, -70.95618</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:21:34</t>
+          <t>00:15:16</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.37</v>
+        <v>1.02</v>
       </c>
       <c r="M99" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N99" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/01 19:09:05</t>
+          <t>2026/07/01 18:56:17</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.83838, -70.955483</t>
+          <t>-33.3621316, -70.67014</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95548</t>
+          <t>-33.36213, -70.67014</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/02 09:35:22</t>
+          <t>2026/07/01 19:49:48</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.83736, -70.967134</t>
+          <t>-33.4761366, -70.6985283</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.83736, -70.96713</t>
+          <t>-33.47614, -70.69853</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>14:26:17</t>
+          <t>00:53:31</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.15</v>
+        <v>18.19</v>
       </c>
       <c r="M100" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="N100" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/01 19:13:06</t>
+          <t>2026/07/01 19:04:34</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.466, -70.59085</t>
+          <t>-32.7433216, -70.7327416</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.46600, -70.59085</t>
+          <t>-32.74332, -70.73274</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/01 21:09:14</t>
+          <t>2026/07/01 19:26:08</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.4358966, -70.630045</t>
+          <t>-32.7431749, -70.7296599</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.43590, -70.63004</t>
+          <t>-32.74317, -70.72966</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>01:56:08</t>
+          <t>00:21:34</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>8.27</v>
+        <v>0.37</v>
       </c>
       <c r="M101" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="N101" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/01 19:26:31</t>
+          <t>2026/07/01 19:09:05</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.7430433, -70.7297616</t>
+          <t>-32.83838, -70.955483</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.74304, -70.72976</t>
+          <t>-32.83838, -70.95548</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/02 08:14:22</t>
+          <t>2026/07/02 09:35:22</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-33.4821016, -70.7654016</t>
+          <t>-32.83736, -70.967134</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-33.48210, -70.76540</t>
+          <t>-32.83736, -70.96713</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>12:47:51</t>
+          <t>14:26:17</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>95.72</v>
+        <v>3.15</v>
       </c>
       <c r="M102" t="n">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="N102" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/01 19:50:56</t>
+          <t>2026/07/01 19:13:06</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.4761066, -70.6985333</t>
+          <t>-33.466, -70.59085</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69853</t>
+          <t>-33.46600, -70.59085</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/02 08:43:30</t>
+          <t>2026/07/01 21:09:14</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.47627, -70.698345</t>
+          <t>-33.4358966, -70.630045</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69835</t>
+          <t>-33.43590, -70.63004</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>12:52:34</t>
+          <t>01:56:08</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0.03</v>
+        <v>8.27</v>
       </c>
       <c r="M103" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="N103" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/01 21:03:17</t>
+          <t>2026/07/01 19:26:31</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.879205, -70.60883</t>
+          <t>-32.7430433, -70.7297616</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60883</t>
+          <t>-32.74304, -70.72976</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/02 10:10:43</t>
+          <t>2026/07/02 08:14:22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.3363116, -70.7193983</t>
+          <t>-33.4821016, -70.7654016</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.33631, -70.71940</t>
+          <t>-33.48210, -70.76540</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>13:07:26</t>
+          <t>12:47:51</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>65.22</v>
+        <v>95.72</v>
       </c>
       <c r="M104" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="N104" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/01 21:10:29</t>
+          <t>2026/07/01 19:50:56</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-33.4364533, -70.6295916</t>
+          <t>-33.4761066, -70.6985333</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-33.43645, -70.62959</t>
+          <t>-33.47611, -70.69853</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/02 12:50:54</t>
+          <t>2026/07/02 08:43:30</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.3673183, -70.6960249</t>
+          <t>-33.47627, -70.698345</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.36732, -70.69602</t>
+          <t>-33.47627, -70.69835</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>15:40:25</t>
+          <t>12:52:34</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>13.73</v>
+        <v>0.03</v>
       </c>
       <c r="M105" t="n">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="N105" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/01 21:10:55</t>
+          <t>2026/07/01 21:03:17</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.7975766, -70.8870866</t>
+          <t>-32.879205, -70.60883</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88709</t>
+          <t>-32.87920, -70.60883</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/02 07:49:14</t>
+          <t>2026/07/02 10:10:43</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-32.8517066, -70.6845583</t>
+          <t>-33.3363116, -70.7193983</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-32.85171, -70.68456</t>
+          <t>-33.33631, -70.71940</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>10:38:19</t>
+          <t>13:07:26</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>29.01</v>
+        <v>65.22</v>
       </c>
       <c r="M106" t="n">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="N106" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,47 +6622,47 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/02 14:03:25</t>
+          <t>2026/07/01 21:10:29</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-34.20837, -70.6774733</t>
+          <t>-33.4364533, -70.6295916</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-34.20837, -70.67747</t>
+          <t>-33.43645, -70.62959</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/02 14:34:28</t>
+          <t>2026/07/02 12:50:54</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-34.2054716, -70.679015</t>
+          <t>-33.3673183, -70.6960249</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67902</t>
+          <t>-33.36732, -70.69602</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:31:03</t>
+          <t>15:40:25</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.12</v>
+        <v>13.73</v>
       </c>
       <c r="M107" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="N107" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,47 +6681,47 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/02 14:34:42</t>
+          <t>2026/07/01 21:10:55</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-34.205505, -70.6783</t>
+          <t>-32.7975766, -70.8870866</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67830</t>
+          <t>-32.79758, -70.88709</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/02 15:07:31</t>
+          <t>2026/07/02 07:49:14</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-34.205605, -70.6770266</t>
+          <t>-32.8517066, -70.6845583</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-34.20560, -70.67703</t>
+          <t>-32.85171, -70.68456</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>00:32:49</t>
+          <t>10:38:19</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.16</v>
+        <v>29.01</v>
       </c>
       <c r="M108" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="N108" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,53 +6740,53 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/02 15:08:46</t>
+          <t>2026/07/02 14:03:25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-34.20555, -70.6775616</t>
+          <t>-34.20837, -70.6774733</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67756</t>
+          <t>-34.20837, -70.67747</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/02 18:26:46</t>
+          <t>2026/07/02 14:34:28</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.8874383</t>
+          <t>-34.2054716, -70.679015</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88744</t>
+          <t>-34.20547, -70.67902</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>03:18:00</t>
+          <t>00:31:03</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>196.44</v>
+        <v>1.12</v>
       </c>
       <c r="M109" t="n">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="N109" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6799,106 +6799,106 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/02 15:30:04</t>
+          <t>2026/07/02 14:34:42</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-33.3603466, -70.8100116</t>
+          <t>-34.205505, -70.6783</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-33.36035, -70.81001</t>
+          <t>-34.20551, -70.67830</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/02 15:59:47</t>
+          <t>2026/07/02 15:07:31</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-33.3592333, -70.8099633</t>
+          <t>-34.205605, -70.6770266</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-33.35923, -70.80996</t>
+          <t>-34.20560, -70.67703</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:29:43</t>
+          <t>00:32:49</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="M110" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/02 15:38:12</t>
+          <t>2026/07/02 15:08:46</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.359985, -70.807068</t>
+          <t>-34.20555, -70.6775616</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80707</t>
+          <t>-34.20555, -70.67756</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/03 15:48:05</t>
+          <t>2026/07/02 18:26:46</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-33.359771, -70.807271</t>
+          <t>-32.7977149, -70.8874383</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-33.35977, -70.80727</t>
+          <t>-32.79771, -70.88744</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>24:09:53</t>
+          <t>03:18:00</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.06</v>
+        <v>196.44</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112">
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,116 +6917,116 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/02 16:00:01</t>
+          <t>2026/07/02 15:30:04</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-33.35928, -70.8097799</t>
+          <t>-33.3603466, -70.8100116</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-33.35928, -70.80978</t>
+          <t>-33.36035, -70.81001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/02 16:19:50</t>
+          <t>2026/07/02 15:59:47</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-33.3612449, -70.8117633</t>
+          <t>-33.3592333, -70.8099633</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-33.36124, -70.81176</t>
+          <t>-33.35923, -70.80996</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:19:49</t>
+          <t>00:29:43</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="M112" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N112" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/07/02 16:19:55</t>
+          <t>2026/07/02 15:38:12</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.3612433, -70.8117233</t>
+          <t>-33.359985, -70.807068</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.36124, -70.81172</t>
+          <t>-33.35999, -70.80707</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/02 18:28:33</t>
+          <t>2026/07/03 15:48:05</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-32.7568816, -70.7350316</t>
+          <t>-33.359771, -70.807271</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-32.75688, -70.73503</t>
+          <t>-33.35977, -70.80727</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>02:08:38</t>
+          <t>24:09:53</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>114.06</v>
+        <v>0.06</v>
       </c>
       <c r="M113" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,47 +7035,47 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/02 18:27:40</t>
+          <t>2026/07/02 16:00:01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-32.7975916, -70.88712</t>
+          <t>-33.35928, -70.8097799</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88712</t>
+          <t>-33.35928, -70.80978</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/03 08:37:23</t>
+          <t>2026/07/02 16:19:50</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-32.7568733, -70.7339866</t>
+          <t>-33.3612449, -70.8117633</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-32.75687, -70.73399</t>
+          <t>-33.36124, -70.81176</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>14:09:43</t>
+          <t>00:19:49</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>17.39</v>
+        <v>0.34</v>
       </c>
       <c r="M114" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="N114" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/02 18:29:48</t>
+          <t>2026/07/02 16:19:55</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-32.7569433, -70.7346383</t>
+          <t>-33.3612433, -70.8117233</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-32.75694, -70.73464</t>
+          <t>-33.36124, -70.81172</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/02 18:45:19</t>
+          <t>2026/07/02 18:28:33</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-32.74318, -70.7331016</t>
+          <t>-32.7568816, -70.7350316</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-32.74318, -70.73310</t>
+          <t>-32.75688, -70.73503</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:15:31</t>
+          <t>02:08:38</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.8</v>
+        <v>114.06</v>
       </c>
       <c r="M115" t="n">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="N115" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,47 +7153,47 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/02 18:45:31</t>
+          <t>2026/07/02 18:27:40</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-32.74332, -70.732715</t>
+          <t>-32.7975916, -70.88712</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-32.74332, -70.73271</t>
+          <t>-32.79759, -70.88712</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/02 19:06:58</t>
+          <t>2026/07/03 08:37:23</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-32.7431666, -70.7296599</t>
+          <t>-32.7568733, -70.7339866</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72966</t>
+          <t>-32.75687, -70.73399</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>00:21:27</t>
+          <t>14:09:43</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0.37</v>
+        <v>17.39</v>
       </c>
       <c r="M116" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="N116" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/02 19:08:13</t>
+          <t>2026/07/02 18:29:48</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.7430483, -70.7297816</t>
+          <t>-32.7569433, -70.7346383</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.74305, -70.72978</t>
+          <t>-32.75694, -70.73464</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/03 09:06:28</t>
+          <t>2026/07/02 18:45:19</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-33.3599466, -70.8069483</t>
+          <t>-32.74318, -70.7331016</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80695</t>
+          <t>-32.74318, -70.73310</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>13:58:15</t>
+          <t>00:15:31</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>90.03</v>
+        <v>1.8</v>
       </c>
       <c r="M117" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="N117" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/07/02 19:25:25</t>
+          <t>2026/07/02 18:45:31</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-32.8351466, -70.5981016</t>
+          <t>-32.74332, -70.732715</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-32.83515, -70.59810</t>
+          <t>-32.74332, -70.73271</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/02 19:35:35</t>
+          <t>2026/07/02 19:06:58</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-32.829985, -70.5961166</t>
+          <t>-32.7431666, -70.7296599</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-32.82999, -70.59612</t>
+          <t>-32.74317, -70.72966</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:10:10</t>
+          <t>00:21:27</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
       <c r="M118" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,47 +7330,47 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/02 19:35:58</t>
+          <t>2026/07/02 19:08:13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-32.8296933, -70.59693</t>
+          <t>-32.7430483, -70.7297816</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-32.82969, -70.59693</t>
+          <t>-32.74305, -70.72978</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/02 19:52:58</t>
+          <t>2026/07/03 09:06:28</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-32.8438816, -70.5976683</t>
+          <t>-33.3599466, -70.8069483</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-32.84388, -70.59767</t>
+          <t>-33.35995, -70.80695</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:17:00</t>
+          <t>13:58:15</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.38</v>
+        <v>90.03</v>
       </c>
       <c r="M119" t="n">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="N119" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120">
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7389,47 +7389,47 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/02 19:54:13</t>
+          <t>2026/07/02 19:25:25</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-32.84522, -70.5986183</t>
+          <t>-32.8351466, -70.5981016</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-32.84522, -70.59862</t>
+          <t>-32.83515, -70.59810</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/02 20:18:57</t>
+          <t>2026/07/02 19:35:35</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-32.8358783, -70.5712266</t>
+          <t>-32.829985, -70.5961166</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-32.83588, -70.57123</t>
+          <t>-32.82999, -70.59612</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>00:24:44</t>
+          <t>00:10:10</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.68</v>
+        <v>0.61</v>
       </c>
       <c r="M120" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N120" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,47 +7448,47 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/02 20:19:46</t>
+          <t>2026/07/02 19:35:58</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-32.8345466, -70.5704883</t>
+          <t>-32.8296933, -70.59693</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-32.83455, -70.57049</t>
+          <t>-32.82969, -70.59693</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/02 21:03:15</t>
+          <t>2026/07/02 19:52:58</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-32.8452433, -70.5986616</t>
+          <t>-32.8438816, -70.5976683</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-32.84524, -70.59866</t>
+          <t>-32.84388, -70.59767</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:43:29</t>
+          <t>00:17:00</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4.85</v>
+        <v>2.38</v>
       </c>
       <c r="M121" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="N121" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,44 +7507,44 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/07/02 21:04:30</t>
+          <t>2026/07/02 19:54:13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.8452483, -70.5986783</t>
+          <t>-32.84522, -70.5986183</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.84525, -70.59868</t>
+          <t>-32.84522, -70.59862</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/02 21:41:37</t>
+          <t>2026/07/02 20:18:57</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.8345933, -70.5706366</t>
+          <t>-32.8358783, -70.5712266</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.83459, -70.57064</t>
+          <t>-32.83588, -70.57123</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:37:07</t>
+          <t>00:24:44</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="M122" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N122" t="n">
         <v>21</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,47 +7566,47 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/02 21:42:52</t>
+          <t>2026/07/02 20:19:46</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.8345683, -70.5706116</t>
+          <t>-32.8345466, -70.5704883</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.83457, -70.57061</t>
+          <t>-32.83455, -70.57049</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/02 22:16:43</t>
+          <t>2026/07/02 21:03:15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.8793333, -70.6089049</t>
+          <t>-32.8452433, -70.5986616</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.87933, -70.60890</t>
+          <t>-32.84524, -70.59866</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>00:33:51</t>
+          <t>00:43:29</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>9.69</v>
+        <v>4.85</v>
       </c>
       <c r="M123" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N123" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,44 +7625,44 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/02 22:17:58</t>
+          <t>2026/07/02 21:04:30</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.879225, -70.6087949</t>
+          <t>-32.8452483, -70.5986783</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-32.84525, -70.59868</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/03 12:56:31</t>
+          <t>2026/07/02 21:41:37</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.8319416, -70.5967766</t>
+          <t>-32.8345933, -70.5706366</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.83194, -70.59678</t>
+          <t>-32.83459, -70.57064</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>14:38:33</t>
+          <t>00:37:07</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>7.74</v>
+        <v>3.95</v>
       </c>
       <c r="M124" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="N124" t="n">
         <v>21</v>
@@ -7671,70 +7671,70 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/03 11:49:26</t>
+          <t>2026/07/02 21:42:52</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.3672966, -70.6958899</t>
+          <t>-32.8345683, -70.5706116</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69589</t>
+          <t>-32.83457, -70.57061</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/04 22:41:12</t>
+          <t>2026/07/02 22:16:43</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.3672966, -70.6958899</t>
+          <t>-32.8793333, -70.6089049</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69589</t>
+          <t>-32.87933, -70.60890</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>34:51:46</t>
+          <t>00:33:51</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>9.69</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,165 +7743,165 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/03 14:17:56</t>
+          <t>2026/07/02 22:17:58</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.3595616, -70.8090049</t>
+          <t>-32.879225, -70.6087949</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.35956, -70.80900</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/03 14:28:37</t>
+          <t>2026/07/03 12:56:31</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.3601516, -70.807085</t>
+          <t>-32.8319416, -70.5967766</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80709</t>
+          <t>-32.83194, -70.59678</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>00:10:41</t>
+          <t>14:38:33</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.29</v>
+        <v>7.74</v>
       </c>
       <c r="M126" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="N126" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/07/03 14:29:52</t>
+          <t>2026/07/03 11:49:26</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-33.3600166, -70.8069183</t>
+          <t>-33.3672966, -70.6958899</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80692</t>
+          <t>-33.36730, -70.69589</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/03 15:13:44</t>
+          <t>2026/07/05 22:41:12</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-33.3665599, -70.6955966</t>
+          <t>-33.3672966, -70.6958899</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-33.36656, -70.69560</t>
+          <t>-33.36730, -70.69589</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>00:43:52</t>
+          <t>58:51:46</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>13.92</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/07/03 15:00:11</t>
+          <t>2026/07/03 14:17:56</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-32.840477, -70.964531</t>
+          <t>-33.3595616, -70.8090049</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-32.84048, -70.96453</t>
+          <t>-33.35956, -70.80900</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/03 15:16:03</t>
+          <t>2026/07/03 14:28:37</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-32.840579, -70.964609</t>
+          <t>-33.3601516, -70.807085</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-32.84058, -70.96461</t>
+          <t>-33.36015, -70.80709</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>00:15:52</t>
+          <t>00:10:41</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,106 +7920,106 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/07/03 15:14:18</t>
+          <t>2026/07/03 14:29:52</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-33.3665483, -70.695875</t>
+          <t>-33.3600166, -70.8069183</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-33.36655, -70.69588</t>
+          <t>-33.36002, -70.80692</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/03 16:17:44</t>
+          <t>2026/07/03 15:13:44</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-33.4159316, -70.6119666</t>
+          <t>-33.3665599, -70.6955966</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-33.41593, -70.61197</t>
+          <t>-33.36656, -70.69560</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>01:03:26</t>
+          <t>00:43:52</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>12.12</v>
+        <v>13.92</v>
       </c>
       <c r="M129" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="N129" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/07/03 16:18:59</t>
+          <t>2026/07/03 15:00:11</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-33.41755, -70.61364</t>
+          <t>-32.840477, -70.964531</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-33.41755, -70.61364</t>
+          <t>-32.84048, -70.96453</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/07/03 16:31:06</t>
+          <t>2026/07/03 15:16:03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-33.4362766, -70.6296133</t>
+          <t>-32.840579, -70.964609</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62961</t>
+          <t>-32.84058, -70.96461</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>00:12:07</t>
+          <t>00:15:52</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.76</v>
+        <v>0.02</v>
       </c>
       <c r="M130" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8038,175 +8038,175 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/07/03 16:32:01</t>
+          <t>2026/07/03 15:14:18</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-33.437295, -70.6293983</t>
+          <t>-33.3665483, -70.695875</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-33.43729, -70.62940</t>
+          <t>-33.36655, -70.69588</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/04 15:45:53</t>
+          <t>2026/07/03 16:17:44</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-33.3841349, -70.621735</t>
+          <t>-33.4159316, -70.6119666</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-33.38413, -70.62174</t>
+          <t>-33.41593, -70.61197</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>23:13:52</t>
+          <t>01:03:26</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>12.52</v>
+        <v>12.12</v>
       </c>
       <c r="M131" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N131" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/07/04 12:42:53</t>
+          <t>2026/07/03 16:18:59</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-32.743075, -70.7297533</t>
+          <t>-33.41755, -70.61364</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-32.74307, -70.72975</t>
+          <t>-33.41755, -70.61364</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/04 12:49:08</t>
+          <t>2026/07/03 16:31:06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-32.74303, -70.7298016</t>
+          <t>-33.4362766, -70.6296133</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72980</t>
+          <t>-33.43628, -70.62961</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>00:06:15</t>
+          <t>00:12:07</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0.01</v>
+        <v>2.76</v>
       </c>
       <c r="M132" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/07/04 12:49:23</t>
+          <t>2026/07/03 16:32:01</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-32.7430266, -70.7298083</t>
+          <t>-33.437295, -70.6293983</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72981</t>
+          <t>-33.43729, -70.62940</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/04 22:49:23</t>
+          <t>2026/07/04 15:45:53</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-32.7430266, -70.7298083</t>
+          <t>-33.3841349, -70.621735</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72981</t>
+          <t>-33.38413, -70.62174</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>23:13:52</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>12.52</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8215,57 +8215,57 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/07/04 14:46:55</t>
+          <t>2026/07/04 12:42:53</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-33.0872766, -71.3623033</t>
+          <t>-32.743075, -70.7297533</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36230</t>
+          <t>-32.74307, -70.72975</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/04 20:51:57</t>
+          <t>2026/07/04 12:49:08</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-33.0872983, -71.3623833</t>
+          <t>-32.74303, -70.7298016</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36238</t>
+          <t>-32.74303, -70.72980</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>06:05:02</t>
+          <t>00:06:15</t>
         </is>
       </c>
       <c r="L134" t="n">
         <v>0.01</v>
       </c>
       <c r="M134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8274,57 +8274,57 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/07/04 17:23:45</t>
+          <t>2026/07/04 14:46:55</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-32.7976233, -70.8871516</t>
+          <t>-33.0872766, -71.3623033</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88715</t>
+          <t>-33.08728, -71.36230</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/07/04 23:25:06</t>
+          <t>2026/07/04 20:51:57</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.887105</t>
+          <t>-33.0872983, -71.3623833</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88711</t>
+          <t>-33.08730, -71.36238</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>06:01:21</t>
+          <t>06:05:02</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8333,37 +8333,37 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/07/04 18:00:43</t>
+          <t>2026/07/05 12:41:45</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-33.4760866, -70.6985016</t>
+          <t>-32.79761, -70.8870783</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-33.47609, -70.69850</t>
+          <t>-32.79761, -70.88708</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/07/04 22:00:43</t>
+          <t>2026/07/05 22:41:45</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-33.4760866, -70.6985016</t>
+          <t>-32.79761, -70.8870783</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-33.47609, -70.69850</t>
+          <t>-32.79761, -70.88708</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -8379,7 +8379,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -8392,41 +8392,41 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026/07/04 18:01:58</t>
+          <t>2026/07/05 18:15:28</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-32.87922, -70.608745</t>
+          <t>-33.0872916, -71.3623633</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60874</t>
+          <t>-33.08729, -71.36236</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/04 22:01:58</t>
+          <t>2026/07/05 22:15:57</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-32.87922, -70.608745</t>
+          <t>-33.0872266, -71.3622533</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60874</t>
+          <t>-33.08723, -71.36225</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>04:00:29</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -8438,11 +8438,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8451,37 +8451,37 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026/07/04 20:25:26</t>
+          <t>2026/07/05 18:16:17</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-33.4363883, -70.6291633</t>
+          <t>-32.7430816, -70.7297266</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-33.43639, -70.62916</t>
+          <t>-32.74308, -70.72973</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/07/04 22:25:33</t>
+          <t>2026/07/05 22:17:45</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-33.4363883, -70.6291633</t>
+          <t>-32.7430816, -70.7297266</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>-33.43639, -70.62916</t>
+          <t>-32.74308, -70.72973</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>02:00:07</t>
+          <t>04:01:28</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -8497,11 +8497,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8510,37 +8510,37 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026/07/04 20:52:25</t>
+          <t>2026/07/05 18:38:14</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-33.0872366, -71.3622716</t>
+          <t>-32.8791783, -70.6089483</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-33.08724, -71.36227</t>
+          <t>-32.87918, -70.60895</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026/07/04 22:52:25</t>
+          <t>2026/07/05 22:38:14</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-33.0872366, -71.3622716</t>
+          <t>-32.8791783, -70.6089483</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>-33.08724, -71.36227</t>
+          <t>-32.87918, -70.60895</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -8556,11 +8556,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8569,37 +8569,37 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026/07/04 21:35:55</t>
+          <t>2026/07/05 19:43:58</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-32.841836, -70.936884</t>
+          <t>-33.4363716, -70.6291933</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-32.84184, -70.93688</t>
+          <t>-33.43637, -70.62919</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/07/04 23:38:58</t>
+          <t>2026/07/05 21:43:59</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>-32.841836, -70.936884</t>
+          <t>-33.4363716, -70.6291933</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>-32.84184, -70.93688</t>
+          <t>-33.43637, -70.62919</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>02:03:03</t>
+          <t>02:00:01</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8628,37 +8628,37 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026/07/04 21:52:40</t>
+          <t>2026/07/05 20:02:23</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-32.780851, -70.981255</t>
+          <t>-32.838349, -70.955543</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-32.78085, -70.98126</t>
+          <t>-32.83835, -70.95554</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/07/04 23:50:10</t>
+          <t>2026/07/05 22:59:54</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>-32.780851, -70.981255</t>
+          <t>-32.838349, -70.955543</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>-32.78085, -70.98126</t>
+          <t>-32.83835, -70.95554</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>01:57:30</t>
+          <t>02:57:31</t>
         </is>
       </c>
       <c r="L141" t="n">
@@ -8668,6 +8668,65 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>5</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026/07/05 22:01:33</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-32.841623, -70.936834</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-32.84162, -70.93683</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026/07/05 23:04:34</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-32.841623, -70.936834</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-32.84162, -70.93683</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>01:03:01</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8719,10 +8778,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1565.81</v>
+        <v>1510.79</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8738,13 +8797,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>749.15</v>
+        <v>748.99</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>141</v>
@@ -8757,10 +8816,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>313.86</v>
+        <v>339.73</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -8776,7 +8835,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1045.89</v>
+        <v>1044.91</v>
       </c>
       <c r="C5" t="n">
         <v>36</v>
@@ -8795,7 +8854,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -8820,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -8877,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -8915,7 +8974,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -8947,13 +9006,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>929.22</v>
+        <v>904.13</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>122</v>
@@ -8966,16 +9025,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>773.34</v>
+        <v>277.95</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -9042,10 +9101,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>567.87</v>
+        <v>559.7</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -9061,10 +9120,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>769.6900000000001</v>
+        <v>764.91</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/05 22:56:09</t>
+          <t>2026/07/05 23:56:09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>165:59:59</t>
+          <t>166:59:59</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/05 22:57:39</t>
+          <t>2026/07/05 23:57:26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:58:31</t>
+          <t>166:58:18</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/07/05 21:43:59</t>
+          <t>2026/07/05 23:43:59</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>02:00:01</t>
+          <t>04:00:01</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/07/05 22:59:54</t>
+          <t>2026/07/05 23:59:55</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>02:57:31</t>
+          <t>03:57:32</t>
         </is>
       </c>
       <c r="L141" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/06 22:01:21</t>
+          <t>2026/07/06 23:01:39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>165:59:44</t>
+          <t>167:00:02</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/06 22:13:30</t>
+          <t>2026/07/06 23:13:37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>166:00:04</t>
+          <t>167:00:11</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/06 22:56:11</t>
+          <t>2026/07/06 23:56:11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>166:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/06 21:57:22</t>
+          <t>2026/07/06 23:57:24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>164:59:44</t>
+          <t>166:59:46</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/07/06 22:11:21</t>
+          <t>2026/07/06 23:11:38</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>148:41:47</t>
+          <t>149:42:04</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -9233,22 +9233,22 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026/07/06 22:44:08</t>
+          <t>2026/07/06 23:44:07</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>-33.360033, -70.807094</t>
+          <t>-33.360032, -70.807101</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80709</t>
+          <t>-33.36003, -70.80710</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>06:05:22</t>
+          <t>07:05:21</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/07/06 22:40:06</t>
+          <t>2026/07/06 23:40:09</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>04:03:45</t>
+          <t>05:03:48</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026/07/06 21:33:58</t>
+          <t>2026/07/06 23:33:58</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>02:11:43</t>
+          <t>04:11:43</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026/07/06 21:23:29</t>
+          <t>2026/07/06 23:23:29</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/07/06 21:45:04</t>
+          <t>2026/07/06 23:45:04</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/07/06 21:57:58</t>
+          <t>2026/07/06 23:57:58</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>02:00:08</t>
+          <t>04:00:08</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -9730,6 +9730,124 @@
         <v>0</v>
       </c>
       <c r="N159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026/07/06 21:08:29</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-32.838348, -70.955692</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-32.83835, -70.95569</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026/07/06 23:06:48</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-32.838348, -70.955692</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-32.83835, -70.95569</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>01:58:19</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>10</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026/07/06 21:15:50</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-33.4362633, -70.6293216</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-33.43626, -70.62932</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026/07/06 23:15:50</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-33.4362633, -70.6293216</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-33.43626, -70.62932</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9800,13 +9918,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>882.66</v>
+        <v>882.62</v>
       </c>
       <c r="C3" t="n">
         <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>141</v>
@@ -10028,13 +10146,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>320.91</v>
       </c>
       <c r="C15" t="n">
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>126</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -9351,26 +9351,26 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/07/06 22:48:07</t>
+          <t>2026/07/06 22:50:17</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-33.400785, -70.5716966</t>
+          <t>-33.40065, -70.5716883</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>-33.40078, -70.57170</t>
+          <t>-33.40065, -70.57169</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>05:57:54</t>
+          <t>06:00:04</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="M153" t="n">
         <v>98</v>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>275.26</v>
+        <v>275.28</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/07 22:01:21</t>
+          <t>2026/07/07 23:01:21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>165:59:45</t>
+          <t>166:59:45</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/07 22:13:21</t>
+          <t>2026/07/07 23:13:40</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>165:59:57</t>
+          <t>167:00:16</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/07 22:11:21</t>
+          <t>2026/07/07 23:12:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>165:40:46</t>
+          <t>166:41:25</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/07 21:56:11</t>
+          <t>2026/07/07 23:56:11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>165:00:03</t>
+          <t>167:00:03</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/07/07 21:31:16</t>
+          <t>2026/07/07 23:31:15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>157:15:02</t>
+          <t>159:15:01</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/07/07 21:40:08</t>
+          <t>2026/07/07 23:40:11</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>04:03:54</t>
+          <t>06:03:57</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026/07/07 20:53:09</t>
+          <t>2026/07/07 22:53:09</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>02:00:04</t>
+          <t>04:00:04</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/07/07 21:20:49</t>
+          <t>2026/07/07 23:20:49</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/07/07 21:24:06</t>
+          <t>2026/07/07 23:24:06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026/07/07 21:25:38</t>
+          <t>2026/07/07 23:25:38</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>02:00:11</t>
+          <t>04:00:11</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -10202,65 +10202,6 @@
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>2026/07/07 19:34:40</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>-33.4133183, -70.5978216</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-33.41332, -70.59782</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>2026/07/07 21:37:43</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-33.4132783, -70.5975683</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-33.41328, -70.59757</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>02:03:03</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10331,13 +10272,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1078.76</v>
+        <v>1078.7</v>
       </c>
       <c r="C3" t="n">
         <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>141</v>
@@ -10559,13 +10500,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>298.84</v>
+        <v>307.17</v>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>126</v>
@@ -10578,7 +10519,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>329.24</v>
+        <v>335.8</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>335.8</v>
+        <v>335.82</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/08 22:01:21</t>
+          <t>2026/07/08 23:01:38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:17</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/08 22:13:38</t>
+          <t>2026/07/08 23:13:21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>166:00:21</t>
+          <t>167:00:04</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/08 22:31:51</t>
+          <t>2026/07/08 23:31:23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>166:16:27</t>
+          <t>167:15:59</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/08 21:56:09</t>
+          <t>2026/07/08 23:56:09</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026/07/08 22:49:09</t>
+          <t>2026/07/08 23:49:09</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>06:01:01</t>
+          <t>07:01:01</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026/07/08 21:37:54</t>
+          <t>2026/07/08 23:37:54</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>03:58:22</t>
+          <t>05:58:22</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/07/08 21:37:25</t>
+          <t>2026/07/08 23:37:25</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -10208,11 +10208,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10221,37 +10221,37 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026/07/08 21:39:36</t>
+          <t>2026/07/08 21:12:09</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-32.838381, -70.955498</t>
+          <t>-32.743035, -70.7297883</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95550</t>
+          <t>-32.74303, -70.72979</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026/07/08 22:38:05</t>
+          <t>2026/07/08 23:12:09</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>-32.838381, -70.955498</t>
+          <t>-32.743035, -70.7297883</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95550</t>
+          <t>-32.74303, -70.72979</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>00:58:29</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L168" t="n">
@@ -10267,11 +10267,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10280,37 +10280,37 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026/07/08 21:43:27</t>
+          <t>2026/07/08 21:14:57</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-32.841869, -70.9368</t>
+          <t>-33.4374016, -70.6293816</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>-32.84187, -70.93680</t>
+          <t>-33.43740, -70.62938</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026/07/08 22:46:39</t>
+          <t>2026/07/08 23:15:05</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>-32.841869, -70.9368</t>
+          <t>-33.4374016, -70.6293816</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>-32.84187, -70.93680</t>
+          <t>-33.43740, -70.62938</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>01:03:12</t>
+          <t>02:00:08</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -10320,6 +10320,183 @@
         <v>0</v>
       </c>
       <c r="N169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>10</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026/07/08 21:25:13</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-33.4761066, -70.6985216</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-33.47611, -70.69852</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026/07/08 23:25:37</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-33.4761066, -70.6985216</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-33.47611, -70.69852</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>02:00:24</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>12</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026/07/08 21:39:36</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-32.838381, -70.955498</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-32.83838, -70.95550</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2026/07/08 23:38:05</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-32.838381, -70.955498</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-32.83838, -70.95550</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>01:58:29</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>12</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026/07/08 21:43:27</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-32.841869, -70.9368</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-32.84187, -70.93680</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2026/07/08 23:46:39</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-32.841869, -70.9368</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-32.84187, -70.93680</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>02:03:12</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10428,13 +10605,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1333.79</v>
+        <v>1333.77</v>
       </c>
       <c r="C5" t="n">
         <v>59</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>134</v>
@@ -10599,13 +10776,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1198.45</v>
+        <v>1198.43</v>
       </c>
       <c r="C14" t="n">
         <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>122</v>
@@ -10618,13 +10795,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>334.53</v>
+        <v>334.4</v>
       </c>
       <c r="C15" t="n">
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>134</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/09 22:23:56</t>
+          <t>2026/07/09 23:23:56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:27:44</t>
+          <t>166:27:44</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/07/09 21:02:21</t>
+          <t>2026/07/09 23:02:21</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/07/09 21:09:50</t>
+          <t>2026/07/09 23:09:50</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>04:18:03</t>
+          <t>06:18:03</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/07/09 22:06:46</t>
+          <t>2026/07/09 23:06:46</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>05:01:00</t>
+          <t>06:01:00</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026/07/09 22:14:38</t>
+          <t>2026/07/09 23:14:22</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>05:00:16</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026/07/09 22:20:44</t>
+          <t>2026/07/09 23:21:36</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>05:01:10</t>
+          <t>06:02:02</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/07/09 22:25:55</t>
+          <t>2026/07/09 23:25:54</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>05:00:29</t>
+          <t>06:00:28</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026/07/09 21:15:28</t>
+          <t>2026/07/09 23:15:28</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/07/09 22:37:24</t>
+          <t>2026/07/09 23:37:23</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>02:57:32</t>
+          <t>03:57:31</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026/07/09 22:40:50</t>
+          <t>2026/07/09 23:40:50</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>02:03:05</t>
+          <t>03:03:05</t>
         </is>
       </c>
       <c r="L183" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N177"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/10 22:23:56</t>
+          <t>2026/07/10 23:23:56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>165:27:44</t>
+          <t>166:27:44</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/07/10 21:02:21</t>
+          <t>2026/07/10 23:02:21</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>36:00:00</t>
+          <t>38:00:00</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/07/10 22:14:21</t>
+          <t>2026/07/10 23:14:41</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>28:59:59</t>
+          <t>30:00:19</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/07/10 22:25:47</t>
+          <t>2026/07/10 23:25:55</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>29:00:21</t>
+          <t>30:00:29</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026/07/10 20:48:31</t>
+          <t>2026/07/10 22:48:31</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/07/10 20:39:24</t>
+          <t>2026/07/10 22:39:24</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>02:25:58</t>
+          <t>04:25:58</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/07/10 20:33:19</t>
+          <t>2026/07/10 22:33:19</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>02:01:50</t>
+          <t>04:01:50</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -10680,70 +10680,70 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026/07/10 21:20:30</t>
+          <t>2026/07/10 20:32:07</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-33.4551016, -70.6583816</t>
+          <t>-32.7431766, -70.7296583</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>-33.45510, -70.65838</t>
+          <t>-32.74318, -70.72966</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026/07/10 21:46:39</t>
+          <t>2026/07/10 22:33:51</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>-33.4763316, -70.6984033</t>
+          <t>-32.7430183, -70.7297866</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>-33.47633, -70.69840</t>
+          <t>-32.74302, -70.72979</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>00:26:09</t>
+          <t>02:01:44</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>7.12</v>
+        <v>0.02</v>
       </c>
       <c r="M176" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10752,47 +10752,283 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026/07/10 21:32:29</t>
+          <t>2026/07/10 20:51:15</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-33.484898, -70.77242</t>
+          <t>-32.8794316, -70.6088516</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>-33.48490, -70.77242</t>
+          <t>-32.87943, -70.60885</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026/07/10 21:44:07</t>
+          <t>2026/07/10 22:52:59</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>-33.484898, -70.77242</t>
+          <t>-32.879205, -70.6088216</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>-33.48490, -70.77242</t>
+          <t>-32.87920, -70.60882</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>00:11:38</t>
+          <t>02:01:44</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
       </c>
       <c r="N177" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>16</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026/07/10 21:20:30</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-33.4551016, -70.6583816</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-33.45510, -70.65838</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2026/07/10 21:46:26</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-33.476, -70.6980066</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-33.47600, -70.69801</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>00:25:56</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="M178" t="n">
+        <v>57</v>
+      </c>
+      <c r="N178" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>8</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026/07/10 21:35:16</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-32.838379, -70.95552</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-32.83838, -70.95552</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2026/07/10 23:32:50</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-32.838379, -70.95552</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-32.83838, -70.95552</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>01:57:34</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>17</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026/07/10 21:46:39</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-33.4763316, -70.6984033</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-33.47633, -70.69840</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2026/07/10 22:53:16</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-33.49691, -70.7077533</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-33.49691, -70.70775</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>01:06:37</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M180" t="n">
+        <v>64</v>
+      </c>
+      <c r="N180" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>18</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026/07/10 22:53:31</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-33.497, -70.7076666</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-33.49700, -70.70767</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2026/07/10 23:11:43</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-33.4761216, -70.6985266</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-33.47612, -70.69853</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>00:18:12</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M181" t="n">
+        <v>48</v>
+      </c>
+      <c r="N181" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10862,13 +11098,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1429.13</v>
+        <v>1429.09</v>
       </c>
       <c r="C3" t="n">
         <v>62</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>145</v>
@@ -10900,13 +11136,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1366.1</v>
+        <v>1366.07</v>
       </c>
       <c r="C5" t="n">
         <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>134</v>
@@ -11071,10 +11307,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1030.83</v>
+        <v>1039.87</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -11166,13 +11402,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1441.48</v>
+        <v>1440.96</v>
       </c>
       <c r="C19" t="n">
         <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
         <v>139</v>
@@ -11185,13 +11421,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>808.5700000000001</v>
+        <v>812.13</v>
       </c>
       <c r="C20" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>144</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N184"/>
+  <dimension ref="A1:N183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/11 22:23:56</t>
+          <t>2026/07/11 23:23:56</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>165:27:47</t>
+          <t>166:27:47</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/07/11 21:02:21</t>
+          <t>2026/07/11 23:02:21</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>60:00:00</t>
+          <t>62:00:00</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026/07/11 22:14:22</t>
+          <t>2026/07/11 23:14:22</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>53:00:00</t>
+          <t>54:00:00</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/07/11 22:25:54</t>
+          <t>2026/07/11 23:25:26</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>53:00:28</t>
+          <t>54:00:00</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/07/11 20:48:31</t>
+          <t>2026/07/11 22:48:31</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>28:00:00</t>
+          <t>30:00:00</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/07/11 20:47:44</t>
+          <t>2026/07/11 22:47:44</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>02:01:06</t>
+          <t>04:01:06</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -11034,11 +11034,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11047,37 +11047,37 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026/07/11 18:52:27</t>
+          <t>2026/07/11 19:13:18</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-32.838398, -70.95549</t>
+          <t>-33.4761183, -70.6984916</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>-32.83840, -70.95549</t>
+          <t>-33.47612, -70.69849</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026/07/11 21:49:58</t>
+          <t>2026/07/11 23:13:18</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>-32.838398, -70.95549</t>
+          <t>-33.4761183, -70.6984916</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>-32.83840, -70.95549</t>
+          <t>-33.47612, -70.69849</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>02:57:31</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -11093,11 +11093,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11106,37 +11106,37 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026/07/11 19:13:18</t>
+          <t>2026/07/11 21:25:31</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-33.4761183, -70.6984916</t>
+          <t>-32.841755, -70.936878</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69849</t>
+          <t>-32.84175, -70.93688</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026/07/11 21:13:18</t>
+          <t>2026/07/11 23:28:31</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>-33.4761183, -70.6984916</t>
+          <t>-32.841755, -70.936878</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69849</t>
+          <t>-32.84175, -70.93688</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>02:03:00</t>
         </is>
       </c>
       <c r="L183" t="n">
@@ -11146,65 +11146,6 @@
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>11</v>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>2026/07/11 21:25:31</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>-32.841755, -70.936878</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-32.84175, -70.93688</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>2026/07/11 22:28:31</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>-32.841755, -70.936878</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-32.84175, -70.93688</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>01:03:00</t>
-        </is>
-      </c>
-      <c r="L184" t="n">
-        <v>0</v>
-      </c>
-      <c r="M184" t="n">
-        <v>0</v>
-      </c>
-      <c r="N184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11275,13 +11216,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1307.7</v>
+        <v>1331.58</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>145</v>
@@ -11579,10 +11520,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1495.03</v>
+        <v>1500.04</v>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N184"/>
+  <dimension ref="A1:N185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/12 21:56:10</t>
+          <t>2026/07/12 23:56:10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/07/12 21:02:21</t>
+          <t>2026/07/12 23:02:21</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>84:00:00</t>
+          <t>86:00:00</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/07/12 22:31:40</t>
+          <t>2026/07/12 23:31:39</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>77:06:14</t>
+          <t>78:06:13</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/07/12 20:48:31</t>
+          <t>2026/07/12 22:48:31</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>52:00:00</t>
+          <t>54:00:00</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/07/12 20:39:59</t>
+          <t>2026/07/12 22:39:59</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>04:46:47</t>
+          <t>06:46:47</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026/07/12 21:09:47</t>
+          <t>2026/07/12 23:09:47</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>04:00:06</t>
+          <t>06:00:06</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -11205,6 +11205,65 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>6</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026/07/12 21:52:01</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-32.841676, -70.936803</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-32.84168, -70.93680</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2026/07/12 23:55:01</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-32.841676, -70.936803</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-32.84168, -70.93680</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>02:03:00</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11275,7 +11334,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1530.9</v>
+        <v>1531.1</v>
       </c>
       <c r="C3" t="n">
         <v>56</v>
@@ -11598,13 +11657,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>894.38</v>
+        <v>894.36</v>
       </c>
       <c r="C20" t="n">
         <v>73</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>144</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N175"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/13 21:56:10</t>
+          <t>2026/07/13 23:56:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>164:59:59</t>
+          <t>166:59:59</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/13 21:34:31</t>
+          <t>2026/07/13 23:34:38</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>139:00:10</t>
+          <t>141:00:17</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/07/13 21:02:21</t>
+          <t>2026/07/13 23:02:21</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>108:00:00</t>
+          <t>110:00:00</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026/07/13 21:31:38</t>
+          <t>2026/07/13 23:31:18</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>100:06:12</t>
+          <t>102:05:52</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026/07/13 21:48:19</t>
+          <t>2026/07/13 23:48:22</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>04:03:00</t>
+          <t>06:03:03</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/07/13 21:14:34</t>
+          <t>2026/07/13 23:14:34</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>02:00:23</t>
+          <t>04:00:23</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/07/13 21:15:19</t>
+          <t>2026/07/13 23:15:19</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026/07/13 21:55:48</t>
+          <t>2026/07/13 23:55:48</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/07/13 21:59:32</t>
+          <t>2026/07/13 23:59:32</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -10674,6 +10674,183 @@
         <v>0</v>
       </c>
       <c r="N175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>6</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026/07/13 20:25:42</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-32.838362, -70.955504</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-32.83836, -70.95550</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2026/07/13 23:23:11</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-32.838362, -70.955504</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-32.83836, -70.95550</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>02:57:29</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>12</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026/07/13 20:29:15</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-33.0873083, -71.3623783</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-33.08731, -71.36238</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2026/07/13 22:29:15</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-33.0873083, -71.3623783</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-33.08731, -71.36238</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>7</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026/07/13 21:25:42</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-33.4364766, -70.6295866</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-33.43648, -70.62959</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2026/07/13 23:25:42</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-33.4364766, -70.6295866</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-33.43648, -70.62959</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10750,7 +10927,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>145</v>
@@ -10763,13 +10940,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1007.38</v>
+        <v>1007.37</v>
       </c>
       <c r="C4" t="n">
         <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>138</v>
@@ -10972,13 +11149,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>389.52</v>
+        <v>389.49</v>
       </c>
       <c r="C15" t="n">
         <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>134</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/14 21:56:11</t>
+          <t>2026/07/14 23:56:11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>165:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/14 21:35:26</t>
+          <t>2026/07/14 23:36:40</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>163:01:05</t>
+          <t>165:02:19</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -4013,70 +4013,70 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>9</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026/07/08 12:27:27</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-34.2050183, -70.678095</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-34.20502, -70.67809</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026/07/08 12:41:16</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-34.2047983, -70.67986</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-34.20480, -70.67986</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>00:13:49</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M63" t="n">
+        <v>13</v>
+      </c>
+      <c r="N63" t="n">
         <v>8</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026/07/08 12:27:27</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-33.1345533, -71.5637166</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-33.13455, -71.56372</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2026/07/08 13:11:21</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-33.0873083, -71.3622866</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-33.08731, -71.36229</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>00:43:54</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="M63" t="n">
-        <v>125</v>
-      </c>
-      <c r="N63" t="n">
-        <v>59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4090,42 +4090,42 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.2050183, -70.678095</t>
+          <t>-33.1345533, -71.5637166</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.20502, -70.67809</t>
+          <t>-33.13455, -71.56372</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/07/08 12:41:16</t>
+          <t>2026/07/08 13:11:21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-34.2047983, -70.67986</t>
+          <t>-33.0873083, -71.3622866</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-34.20480, -70.67986</t>
+          <t>-33.08731, -71.36229</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:13:49</t>
+          <t>00:43:54</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.38</v>
+        <v>43.73</v>
       </c>
       <c r="M64" t="n">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/14 21:25:48</t>
+          <t>2026/07/14 23:25:22</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>136:31:55</t>
+          <t>138:31:29</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/14 21:57:19</t>
+          <t>2026/07/14 23:57:15</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>137:01:46</t>
+          <t>139:01:42</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/14 21:02:21</t>
+          <t>2026/07/14 23:02:21</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>132:00:00</t>
+          <t>134:00:00</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/07/14 21:31:23</t>
+          <t>2026/07/14 23:31:38</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>124:05:57</t>
+          <t>126:06:12</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026/07/14 20:33:04</t>
+          <t>2026/07/14 22:33:04</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>02:09:54</t>
+          <t>04:09:54</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/07/14 21:51:39</t>
+          <t>2026/07/14 23:51:39</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>03:03:06</t>
+          <t>05:03:06</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/07/14 21:28:08</t>
+          <t>2026/07/14 23:28:08</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>02:00:12</t>
+          <t>04:00:12</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/07/14 21:29:22</t>
+          <t>2026/07/14 23:29:22</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>02:00:06</t>
+          <t>04:00:06</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026/07/14 21:43:30</t>
+          <t>2026/07/14 23:43:30</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -10261,6 +10261,65 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026/07/14 20:50:47</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-32.838363, -70.95554</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-32.83836, -70.95554</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026/07/14 23:48:19</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-32.838363, -70.95554</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-32.83836, -70.95554</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>02:57:32</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10331,13 +10390,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1381.92</v>
+        <v>1381.91</v>
       </c>
       <c r="C3" t="n">
         <v>52</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>145</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -4013,11 +4013,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4031,101 +4031,101 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.2050183, -70.678095</t>
+          <t>-33.1345533, -71.5637166</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.20502, -70.67809</t>
+          <t>-33.13455, -71.56372</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/07/08 12:41:16</t>
+          <t>2026/07/08 13:11:21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.2047983, -70.67986</t>
+          <t>-33.0873083, -71.3622866</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.20480, -70.67986</t>
+          <t>-33.08731, -71.36229</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:13:49</t>
+          <t>00:43:54</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.38</v>
+        <v>43.73</v>
       </c>
       <c r="M63" t="n">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C64" t="n">
+        <v>9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026/07/08 12:27:27</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-34.2050183, -70.678095</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-34.20502, -70.67809</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026/07/08 12:41:16</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-34.2047983, -70.67986</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-34.20480, -70.67986</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>00:13:49</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M64" t="n">
+        <v>13</v>
+      </c>
+      <c r="N64" t="n">
         <v>8</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026/07/08 12:27:27</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-33.1345533, -71.5637166</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-33.13455, -71.56372</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2026/07/08 13:11:21</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-33.0873083, -71.3622866</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>-33.08731, -71.36229</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>00:43:54</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="M64" t="n">
-        <v>125</v>
-      </c>
-      <c r="N64" t="n">
-        <v>59</v>
       </c>
     </row>
     <row r="65">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N161"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/15 21:56:11</t>
+          <t>2026/07/15 23:56:11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>162:17:15</t>
+          <t>164:17:15</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/15 21:35:06</t>
+          <t>2026/07/15 23:36:26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>161:50:11</t>
+          <t>163:51:31</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/15 22:24:46</t>
+          <t>2026/07/15 23:25:59</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>161:30:53</t>
+          <t>162:32:06</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/15 21:57:24</t>
+          <t>2026/07/15 23:57:16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>161:01:51</t>
+          <t>163:01:43</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/07/15 21:02:21</t>
+          <t>2026/07/15 23:02:21</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>156:00:00</t>
+          <t>158:00:00</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/15 22:13:14</t>
+          <t>2026/07/15 23:13:37</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>148:58:51</t>
+          <t>149:59:14</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/15 21:31:21</t>
+          <t>2026/07/15 23:31:21</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>148:05:55</t>
+          <t>150:05:55</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/07/15 21:41:32</t>
+          <t>2026/07/15 23:39:24</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>89:02:14</t>
+          <t>91:00:06</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/07/15 21:12:02</t>
+          <t>2026/07/15 23:12:02</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>02:08:22</t>
+          <t>04:08:22</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/07/15 22:07:57</t>
+          <t>2026/07/15 23:07:57</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>02:57:56</t>
+          <t>03:57:56</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/07/15 21:20:18</t>
+          <t>2026/07/15 23:20:18</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9823,22 +9823,22 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/07/15 21:35:22</t>
+          <t>2026/07/15 21:31:52</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>-32.841741, -70.936882</t>
+          <t>-32.841759, -70.936896</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>-32.84174, -70.93688</t>
+          <t>-32.84176, -70.93690</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>01:32:41</t>
+          <t>01:29:11</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -9849,6 +9849,242 @@
       </c>
       <c r="N161" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>16</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026/07/15 20:51:39</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-33.4761616, -70.698455</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-33.47616, -70.69845</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026/07/15 22:56:09</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-33.4761616, -70.698455</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-33.47616, -70.69845</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>02:04:30</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026/07/15 21:16:54</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-32.743215, -70.7296266</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-32.74321, -70.72963</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026/07/15 23:21:50</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-32.7430133, -70.72982</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-32.74301, -70.72982</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>02:04:56</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>15</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026/07/15 21:32:18</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-32.841741, -70.936882</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-32.84174, -70.93688</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026/07/15 23:35:22</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-32.841741, -70.936882</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-32.84174, -70.93688</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>02:03:04</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>6</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026/07/15 21:41:29</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-33.4364349, -70.6291566</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-33.43643, -70.62916</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026/07/15 23:42:00</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-33.4364349, -70.6291566</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-33.43643, -70.62916</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>02:00:31</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9956,13 +10192,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1108.19</v>
+        <v>1108.15</v>
       </c>
       <c r="C5" t="n">
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>134</v>
@@ -10127,13 +10363,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1082.46</v>
+        <v>1082.44</v>
       </c>
       <c r="C14" t="n">
         <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>128</v>
@@ -10146,13 +10382,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>402.94</v>
+        <v>402.9</v>
       </c>
       <c r="C15" t="n">
         <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>124</v>
@@ -10241,13 +10477,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>842.54</v>
+        <v>842.53</v>
       </c>
       <c r="C20" t="n">
         <v>74</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>144</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/16 22:13:16</t>
+          <t>2026/07/16 23:13:38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>165:58:56</t>
+          <t>166:59:18</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/16 21:35:30</t>
+          <t>2026/07/16 23:34:30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>165:21:07</t>
+          <t>167:20:07</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/16 22:24:08</t>
+          <t>2026/07/16 23:23:39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>166:08:03</t>
+          <t>167:07:34</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/16 21:57:55</t>
+          <t>2026/07/16 23:57:29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>165:41:46</t>
+          <t>167:41:20</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/16 21:56:09</t>
+          <t>2026/07/16 23:56:09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>165:32:13</t>
+          <t>167:32:13</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/16 21:31:38</t>
+          <t>2026/07/16 23:31:21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:06:04</t>
+          <t>167:05:47</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/16 21:02:21</t>
+          <t>2026/07/16 23:02:21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>164:00:00</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/16 21:41:06</t>
+          <t>2026/07/16 23:41:06</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>113:01:48</t>
+          <t>115:01:48</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/07/16 21:12:02</t>
+          <t>2026/07/16 23:12:02</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>26:08:22</t>
+          <t>28:08:22</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/07/16 20:56:09</t>
+          <t>2026/07/16 22:56:09</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>24:04:30</t>
+          <t>26:04:30</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/07/16 21:42:00</t>
+          <t>2026/07/16 23:42:00</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>24:00:31</t>
+          <t>26:00:31</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/07/16 21:33:47</t>
+          <t>2026/07/16 23:33:50</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>09:03:08</t>
+          <t>11:03:11</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/07/16 22:21:39</t>
+          <t>2026/07/16 23:21:40</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>01:57:31</t>
+          <t>02:57:32</t>
         </is>
       </c>
       <c r="L146" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N146"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/10 04:00:00   Hasta : 2026/07/17 03:59:59</t>
+          <t>Desde : 2026/07/11 04:00:00   Hasta : 2026/07/18 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -545,53 +545,53 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/07/10 00:01:57</t>
+          <t>2026/07/11 00:00:16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.8791866, -70.6088583</t>
+          <t>-33.463178, -70.763329</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60886</t>
+          <t>-33.46318, -70.76333</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/10 08:33:17</t>
+          <t>2026/07/11 00:49:34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-33.9219266, -70.723675</t>
+          <t>-32.842017, -70.936795</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.92193, -70.72368</t>
+          <t>-32.84202, -70.93680</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>08:31:20</t>
+          <t>00:49:18</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>128.38</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,58 +599,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/07/10 00:06:46</t>
+          <t>2026/07/11 00:14:10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.36008, -70.807161</t>
+          <t>-33.360009, -70.807034</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80716</t>
+          <t>-33.36001, -70.80703</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/10 13:01:21</t>
+          <t>2026/07/17 22:13:37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.360145, -70.80695</t>
+          <t>-33.360044, -70.807063</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80695</t>
+          <t>-33.36004, -70.80706</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:54:35</t>
+          <t>165:59:27</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -658,58 +658,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/07/10 00:07:33</t>
+          <t>2026/07/11 00:14:15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870999</t>
+          <t>-34.579544, -70.961407</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88710</t>
+          <t>-34.57954, -70.96141</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/10 06:29:54</t>
+          <t>2026/07/17 21:35:07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-32.845275, -70.6859883</t>
+          <t>-34.579676, -70.961385</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.84528, -70.68599</t>
+          <t>-34.57968, -70.96139</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>06:22:21</t>
+          <t>165:20:52</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>33.84</v>
+        <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/07/10 00:11:20</t>
+          <t>2026/07/11 00:14:32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.436595, -70.6295799</t>
+          <t>-34.346017, -71.125783</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.43659, -70.62958</t>
+          <t>-34.34602, -71.12578</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/10 07:01:30</t>
+          <t>2026/07/12 01:04:03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.4454266, -70.6204983</t>
+          <t>-34.346035, -71.125736</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.44543, -70.62050</t>
+          <t>-34.34604, -71.12574</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06:50:10</t>
+          <t>24:49:31</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,41 +781,41 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/07/10 00:14:20</t>
+          <t>2026/07/11 00:15:14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.360009, -70.807034</t>
+          <t>-34.205421, -70.677325</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80703</t>
+          <t>-34.20542, -70.67732</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/16 23:13:38</t>
+          <t>2026/07/12 01:14:34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.360044, -70.807063</t>
+          <t>-34.205228, -70.67741</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80706</t>
+          <t>-34.20523, -70.67741</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:59:18</t>
+          <t>24:59:20</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/07/10 00:14:21</t>
+          <t>2026/07/11 00:15:29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-34.346017, -71.125783</t>
+          <t>-34.876497, -71.127268</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-34.34602, -71.12578</t>
+          <t>-34.87650, -71.12727</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/12 01:04:03</t>
+          <t>2026/07/17 21:24:04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-34.346035, -71.125736</t>
+          <t>-34.876357, -71.127275</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.34604, -71.12574</t>
+          <t>-34.87636, -71.12727</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>48:49:42</t>
+          <t>165:08:35</t>
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -899,41 +899,41 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/07/10 00:14:23</t>
+          <t>2026/07/11 00:16:09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-34.579544, -70.961407</t>
+          <t>-34.042744, -70.681743</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-34.57954, -70.96141</t>
+          <t>-34.04274, -70.68174</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/16 23:34:30</t>
+          <t>2026/07/17 21:57:27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-34.579676, -70.961385</t>
+          <t>-34.042673, -70.681782</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96139</t>
+          <t>-34.04267, -70.68178</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>167:20:07</t>
+          <t>165:41:18</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/07/10 00:15:16</t>
+          <t>2026/07/11 00:22:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677325</t>
+          <t>-33.360077, -70.807139</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67732</t>
+          <t>-33.36008, -70.80714</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/12 01:14:34</t>
+          <t>2026/07/13 08:59:50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.205228, -70.67741</t>
+          <t>-33.360023, -70.806713</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67741</t>
+          <t>-33.36002, -70.80671</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>48:59:18</t>
+          <t>56:36:57</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,41 +1017,41 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/07/10 00:16:05</t>
+          <t>2026/07/11 00:23:56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-34.876497, -71.127268</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-34.87650, -71.12727</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/16 23:23:39</t>
+          <t>2026/07/17 21:56:09</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-34.876357, -71.127275</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.87636, -71.12727</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>167:07:34</t>
+          <t>165:32:13</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,41 +1076,41 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/07/10 00:16:09</t>
+          <t>2026/07/11 00:25:27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.042744, -70.681743</t>
+          <t>-33.899806, -71.429473</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.04274, -70.68174</t>
+          <t>-33.89981, -71.42947</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/16 23:57:29</t>
+          <t>2026/07/17 21:31:24</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.042673, -70.681782</t>
+          <t>-33.899804, -71.429481</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.04267, -70.68178</t>
+          <t>-33.89980, -71.42948</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>167:41:20</t>
+          <t>165:05:57</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,58 +1130,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/07/10 00:21:36</t>
+          <t>2026/07/11 00:32:50</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.366903, -70.696373</t>
+          <t>-32.838379, -70.95552</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36690, -70.69637</t>
+          <t>-32.83838, -70.95552</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/10 02:40:58</t>
+          <t>2026/07/11 11:58:30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.367062, -70.696335</t>
+          <t>-32.841636, -70.954883</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36706, -70.69634</t>
+          <t>-32.84164, -70.95488</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>02:19:22</t>
+          <t>11:25:40</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.02</v>
+        <v>0.68</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/07/10 00:23:56</t>
+          <t>2026/07/11 00:33:19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.7976033, -70.8870816</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.79760, -70.88708</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/16 23:56:09</t>
+          <t>2026/07/11 09:20:04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.795745, -70.82016</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.79574, -70.82016</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>167:32:13</t>
+          <t>08:46:45</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>12.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,58 +1248,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/07/10 00:25:34</t>
+          <t>2026/07/11 00:33:51</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.899806, -71.429473</t>
+          <t>-32.7430183, -70.7297866</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.89981, -71.42947</t>
+          <t>-32.74302, -70.72979</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/16 23:31:21</t>
+          <t>2026/07/12 18:03:39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.899804, -71.429481</t>
+          <t>-32.748345, -70.6528216</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42948</t>
+          <t>-32.74835, -70.65282</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>167:05:47</t>
+          <t>41:29:48</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.01</v>
+        <v>9.07</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,58 +1307,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/07/10 00:37:24</t>
+          <t>2026/07/11 00:38:39</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-32.838371, -70.95549</t>
+          <t>-33.367062, -70.696335</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95549</t>
+          <t>-33.36706, -70.69634</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/10 08:52:39</t>
+          <t>2026/07/12 03:41:06</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-32.845561, -70.946014</t>
+          <t>-33.3674, -70.696184</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-32.84556, -70.94601</t>
+          <t>-33.36740, -70.69618</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>08:15:15</t>
+          <t>27:02:27</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.54</v>
+        <v>0.04</v>
       </c>
       <c r="M17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,53 +1371,53 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/07/10 00:40:50</t>
+          <t>2026/07/11 00:39:24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.48223, -70.764905</t>
+          <t>-33.0872966, -71.3623133</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.48223, -70.76490</t>
+          <t>-33.08730, -71.36231</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/10 09:06:26</t>
+          <t>2026/07/11 10:33:30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.359895, -70.806819</t>
+          <t>-33.0873116, -71.3622666</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80682</t>
+          <t>-33.08731, -71.36227</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>08:25:36</t>
+          <t>09:54:06</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>22.71</v>
+        <v>0.02</v>
       </c>
       <c r="M18" t="n">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,112 +1430,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/07/10 00:49:34</t>
+          <t>2026/07/11 00:48:31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-32.7430283, -70.7297933</t>
+          <t>-33.4362783, -70.629345</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72979</t>
+          <t>-33.43628, -70.62935</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/10 08:15:58</t>
+          <t>2026/07/13 07:06:26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.3599816, -70.8069633</t>
+          <t>-33.4449966, -70.61965</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80696</t>
+          <t>-33.44500, -70.61965</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07:26:24</t>
+          <t>54:17:55</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>89.73999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="M19" t="n">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="N19" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/07/10 01:02:21</t>
+          <t>2026/07/11 00:50:34</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.69573</t>
+          <t>-32.841721, -70.936771</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-32.84172, -70.93677</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/16 23:02:21</t>
+          <t>2026/07/11 11:01:46</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.69573</t>
+          <t>-32.840225, -70.950481</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-32.84022, -70.95048</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>10:11:12</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/07/10 01:09:50</t>
+          <t>2026/07/11 00:52:59</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36224</t>
+          <t>-32.879205, -70.6088216</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36224</t>
+          <t>-32.87920, -70.60882</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/07/10 07:48:03</t>
+          <t>2026/07/11 11:23:42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.0874916, -71.3605433</t>
+          <t>-32.7577933, -70.70241</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.08749, -71.36054</t>
+          <t>-32.75779, -70.70241</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06:38:13</t>
+          <t>10:30:43</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13.82</v>
+        <v>24.55</v>
       </c>
       <c r="M21" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="N21" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1602,111 +1602,111 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/07/10 01:15:28</t>
+          <t>2026/07/11 01:02:21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-33.4761083, -70.6985183</t>
+          <t>-33.3672816, -70.69573</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69852</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/07/10 09:44:44</t>
+          <t>2026/07/17 21:02:21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.4762949, -70.6983283</t>
+          <t>-33.3672816, -70.69573</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69833</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>08:29:16</t>
+          <t>164:00:00</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/07/10 03:40:26</t>
+          <t>2026/07/11 01:11:43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.367062, -70.696335</t>
+          <t>-33.4761216, -70.6985266</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.36706, -70.69634</t>
+          <t>-33.47612, -70.69853</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/07/12 03:41:06</t>
+          <t>2026/07/11 09:39:27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.4762599, -70.6983066</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.47626, -70.69831</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>48:00:40</t>
+          <t>08:27:44</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/07/10 06:31:09</t>
+          <t>2026/07/11 09:20:11</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.8519216, -70.6846433</t>
+          <t>-32.7958066, -70.8201433</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.85192, -70.68464</t>
+          <t>-32.79581, -70.82014</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/10 08:34:54</t>
+          <t>2026/07/11 12:58:56</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-34.2042633, -70.6791499</t>
+          <t>-32.7976783, -70.8873716</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-34.20426, -70.67915</t>
+          <t>-32.79768, -70.88737</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>02:03:45</t>
+          <t>03:38:45</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>162.12</v>
+        <v>10.68</v>
       </c>
       <c r="M24" t="n">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="N24" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/07/10 07:01:47</t>
+          <t>2026/07/11 09:40:42</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.4454533, -70.6204983</t>
+          <t>-33.47631, -70.6983433</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.44545, -70.62050</t>
+          <t>-33.47631, -70.69834</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/10 08:54:40</t>
+          <t>2026/07/11 10:04:32</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.4451566, -70.6213166</t>
+          <t>-33.3622616, -70.67011</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.44516, -70.62132</t>
+          <t>-33.36226, -70.67011</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01:52:53</t>
+          <t>00:23:50</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.1</v>
+        <v>18.73</v>
       </c>
       <c r="M25" t="n">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,47 +1843,47 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/07/10 07:49:18</t>
+          <t>2026/07/11 10:04:52</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.0869483, -71.3615533</t>
+          <t>-33.3620883, -70.6701433</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.08695, -71.36155</t>
+          <t>-33.36209, -70.67014</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/10 07:56:30</t>
+          <t>2026/07/11 13:44:08</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.0868966, -71.361895</t>
+          <t>-33.4501933, -70.5959533</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.08690, -71.36190</t>
+          <t>-33.45019, -70.59595</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>00:07:12</t>
+          <t>03:39:16</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.03</v>
+        <v>14.18</v>
       </c>
       <c r="M26" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,57 +1902,57 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/07/10 07:57:45</t>
+          <t>2026/07/11 10:33:52</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.0872916, -71.36234</t>
+          <t>-33.0873449, -71.362225</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36234</t>
+          <t>-33.08734, -71.36222</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/07/10 09:13:20</t>
+          <t>2026/07/11 11:24:44</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.0977616, -71.3297383</t>
+          <t>-33.0532533, -71.35565</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.09776, -71.32974</t>
+          <t>-33.05325, -71.35565</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01:15:35</t>
+          <t>00:50:52</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.19</v>
+        <v>5.32</v>
       </c>
       <c r="M27" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="N27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/07/10 08:16:12</t>
+          <t>2026/07/11 11:02:01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.3599566, -70.8071633</t>
+          <t>-32.840182, -70.950451</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80716</t>
+          <t>-32.84018, -70.95045</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/07/10 18:11:03</t>
+          <t>2026/07/11 11:09:43</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.7431983, -70.7329616</t>
+          <t>-32.838564, -70.953955</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.74320, -70.73296</t>
+          <t>-32.83856, -70.95395</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09:54:51</t>
+          <t>00:07:42</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>89.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="N28" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,57 +2020,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/07/10 08:34:30</t>
+          <t>2026/07/11 11:10:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-33.9318616, -70.715385</t>
+          <t>-32.838856, -70.954139</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-33.93186, -70.71538</t>
+          <t>-32.83886, -70.95414</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/07/10 09:24:20</t>
+          <t>2026/07/11 11:42:19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.2049783, -70.678645</t>
+          <t>-32.840186, -70.95055</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.20498, -70.67865</t>
+          <t>-32.84019, -70.95055</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:49:50</t>
+          <t>00:32:06</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>35.08</v>
+        <v>0.68</v>
       </c>
       <c r="M29" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="N29" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,112 +2079,112 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/07/10 08:36:09</t>
+          <t>2026/07/11 11:24:57</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-34.2042716, -70.6791216</t>
+          <t>-32.7578449, -70.7023266</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67912</t>
+          <t>-32.75784, -70.70233</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/07/10 08:44:07</t>
+          <t>2026/07/11 11:51:57</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-34.2054633, -70.6782166</t>
+          <t>-32.7581016, -70.7020483</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-34.20546, -70.67822</t>
+          <t>-32.75810, -70.70205</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:07:58</t>
+          <t>00:27:00</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
       <c r="M30" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/07/10 08:45:22</t>
+          <t>2026/07/11 11:25:59</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-34.2054, -70.67853</t>
+          <t>-33.053245, -71.3556866</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67853</t>
+          <t>-33.05324, -71.35569</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/07/10 08:51:37</t>
+          <t>2026/07/11 12:03:12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-34.2054, -70.67853</t>
+          <t>-33.0479799, -71.4053666</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67853</t>
+          <t>-33.04798, -71.40537</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:06:15</t>
+          <t>00:37:13</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/07/10 08:52:52</t>
+          <t>2026/07/11 11:42:25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-34.2049783, -70.678515</t>
+          <t>-32.84019, -70.950553</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-34.20498, -70.67852</t>
+          <t>-32.84019, -70.95055</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/07/10 09:24:42</t>
+          <t>2026/07/11 11:55:58</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-34.2055316, -70.6784566</t>
+          <t>-32.838552, -70.953968</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-34.20553, -70.67846</t>
+          <t>-32.83855, -70.95397</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:31:50</t>
+          <t>00:13:33</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.06</v>
+        <v>0.57</v>
       </c>
       <c r="M32" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/07/10 08:53:23</t>
+          <t>2026/07/11 11:53:12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.845294, -70.94578</t>
+          <t>-32.7581866, -70.7021666</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.84529, -70.94578</t>
+          <t>-32.75819, -70.70217</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/07/10 10:38:25</t>
+          <t>2026/07/11 12:13:26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-33.454408, -70.636503</t>
+          <t>-32.7500116, -70.7258933</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-33.45441, -70.63650</t>
+          <t>-32.75001, -70.72589</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>01:45:02</t>
+          <t>00:20:14</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>91.62</v>
+        <v>3.82</v>
       </c>
       <c r="M33" t="n">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="N33" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,53 +2315,53 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/07/10 08:55:24</t>
+          <t>2026/07/11 11:56:19</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-33.4442516, -70.621465</t>
+          <t>-32.838858, -70.95415</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-33.44425, -70.62147</t>
+          <t>-32.83886, -70.95415</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/07/10 10:49:00</t>
+          <t>2026/07/11 13:27:40</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-33.4358966, -70.6300566</t>
+          <t>-32.840831, -70.957916</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-33.43590, -70.63006</t>
+          <t>-32.84083, -70.95792</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:53:36</t>
+          <t>01:31:21</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6.01</v>
+        <v>0.48</v>
       </c>
       <c r="M34" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N34" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2374,47 +2374,47 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/07/10 09:07:26</t>
+          <t>2026/07/11 11:59:27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-33.360036, -70.807148</t>
+          <t>-32.842681, -70.955194</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80715</t>
+          <t>-32.84268, -70.95519</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/07/10 10:25:14</t>
+          <t>2026/07/11 12:07:03</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-33.37842, -70.683334</t>
+          <t>-32.840051, -70.958368</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-33.37842, -70.68333</t>
+          <t>-32.84005, -70.95837</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01:17:48</t>
+          <t>00:07:36</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="N35" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
@@ -2433,53 +2433,53 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/07/10 09:13:39</t>
+          <t>2026/07/11 12:04:27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.0977066, -71.3297833</t>
+          <t>-33.0479766, -71.4054033</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.09771, -71.32978</t>
+          <t>-33.04798, -71.40540</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/07/10 12:08:16</t>
+          <t>2026/07/11 12:12:14</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.4528466, -70.976265</t>
+          <t>-33.0485916, -71.40566</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.45285, -70.97626</t>
+          <t>-33.04859, -71.40566</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>02:54:37</t>
+          <t>00:07:47</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>84.26000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="M36" t="n">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/07/10 09:24:43</t>
+          <t>2026/07/11 12:07:39</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-34.2052166, -70.6786583</t>
+          <t>-32.840052, -70.958398</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-34.20522, -70.67866</t>
+          <t>-32.84005, -70.95840</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/07/10 10:22:06</t>
+          <t>2026/07/11 12:44:38</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-34.2055116, -70.6780316</t>
+          <t>-32.780731, -70.967681</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67803</t>
+          <t>-32.78073, -70.96768</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:57:23</t>
+          <t>00:36:59</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.09</v>
+        <v>10.64</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/07/10 09:24:49</t>
+          <t>2026/07/11 12:13:29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-34.2055366, -70.6782983</t>
+          <t>-33.048705, -71.4056916</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67830</t>
+          <t>-33.04870, -71.40569</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/07/10 11:02:46</t>
+          <t>2026/07/11 13:21:53</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-34.2055266, -70.6778766</t>
+          <t>-33.045615, -71.4194633</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-34.20553, -70.67788</t>
+          <t>-33.04561, -71.41946</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01:37:57</t>
+          <t>01:08:24</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.04</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,53 +2610,53 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/07/10 09:45:59</t>
+          <t>2026/07/11 12:14:41</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.47632, -70.6983599</t>
+          <t>-32.7500033, -70.72595</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69836</t>
+          <t>-32.75000, -70.72595</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/07/10 10:37:12</t>
+          <t>2026/07/11 13:07:32</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.3751883, -70.6331416</t>
+          <t>-32.8792033, -70.6089516</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.37519, -70.63314</t>
+          <t>-32.87920, -70.60895</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:51:13</t>
+          <t>00:52:51</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>23.94</v>
+        <v>23.08</v>
       </c>
       <c r="M39" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="N39" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/07/10 10:22:23</t>
+          <t>2026/07/11 12:45:24</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-34.2055216, -70.6778683</t>
+          <t>-32.780678, -70.967698</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-34.20552, -70.67787</t>
+          <t>-32.78068, -70.96770</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/07/10 10:32:47</t>
+          <t>2026/07/11 12:56:21</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-34.2080016, -70.67769</t>
+          <t>-32.790903, -70.976106</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-34.20800, -70.67769</t>
+          <t>-32.79090, -70.97611</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:10:24</t>
+          <t>00:10:57</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.49</v>
+        <v>1.57</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/07/10 10:25:56</t>
+          <t>2026/07/11 12:56:30</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.37841, -70.683386</t>
+          <t>-32.79091, -70.976137</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.37841, -70.68339</t>
+          <t>-32.79091, -70.97614</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/07/10 11:02:59</t>
+          <t>2026/07/11 15:24:03</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.389492, -70.684218</t>
+          <t>-32.790911, -70.976099</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.38949, -70.68422</t>
+          <t>-32.79091, -70.97610</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:37:03</t>
+          <t>02:27:33</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>5.68</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="N41" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/07/10 10:33:30</t>
+          <t>2026/07/11 12:59:11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-34.2080716, -70.6775849</t>
+          <t>-32.7976, -70.8870966</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-34.20807, -70.67758</t>
+          <t>-32.79760, -70.88710</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/07/10 11:06:40</t>
+          <t>2026/07/11 13:27:26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-34.2075799, -70.6768166</t>
+          <t>-32.8006616, -70.82641</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-34.20758, -70.67682</t>
+          <t>-32.80066, -70.82641</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:33:10</t>
+          <t>00:28:15</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.11</v>
+        <v>9.27</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,112 +2846,112 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/07/10 10:37:33</t>
+          <t>2026/07/11 13:07:57</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-33.3751966, -70.6330516</t>
+          <t>-32.8790016, -70.6095083</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-33.37520, -70.63305</t>
+          <t>-32.87900, -70.60951</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/07/10 12:30:46</t>
+          <t>2026/07/11 13:41:35</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-34.2052983, -70.6775349</t>
+          <t>-32.87908, -70.6093549</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-34.20530, -70.67753</t>
+          <t>-32.87908, -70.60935</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>01:53:13</t>
+          <t>00:33:38</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>107.37</v>
+        <v>0.02</v>
       </c>
       <c r="M43" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/07/10 10:39:21</t>
+          <t>2026/07/11 13:23:08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.454504, -70.636984</t>
+          <t>-33.045635, -71.4192533</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.45450, -70.63698</t>
+          <t>-33.04563, -71.41925</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/07/10 10:47:47</t>
+          <t>2026/07/11 14:18:14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.454504, -70.636984</t>
+          <t>-33.094455, -71.3530933</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.45450, -70.63698</t>
+          <t>-33.09446, -71.35309</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:08:26</t>
+          <t>00:55:06</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>12.29</v>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/07/10 10:48:14</t>
+          <t>2026/07/11 13:28:29</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-33.454486, -70.637001</t>
+          <t>-32.805665, -70.8247483</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-33.45449, -70.63700</t>
+          <t>-32.80566, -70.82475</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/07/10 11:26:56</t>
+          <t>2026/07/11 14:26:20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.335549, -70.711538</t>
+          <t>-32.7976383, -70.8872133</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.33555, -70.71154</t>
+          <t>-32.79764, -70.88721</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:38:42</t>
+          <t>00:57:51</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>16.88</v>
+        <v>9.74</v>
       </c>
       <c r="M45" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="N45" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/07/10 10:50:15</t>
+          <t>2026/07/11 13:28:40</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-33.4362316, -70.6295533</t>
+          <t>-32.84062, -70.958921</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-33.43623, -70.62955</t>
+          <t>-32.84062, -70.95892</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/07/10 12:13:59</t>
+          <t>2026/07/11 13:46:13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-33.367415, -70.6960649</t>
+          <t>-32.842, -70.936864</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-33.36742, -70.69606</t>
+          <t>-32.84200, -70.93686</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>01:23:44</t>
+          <t>00:17:33</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>13.57</v>
+        <v>2.77</v>
       </c>
       <c r="M46" t="n">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="N46" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,53 +3082,53 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/07/10 11:03:03</t>
+          <t>2026/07/11 13:42:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-34.2054983, -70.6781466</t>
+          <t>-32.8792166, -70.60879</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-34.20550, -70.67815</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/07/10 11:33:41</t>
+          <t>2026/07/11 14:27:13</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-34.2080433, -70.6770483</t>
+          <t>-32.8297466, -70.5968316</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-34.20804, -70.67705</t>
+          <t>-32.82975, -70.59683</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:30:38</t>
+          <t>00:45:10</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.51</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3141,57 +3141,57 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/07/10 11:03:08</t>
+          <t>2026/07/11 13:45:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.389471, -70.684119</t>
+          <t>-33.451215, -70.59607</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.38947, -70.68412</t>
+          <t>-33.45121, -70.59607</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/07/10 11:26:05</t>
+          <t>2026/07/11 15:03:52</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.366996, -70.685469</t>
+          <t>-33.2784999, -70.70501</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.36700, -70.68547</t>
+          <t>-33.27850, -70.70501</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:22:57</t>
+          <t>01:18:29</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.66</v>
+        <v>28.24</v>
       </c>
       <c r="M48" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="N48" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,47 +3200,47 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/07/10 11:07:55</t>
+          <t>2026/07/11 13:46:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-34.2074249, -70.6767116</t>
+          <t>-32.841751, -70.936874</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-34.20742, -70.67671</t>
+          <t>-32.84175, -70.93687</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/07/10 11:35:24</t>
+          <t>2026/07/11 14:07:16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-34.2042699, -70.6791383</t>
+          <t>-32.842912, -70.955311</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67914</t>
+          <t>-32.84291, -70.95531</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:27:29</t>
+          <t>00:20:23</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.75</v>
+        <v>2.2</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/07/10 11:26:21</t>
+          <t>2026/07/11 14:08:12</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.367005, -70.68547</t>
+          <t>-32.842996, -70.955344</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.36700, -70.68547</t>
+          <t>-32.84300, -70.95534</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/07/10 12:08:47</t>
+          <t>2026/07/11 15:07:19</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.36309, -70.786291</t>
+          <t>-32.841767, -70.936908</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.36309, -70.78629</t>
+          <t>-32.84177, -70.93691</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:42:26</t>
+          <t>00:59:07</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>13.64</v>
+        <v>2.09</v>
       </c>
       <c r="M50" t="n">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="N50" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,47 +3318,47 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/07/10 11:27:12</t>
+          <t>2026/07/11 14:18:30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-33.335553, -70.711545</t>
+          <t>-33.0942783, -71.3530133</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-33.33555, -70.71155</t>
+          <t>-33.09428, -71.35301</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/07/10 13:57:56</t>
+          <t>2026/07/11 14:29:41</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-32.838371, -70.956152</t>
+          <t>-33.0873066, -71.3622666</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95615</t>
+          <t>-33.08731, -71.36227</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>02:30:44</t>
+          <t>00:11:11</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>73.3</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="N51" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,47 +3377,47 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/07/10 11:34:05</t>
+          <t>2026/07/11 14:27:07</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-34.2078466, -70.6769966</t>
+          <t>-32.797605, -70.8870833</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-34.20785, -70.67700</t>
+          <t>-32.79760, -70.88708</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/07/10 11:57:10</t>
+          <t>2026/07/11 15:59:09</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-34.20428, -70.6786599</t>
+          <t>-32.5634416, -70.6947283</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67866</t>
+          <t>-32.56344, -70.69473</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:23:05</t>
+          <t>01:32:02</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.62</v>
+        <v>41.6</v>
       </c>
       <c r="M52" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="N52" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
@@ -3436,57 +3436,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/07/10 11:35:29</t>
+          <t>2026/07/11 14:27:39</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-34.2042616, -70.6791116</t>
+          <t>-32.8295516, -70.5973733</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-34.20426, -70.67911</t>
+          <t>-32.82955, -70.59737</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/07/10 12:17:25</t>
+          <t>2026/07/11 16:40:35</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-34.2049233, -70.6781116</t>
+          <t>-32.85666, -70.5865149</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-34.20492, -70.67811</t>
+          <t>-32.85666, -70.58651</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:41:56</t>
+          <t>02:12:56</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.13</v>
+        <v>5.39</v>
       </c>
       <c r="M53" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/07/10 11:58:25</t>
+          <t>2026/07/11 14:29:54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-34.2042866, -70.679065</t>
+          <t>-33.0872833, -71.36232</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-34.20429, -70.67906</t>
+          <t>-33.08728, -71.36232</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/07/10 12:07:17</t>
+          <t>2026/07/12 11:16:46</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-34.204865, -70.6780933</t>
+          <t>-33.087305, -71.3623016</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-34.20486, -70.67809</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:08:52</t>
+          <t>20:46:52</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="M54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/07/10 12:07:23</t>
+          <t>2026/07/11 15:05:07</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-34.2049366, -70.67809</t>
+          <t>-33.27849, -70.7050983</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-34.20494, -70.67809</t>
+          <t>-33.27849, -70.70510</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/07/10 12:17:51</t>
+          <t>2026/07/11 16:24:16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-34.2049383, -70.6780766</t>
+          <t>-33.4762616, -70.6983416</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-34.20494, -70.67808</t>
+          <t>-33.47626, -70.69834</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:10:28</t>
+          <t>01:19:09</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>39.2</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,53 +3613,53 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/07/10 12:09:31</t>
+          <t>2026/07/11 15:07:25</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-33.4529216, -70.976095</t>
+          <t>-32.841764, -70.936909</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-33.45292, -70.97610</t>
+          <t>-32.84176, -70.93691</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/07/10 12:50:19</t>
+          <t>2026/07/11 20:42:43</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-33.4028166, -70.7453866</t>
+          <t>-32.838737, -70.954064</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-33.40282, -70.74539</t>
+          <t>-32.83874, -70.95406</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:40:48</t>
+          <t>05:35:18</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>24.99</v>
+        <v>2.29</v>
       </c>
       <c r="M56" t="n">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="N56" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/07/10 12:09:47</t>
+          <t>2026/07/11 15:24:16</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.363014, -70.786392</t>
+          <t>-32.790913, -70.976126</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.36301, -70.78639</t>
+          <t>-32.79091, -70.97613</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/07/10 12:20:47</t>
+          <t>2026/07/11 18:51:35</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.35995, -70.806986</t>
+          <t>-32.838389, -70.955829</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80699</t>
+          <t>-32.83839, -70.95583</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:11:00</t>
+          <t>03:27:19</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.06</v>
+        <v>15.11</v>
       </c>
       <c r="M57" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="N57" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/07/10 12:14:36</t>
+          <t>2026/07/11 16:00:24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-33.367395, -70.6960233</t>
+          <t>-32.5634049, -70.6950866</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69602</t>
+          <t>-32.56340, -70.69509</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/07/10 16:48:01</t>
+          <t>2026/07/11 18:11:32</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-33.43609, -70.6298866</t>
+          <t>-32.7416316, -70.7269533</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-33.43609, -70.62989</t>
+          <t>-32.74163, -70.72695</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>04:33:25</t>
+          <t>02:11:08</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>19.55</v>
+        <v>22.16</v>
       </c>
       <c r="M58" t="n">
         <v>94</v>
       </c>
       <c r="N58" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,47 +3790,47 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/07/10 12:18:05</t>
+          <t>2026/07/11 16:24:33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-34.205, -70.6780483</t>
+          <t>-33.4763066, -70.6983766</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-34.20500, -70.67805</t>
+          <t>-33.47631, -70.69838</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/07/10 12:45:07</t>
+          <t>2026/07/11 18:01:34</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-34.1899183, -70.7092083</t>
+          <t>-33.3895366, -70.6738566</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-34.18992, -70.70921</t>
+          <t>-33.38954, -70.67386</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:27:02</t>
+          <t>01:37:01</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.64</v>
+        <v>17.06</v>
       </c>
       <c r="M59" t="n">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="N59" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/07/10 12:18:40</t>
+          <t>2026/07/11 16:40:51</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.2052233, -70.6780916</t>
+          <t>-32.85676, -70.586175</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.20522, -70.67809</t>
+          <t>-32.85676, -70.58617</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/07/10 12:32:25</t>
+          <t>2026/07/11 17:31:47</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-34.2042999, -70.6789233</t>
+          <t>-32.8791349, -70.60927</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-34.20430, -70.67892</t>
+          <t>-32.87913, -70.60927</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:13:45</t>
+          <t>00:50:56</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.16</v>
+        <v>12.93</v>
       </c>
       <c r="M60" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="N60" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,47 +3908,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/07/10 12:21:47</t>
+          <t>2026/07/11 17:31:59</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-33.360005, -70.807107</t>
+          <t>-32.8790366, -70.6094516</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80711</t>
+          <t>-32.87904, -70.60945</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/07/10 12:53:05</t>
+          <t>2026/07/11 21:59:41</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-33.401615, -70.749443</t>
+          <t>-32.8661516, -70.6240483</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-33.40161, -70.74944</t>
+          <t>-32.86615, -70.62405</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:31:18</t>
+          <t>04:27:42</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>9.84</v>
+        <v>7.89</v>
       </c>
       <c r="M61" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="N61" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/07/10 12:31:03</t>
+          <t>2026/07/11 18:01:57</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-34.20489, -70.6780516</t>
+          <t>-33.389325, -70.6740466</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-34.20489, -70.67805</t>
+          <t>-33.38932, -70.67405</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/07/10 12:38:45</t>
+          <t>2026/07/11 18:18:09</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-34.2048766, -70.6781533</t>
+          <t>-33.3620066, -70.670115</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-34.20488, -70.67815</t>
+          <t>-33.36201, -70.67011</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:07:42</t>
+          <t>00:16:12</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.01</v>
+        <v>3.61</v>
       </c>
       <c r="M62" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,47 +4026,47 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/07/10 12:33:30</t>
+          <t>2026/07/11 18:12:37</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.20495, -70.6780999</t>
+          <t>-32.7446149, -70.7280133</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.20495, -70.67810</t>
+          <t>-32.74461, -70.72801</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/07/10 12:47:14</t>
+          <t>2026/07/11 18:45:23</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.1900799, -70.7094333</t>
+          <t>-32.79772, -70.8874066</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.19008, -70.70943</t>
+          <t>-32.79772, -70.88741</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:13:44</t>
+          <t>00:32:46</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.62</v>
+        <v>18.65</v>
       </c>
       <c r="M63" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="N63" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/07/10 12:39:01</t>
+          <t>2026/07/11 18:18:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.2048916, -70.67865</t>
+          <t>-33.362025, -70.67014</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.20489, -70.67865</t>
+          <t>-33.36203, -70.67014</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/07/10 13:39:24</t>
+          <t>2026/07/11 18:42:37</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-34.20778, -70.6775483</t>
+          <t>-33.353255, -70.6699483</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-34.20778, -70.67755</t>
+          <t>-33.35325, -70.66995</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>01:00:23</t>
+          <t>00:24:17</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="M64" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/07/10 12:45:09</t>
+          <t>2026/07/11 18:43:03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-34.1899183, -70.7092083</t>
+          <t>-33.3532749, -70.6698816</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-34.18992, -70.70921</t>
+          <t>-33.35327, -70.66988</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/07/10 13:38:24</t>
+          <t>2026/07/11 19:12:09</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.205745, -70.67617</t>
+          <t>-33.4762666, -70.69831</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.20575, -70.67617</t>
+          <t>-33.47627, -70.69831</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:53:15</t>
+          <t>00:29:06</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.04</v>
+        <v>18.94</v>
       </c>
       <c r="M65" t="n">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="N65" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,57 +4203,57 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/07/10 12:47:38</t>
+          <t>2026/07/11 18:46:38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.1899233, -70.70925</t>
+          <t>-32.7976, -70.8870766</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.18992, -70.70925</t>
+          <t>-32.79760, -70.88708</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/07/10 13:44:59</t>
+          <t>2026/07/12 11:01:08</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.2071816, -70.6771116</t>
+          <t>-32.7465733, -70.7223516</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.20718, -70.67711</t>
+          <t>-32.74657, -70.72235</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>00:57:21</t>
+          <t>16:14:30</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.18</v>
+        <v>19.65</v>
       </c>
       <c r="M66" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="N66" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,116 +4262,116 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/07/10 12:51:34</t>
+          <t>2026/07/11 18:52:27</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-33.4011949, -70.75039</t>
+          <t>-32.838398, -70.95549</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-33.40119, -70.75039</t>
+          <t>-32.83840, -70.95549</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/07/10 14:06:35</t>
+          <t>2026/07/12 00:07:41</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-33.3632066, -70.7861066</t>
+          <t>-32.785516, -70.960409</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-33.36321, -70.78611</t>
+          <t>-32.78552, -70.96041</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>01:15:01</t>
+          <t>05:15:14</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>6.76</v>
+        <v>31.28</v>
       </c>
       <c r="M67" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N67" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026/07/11 19:13:18</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-33.4761183, -70.6984916</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-33.47612, -70.69849</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026/07/12 14:16:01</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-33.4762183, -70.6983649</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-33.47622, -70.69836</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>19:02:43</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M68" t="n">
         <v>8</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026/07/10 12:53:29</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-33.401248, -70.750304</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-33.40125, -70.75030</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2026/07/10 14:10:50</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-33.360357, -70.805323</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-33.36036, -70.80532</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>01:17:21</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="M68" t="n">
-        <v>103</v>
-      </c>
       <c r="N68" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,57 +4380,57 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/07/10 13:39:24</t>
+          <t>2026/07/11 20:42:55</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.207765, -70.6772416</t>
+          <t>-32.838769, -70.954084</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.20777, -70.67724</t>
+          <t>-32.83877, -70.95408</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/07/10 17:19:39</t>
+          <t>2026/07/11 21:25:19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-32.9742583, -70.689555</t>
+          <t>-32.841774, -70.936893</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-32.97426, -70.68955</t>
+          <t>-32.84177, -70.93689</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>03:40:15</t>
+          <t>00:42:24</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>147.71</v>
+        <v>2.29</v>
       </c>
       <c r="M69" t="n">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="N69" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,47 +4439,47 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/07/10 13:39:29</t>
+          <t>2026/07/11 21:25:31</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-34.2078333, -70.677545</t>
+          <t>-32.841755, -70.936878</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-34.20783, -70.67754</t>
+          <t>-32.84175, -70.93688</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/07/10 13:54:35</t>
+          <t>2026/07/12 11:12:02</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-34.2055466, -70.6768</t>
+          <t>-32.838851, -70.954161</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67680</t>
+          <t>-32.83885, -70.95416</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:15:06</t>
+          <t>13:46:31</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="N70" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/07/10 13:45:30</t>
+          <t>2026/07/11 21:59:54</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.2078116, -70.6771016</t>
+          <t>-32.866115, -70.6240783</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.20781, -70.67710</t>
+          <t>-32.86612, -70.62408</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/07/10 14:35:24</t>
+          <t>2026/07/11 22:43:12</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-34.2081299, -70.6769766</t>
+          <t>-32.8664116, -70.6238883</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-34.20813, -70.67698</t>
+          <t>-32.86641, -70.62389</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:49:54</t>
+          <t>00:43:18</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.04</v>
+        <v>6.75</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/07/10 13:54:54</t>
+          <t>2026/07/11 22:43:40</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-34.2055416, -70.678245</t>
+          <t>-32.8661333, -70.62408</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67825</t>
+          <t>-32.86613, -70.62408</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/07/10 14:19:40</t>
+          <t>2026/07/11 23:22:55</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-34.20489, -70.6779183</t>
+          <t>-32.8792266, -70.6088699</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-34.20489, -70.67792</t>
+          <t>-32.87923, -70.60887</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:24:46</t>
+          <t>00:39:15</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.17</v>
+        <v>3.74</v>
       </c>
       <c r="M72" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="N72" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/07/10 13:58:41</t>
+          <t>2026/07/11 23:23:12</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-32.838381, -70.955498</t>
+          <t>-32.8792216, -70.6087933</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95550</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/07/10 17:41:52</t>
+          <t>2026/07/12 11:16:04</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-32.840309, -70.960032</t>
+          <t>-32.8678316, -70.6224066</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-32.84031, -70.96003</t>
+          <t>-32.86783, -70.62241</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>03:43:11</t>
+          <t>11:52:52</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.72</v>
+        <v>3.46</v>
       </c>
       <c r="M73" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="N73" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,57 +4675,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/07/10 13:59:08</t>
+          <t>2026/07/12 04:39:18</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.360145, -70.80695</t>
+          <t>-33.3674, -70.696184</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80695</t>
+          <t>-33.36740, -70.69618</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/07/10 14:28:54</t>
+          <t>2026/07/17 21:39:23</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.360077, -70.806781</t>
+          <t>-33.366989, -70.69623</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80678</t>
+          <t>-33.36699, -70.69623</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:29:46</t>
+          <t>137:00:05</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,57 +4734,57 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/07/10 14:09:05</t>
+          <t>2026/07/12 18:43:14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.3614333, -70.7884233</t>
+          <t>-32.7435066, -70.7327433</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.36143, -70.78842</t>
+          <t>-32.74351, -70.73274</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/10 14:18:50</t>
+          <t>2026/07/12 19:12:44</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.359845, -70.8067533</t>
+          <t>-32.7435616, -70.736105</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.35984, -70.80675</t>
+          <t>-32.74356, -70.73610</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:09:45</t>
+          <t>00:29:30</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.78</v>
+        <v>1.77</v>
       </c>
       <c r="M75" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="N75" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,44 +4793,44 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/07/10 14:11:41</t>
+          <t>2026/07/12 19:13:42</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.360051, -70.80718</t>
+          <t>-32.743345, -70.7326616</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80718</t>
+          <t>-32.74334, -70.73266</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/07/10 14:51:23</t>
+          <t>2026/07/12 20:25:18</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.360023, -70.807053</t>
+          <t>-32.74317, -70.729675</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80705</t>
+          <t>-32.74317, -70.72968</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>00:39:42</t>
+          <t>01:11:36</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.46</v>
+        <v>2.07</v>
       </c>
       <c r="M76" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N76" t="n">
         <v>14</v>
@@ -4839,11 +4839,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/07/10 14:19:47</t>
+          <t>2026/07/12 20:26:33</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.3600366, -70.80699</t>
+          <t>-32.7430583, -70.7297799</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80699</t>
+          <t>-32.74306, -70.72978</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/07/10 14:35:06</t>
+          <t>2026/07/13 07:15:14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.3601833, -70.8090166</t>
+          <t>-32.8657616, -70.681495</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.36018, -70.80902</t>
+          <t>-32.86576, -70.68149</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:15:19</t>
+          <t>10:48:41</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.19</v>
+        <v>16.37</v>
       </c>
       <c r="M77" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="N77" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,106 +4911,106 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/07/10 14:19:52</t>
+          <t>2026/07/13 08:58:50</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-34.204965, -70.67809</t>
+          <t>-33.4362533, -70.6295033</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-34.20497, -70.67809</t>
+          <t>-33.43625, -70.62950</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/07/10 14:28:35</t>
+          <t>2026/07/13 10:02:50</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-34.2045633, -70.6777733</t>
+          <t>-33.3672499, -70.6955516</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-34.20456, -70.67777</t>
+          <t>-33.36725, -70.69555</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:08:43</t>
+          <t>01:04:00</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.06</v>
+        <v>13.38</v>
       </c>
       <c r="M78" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="N78" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/07/10 14:28:39</t>
+          <t>2026/07/13 09:23:56</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-34.2045816, -70.67773</t>
+          <t>-33.359904, -70.807156</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-34.20458, -70.67773</t>
+          <t>-33.35990, -70.80716</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/07/10 14:36:18</t>
+          <t>2026/07/13 09:45:20</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-34.2057683, -70.676135</t>
+          <t>-33.360145, -70.80659</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-34.20577, -70.67614</t>
+          <t>-33.36015, -70.80659</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:07:39</t>
+          <t>00:21:24</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -5029,44 +5029,44 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/07/10 14:29:07</t>
+          <t>2026/07/13 09:45:47</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-33.360089, -70.806739</t>
+          <t>-33.360123, -70.806616</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-33.36009, -70.80674</t>
+          <t>-33.36012, -70.80662</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/07/10 14:39:37</t>
+          <t>2026/07/13 10:36:19</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.359947, -70.807052</t>
+          <t>-33.360119, -70.806713</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80705</t>
+          <t>-33.36012, -70.80671</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:10:30</t>
+          <t>00:50:32</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
         <v>3</v>
@@ -5075,11 +5075,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,116 +5088,116 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/07/10 14:36:12</t>
+          <t>2026/07/13 10:03:12</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-34.207795, -70.6768433</t>
+          <t>-33.36728, -70.695735</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-34.20779, -70.67684</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/07/10 14:51:13</t>
+          <t>2026/07/13 18:48:27</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-34.2057433, -70.6761733</t>
+          <t>-33.4360999, -70.6298916</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-34.20574, -70.67617</t>
+          <t>-33.43610, -70.62989</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:15:01</t>
+          <t>08:45:15</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.15</v>
+        <v>19.08</v>
       </c>
       <c r="M81" t="n">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="N81" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/07/10 14:36:21</t>
+          <t>2026/07/13 10:36:41</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-33.360575, -70.8090283</t>
+          <t>-33.360039, -70.806789</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-33.36057, -70.80903</t>
+          <t>-33.36004, -70.80679</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/07/10 15:13:25</t>
+          <t>2026/07/13 10:48:50</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-33.3601616, -70.8070583</t>
+          <t>-33.360072, -70.806802</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-33.36016, -70.80706</t>
+          <t>-33.36007, -70.80680</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:37:04</t>
+          <t>00:12:09</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N82" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,47 +5206,47 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/07/10 14:36:52</t>
+          <t>2026/07/13 10:49:00</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-34.2072933, -70.6768349</t>
+          <t>-33.360103, -70.806819</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-34.20729, -70.67683</t>
+          <t>-33.36010, -70.80682</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/07/10 15:31:07</t>
+          <t>2026/07/13 12:24:43</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-34.2055466, -70.6768633</t>
+          <t>-33.359879, -70.807133</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67686</t>
+          <t>-33.35988, -70.80713</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>00:54:15</t>
+          <t>01:35:43</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="M83" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/07/10 14:40:14</t>
+          <t>2026/07/13 12:25:07</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.359899, -70.807137</t>
+          <t>-33.359881, -70.807152</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80714</t>
+          <t>-33.35988, -70.80715</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/07/10 14:53:05</t>
+          <t>2026/07/13 14:25:09</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.359917, -70.807078</t>
+          <t>-33.360174, -70.806587</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.35992, -70.80708</t>
+          <t>-33.36017, -70.80659</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:12:51</t>
+          <t>02:00:02</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,112 +5324,112 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/07/10 14:51:37</t>
+          <t>2026/07/13 14:22:11</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-33.36004, -70.807149</t>
+          <t>-34.2055566, -70.6783433</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80715</t>
+          <t>-34.20556, -70.67834</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/07/10 17:10:16</t>
+          <t>2026/07/13 16:00:08</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.48211, -70.76537</t>
+          <t>-33.744805, -70.7382516</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.48211, -70.76537</t>
+          <t>-33.74480, -70.73825</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>02:18:39</t>
+          <t>01:37:57</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>19.42</v>
+        <v>56.03</v>
       </c>
       <c r="M85" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="N85" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/07/10 14:52:27</t>
+          <t>2026/07/13 14:25:31</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-34.207195, -70.6768216</t>
+          <t>-33.360108, -70.806563</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-34.20719, -70.67682</t>
+          <t>-33.36011, -70.80656</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/10 17:00:57</t>
+          <t>2026/07/13 15:19:07</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.21665, -70.7669633</t>
+          <t>-33.360027, -70.807117</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.21665, -70.76696</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>02:08:30</t>
+          <t>00:53:36</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>117.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="N86" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/07/10 14:53:41</t>
+          <t>2026/07/13 14:27:42</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.359971, -70.806977</t>
+          <t>-33.3601166, -70.8064883</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80698</t>
+          <t>-33.36012, -70.80649</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/07/10 15:22:39</t>
+          <t>2026/07/13 15:17:08</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.360036, -70.806665</t>
+          <t>-33.36016, -70.8067916</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80666</t>
+          <t>-33.36016, -70.80679</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>00:28:58</t>
+          <t>00:49:26</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,175 +5501,175 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/07/10 15:14:16</t>
+          <t>2026/07/13 15:18:23</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.3600416, -70.8068283</t>
+          <t>-33.359985, -70.80697</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80683</t>
+          <t>-33.35999, -70.80697</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/10 15:21:10</t>
+          <t>2026/07/13 15:39:55</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.3601766, -70.8089916</t>
+          <t>-33.3797383, -70.7528033</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.36018, -70.80899</t>
+          <t>-33.37974, -70.75280</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:06:54</t>
+          <t>00:21:32</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.22</v>
+        <v>7.56</v>
       </c>
       <c r="M88" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="N88" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/10 15:21:24</t>
+          <t>2026/07/13 15:19:48</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-33.3607516, -70.8090433</t>
+          <t>-33.360031, -70.807117</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-33.36075, -70.80904</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/10 15:40:02</t>
+          <t>2026/07/13 16:32:46</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-33.3604966, -70.809295</t>
+          <t>-33.35997, -70.807061</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-33.36050, -70.80930</t>
+          <t>-33.35997, -70.80706</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:18:38</t>
+          <t>01:12:58</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="M89" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/07/10 15:22:49</t>
+          <t>2026/07/13 15:40:13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.360044, -70.806653</t>
+          <t>-33.3797466, -70.7528116</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80665</t>
+          <t>-33.37975, -70.75281</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/07/10 16:24:10</t>
+          <t>2026/07/13 16:14:59</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.360058, -70.807142</t>
+          <t>-33.3599716, -70.8070499</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.36006, -70.80714</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>01:01:21</t>
+          <t>00:34:46</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.07000000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/07/10 15:31:28</t>
+          <t>2026/07/13 16:01:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-34.2055066, -70.678245</t>
+          <t>-33.7441016, -70.738085</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67825</t>
+          <t>-33.74410, -70.73808</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/07/10 15:59:38</t>
+          <t>2026/07/13 16:46:22</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-34.2052183, -70.68033</t>
+          <t>-33.501845, -70.7686866</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-34.20522, -70.68033</t>
+          <t>-33.50185, -70.76869</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:28:10</t>
+          <t>00:44:59</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.21</v>
+        <v>35</v>
       </c>
       <c r="M91" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="N91" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,116 +5737,116 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/07/10 15:40:21</t>
+          <t>2026/07/13 16:15:08</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-33.3603949, -70.809775</t>
+          <t>-33.3599866, -70.8071883</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-33.36039, -70.80978</t>
+          <t>-33.35999, -70.80719</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/07/10 16:00:08</t>
+          <t>2026/07/13 18:54:29</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-33.3606366, -70.8090283</t>
+          <t>-32.7431899, -70.733085</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-33.36064, -70.80903</t>
+          <t>-32.74319, -70.73309</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>00:19:47</t>
+          <t>02:39:21</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.08</v>
+        <v>90.23</v>
       </c>
       <c r="M92" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="N92" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/10 16:00:15</t>
+          <t>2026/07/13 16:33:02</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-34.2040866, -70.6789966</t>
+          <t>-33.360044, -70.807116</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-34.20409, -70.67900</t>
+          <t>-33.36004, -70.80712</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/10 17:34:53</t>
+          <t>2026/07/14 11:24:00</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.4401383, -70.656665</t>
+          <t>-33.359965, -70.807053</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.44014, -70.65667</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>01:34:38</t>
+          <t>18:50:58</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>91.78</v>
+        <v>0.05</v>
       </c>
       <c r="M93" t="n">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,47 +5855,47 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/10 16:01:23</t>
+          <t>2026/07/13 16:46:32</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.3606699, -70.8090283</t>
+          <t>-33.501865, -70.76861</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.36067, -70.80903</t>
+          <t>-33.50187, -70.76861</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/10 16:18:08</t>
+          <t>2026/07/13 18:38:20</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.3601183, -70.80895</t>
+          <t>-32.8823216, -70.6119916</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80895</t>
+          <t>-32.88232, -70.61199</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>00:16:45</t>
+          <t>01:51:48</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.07000000000000001</v>
+        <v>88.83</v>
       </c>
       <c r="M94" t="n">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="N94" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/10 16:18:45</t>
+          <t>2026/07/13 17:09:09</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-33.3599933, -70.8069466</t>
+          <t>-33.0872883, -71.36232</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80695</t>
+          <t>-33.08729, -71.36232</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/10 18:13:13</t>
+          <t>2026/07/13 17:47:39</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-33.0873166, -71.36229</t>
+          <t>-33.0872316, -71.3622516</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36229</t>
+          <t>-33.08723, -71.36225</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>01:54:28</t>
+          <t>00:38:30</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>112.57</v>
+        <v>0.01</v>
       </c>
       <c r="M95" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="N95" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,116 +5973,116 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/10 16:24:20</t>
+          <t>2026/07/13 17:48:54</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-33.360077, -70.807139</t>
+          <t>-33.08732, -71.3622916</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80714</t>
+          <t>-33.08732, -71.36229</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/13 08:59:50</t>
+          <t>2026/07/13 19:49:19</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-33.360023, -70.806713</t>
+          <t>-33.0461516, -71.4201666</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80671</t>
+          <t>-33.04615, -71.42017</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>64:35:30</t>
+          <t>02:00:25</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.14</v>
+        <v>10.39</v>
       </c>
       <c r="M96" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>16</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026/07/13 18:39:35</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-32.8794099, -70.6088433</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-32.87941, -70.60884</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026/07/13 19:14:47</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-32.8791466, -70.6092666</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-32.87915, -70.60927</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>00:35:12</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M97" t="n">
         <v>6</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2026/07/10 16:48:31</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-33.4362783, -70.629345</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.62935</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>2026/07/13 07:06:26</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-33.4449966, -70.61965</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-33.44500, -70.61965</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>62:17:55</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="M97" t="n">
-        <v>32</v>
-      </c>
       <c r="N97" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,57 +6091,57 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/10 17:02:12</t>
+          <t>2026/07/13 18:48:42</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.2164566, -70.7668183</t>
+          <t>-33.436315, -70.6293299</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.21646, -70.76682</t>
+          <t>-33.43632, -70.62933</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/10 18:10:41</t>
+          <t>2026/07/13 19:31:57</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.8660483, -70.6223633</t>
+          <t>-33.466985, -70.6068116</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.86605, -70.62236</t>
+          <t>-33.46699, -70.60681</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>01:08:29</t>
+          <t>00:43:15</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>54.36</v>
+        <v>5.39</v>
       </c>
       <c r="M98" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="N98" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/10 17:10:37</t>
+          <t>2026/07/13 18:54:41</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-33.482165, -70.764916</t>
+          <t>-32.7433, -70.7327583</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-33.48217, -70.76492</t>
+          <t>-32.74330, -70.73276</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/10 21:31:46</t>
+          <t>2026/07/13 19:59:23</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-33.485241, -70.771532</t>
+          <t>-32.7430866, -70.7297566</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-33.48524, -70.77153</t>
+          <t>-32.74309, -70.72976</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>04:21:09</t>
+          <t>01:04:42</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="M99" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N99" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/10 17:20:54</t>
+          <t>2026/07/13 19:15:19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.9648116, -70.689025</t>
+          <t>-32.8792316, -70.6088066</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.96481, -70.68903</t>
+          <t>-32.87923, -70.60881</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/10 18:30:14</t>
+          <t>2026/07/14 09:00:09</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.7976183, -70.8872049</t>
+          <t>-34.2055083, -70.6783166</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88720</t>
+          <t>-34.20551, -70.67832</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>01:09:20</t>
+          <t>13:44:50</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>48.61</v>
+        <v>164.8</v>
       </c>
       <c r="M100" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="N100" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/10 17:36:08</t>
+          <t>2026/07/13 19:33:12</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.440235, -70.657545</t>
+          <t>-33.4670566, -70.6068533</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.44024, -70.65754</t>
+          <t>-33.46706, -70.60685</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/10 18:02:13</t>
+          <t>2026/07/13 21:01:57</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.3895033, -70.673885</t>
+          <t>-33.44084, -70.6303416</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.38950, -70.67388</t>
+          <t>-33.44084, -70.63034</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:26:05</t>
+          <t>01:28:45</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>8.94</v>
+        <v>4.58</v>
       </c>
       <c r="M101" t="n">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="N101" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/10 17:42:02</t>
+          <t>2026/07/13 19:35:28</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.840312, -70.960005</t>
+          <t>-32.7832333, -70.85493</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.84031, -70.96000</t>
+          <t>-32.78323, -70.85493</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/10 19:21:25</t>
+          <t>2026/07/13 19:55:29</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.694982, -70.9342</t>
+          <t>-32.7976249, -70.8871633</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.69498, -70.93420</t>
+          <t>-32.79762, -70.88716</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>01:39:23</t>
+          <t>00:20:01</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>20.77</v>
+        <v>3.72</v>
       </c>
       <c r="M102" t="n">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="N102" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/10 18:02:35</t>
+          <t>2026/07/13 19:49:28</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.3893183, -70.6739966</t>
+          <t>-33.0461283, -71.4200833</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67400</t>
+          <t>-33.04613, -71.42008</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/10 18:45:16</t>
+          <t>2026/07/13 20:28:02</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.36234, -70.6701183</t>
+          <t>-33.08734, -71.3622683</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.36234, -70.67012</t>
+          <t>-33.08734, -71.36227</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:42:41</t>
+          <t>00:38:34</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.58</v>
+        <v>10.28</v>
       </c>
       <c r="M103" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/10 18:11:24</t>
+          <t>2026/07/13 19:55:48</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.7432883, -70.7324699</t>
+          <t>-32.7976016, -70.887115</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.74329, -70.73247</t>
+          <t>-32.79760, -70.88711</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/10 20:31:59</t>
+          <t>2026/07/14 08:40:37</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-32.7431716, -70.7297283</t>
+          <t>-34.2052916, -70.682345</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72973</t>
+          <t>-34.20529, -70.68234</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>02:20:35</t>
+          <t>12:44:49</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.8100000000000001</v>
+        <v>190.85</v>
       </c>
       <c r="M104" t="n">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="N104" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,47 +6504,47 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/10 18:11:56</t>
+          <t>2026/07/13 19:59:32</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.8664183, -70.6237016</t>
+          <t>-32.7430283, -70.7297866</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.86642, -70.62370</t>
+          <t>-32.74303, -70.72979</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/10 18:25:48</t>
+          <t>2026/07/14 08:15:13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.60888</t>
+          <t>-33.3598283, -70.806785</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60888</t>
+          <t>-33.35983, -70.80679</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>00:13:52</t>
+          <t>12:15:41</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.69</v>
+        <v>90</v>
       </c>
       <c r="M105" t="n">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="N105" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/10 18:13:26</t>
+          <t>2026/07/13 20:29:15</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-33.0872966, -71.3623133</t>
+          <t>-33.0873083, -71.3623783</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36231</t>
+          <t>-33.08731, -71.36238</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/11 10:33:30</t>
+          <t>2026/07/14 07:46:35</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.0873116, -71.3622666</t>
+          <t>-33.0868883, -71.3619016</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36227</t>
+          <t>-33.08689, -71.36190</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>16:20:04</t>
+          <t>11:17:20</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.02</v>
+        <v>14</v>
       </c>
       <c r="M106" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="N106" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/10 18:27:03</t>
+          <t>2026/07/13 21:02:13</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088099</t>
+          <t>-33.440555, -70.63033</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-33.44056, -70.63033</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/10 20:32:48</t>
+          <t>2026/07/13 21:24:44</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.86605, -70.62237</t>
+          <t>-33.4362516, -70.629595</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.86605, -70.62237</t>
+          <t>-33.43625, -70.62959</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>02:05:45</t>
+          <t>00:22:31</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.45</v>
+        <v>0.72</v>
       </c>
       <c r="M107" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="N107" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,116 +6681,116 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/10 18:31:29</t>
+          <t>2026/07/13 21:25:42</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-32.7976033, -70.8870816</t>
+          <t>-33.4364766, -70.6295866</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-33.43648, -70.62959</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/11 09:20:04</t>
+          <t>2026/07/14 10:57:49</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-32.795745, -70.82016</t>
+          <t>-33.3661216, -70.6955083</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-32.79574, -70.82016</t>
+          <t>-33.36612, -70.69551</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>14:48:35</t>
+          <t>13:32:07</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>12.41</v>
+        <v>13.47</v>
       </c>
       <c r="M108" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="N108" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/10 18:46:31</t>
+          <t>2026/07/14 11:24:17</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-33.3620066, -70.6701166</t>
+          <t>-33.359942, -70.807084</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-33.36201, -70.67012</t>
+          <t>-33.35994, -70.80708</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/10 20:31:14</t>
+          <t>2026/07/14 12:02:22</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-33.4761716, -70.6982216</t>
+          <t>-33.360005, -70.806977</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69822</t>
+          <t>-33.36001, -70.80698</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>01:44:43</t>
+          <t>00:38:05</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>18.06</v>
+        <v>0.04</v>
       </c>
       <c r="M109" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,57 +6799,57 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/10 19:21:29</t>
+          <t>2026/07/14 12:03:21</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-32.694982, -70.9342</t>
+          <t>-33.360075, -70.806905</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-32.69498, -70.93420</t>
+          <t>-33.36008, -70.80691</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/10 21:34:25</t>
+          <t>2026/07/14 12:25:04</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-32.838372, -70.956024</t>
+          <t>-33.360001, -70.807087</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95602</t>
+          <t>-33.36000, -70.80709</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>02:12:56</t>
+          <t>00:21:43</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>24.54</v>
+        <v>0.19</v>
       </c>
       <c r="M110" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="N110" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,57 +6858,57 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/10 20:31:53</t>
+          <t>2026/07/14 18:23:10</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.4762933, -70.698405</t>
+          <t>-33.087325, -71.3623016</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69840</t>
+          <t>-33.08732, -71.36230</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/10 21:19:15</t>
+          <t>2026/07/15 08:27:37</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-33.4556166, -70.6610433</t>
+          <t>-33.0872683, -71.3623066</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-33.45562, -70.66104</t>
+          <t>-33.08727, -71.36231</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:47:22</t>
+          <t>14:04:27</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.49</v>
+        <v>0.04</v>
       </c>
       <c r="M111" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="N111" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,116 +6917,116 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/10 20:32:07</t>
+          <t>2026/07/15 14:43:03</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-32.7431766, -70.7296583</t>
+          <t>-33.3604783, -70.8090416</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-32.74318, -70.72966</t>
+          <t>-33.36048, -70.80904</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/12 18:03:39</t>
+          <t>2026/07/15 15:29:09</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-32.748345, -70.6528216</t>
+          <t>-33.3895116, -70.6738666</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-32.74835, -70.65282</t>
+          <t>-33.38951, -70.67387</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>45:31:32</t>
+          <t>00:46:06</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>9.09</v>
+        <v>17.34</v>
       </c>
       <c r="M112" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="N112" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026/07/15 15:29:42</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-33.3893049, -70.6740016</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-33.38930, -70.67400</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026/07/15 16:07:40</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-33.3654, -70.6799283</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-33.36540, -70.67993</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>00:37:58</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M113" t="n">
+        <v>28</v>
+      </c>
+      <c r="N113" t="n">
         <v>17</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2026/07/10 20:34:03</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-32.8663633, -70.6235466</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-32.86636, -70.62355</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2026/07/10 20:50:00</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-32.8800883, -70.60363</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-32.88009, -70.60363</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>00:15:57</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M113" t="n">
-        <v>39</v>
-      </c>
-      <c r="N113" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,47 +7035,47 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/10 20:51:15</t>
+          <t>2026/07/15 16:08:55</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-32.8794316, -70.6088516</t>
+          <t>-33.3653549, -70.6799433</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-32.87943, -70.60885</t>
+          <t>-33.36535, -70.67994</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/11 11:23:42</t>
+          <t>2026/07/15 16:59:15</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-32.7577933, -70.70241</t>
+          <t>-33.362085, -70.6701533</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-32.75779, -70.70241</t>
+          <t>-33.36209, -70.67015</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>14:32:27</t>
+          <t>00:50:20</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>24.58</v>
+        <v>1.66</v>
       </c>
       <c r="M114" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="N114" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,106 +7094,106 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/10 21:20:30</t>
+          <t>2026/07/15 16:59:50</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.4551016, -70.6583816</t>
+          <t>-33.3621033, -70.6702233</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.45510, -70.65838</t>
+          <t>-33.36210, -70.67022</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/10 21:46:26</t>
+          <t>2026/07/15 20:07:09</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.476, -70.6980066</t>
+          <t>-33.3895, -70.6736916</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.47600, -70.69801</t>
+          <t>-33.38950, -70.67369</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:25:56</t>
+          <t>03:07:19</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>7.07</v>
+        <v>4.04</v>
       </c>
       <c r="M115" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="N115" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/10 21:32:29</t>
+          <t>2026/07/15 18:24:10</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-33.484898, -70.77242</t>
+          <t>-33.0872466, -71.362245</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-33.48490, -70.77242</t>
+          <t>-33.08725, -71.36225</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/10 23:22:22</t>
+          <t>2026/07/17 20:24:22</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-33.482155, -70.765278</t>
+          <t>-33.0872466, -71.362245</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-33.48215, -70.76528</t>
+          <t>-33.08725, -71.36225</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>01:49:53</t>
+          <t>50:00:12</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/10 21:35:16</t>
+          <t>2026/07/15 18:32:49</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.838379, -70.95552</t>
+          <t>-32.840415, -70.960116</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95552</t>
+          <t>-32.84042, -70.96012</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/11 11:58:30</t>
+          <t>2026/07/15 19:09:21</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-32.841636, -70.954883</t>
+          <t>-32.838369, -70.956136</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-32.84164, -70.95488</t>
+          <t>-32.83837, -70.95614</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>14:23:14</t>
+          <t>00:36:32</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="M117" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/07/10 21:46:39</t>
+          <t>2026/07/15 18:38:03</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-33.4763316, -70.6984033</t>
+          <t>-32.7917783, -70.872935</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-33.47633, -70.69840</t>
+          <t>-32.79178, -70.87293</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/10 22:53:16</t>
+          <t>2026/07/15 19:19:22</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-33.49691, -70.7077533</t>
+          <t>-32.7977149, -70.88742</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-33.49691, -70.70775</t>
+          <t>-32.79771, -70.88742</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>01:06:37</t>
+          <t>00:41:19</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="M118" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N118" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,116 +7330,116 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/10 22:53:31</t>
+          <t>2026/07/15 18:55:01</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-33.497, -70.7076666</t>
+          <t>-33.479699, -70.758226</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-33.49700, -70.70767</t>
+          <t>-33.47970, -70.75823</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/10 23:10:12</t>
+          <t>2026/07/15 20:02:31</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.4761666, -70.6984583</t>
+          <t>-32.838758, -70.954109</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69846</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:16:41</t>
+          <t>01:07:30</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>5.29</v>
+        <v>95.33</v>
       </c>
       <c r="M119" t="n">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="N119" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/10 23:11:27</t>
+          <t>2026/07/15 19:03:40</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.4761216, -70.6985266</t>
+          <t>-32.87923, -70.6088166</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69853</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/11 09:39:27</t>
+          <t>2026/07/17 21:12:02</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.4762599, -70.6983066</t>
+          <t>-32.8792333, -70.608815</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69831</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>10:28:00</t>
+          <t>50:08:22</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="M120" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,57 +7448,57 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/10 23:23:22</t>
+          <t>2026/07/15 19:10:01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-33.482166, -70.764909</t>
+          <t>-32.838366, -70.955481</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-33.48217, -70.76491</t>
+          <t>-32.83837, -70.95548</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/11 00:49:34</t>
+          <t>2026/07/16 14:53:29</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-32.842017, -70.936795</t>
+          <t>-32.840584, -70.99572</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-32.84202, -70.93680</t>
+          <t>-32.84058, -70.99572</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>01:26:12</t>
+          <t>19:43:28</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>94.34999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M121" t="n">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="N121" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,57 +7507,57 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/07/11 12:45:24</t>
+          <t>2026/07/15 19:20:18</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.780678, -70.967698</t>
+          <t>-32.797605, -70.8870916</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.78068, -70.96770</t>
+          <t>-32.79760, -70.88709</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/11 12:56:21</t>
+          <t>2026/07/16 10:28:18</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.790903, -70.976106</t>
+          <t>-32.7976766, -70.88739</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.79090, -70.97611</t>
+          <t>-32.79768, -70.88739</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:10:57</t>
+          <t>15:08:00</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.57</v>
+        <v>13.03</v>
       </c>
       <c r="M122" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="N122" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,57 +7566,57 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/11 14:27:07</t>
+          <t>2026/07/15 20:02:41</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870833</t>
+          <t>-32.838757, -70.954109</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/11 15:59:09</t>
+          <t>2026/07/15 21:31:52</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.5634416, -70.6947283</t>
+          <t>-32.841759, -70.936896</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.56344, -70.69473</t>
+          <t>-32.84176, -70.93690</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>01:32:02</t>
+          <t>01:29:11</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>41.6</v>
+        <v>2.27</v>
       </c>
       <c r="M123" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="N123" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,116 +7625,116 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/12 04:39:18</t>
+          <t>2026/07/15 20:07:32</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.38955, -70.6736383</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.38955, -70.67364</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/16 23:41:06</t>
+          <t>2026/07/15 20:50:24</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-33.366989, -70.69623</t>
+          <t>-33.476245, -70.6983</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-33.36699, -70.69623</t>
+          <t>-33.47624, -70.69830</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>115:01:48</t>
+          <t>00:42:52</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0.27</v>
+        <v>13.57</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/13 09:23:56</t>
+          <t>2026/07/15 20:51:39</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.359904, -70.807156</t>
+          <t>-33.4761616, -70.698455</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80716</t>
+          <t>-33.47616, -70.69845</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:20</t>
+          <t>2026/07/17 10:16:04</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.360145, -70.80659</t>
+          <t>-33.3621016, -70.67012</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80659</t>
+          <t>-33.36210, -70.67012</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>00:21:24</t>
+          <t>37:24:25</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.07000000000000001</v>
+        <v>18.78</v>
       </c>
       <c r="M125" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="N125" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,57 +7743,57 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:31</t>
+          <t>2026/07/15 21:16:54</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.360108, -70.806563</t>
+          <t>-32.743215, -70.7296266</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.36011, -70.80656</t>
+          <t>-32.74321, -70.72963</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:07</t>
+          <t>2026/07/17 22:21:15</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.360027, -70.807117</t>
+          <t>-32.7429883, -70.7298566</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-32.74299, -70.72986</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>00:53:36</t>
+          <t>49:04:21</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="M126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -7802,116 +7802,116 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/07/13 14:27:42</t>
+          <t>2026/07/15 21:32:18</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-33.3601166, -70.8064883</t>
+          <t>-32.841741, -70.936882</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80649</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/13 15:17:08</t>
+          <t>2026/07/16 11:02:40</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-33.36016, -70.8067916</t>
+          <t>-32.840636, -70.958522</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-33.36016, -70.80679</t>
+          <t>-32.84064, -70.95852</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>00:49:26</t>
+          <t>13:30:22</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0.04</v>
+        <v>2.86</v>
       </c>
       <c r="M127" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="N127" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/07/13 15:18:23</t>
+          <t>2026/07/17 12:50:36</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-33.359985, -70.80697</t>
+          <t>-32.79759, -70.8871066</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80697</t>
+          <t>-32.79759, -70.88711</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/13 15:39:55</t>
+          <t>2026/07/17 20:50:36</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-33.3797383, -70.7528033</t>
+          <t>-32.79759, -70.8871066</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-33.37974, -70.75280</t>
+          <t>-32.79759, -70.88711</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>00:21:32</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,57 +7920,57 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:48</t>
+          <t>2026/07/17 15:37:33</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-33.360031, -70.807117</t>
+          <t>-32.841776, -70.936812</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-32.84178, -70.93681</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/13 16:32:46</t>
+          <t>2026/07/17 21:40:40</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-33.35997, -70.807061</t>
+          <t>-32.841776, -70.936812</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80706</t>
+          <t>-32.84178, -70.93681</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>01:12:58</t>
+          <t>06:03:07</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,116 +7979,116 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/07/13 15:40:13</t>
+          <t>2026/07/17 16:51:20</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-33.3797466, -70.7528116</t>
+          <t>-33.3665833, -70.6954649</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-33.37975, -70.75281</t>
+          <t>-33.36658, -70.69546</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/07/13 16:14:59</t>
+          <t>2026/07/17 17:48:13</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-33.3599716, -70.8070499</t>
+          <t>-33.4358716, -70.6300966</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-33.43587, -70.63010</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>00:34:46</t>
+          <t>00:56:53</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>7.79</v>
+        <v>13.29</v>
       </c>
       <c r="M130" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="N130" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/07/13 16:15:08</t>
+          <t>2026/07/17 17:49:25</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-33.3599866, -70.8071883</t>
+          <t>-33.43628, -70.629375</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80719</t>
+          <t>-33.43628, -70.62937</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/13 18:54:29</t>
+          <t>2026/07/17 21:49:25</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-32.7431899, -70.733085</t>
+          <t>-33.43628, -70.629375</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73309</t>
+          <t>-33.43628, -70.62937</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>02:39:21</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>90.23</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8097,872 +8097,46 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/07/13 16:33:02</t>
+          <t>2026/07/17 18:52:06</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-33.360044, -70.807116</t>
+          <t>-32.838358, -70.955537</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-32.83836, -70.95554</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:00</t>
+          <t>2026/07/17 21:49:36</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-33.359965, -70.807053</t>
+          <t>-32.838358, -70.955537</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-32.83836, -70.95554</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>18:50:58</t>
+          <t>02:57:30</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>9</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026/07/13 18:54:41</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-32.7433, -70.7327583</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-32.74330, -70.73276</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>2026/07/13 19:59:23</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-32.7430866, -70.7297566</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>-32.74309, -70.72976</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>01:04:42</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M133" t="n">
-        <v>36</v>
-      </c>
-      <c r="N133" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>10</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026/07/13 19:59:32</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-32.7430283, -70.7297866</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-32.74303, -70.72979</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2026/07/14 08:15:13</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-33.3598283, -70.806785</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-33.35983, -70.80679</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>12:15:41</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>90</v>
-      </c>
-      <c r="M134" t="n">
-        <v>114</v>
-      </c>
-      <c r="N134" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>7</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026/07/13 21:25:42</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-33.4364766, -70.6295866</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-33.43648, -70.62959</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2026/07/14 10:57:49</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-33.3661216, -70.6955083</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-33.36612, -70.69551</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>13:32:07</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="M135" t="n">
-        <v>115</v>
-      </c>
-      <c r="N135" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>SLP20250627045-AC02</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026/07/14 11:24:17</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-33.359942, -70.807084</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-33.35994, -70.80708</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2026/07/14 12:02:22</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-33.360005, -70.806977</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-33.36001, -70.80698</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>00:38:05</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M136" t="n">
-        <v>2</v>
-      </c>
-      <c r="N136" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>13</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026/07/15 18:24:10</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-33.0872466, -71.362245</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-33.08725, -71.36225</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2026/07/16 22:24:22</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-33.0872466, -71.362245</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-33.08725, -71.36225</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>28:00:12</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>3</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026/07/15 19:03:40</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.6088166</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2026/07/16 23:12:02</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-32.8792333, -70.608815</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>28:08:22</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>14</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026/07/15 20:02:41</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-32.838757, -70.954109</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-32.83876, -70.95411</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>2026/07/15 21:31:52</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-32.841759, -70.936896</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-32.84176, -70.93690</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>01:29:11</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="M139" t="n">
-        <v>39</v>
-      </c>
-      <c r="N139" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>16</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026/07/15 20:51:39</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-33.4761616, -70.698455</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-33.47616, -70.69845</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2026/07/16 22:56:09</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-33.4761616, -70.698455</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>-33.47616, -70.69845</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>26:04:30</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>5</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026/07/15 21:16:54</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-32.743215, -70.7296266</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-32.74321, -70.72963</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>2026/07/16 22:16:53</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-32.7430133, -70.72982</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-32.74301, -70.72982</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>24:59:59</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>15</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026/07/15 21:32:18</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-32.841741, -70.936882</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-32.84174, -70.93688</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2026/07/16 11:02:40</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-32.840636, -70.958522</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>-32.84064, -70.95852</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>13:30:22</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M142" t="n">
-        <v>33</v>
-      </c>
-      <c r="N142" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>6</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026/07/15 21:41:29</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-33.4364349, -70.6291566</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-33.43643, -70.62916</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2026/07/16 23:42:00</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-33.4364349, -70.6291566</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-33.43643, -70.62916</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>26:00:31</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>2026/07/16 10:29:33</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-32.7975866, -70.8871166</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-32.79759, -70.88712</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>2026/07/16 22:30:15</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-32.797595, -70.8870783</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>-32.79760, -70.88708</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>12:00:42</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>5</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2026/07/16 12:30:39</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-32.84169, -70.93689</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-32.84169, -70.93689</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>2026/07/16 23:33:50</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-32.84169, -70.93689</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>-32.84169, -70.93689</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>11:03:11</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>2</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>2026/07/16 20:24:08</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-32.838352, -70.95555</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-32.83835, -70.95555</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>2026/07/16 23:21:40</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-32.838352, -70.95555</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-32.83835, -70.95555</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>02:57:32</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9014,13 +8188,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1736.98</v>
+        <v>1359.96</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>148</v>
@@ -9033,13 +8207,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>803.61</v>
+        <v>621.08</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>138</v>
@@ -9052,10 +8226,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>911.83</v>
+        <v>661.3</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -9071,10 +8245,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>760.92</v>
+        <v>580.88</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -9115,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -9242,13 +8416,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1032.13</v>
+        <v>888.86</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>128</v>
@@ -9261,10 +8435,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>193.21</v>
+        <v>213.73</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -9318,16 +8492,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -9337,10 +8511,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1397.48</v>
+        <v>1040.45</v>
       </c>
       <c r="C19" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -9356,10 +8530,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>650.25</v>
+        <v>552.2</v>
       </c>
       <c r="C20" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/17 22:13:37</t>
+          <t>2026/07/17 23:13:21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>165:59:27</t>
+          <t>166:59:11</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/17 21:35:07</t>
+          <t>2026/07/17 23:34:55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>165:20:52</t>
+          <t>167:20:40</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/17 21:24:04</t>
+          <t>2026/07/17 23:23:38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>165:08:35</t>
+          <t>167:08:09</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/17 21:57:27</t>
+          <t>2026/07/17 23:57:30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>165:41:18</t>
+          <t>167:41:21</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/17 21:56:09</t>
+          <t>2026/07/17 23:56:09</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>165:32:13</t>
+          <t>167:32:13</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/17 21:31:24</t>
+          <t>2026/07/17 23:31:22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>165:05:57</t>
+          <t>167:05:55</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/07/17 21:02:21</t>
+          <t>2026/07/17 23:02:21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>164:00:00</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/07/17 21:39:23</t>
+          <t>2026/07/17 23:41:06</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>137:00:05</t>
+          <t>139:01:48</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/17 20:24:22</t>
+          <t>2026/07/17 22:24:22</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>50:00:12</t>
+          <t>52:00:12</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/17 21:12:02</t>
+          <t>2026/07/17 23:12:02</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>50:08:22</t>
+          <t>52:08:22</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/17 22:21:15</t>
+          <t>2026/07/17 23:29:49</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>49:04:21</t>
+          <t>50:12:55</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/17 20:50:36</t>
+          <t>2026/07/17 22:50:36</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/17 21:40:40</t>
+          <t>2026/07/17 23:40:40</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>06:03:07</t>
+          <t>08:03:07</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/17 21:49:25</t>
+          <t>2026/07/17 23:49:25</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/17 21:49:36</t>
+          <t>2026/07/17 23:49:37</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>02:57:30</t>
+          <t>04:57:31</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -8137,6 +8137,65 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>5</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026/07/17 21:10:52</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-33.4761016, -70.6985316</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-33.47610, -70.69853</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026/07/17 23:13:07</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-33.4761466, -70.6985149</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-33.47615, -70.69851</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>02:02:15</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8416,13 +8475,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>888.86</v>
+        <v>888.84</v>
       </c>
       <c r="C14" t="n">
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>128</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/11 04:00:00   Hasta : 2026/07/18 03:59:59</t>
+          <t>Desde : 2026/07/12 04:00:00   Hasta : 2026/07/19 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -545,106 +545,106 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/07/11 00:00:16</t>
+          <t>2026/07/12 00:00:29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-33.463178, -70.763329</t>
+          <t>-32.832254, -70.976477</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-33.46318, -70.76333</t>
+          <t>-32.83225, -70.97648</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/11 00:49:34</t>
+          <t>2026/07/12 00:07:41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-32.842017, -70.936795</t>
+          <t>-32.785516, -70.960409</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.84202, -70.93680</t>
+          <t>-32.78552, -70.96041</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>00:49:18</t>
+          <t>00:07:12</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>91.43000000000001</v>
+        <v>6.74</v>
       </c>
       <c r="M4" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="N4" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/07/11 00:14:10</t>
+          <t>2026/07/12 00:08:25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.360009, -70.807034</t>
+          <t>-32.785335, -70.960448</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80703</t>
+          <t>-32.78534, -70.96045</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/17 23:13:21</t>
+          <t>2026/07/12 08:10:51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.360044, -70.807063</t>
+          <t>-33.384799, -70.532819</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80706</t>
+          <t>-33.38480, -70.53282</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>166:59:11</t>
+          <t>08:02:26</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.01</v>
+        <v>103.98</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/07/11 00:14:15</t>
+          <t>2026/07/12 00:14:16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -678,26 +678,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/17 23:34:55</t>
+          <t>2026/07/18 21:34:34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.579676, -70.961385</t>
+          <t>-34.5796, -70.961366</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96139</t>
+          <t>-34.57960, -70.96137</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>167:20:40</t>
+          <t>165:20:18</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -722,53 +722,53 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/07/11 00:14:32</t>
+          <t>2026/07/12 00:14:20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-34.346017, -71.125783</t>
+          <t>-33.360009, -70.807034</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-34.34602, -71.12578</t>
+          <t>-33.36001, -70.80703</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/12 01:04:03</t>
+          <t>2026/07/18 22:13:24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-34.346035, -71.125736</t>
+          <t>-33.360021, -70.807061</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.34604, -71.12574</t>
+          <t>-33.36002, -70.80706</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24:49:31</t>
+          <t>165:59:04</t>
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,53 +781,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/07/11 00:15:14</t>
+          <t>2026/07/12 00:14:39</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677325</t>
+          <t>-34.346017, -71.125783</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67732</t>
+          <t>-34.34602, -71.12578</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/12 01:14:34</t>
+          <t>2026/07/12 01:04:03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.205228, -70.67741</t>
+          <t>-34.346035, -71.125736</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67741</t>
+          <t>-34.34604, -71.12574</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24:59:20</t>
+          <t>00:49:24</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,41 +840,41 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/07/11 00:15:29</t>
+          <t>2026/07/12 00:15:09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-34.876497, -71.127268</t>
+          <t>-34.205421, -70.677325</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-34.87650, -71.12727</t>
+          <t>-34.20542, -70.67732</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/17 23:23:38</t>
+          <t>2026/07/12 01:14:34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-34.876357, -71.127275</t>
+          <t>-34.205228, -70.67741</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.87636, -71.12727</t>
+          <t>-34.20523, -70.67741</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>167:08:09</t>
+          <t>00:59:25</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -899,41 +899,41 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/07/11 00:16:09</t>
+          <t>2026/07/12 00:16:27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-34.042744, -70.681743</t>
+          <t>-34.876497, -71.127268</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-34.04274, -70.68174</t>
+          <t>-34.87650, -71.12727</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/17 23:57:30</t>
+          <t>2026/07/18 22:24:44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-34.042673, -70.681782</t>
+          <t>-34.876517, -71.127094</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.04267, -70.68178</t>
+          <t>-34.87652, -71.12709</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>167:41:21</t>
+          <t>166:08:17</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/07/11 00:22:53</t>
+          <t>2026/07/12 00:16:36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-33.360077, -70.807139</t>
+          <t>-34.042744, -70.681743</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80714</t>
+          <t>-34.04274, -70.68174</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/13 08:59:50</t>
+          <t>2026/07/18 21:57:21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.360023, -70.806713</t>
+          <t>-34.042596, -70.681656</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80671</t>
+          <t>-34.04260, -70.68166</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>56:36:57</t>
+          <t>165:40:45</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/07/11 00:23:56</t>
+          <t>2026/07/12 00:18:15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.7429983, -70.7298549</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.74300, -70.72985</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/17 23:56:09</t>
+          <t>2026/07/12 18:03:39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.748345, -70.6528216</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.74835, -70.65282</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>167:32:13</t>
+          <t>17:45:24</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,41 +1076,41 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/07/11 00:25:27</t>
+          <t>2026/07/12 00:23:56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.899806, -71.429473</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.89981, -71.42947</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/17 23:31:22</t>
+          <t>2026/07/18 21:56:11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.899804, -71.429481</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42948</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>167:05:55</t>
+          <t>165:32:15</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/07/11 00:32:50</t>
+          <t>2026/07/12 00:24:08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-32.838379, -70.95552</t>
+          <t>-33.360092, -70.807118</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-32.83838, -70.95552</t>
+          <t>-33.36009, -70.80712</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/11 11:58:30</t>
+          <t>2026/07/13 08:59:50</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-32.841636, -70.954883</t>
+          <t>-33.360023, -70.806713</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-32.84164, -70.95488</t>
+          <t>-33.36002, -70.80671</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11:25:40</t>
+          <t>32:35:42</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.68</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/07/11 00:33:19</t>
+          <t>2026/07/12 00:25:53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-32.7976033, -70.8870816</t>
+          <t>-33.899806, -71.429473</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-33.89981, -71.42947</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/11 09:20:04</t>
+          <t>2026/07/18 22:31:37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-32.795745, -70.82016</t>
+          <t>-33.89987, -71.429483</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.79574, -70.82016</t>
+          <t>-33.89987, -71.42948</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08:46:45</t>
+          <t>166:05:44</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12.41</v>
+        <v>0.02</v>
       </c>
       <c r="M15" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/07/11 00:33:51</t>
+          <t>2026/07/12 00:28:02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-32.7430183, -70.7297866</t>
+          <t>-33.087215, -71.3622349</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-32.74302, -70.72979</t>
+          <t>-33.08722, -71.36223</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/12 18:03:39</t>
+          <t>2026/07/12 11:16:46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-32.748345, -70.6528216</t>
+          <t>-33.087305, -71.3623016</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-32.74835, -70.65282</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>41:29:48</t>
+          <t>10:48:44</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.07</v>
+        <v>0.01</v>
       </c>
       <c r="M16" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,58 +1307,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/07/11 00:38:39</t>
+          <t>2026/07/12 00:28:31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.367062, -70.696335</t>
+          <t>-32.841755, -70.936878</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-33.36706, -70.69634</t>
+          <t>-32.84175, -70.93688</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/12 03:41:06</t>
+          <t>2026/07/12 11:12:02</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-32.838851, -70.954161</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-32.83885, -70.95416</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27:02:27</t>
+          <t>10:43:31</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.04</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/07/11 00:39:24</t>
+          <t>2026/07/12 00:39:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.0872966, -71.3623133</t>
+          <t>-33.367062, -70.696335</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36231</t>
+          <t>-33.36706, -70.69634</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/11 10:33:30</t>
+          <t>2026/07/12 03:41:06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.0873116, -71.3622666</t>
+          <t>-33.3674, -70.696184</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36227</t>
+          <t>-33.36740, -70.69618</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>09:54:06</t>
+          <t>03:02:06</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,57 +1430,57 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/07/11 00:48:31</t>
+          <t>2026/07/12 00:47:44</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.4362783, -70.629345</t>
+          <t>-32.7976, -70.8870766</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62935</t>
+          <t>-32.79760, -70.88708</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/13 07:06:26</t>
+          <t>2026/07/12 11:01:08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.4449966, -70.61965</t>
+          <t>-32.7465733, -70.7223516</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.44500, -70.61965</t>
+          <t>-32.74657, -70.72235</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>54:17:55</t>
+          <t>10:13:24</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>19.65</v>
       </c>
       <c r="M19" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/07/11 00:50:34</t>
+          <t>2026/07/12 00:48:31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-32.841721, -70.936771</t>
+          <t>-33.4362783, -70.629345</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-32.84172, -70.93677</t>
+          <t>-33.43628, -70.62935</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/11 11:01:46</t>
+          <t>2026/07/13 07:06:26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-32.840225, -70.950481</t>
+          <t>-33.4449966, -70.61965</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.84022, -70.95048</t>
+          <t>-33.44500, -70.61965</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10:11:12</t>
+          <t>30:17:55</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.98</v>
+        <v>1.97</v>
       </c>
       <c r="M20" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,44 +1548,44 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/07/11 00:52:59</t>
+          <t>2026/07/12 01:02:21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-32.879205, -70.6088216</t>
+          <t>-33.3672816, -70.69573</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60882</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/07/11 11:23:42</t>
+          <t>2026/07/18 09:59:20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-32.7577933, -70.70241</t>
+          <t>-33.4640433, -70.6511716</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.75779, -70.70241</t>
+          <t>-33.46404, -70.65117</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10:30:43</t>
+          <t>152:56:59</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>24.55</v>
+        <v>16.4</v>
       </c>
       <c r="M21" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
@@ -1594,7 +1594,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1602,58 +1602,58 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/07/11 01:02:21</t>
+          <t>2026/07/12 01:13:18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.69573</t>
+          <t>-33.4761183, -70.6984916</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-33.47612, -70.69849</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/07/17 23:02:21</t>
+          <t>2026/07/12 14:16:01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.69573</t>
+          <t>-33.4762183, -70.6983649</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-33.47622, -70.69836</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>13:02:43</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/07/11 01:11:43</t>
+          <t>2026/07/12 01:23:12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.4761216, -70.6985266</t>
+          <t>-32.8792216, -70.6087933</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69853</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/07/11 09:39:27</t>
+          <t>2026/07/12 11:16:04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.4762599, -70.6983066</t>
+          <t>-32.8678316, -70.6224066</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69831</t>
+          <t>-32.86783, -70.62241</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08:27:44</t>
+          <t>09:52:52</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.03</v>
+        <v>3.46</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1720,58 +1720,58 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/07/11 09:20:11</t>
+          <t>2026/07/12 02:01:28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.7958066, -70.8201433</t>
+          <t>-34.346035, -71.125736</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.79581, -70.82014</t>
+          <t>-34.34604, -71.12574</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/11 12:58:56</t>
+          <t>2026/07/18 22:01:29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-32.7976783, -70.8873716</t>
+          <t>-34.345949, -71.125868</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-32.79768, -70.88737</t>
+          <t>-34.34595, -71.12587</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>03:38:45</t>
+          <t>164:00:01</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>10.68</v>
+        <v>0.03</v>
       </c>
       <c r="M24" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1779,62 +1779,62 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/07/11 09:40:42</t>
+          <t>2026/07/12 02:12:14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.47631, -70.6983433</t>
+          <t>-34.205228, -70.67741</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69834</t>
+          <t>-34.20523, -70.67741</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/11 10:04:32</t>
+          <t>2026/07/18 22:11:21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.3622616, -70.67011</t>
+          <t>-34.205402, -70.677263</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.36226, -70.67011</t>
+          <t>-34.20540, -70.67726</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>00:23:50</t>
+          <t>163:59:07</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.73</v>
+        <v>0.05</v>
       </c>
       <c r="M25" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/07/11 10:04:52</t>
+          <t>2026/07/12 04:39:18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.3620883, -70.6701433</t>
+          <t>-33.3674, -70.696184</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67014</t>
+          <t>-33.36740, -70.69618</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/11 13:44:08</t>
+          <t>2026/07/18 21:40:20</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.4501933, -70.5959533</t>
+          <t>-33.36714, -70.696418</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.45019, -70.59595</t>
+          <t>-33.36714, -70.69642</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03:39:16</t>
+          <t>161:01:02</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>14.18</v>
+        <v>0.29</v>
       </c>
       <c r="M26" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,57 +1902,57 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/07/11 10:33:52</t>
+          <t>2026/07/12 08:11:36</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.0873449, -71.362225</t>
+          <t>-33.384819, -70.532828</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36222</t>
+          <t>-33.38482, -70.53283</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/07/11 11:24:44</t>
+          <t>2026/07/12 19:16:21</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.0532533, -71.35565</t>
+          <t>-32.838361, -70.955691</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.05325, -71.35565</t>
+          <t>-32.83836, -70.95569</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:50:52</t>
+          <t>11:04:45</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.32</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="N27" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,47 +1961,47 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/07/11 11:02:01</t>
+          <t>2026/07/12 11:01:14</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.840182, -70.950451</t>
+          <t>-32.7465633, -70.7223533</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.84018, -70.95045</t>
+          <t>-32.74656, -70.72235</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/07/11 11:09:43</t>
+          <t>2026/07/12 11:16:51</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.838564, -70.953955</t>
+          <t>-32.7547866, -70.7279983</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.83856, -70.95395</t>
+          <t>-32.75479, -70.72800</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:07:42</t>
+          <t>00:15:37</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,53 +2020,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/07/11 11:10:13</t>
+          <t>2026/07/12 11:12:22</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-32.838856, -70.954139</t>
+          <t>-32.838852, -70.954163</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.83886, -70.95414</t>
+          <t>-32.83885, -70.95416</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/07/11 11:42:19</t>
+          <t>2026/07/12 11:20:31</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-32.840186, -70.95055</t>
+          <t>-32.838273, -70.954522</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-32.84019, -70.95055</t>
+          <t>-32.83827, -70.95452</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:32:06</t>
+          <t>00:08:09</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="M29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2079,57 +2079,57 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/07/11 11:24:57</t>
+          <t>2026/07/12 11:17:03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-32.7578449, -70.7023266</t>
+          <t>-33.0873483, -71.3622483</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-32.75784, -70.70233</t>
+          <t>-33.08735, -71.36225</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/07/11 11:51:57</t>
+          <t>2026/07/12 15:41:38</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-32.7581016, -70.7020483</t>
+          <t>-33.0904616, -71.3605616</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.75810, -70.70205</t>
+          <t>-33.09046, -71.36056</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:27:00</t>
+          <t>04:24:35</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.04</v>
+        <v>0.61</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,44 +2138,44 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/07/11 11:25:59</t>
+          <t>2026/07/12 11:17:19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-33.053245, -71.3556866</t>
+          <t>-32.866175, -70.624015</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-33.05324, -71.35569</t>
+          <t>-32.86617, -70.62401</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/07/11 12:03:12</t>
+          <t>2026/07/12 12:11:20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-33.0479799, -71.4053666</t>
+          <t>-32.69114, -70.7803549</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-33.04798, -71.40537</t>
+          <t>-32.69114, -70.78035</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:37:13</t>
+          <t>00:54:01</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>13.2</v>
+        <v>28.08</v>
       </c>
       <c r="M31" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="N31" t="n">
         <v>32</v>
@@ -2184,11 +2184,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,53 +2197,53 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/07/11 11:42:25</t>
+          <t>2026/07/12 11:17:57</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-32.84019, -70.950553</t>
+          <t>-32.7549149, -70.7280916</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-32.84019, -70.95055</t>
+          <t>-32.75491, -70.72809</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/07/11 11:55:58</t>
+          <t>2026/07/12 11:58:42</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-32.838552, -70.953968</t>
+          <t>-32.757665, -70.7028433</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.83855, -70.95397</t>
+          <t>-32.75767, -70.70284</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:13:33</t>
+          <t>00:40:45</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.57</v>
+        <v>3.3</v>
       </c>
       <c r="M32" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="N32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/07/11 11:53:12</t>
+          <t>2026/07/12 11:21:27</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.7581866, -70.7021666</t>
+          <t>-32.837088, -70.954738</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.75819, -70.70217</t>
+          <t>-32.83709, -70.95474</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/07/11 12:13:26</t>
+          <t>2026/07/12 13:24:49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-32.7500116, -70.7258933</t>
+          <t>-32.841915, -70.936828</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.75001, -70.72589</t>
+          <t>-32.84192, -70.93683</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:20:14</t>
+          <t>02:03:22</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.82</v>
+        <v>2.73</v>
       </c>
       <c r="M33" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="N33" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/07/11 11:56:19</t>
+          <t>2026/07/12 11:59:57</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.838858, -70.95415</t>
+          <t>-32.7577416, -70.7025466</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.83886, -70.95415</t>
+          <t>-32.75774, -70.70255</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/07/11 13:27:40</t>
+          <t>2026/07/12 13:04:51</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.840831, -70.957916</t>
+          <t>-32.797665, -70.8874083</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.84083, -70.95792</t>
+          <t>-32.79767, -70.88741</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:31:21</t>
+          <t>01:04:54</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.48</v>
+        <v>22.46</v>
       </c>
       <c r="M34" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="N34" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,53 +2374,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/07/11 11:59:27</t>
+          <t>2026/07/12 12:12:35</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.842681, -70.955194</t>
+          <t>-32.690825, -70.78046</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.84268, -70.95519</t>
+          <t>-32.69082, -70.78046</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/07/11 12:07:03</t>
+          <t>2026/07/12 12:48:28</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.840051, -70.958368</t>
+          <t>-32.7409383, -70.7324083</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.84005, -70.95837</t>
+          <t>-32.74094, -70.73241</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:07:36</t>
+          <t>00:35:53</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.8100000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="M35" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="N35" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/07/11 12:04:27</t>
+          <t>2026/07/12 12:49:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.0479766, -71.4054033</t>
+          <t>-32.7436883, -70.7306733</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.04798, -71.40540</t>
+          <t>-32.74369, -70.73067</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/07/11 12:12:14</t>
+          <t>2026/07/12 13:28:21</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.0485916, -71.40566</t>
+          <t>-32.865405, -70.638115</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.04859, -71.40566</t>
+          <t>-32.86541, -70.63811</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:07:47</t>
+          <t>00:38:38</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.11</v>
+        <v>19.87</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/07/11 12:07:39</t>
+          <t>2026/07/12 13:06:06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-32.840052, -70.958398</t>
+          <t>-32.79756, -70.8870783</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-32.84005, -70.95840</t>
+          <t>-32.79756, -70.88708</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/07/11 12:44:38</t>
+          <t>2026/07/12 15:58:52</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-32.780731, -70.967681</t>
+          <t>-32.7957266, -70.8201483</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-32.78073, -70.96768</t>
+          <t>-32.79573, -70.82015</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:36:59</t>
+          <t>02:52:46</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>10.64</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="N37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,47 +2551,47 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/07/11 12:13:29</t>
+          <t>2026/07/12 13:25:48</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-33.048705, -71.4056916</t>
+          <t>-32.841778, -70.936838</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.04870, -71.40569</t>
+          <t>-32.84178, -70.93684</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/07/11 13:21:53</t>
+          <t>2026/07/12 20:45:45</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.045615, -71.4194633</t>
+          <t>-32.838513, -70.95394</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.04561, -71.41946</t>
+          <t>-32.83851, -70.95394</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01:08:24</t>
+          <t>07:19:57</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="N38" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/07/11 12:14:41</t>
+          <t>2026/07/12 13:29:36</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-32.7500033, -70.72595</t>
+          <t>-32.8660333, -70.6373499</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-32.75000, -70.72595</t>
+          <t>-32.86603, -70.63735</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/07/11 13:07:32</t>
+          <t>2026/07/12 14:04:28</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-32.8792033, -70.6089516</t>
+          <t>-32.8791933, -70.608835</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60895</t>
+          <t>-32.87919, -70.60883</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:52:51</t>
+          <t>00:34:52</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>23.08</v>
+        <v>12.43</v>
       </c>
       <c r="M39" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="N39" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/07/11 12:45:24</t>
+          <t>2026/07/12 14:04:34</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-32.780678, -70.967698</t>
+          <t>-32.879205, -70.6087833</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-32.78068, -70.96770</t>
+          <t>-32.87920, -70.60878</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/07/11 12:56:21</t>
+          <t>2026/07/12 15:10:32</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-32.790903, -70.976106</t>
+          <t>-32.8911866, -70.62515</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-32.79090, -70.97611</t>
+          <t>-32.89119, -70.62515</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:10:57</t>
+          <t>01:05:58</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>3.08</v>
       </c>
       <c r="M40" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="N40" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/07/11 12:56:30</t>
+          <t>2026/07/12 14:16:36</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-32.79091, -70.976137</t>
+          <t>-33.4763283, -70.6983683</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-32.79091, -70.97614</t>
+          <t>-33.47633, -70.69837</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/07/11 15:24:03</t>
+          <t>2026/07/12 15:27:20</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-32.790911, -70.976099</t>
+          <t>-33.451265, -70.59669</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-32.79091, -70.97610</t>
+          <t>-33.45126, -70.59669</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>02:27:33</t>
+          <t>01:10:44</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.68</v>
+        <v>13.33</v>
       </c>
       <c r="M41" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="N41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,47 +2787,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/07/11 12:59:11</t>
+          <t>2026/07/12 15:11:47</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-32.7976, -70.8870966</t>
+          <t>-32.891345, -70.624735</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88710</t>
+          <t>-32.89135, -70.62474</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/07/11 13:27:26</t>
+          <t>2026/07/12 15:25:22</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-32.8006616, -70.82641</t>
+          <t>-32.8793, -70.6088716</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-32.80066, -70.82641</t>
+          <t>-32.87930, -70.60887</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:28:15</t>
+          <t>00:13:35</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>9.27</v>
+        <v>2.96</v>
       </c>
       <c r="M42" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="N42" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/07/11 13:07:57</t>
+          <t>2026/07/12 15:26:03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-32.8790016, -70.6095083</t>
+          <t>-32.8791933, -70.6088633</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-32.87900, -70.60951</t>
+          <t>-32.87919, -70.60886</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/07/11 13:41:35</t>
+          <t>2026/07/12 16:09:05</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-32.87908, -70.6093549</t>
+          <t>-32.8299833, -70.5961333</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-32.87908, -70.60935</t>
+          <t>-32.82998, -70.59613</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:33:38</t>
+          <t>00:43:02</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.02</v>
+        <v>9.4</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/07/11 13:23:08</t>
+          <t>2026/07/12 15:28:35</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.045635, -71.4192533</t>
+          <t>-33.451405, -70.5962799</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.04563, -71.41925</t>
+          <t>-33.45141, -70.59628</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/07/11 14:18:14</t>
+          <t>2026/07/12 16:17:13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.094455, -71.3530933</t>
+          <t>-33.4648449, -70.5975416</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.09446, -71.35309</t>
+          <t>-33.46484, -70.59754</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:55:06</t>
+          <t>00:48:38</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.29</v>
+        <v>2.16</v>
       </c>
       <c r="M44" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="N44" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,112 +2964,112 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/07/11 13:28:29</t>
+          <t>2026/07/12 15:42:53</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-32.805665, -70.8247483</t>
+          <t>-33.09078, -71.3609549</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-32.80566, -70.82475</t>
+          <t>-33.09078, -71.36095</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/07/11 14:26:20</t>
+          <t>2026/07/12 15:52:13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-32.7976383, -70.8872133</t>
+          <t>-33.0869333, -71.36188</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-32.79764, -70.88721</t>
+          <t>-33.08693, -71.36188</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:57:51</t>
+          <t>00:09:20</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>9.74</v>
+        <v>0.58</v>
       </c>
       <c r="M45" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="N45" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026/07/12 15:53:12</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-33.0873099, -71.3623416</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-33.08731, -71.36234</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026/07/13 08:11:09</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-33.087285, -71.36232</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-33.08729, -71.36232</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>16:17:57</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M46" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" t="n">
         <v>7</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026/07/11 13:28:40</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-32.84062, -70.958921</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-32.84062, -70.95892</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026/07/11 13:46:13</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-32.842, -70.936864</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-32.84200, -70.93686</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>00:17:33</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M46" t="n">
-        <v>37</v>
-      </c>
-      <c r="N46" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/07/11 13:42:03</t>
+          <t>2026/07/12 15:59:04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-32.8792166, -70.60879</t>
+          <t>-32.7958466, -70.8200833</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-32.79585, -70.82008</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/07/11 14:27:13</t>
+          <t>2026/07/12 17:08:26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-32.8297466, -70.5968316</t>
+          <t>-32.7977149, -70.887415</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-32.82975, -70.59683</t>
+          <t>-32.79771, -70.88742</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:45:10</t>
+          <t>01:09:22</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.029999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="N47" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,57 +3141,57 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/07/11 13:45:23</t>
+          <t>2026/07/12 16:09:37</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.451215, -70.59607</t>
+          <t>-32.8295983, -70.597325</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.45121, -70.59607</t>
+          <t>-32.82960, -70.59732</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/07/11 15:03:52</t>
+          <t>2026/07/12 18:40:20</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.2784999, -70.70501</t>
+          <t>-32.8792083, -70.6088483</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.27850, -70.70501</t>
+          <t>-32.87921, -70.60885</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>01:18:29</t>
+          <t>02:30:43</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>28.24</v>
+        <v>8.18</v>
       </c>
       <c r="M48" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="N48" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/07/11 13:46:53</t>
+          <t>2026/07/12 16:18:28</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.841751, -70.936874</t>
+          <t>-33.4649216, -70.5971233</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.84175, -70.93687</t>
+          <t>-33.46492, -70.59712</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/07/11 14:07:16</t>
+          <t>2026/07/12 16:37:12</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.842912, -70.955311</t>
+          <t>-33.4508833, -70.5960266</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.84291, -70.95531</t>
+          <t>-33.45088, -70.59603</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:20:23</t>
+          <t>00:18:44</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="M49" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,53 +3259,53 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/07/11 14:08:12</t>
+          <t>2026/07/12 16:37:37</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-32.842996, -70.955344</t>
+          <t>-33.45125, -70.5959933</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-32.84300, -70.95534</t>
+          <t>-33.45125, -70.59599</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/07/11 15:07:19</t>
+          <t>2026/07/12 17:12:43</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-32.841767, -70.936908</t>
+          <t>-33.4549116, -70.6270566</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-32.84177, -70.93691</t>
+          <t>-33.45491, -70.62706</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:59:07</t>
+          <t>00:35:06</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.09</v>
+        <v>3.87</v>
       </c>
       <c r="M50" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/07/11 14:18:30</t>
+          <t>2026/07/12 17:09:41</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-33.0942783, -71.3530133</t>
+          <t>-32.79757, -70.8870583</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-33.09428, -71.35301</t>
+          <t>-32.79757, -70.88706</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/07/11 14:29:41</t>
+          <t>2026/07/13 07:47:17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.0873066, -71.3622666</t>
+          <t>-33.3672916, -70.696675</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36227</t>
+          <t>-33.36729, -70.69667</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>00:11:11</t>
+          <t>14:37:36</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>92.58</v>
       </c>
       <c r="M51" t="n">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="N51" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,53 +3377,53 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/07/11 14:27:07</t>
+          <t>2026/07/12 17:12:58</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870833</t>
+          <t>-33.4549566, -70.6270666</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-33.45496, -70.62707</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/07/11 15:59:09</t>
+          <t>2026/07/12 17:39:59</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-32.5634416, -70.6947283</t>
+          <t>-33.4762766, -70.69834</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-32.56344, -70.69473</t>
+          <t>-33.47628, -70.69834</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>01:32:02</t>
+          <t>00:27:01</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>41.6</v>
+        <v>8.73</v>
       </c>
       <c r="M52" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="N52" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3436,57 +3436,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/07/11 14:27:39</t>
+          <t>2026/07/12 17:40:07</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-32.8295516, -70.5973733</t>
+          <t>-33.4763166, -70.6983783</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-32.82955, -70.59737</t>
+          <t>-33.47632, -70.69838</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/07/11 16:40:35</t>
+          <t>2026/07/12 21:07:31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-32.85666, -70.5865149</t>
+          <t>-33.3895299, -70.6739</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-32.85666, -70.58651</t>
+          <t>-33.38953, -70.67390</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>02:12:56</t>
+          <t>03:27:24</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5.39</v>
+        <v>23.37</v>
       </c>
       <c r="M53" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="N53" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/07/11 14:29:54</t>
+          <t>2026/07/12 18:03:54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.0872833, -71.36232</t>
+          <t>-32.7483666, -70.6526849</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36232</t>
+          <t>-32.74837, -70.65268</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/07/12 11:16:46</t>
+          <t>2026/07/12 18:42:42</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.087305, -71.3623016</t>
+          <t>-32.7434416, -70.7326933</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36230</t>
+          <t>-32.74344, -70.73269</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>20:46:52</t>
+          <t>00:38:48</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.02</v>
+        <v>8.51</v>
       </c>
       <c r="M54" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/07/11 15:05:07</t>
+          <t>2026/07/12 18:41:35</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.27849, -70.7050983</t>
+          <t>-32.8791383, -70.608845</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.27849, -70.70510</t>
+          <t>-32.87914, -70.60885</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/07/11 16:24:16</t>
+          <t>2026/07/12 20:07:16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.4762616, -70.6983416</t>
+          <t>-32.8792099, -70.6089083</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69834</t>
+          <t>-32.87921, -70.60891</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>01:19:09</t>
+          <t>01:25:41</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>39.2</v>
+        <v>11.39</v>
       </c>
       <c r="M55" t="n">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="N55" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,57 +3613,57 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/07/11 15:07:25</t>
+          <t>2026/07/12 18:43:14</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-32.841764, -70.936909</t>
+          <t>-32.7435066, -70.7327433</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-32.84176, -70.93691</t>
+          <t>-32.74351, -70.73274</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/07/11 20:42:43</t>
+          <t>2026/07/12 19:12:44</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-32.838737, -70.954064</t>
+          <t>-32.7435616, -70.736105</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-32.83874, -70.95406</t>
+          <t>-32.74356, -70.73610</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>05:35:18</t>
+          <t>00:29:30</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.29</v>
+        <v>1.77</v>
       </c>
       <c r="M56" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N56" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/07/11 15:24:16</t>
+          <t>2026/07/12 19:13:42</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-32.790913, -70.976126</t>
+          <t>-32.743345, -70.7326616</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-32.79091, -70.97613</t>
+          <t>-32.74334, -70.73266</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/07/11 18:51:35</t>
+          <t>2026/07/12 20:25:18</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-32.838389, -70.955829</t>
+          <t>-32.74317, -70.729675</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-32.83839, -70.95583</t>
+          <t>-32.74317, -70.72968</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03:27:19</t>
+          <t>01:11:36</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>15.11</v>
+        <v>2.07</v>
       </c>
       <c r="M57" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="N57" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/07/11 16:00:24</t>
+          <t>2026/07/12 19:16:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.5634049, -70.6950866</t>
+          <t>-32.838355, -70.955537</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.56340, -70.69509</t>
+          <t>-32.83835, -70.95554</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/07/11 18:11:32</t>
+          <t>2026/07/12 20:54:06</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.7416316, -70.7269533</t>
+          <t>-32.785477, -70.960406</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.74163, -70.72695</t>
+          <t>-32.78548, -70.96041</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>02:11:08</t>
+          <t>01:37:23</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>22.16</v>
+        <v>9.66</v>
       </c>
       <c r="M58" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="N58" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/07/11 16:24:33</t>
+          <t>2026/07/12 20:08:31</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.4763066, -70.6983766</t>
+          <t>-32.8792216, -70.608875</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69838</t>
+          <t>-32.87922, -70.60887</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/07/11 18:01:34</t>
+          <t>2026/07/13 08:58:40</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.3895366, -70.6738566</t>
+          <t>-34.2033433, -70.68859</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.38954, -70.67386</t>
+          <t>-34.20334, -70.68859</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>01:37:01</t>
+          <t>12:50:09</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>17.06</v>
+        <v>164.51</v>
       </c>
       <c r="M59" t="n">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="N59" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/07/11 16:40:51</t>
+          <t>2026/07/12 20:26:33</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-32.85676, -70.586175</t>
+          <t>-32.7430583, -70.7297799</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-32.85676, -70.58617</t>
+          <t>-32.74306, -70.72978</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/07/11 17:31:47</t>
+          <t>2026/07/13 07:15:14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-32.8791349, -70.60927</t>
+          <t>-32.8657616, -70.681495</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-32.87913, -70.60927</t>
+          <t>-32.86576, -70.68149</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:50:56</t>
+          <t>10:48:41</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>12.93</v>
+        <v>16.37</v>
       </c>
       <c r="M60" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/07/11 17:31:59</t>
+          <t>2026/07/12 20:46:45</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-32.8790366, -70.6094516</t>
+          <t>-32.838826, -70.954145</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-32.87904, -70.60945</t>
+          <t>-32.83883, -70.95414</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/07/11 21:59:41</t>
+          <t>2026/07/12 21:29:28</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.8661516, -70.6240483</t>
+          <t>-32.837137, -70.967133</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.86615, -70.62405</t>
+          <t>-32.83714, -70.96713</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>04:27:42</t>
+          <t>00:42:43</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>7.89</v>
+        <v>1.49</v>
       </c>
       <c r="M61" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="N61" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/07/11 18:01:57</t>
+          <t>2026/07/12 20:54:32</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-33.389325, -70.6740466</t>
+          <t>-32.785335, -70.960431</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-33.38932, -70.67405</t>
+          <t>-32.78534, -70.96043</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/07/11 18:18:09</t>
+          <t>2026/07/12 22:21:16</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-33.3620066, -70.670115</t>
+          <t>-32.840285, -70.960044</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-33.36201, -70.67011</t>
+          <t>-32.84029, -70.96004</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:16:12</t>
+          <t>01:26:44</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.61</v>
+        <v>13.09</v>
       </c>
       <c r="M62" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="N62" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,57 +4026,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/07/11 18:12:37</t>
+          <t>2026/07/12 21:07:56</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-32.7446149, -70.7280133</t>
+          <t>-33.3893316, -70.6740566</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-32.74461, -70.72801</t>
+          <t>-33.38933, -70.67406</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/07/11 18:45:23</t>
+          <t>2026/07/12 22:04:25</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-32.79772, -70.8874066</t>
+          <t>-33.4762683, -70.6983366</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88741</t>
+          <t>-33.47627, -70.69834</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:32:46</t>
+          <t>00:56:29</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>18.65</v>
+        <v>13.52</v>
       </c>
       <c r="M63" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="N63" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/07/11 18:18:20</t>
+          <t>2026/07/12 21:29:55</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.362025, -70.67014</t>
+          <t>-32.837103, -70.967171</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.36203, -70.67014</t>
+          <t>-32.83710, -70.96717</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/07/11 18:42:37</t>
+          <t>2026/07/12 21:51:25</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.353255, -70.6699483</t>
+          <t>-32.841867, -70.936848</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.35325, -70.66995</t>
+          <t>-32.84187, -70.93685</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:24:17</t>
+          <t>00:21:30</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.13</v>
+        <v>3.52</v>
       </c>
       <c r="M64" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N64" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/07/11 18:43:03</t>
+          <t>2026/07/12 21:52:01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.3532749, -70.6698816</t>
+          <t>-32.841676, -70.936803</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.35327, -70.66988</t>
+          <t>-32.84168, -70.93680</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/07/11 19:12:09</t>
+          <t>2026/07/13 09:51:07</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.4762666, -70.69831</t>
+          <t>-33.367377, -70.695938</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69831</t>
+          <t>-33.36738, -70.69594</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:29:06</t>
+          <t>11:59:06</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>18.94</v>
+        <v>76.92</v>
       </c>
       <c r="M65" t="n">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="N65" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,47 +4203,47 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/07/11 18:46:38</t>
+          <t>2026/07/12 22:05:35</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-32.7976, -70.8870766</t>
+          <t>-33.476115, -70.6985383</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-33.47612, -70.69854</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/07/12 11:01:08</t>
+          <t>2026/07/13 09:32:34</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-32.7465733, -70.7223516</t>
+          <t>-34.2048766, -70.6856249</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-32.74657, -70.72235</t>
+          <t>-34.20488, -70.68562</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>16:14:30</t>
+          <t>11:26:59</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>19.65</v>
+        <v>87.7</v>
       </c>
       <c r="M66" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="N66" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,57 +4262,57 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/07/11 18:52:27</t>
+          <t>2026/07/12 22:21:24</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-32.838398, -70.95549</t>
+          <t>-32.840256, -70.960131</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-32.83840, -70.95549</t>
+          <t>-32.84026, -70.96013</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/07/12 00:07:41</t>
+          <t>2026/07/12 22:39:06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-32.785516, -70.960409</t>
+          <t>-32.838368, -70.955964</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-32.78552, -70.96041</t>
+          <t>-32.83837, -70.95596</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>05:15:14</t>
+          <t>00:17:42</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>31.28</v>
+        <v>1.16</v>
       </c>
       <c r="M67" t="n">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/07/11 19:13:18</t>
+          <t>2026/07/12 22:39:34</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-33.4761183, -70.6984916</t>
+          <t>-32.838343, -70.955543</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69849</t>
+          <t>-32.83834, -70.95554</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/07/12 14:16:01</t>
+          <t>2026/07/13 12:12:25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-33.4762183, -70.6983649</t>
+          <t>-32.839701, -70.954577</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69836</t>
+          <t>-32.83970, -70.95458</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>19:02:43</t>
+          <t>13:32:51</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.02</v>
+        <v>204.05</v>
       </c>
       <c r="M68" t="n">
-        <v>8</v>
+        <v>138</v>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,175 +4380,175 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/07/11 20:42:55</t>
+          <t>2026/07/13 08:58:50</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-32.838769, -70.954084</t>
+          <t>-33.4362533, -70.6295033</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-32.83877, -70.95408</t>
+          <t>-33.43625, -70.62950</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/07/11 21:25:19</t>
+          <t>2026/07/13 10:02:50</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-32.841774, -70.936893</t>
+          <t>-33.3672499, -70.6955516</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-32.84177, -70.93689</t>
+          <t>-33.36725, -70.69555</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:42:24</t>
+          <t>01:04:00</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.29</v>
+        <v>13.38</v>
       </c>
       <c r="M69" t="n">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/07/11 21:25:31</t>
+          <t>2026/07/13 09:23:56</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-32.841755, -70.936878</t>
+          <t>-33.359904, -70.807156</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-32.84175, -70.93688</t>
+          <t>-33.35990, -70.80716</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/07/12 11:12:02</t>
+          <t>2026/07/13 09:45:20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-32.838851, -70.954161</t>
+          <t>-33.360145, -70.80659</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-32.83885, -70.95416</t>
+          <t>-33.36015, -70.80659</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>13:46:31</t>
+          <t>00:21:24</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.3</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/07/11 21:59:54</t>
+          <t>2026/07/13 09:45:47</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-32.866115, -70.6240783</t>
+          <t>-33.360123, -70.806616</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-32.86612, -70.62408</t>
+          <t>-33.36012, -70.80662</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/07/11 22:43:12</t>
+          <t>2026/07/13 10:36:19</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-32.8664116, -70.6238883</t>
+          <t>-33.360119, -70.806713</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-32.86641, -70.62389</t>
+          <t>-33.36012, -70.80671</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:43:18</t>
+          <t>00:50:32</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>6.75</v>
+        <v>0.01</v>
       </c>
       <c r="M71" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,116 +4557,116 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/07/11 22:43:40</t>
+          <t>2026/07/13 10:03:12</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-32.8661333, -70.62408</t>
+          <t>-33.36728, -70.695735</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-32.86613, -70.62408</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/07/11 23:22:55</t>
+          <t>2026/07/13 18:48:27</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-32.8792266, -70.6088699</t>
+          <t>-33.4360999, -70.6298916</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60887</t>
+          <t>-33.43610, -70.62989</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:39:15</t>
+          <t>08:45:15</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.74</v>
+        <v>19.08</v>
       </c>
       <c r="M72" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="N72" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/07/11 23:23:12</t>
+          <t>2026/07/13 10:36:41</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.6087933</t>
+          <t>-33.360039, -70.806789</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-33.36004, -70.80679</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/07/12 11:16:04</t>
+          <t>2026/07/13 10:48:50</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-32.8678316, -70.6224066</t>
+          <t>-33.360072, -70.806802</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-32.86783, -70.62241</t>
+          <t>-33.36007, -70.80680</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>11:52:52</t>
+          <t>00:12:09</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,116 +4675,116 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/07/12 04:39:18</t>
+          <t>2026/07/13 10:49:00</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.360103, -70.806819</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.36010, -70.80682</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/07/17 23:41:06</t>
+          <t>2026/07/13 12:24:43</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.366989, -70.69623</t>
+          <t>-33.359879, -70.807133</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.36699, -70.69623</t>
+          <t>-33.35988, -70.80713</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>139:01:48</t>
+          <t>01:35:43</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/07/12 18:43:14</t>
+          <t>2026/07/13 12:25:07</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-32.7435066, -70.7327433</t>
+          <t>-33.359881, -70.807152</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-32.74351, -70.73274</t>
+          <t>-33.35988, -70.80715</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/12 19:12:44</t>
+          <t>2026/07/13 14:25:09</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-32.7435616, -70.736105</t>
+          <t>-33.360174, -70.806587</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-32.74356, -70.73610</t>
+          <t>-33.36017, -70.80659</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:29:30</t>
+          <t>02:00:02</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.77</v>
+        <v>0.06</v>
       </c>
       <c r="M75" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/07/12 19:13:42</t>
+          <t>2026/07/13 13:06:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-32.743345, -70.7326616</t>
+          <t>-33.401135, -70.7505233</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-32.74334, -70.73266</t>
+          <t>-33.40113, -70.75052</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/07/12 20:25:18</t>
+          <t>2026/07/13 14:10:37</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-32.74317, -70.729675</t>
+          <t>-33.360195, -70.8090133</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72968</t>
+          <t>-33.36019, -70.80901</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01:11:36</t>
+          <t>01:04:34</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.07</v>
+        <v>10.86</v>
       </c>
       <c r="M76" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/07/12 20:26:33</t>
+          <t>2026/07/13 14:08:38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-32.7430583, -70.7297799</t>
+          <t>-34.2055233, -70.6782049</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-32.74306, -70.72978</t>
+          <t>-34.20552, -70.67820</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/07/13 07:15:14</t>
+          <t>2026/07/13 14:21:45</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-32.8657616, -70.681495</t>
+          <t>-34.20556, -70.6782116</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-32.86576, -70.68149</t>
+          <t>-34.20556, -70.67821</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>10:48:41</t>
+          <t>00:13:07</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>16.37</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="N77" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,283 +4911,283 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/07/13 08:58:50</t>
+          <t>2026/07/13 14:11:52</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.4362533, -70.6295033</t>
+          <t>-33.36071, -70.809025</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.43625, -70.62950</t>
+          <t>-33.36071, -70.80903</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/07/13 10:02:50</t>
+          <t>2026/07/13 14:19:52</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.3672499, -70.6955516</t>
+          <t>-33.3605066, -70.8091083</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69555</t>
+          <t>-33.36051, -70.80911</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>01:04:00</t>
+          <t>00:08:00</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>13.38</v>
+        <v>0.02</v>
       </c>
       <c r="M78" t="n">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="N78" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/07/13 09:23:56</t>
+          <t>2026/07/13 14:20:10</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.359904, -70.807156</t>
+          <t>-33.360525, -70.8092616</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80716</t>
+          <t>-33.36053, -70.80926</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:20</t>
+          <t>2026/07/13 16:09:51</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.360145, -70.80659</t>
+          <t>-33.1345899, -71.5636699</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80659</t>
+          <t>-33.13459, -71.56367</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:21:24</t>
+          <t>01:49:41</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.07000000000000001</v>
+        <v>104.92</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:47</t>
+          <t>2026/07/13 14:22:11</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-33.360123, -70.806616</t>
+          <t>-34.2055566, -70.6783433</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80662</t>
+          <t>-34.20556, -70.67834</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/07/13 10:36:19</t>
+          <t>2026/07/13 16:00:08</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.360119, -70.806713</t>
+          <t>-33.744805, -70.7382516</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80671</t>
+          <t>-33.74480, -70.73825</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:50:32</t>
+          <t>01:37:57</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.01</v>
+        <v>56.03</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026/07/13 14:25:31</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-33.360108, -70.806563</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-33.36011, -70.80656</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026/07/13 15:19:07</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-33.360027, -70.807117</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-33.36003, -70.80712</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>00:53:36</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4</v>
+      </c>
+      <c r="N81" t="n">
         <v>3</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026/07/13 10:03:12</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-33.36728, -70.695735</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-33.36728, -70.69573</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2026/07/13 18:48:27</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-33.4360999, -70.6298916</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>-33.43610, -70.62989</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>08:45:15</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="M81" t="n">
-        <v>112</v>
-      </c>
-      <c r="N81" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/07/13 10:36:41</t>
+          <t>2026/07/13 15:18:23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-33.360039, -70.806789</t>
+          <t>-33.359985, -70.80697</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80679</t>
+          <t>-33.35999, -70.80697</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/07/13 10:48:50</t>
+          <t>2026/07/13 15:39:55</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-33.360072, -70.806802</t>
+          <t>-33.3797383, -70.7528033</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80680</t>
+          <t>-33.37974, -70.75280</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:12:09</t>
+          <t>00:21:32</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -5197,50 +5197,50 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/07/13 10:49:00</t>
+          <t>2026/07/13 15:19:48</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.360103, -70.806819</t>
+          <t>-33.360031, -70.807117</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80682</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/07/13 12:24:43</t>
+          <t>2026/07/13 16:32:46</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.359879, -70.807133</t>
+          <t>-33.35997, -70.807061</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.35988, -70.80713</t>
+          <t>-33.35997, -70.80706</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>01:35:43</t>
+          <t>01:12:58</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="M83" t="n">
         <v>4</v>
@@ -5252,60 +5252,60 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/07/13 12:25:07</t>
+          <t>2026/07/13 15:40:13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.359881, -70.807152</t>
+          <t>-33.3797466, -70.7528116</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.35988, -70.80715</t>
+          <t>-33.37975, -70.75281</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:09</t>
+          <t>2026/07/13 16:14:59</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.360174, -70.806587</t>
+          <t>-33.3599716, -70.8070499</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80659</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>02:00:02</t>
+          <t>00:34:46</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.06</v>
+        <v>7.79</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="N84" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,106 +5324,106 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/07/13 14:22:11</t>
+          <t>2026/07/13 16:01:23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-34.2055566, -70.6783433</t>
+          <t>-33.7441016, -70.738085</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67834</t>
+          <t>-33.74410, -70.73808</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/07/13 16:00:08</t>
+          <t>2026/07/13 16:46:22</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.744805, -70.7382516</t>
+          <t>-33.501845, -70.7686866</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.74480, -70.73825</t>
+          <t>-33.50185, -70.76869</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>01:37:57</t>
+          <t>00:44:59</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>56.03</v>
+        <v>35</v>
       </c>
       <c r="M85" t="n">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="N85" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:31</t>
+          <t>2026/07/13 16:11:06</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.360108, -70.806563</t>
+          <t>-33.1347083, -71.5636116</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.36011, -70.80656</t>
+          <t>-33.13471, -71.56361</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:07</t>
+          <t>2026/07/13 17:07:54</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.360027, -70.807117</t>
+          <t>-33.0873133, -71.3622983</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:53:36</t>
+          <t>00:56:48</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.07000000000000001</v>
+        <v>43.75</v>
       </c>
       <c r="M86" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,234 +5442,234 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/07/13 14:27:42</t>
+          <t>2026/07/13 16:15:08</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.3601166, -70.8064883</t>
+          <t>-33.3599866, -70.8071883</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80649</t>
+          <t>-33.35999, -70.80719</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/07/13 15:17:08</t>
+          <t>2026/07/13 18:54:29</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.36016, -70.8067916</t>
+          <t>-32.7431899, -70.733085</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.36016, -70.80679</t>
+          <t>-32.74319, -70.73309</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>00:49:26</t>
+          <t>02:39:21</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.04</v>
+        <v>90.23</v>
       </c>
       <c r="M87" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="N87" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/07/13 15:18:23</t>
+          <t>2026/07/13 16:33:02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.359985, -70.80697</t>
+          <t>-33.360044, -70.807116</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80697</t>
+          <t>-33.36004, -70.80712</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/13 15:39:55</t>
+          <t>2026/07/14 11:24:00</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.3797383, -70.7528033</t>
+          <t>-33.359965, -70.807053</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.37974, -70.75280</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:21:32</t>
+          <t>18:50:58</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.56</v>
+        <v>0.05</v>
       </c>
       <c r="M88" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:48</t>
+          <t>2026/07/13 16:46:32</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-33.360031, -70.807117</t>
+          <t>-33.501865, -70.76861</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-33.50187, -70.76861</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/13 16:32:46</t>
+          <t>2026/07/13 18:38:20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-33.35997, -70.807061</t>
+          <t>-32.8823216, -70.6119916</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80706</t>
+          <t>-32.88232, -70.61199</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>01:12:58</t>
+          <t>01:51:48</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.1</v>
+        <v>88.83</v>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026/07/13 17:09:09</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-33.0872883, -71.36232</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-33.08729, -71.36232</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026/07/13 17:47:39</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-33.0872316, -71.3622516</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-33.08723, -71.36225</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>00:38:30</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M90" t="n">
         <v>7</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2026/07/13 15:40:13</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-33.3797466, -70.7528116</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-33.37975, -70.75281</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2026/07/13 16:14:59</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-33.3599716, -70.8070499</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-33.35997, -70.80705</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>00:34:46</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="M90" t="n">
-        <v>86</v>
-      </c>
       <c r="N90" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/07/13 16:01:23</t>
+          <t>2026/07/13 17:45:19</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-33.7441016, -70.738085</t>
+          <t>-33.482188, -70.764925</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-33.74410, -70.73808</t>
+          <t>-33.48219, -70.76493</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/07/13 16:46:22</t>
+          <t>2026/07/14 09:05:33</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.501845, -70.7686866</t>
+          <t>-33.359932, -70.806898</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.50185, -70.76869</t>
+          <t>-33.35993, -70.80690</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:44:59</t>
+          <t>15:20:14</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>35</v>
+        <v>25.07</v>
       </c>
       <c r="M91" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N91" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,116 +5737,116 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/07/13 16:15:08</t>
+          <t>2026/07/13 17:48:54</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-33.3599866, -70.8071883</t>
+          <t>-33.08732, -71.3622916</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80719</t>
+          <t>-33.08732, -71.36229</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/07/13 18:54:29</t>
+          <t>2026/07/13 19:49:19</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-32.7431899, -70.733085</t>
+          <t>-33.0461516, -71.4201666</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73309</t>
+          <t>-33.04615, -71.42017</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>02:39:21</t>
+          <t>02:00:25</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>90.23</v>
+        <v>10.39</v>
       </c>
       <c r="M92" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="N92" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/13 16:33:02</t>
+          <t>2026/07/13 18:39:35</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.360044, -70.807116</t>
+          <t>-32.8794099, -70.6088433</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-32.87941, -70.60884</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:00</t>
+          <t>2026/07/13 19:14:47</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.359965, -70.807053</t>
+          <t>-32.8791466, -70.6092666</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-32.87915, -70.60927</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>18:50:58</t>
+          <t>00:35:12</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/13 16:46:32</t>
+          <t>2026/07/13 18:40:01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.501865, -70.76861</t>
+          <t>-32.79761, -70.8871099</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.50187, -70.76861</t>
+          <t>-32.79761, -70.88711</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/13 18:38:20</t>
+          <t>2026/07/13 19:35:24</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-32.8823216, -70.6119916</t>
+          <t>-32.7832683, -70.8549766</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-32.88232, -70.61199</t>
+          <t>-32.78327, -70.85498</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>01:51:48</t>
+          <t>00:55:23</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>88.83</v>
+        <v>3.86</v>
       </c>
       <c r="M94" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="N94" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/13 17:09:09</t>
+          <t>2026/07/13 18:48:42</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-33.0872883, -71.36232</t>
+          <t>-33.436315, -70.6293299</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36232</t>
+          <t>-33.43632, -70.62933</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/13 17:47:39</t>
+          <t>2026/07/13 19:31:57</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-33.0872316, -71.3622516</t>
+          <t>-33.466985, -70.6068116</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-33.08723, -71.36225</t>
+          <t>-33.46699, -70.60681</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:38:30</t>
+          <t>00:43:15</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.01</v>
+        <v>5.39</v>
       </c>
       <c r="M95" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="N95" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,47 +5973,47 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/13 17:48:54</t>
+          <t>2026/07/13 18:54:41</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-33.08732, -71.3622916</t>
+          <t>-32.7433, -70.7327583</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36229</t>
+          <t>-32.74330, -70.73276</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/13 19:49:19</t>
+          <t>2026/07/13 19:59:23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-33.0461516, -71.4201666</t>
+          <t>-32.7430866, -70.7297566</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-33.04615, -71.42017</t>
+          <t>-32.74309, -70.72976</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>02:00:25</t>
+          <t>01:04:42</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>10.39</v>
+        <v>1.38</v>
       </c>
       <c r="M96" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="N96" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,47 +6032,47 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/07/13 18:39:35</t>
+          <t>2026/07/13 19:15:19</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-32.8794099, -70.6088433</t>
+          <t>-32.8792316, -70.6088066</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-32.87941, -70.60884</t>
+          <t>-32.87923, -70.60881</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/07/13 19:14:47</t>
+          <t>2026/07/14 09:00:09</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-32.8791466, -70.6092666</t>
+          <t>-34.2055083, -70.6783166</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-32.87915, -70.60927</t>
+          <t>-34.20551, -70.67832</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:35:12</t>
+          <t>13:44:50</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.09</v>
+        <v>164.8</v>
       </c>
       <c r="M97" t="n">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
     </row>
     <row r="98">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,53 +6091,53 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/13 18:48:42</t>
+          <t>2026/07/13 19:33:12</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.436315, -70.6293299</t>
+          <t>-33.4670566, -70.6068533</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.43632, -70.62933</t>
+          <t>-33.46706, -70.60685</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/13 19:31:57</t>
+          <t>2026/07/13 21:01:57</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-33.466985, -70.6068116</t>
+          <t>-33.44084, -70.6303416</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-33.46699, -70.60681</t>
+          <t>-33.44084, -70.63034</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:43:15</t>
+          <t>01:28:45</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>5.39</v>
+        <v>4.58</v>
       </c>
       <c r="M98" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N98" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/13 18:54:41</t>
+          <t>2026/07/13 19:35:28</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.7433, -70.7327583</t>
+          <t>-32.7832333, -70.85493</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.74330, -70.73276</t>
+          <t>-32.78323, -70.85493</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/13 19:59:23</t>
+          <t>2026/07/13 19:55:29</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-32.7430866, -70.7297566</t>
+          <t>-32.7976249, -70.8871633</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-32.74309, -70.72976</t>
+          <t>-32.79762, -70.88716</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>01:04:42</t>
+          <t>00:20:01</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.38</v>
+        <v>3.72</v>
       </c>
       <c r="M99" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="N99" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/13 19:15:19</t>
+          <t>2026/07/13 19:49:28</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088066</t>
+          <t>-33.0461283, -71.4200833</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-33.04613, -71.42008</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/14 09:00:09</t>
+          <t>2026/07/13 20:28:02</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-34.2055083, -70.6783166</t>
+          <t>-33.08734, -71.3622683</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67832</t>
+          <t>-33.08734, -71.36227</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>13:44:50</t>
+          <t>00:38:34</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>164.8</v>
+        <v>10.28</v>
       </c>
       <c r="M100" t="n">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="N100" t="n">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/13 19:33:12</t>
+          <t>2026/07/13 19:55:48</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.4670566, -70.6068533</t>
+          <t>-32.7976016, -70.887115</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.46706, -70.60685</t>
+          <t>-32.79760, -70.88711</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/13 21:01:57</t>
+          <t>2026/07/14 08:40:37</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.44084, -70.6303416</t>
+          <t>-34.2052916, -70.682345</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.44084, -70.63034</t>
+          <t>-34.20529, -70.68234</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>01:28:45</t>
+          <t>12:44:49</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.58</v>
+        <v>190.85</v>
       </c>
       <c r="M101" t="n">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="N101" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,47 +6327,47 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/13 19:35:28</t>
+          <t>2026/07/13 19:59:32</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.7832333, -70.85493</t>
+          <t>-32.7430283, -70.7297866</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.78323, -70.85493</t>
+          <t>-32.74303, -70.72979</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:29</t>
+          <t>2026/07/14 08:15:13</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871633</t>
+          <t>-33.3598283, -70.806785</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88716</t>
+          <t>-33.35983, -70.80679</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:20:01</t>
+          <t>12:15:41</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.72</v>
+        <v>90</v>
       </c>
       <c r="M102" t="n">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="N102" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/13 19:49:28</t>
+          <t>2026/07/13 20:29:15</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.0461283, -71.4200833</t>
+          <t>-33.0873083, -71.3623783</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.04613, -71.42008</t>
+          <t>-33.08731, -71.36238</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/13 20:28:02</t>
+          <t>2026/07/14 07:46:35</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.08734, -71.3622683</t>
+          <t>-33.0868883, -71.3619016</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36227</t>
+          <t>-33.08689, -71.36190</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:38:34</t>
+          <t>11:17:20</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>10.28</v>
+        <v>14</v>
       </c>
       <c r="M103" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N103" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:48</t>
+          <t>2026/07/13 21:02:13</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.7976016, -70.887115</t>
+          <t>-33.440555, -70.63033</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88711</t>
+          <t>-33.44056, -70.63033</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/14 08:40:37</t>
+          <t>2026/07/13 21:24:44</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.682345</t>
+          <t>-33.4362516, -70.629595</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68234</t>
+          <t>-33.43625, -70.62959</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>12:44:49</t>
+          <t>00:22:31</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>190.85</v>
+        <v>0.72</v>
       </c>
       <c r="M104" t="n">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="N104" t="n">
-        <v>78</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,116 +6504,116 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/13 19:59:32</t>
+          <t>2026/07/13 21:25:42</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.7430283, -70.7297866</t>
+          <t>-33.4364766, -70.6295866</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72979</t>
+          <t>-33.43648, -70.62959</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/14 08:15:13</t>
+          <t>2026/07/14 10:57:49</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.3598283, -70.806785</t>
+          <t>-33.3661216, -70.6955083</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.35983, -70.80679</t>
+          <t>-33.36612, -70.69551</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12:15:41</t>
+          <t>13:32:07</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>90</v>
+        <v>13.47</v>
       </c>
       <c r="M105" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N105" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/13 20:29:15</t>
+          <t>2026/07/14 11:24:17</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-33.0873083, -71.3623783</t>
+          <t>-33.359942, -70.807084</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36238</t>
+          <t>-33.35994, -70.80708</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/14 07:46:35</t>
+          <t>2026/07/14 12:02:22</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.0868883, -71.3619016</t>
+          <t>-33.360005, -70.806977</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.08689, -71.36190</t>
+          <t>-33.36001, -70.80698</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>11:17:20</t>
+          <t>00:38:05</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>14</v>
+        <v>0.04</v>
       </c>
       <c r="M106" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="N106" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/13 21:02:13</t>
+          <t>2026/07/14 12:03:21</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-33.440555, -70.63033</t>
+          <t>-33.360075, -70.806905</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-33.44056, -70.63033</t>
+          <t>-33.36008, -70.80691</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/13 21:24:44</t>
+          <t>2026/07/14 12:25:04</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-33.4362516, -70.629595</t>
+          <t>-33.360001, -70.807087</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-33.43625, -70.62959</t>
+          <t>-33.36000, -70.80709</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:22:31</t>
+          <t>00:21:43</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.72</v>
+        <v>0.19</v>
       </c>
       <c r="M107" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N107" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,116 +6681,116 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/13 21:25:42</t>
+          <t>2026/07/14 14:09:00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-33.4364766, -70.6295866</t>
+          <t>-33.360079, -70.806683</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-33.43648, -70.62959</t>
+          <t>-33.36008, -70.80668</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/14 10:57:49</t>
+          <t>2026/07/14 15:09:39</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-33.3661216, -70.6955083</t>
+          <t>-33.36007, -70.808767</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-33.36612, -70.69551</t>
+          <t>-33.36007, -70.80877</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>13:32:07</t>
+          <t>01:00:39</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>13.47</v>
+        <v>0.5</v>
       </c>
       <c r="M108" t="n">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="N108" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:17</t>
+          <t>2026/07/14 15:10:31</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-33.359942, -70.807084</t>
+          <t>-33.360105, -70.806689</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80708</t>
+          <t>-33.36010, -70.80669</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/14 12:02:22</t>
+          <t>2026/07/14 18:47:39</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-33.360005, -70.806977</t>
+          <t>-33.482123, -70.765334</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80698</t>
+          <t>-33.48212, -70.76533</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:38:05</t>
+          <t>03:37:08</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.04</v>
+        <v>19.34</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,57 +6799,57 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/14 12:03:21</t>
+          <t>2026/07/14 18:23:10</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-33.360075, -70.806905</t>
+          <t>-33.087325, -71.3623016</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80691</t>
+          <t>-33.08732, -71.36230</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/14 12:25:04</t>
+          <t>2026/07/15 08:27:37</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-33.360001, -70.807087</t>
+          <t>-33.0872683, -71.3623066</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80709</t>
+          <t>-33.08727, -71.36231</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:21:43</t>
+          <t>14:04:27</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="M110" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,47 +6858,47 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/14 18:23:10</t>
+          <t>2026/07/14 18:48:33</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.087325, -71.3623016</t>
+          <t>-33.482178, -70.764895</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36230</t>
+          <t>-33.48218, -70.76489</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/15 08:27:37</t>
+          <t>2026/07/15 08:54:52</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-33.0872683, -71.3623066</t>
+          <t>-33.359961, -70.806992</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36231</t>
+          <t>-33.35996, -70.80699</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>14:04:27</t>
+          <t>14:06:19</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.04</v>
+        <v>22.72</v>
       </c>
       <c r="M111" t="n">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="N111" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112">
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,47 +6917,47 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/15 14:43:03</t>
+          <t>2026/07/15 13:46:36</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-33.3604783, -70.8090416</t>
+          <t>-33.3604683, -70.8083033</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-33.36048, -70.80904</t>
+          <t>-33.36047, -70.80830</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:09</t>
+          <t>2026/07/15 14:41:48</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-33.3895116, -70.6738666</t>
+          <t>-33.3612533, -70.8090166</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-33.38951, -70.67387</t>
+          <t>-33.36125, -70.80902</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:46:06</t>
+          <t>00:55:12</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>17.34</v>
+        <v>0.15</v>
       </c>
       <c r="M112" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="N112" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6976,47 +6976,47 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:42</t>
+          <t>2026/07/15 14:43:03</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.3893049, -70.6740016</t>
+          <t>-33.3604783, -70.8090416</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.38930, -70.67400</t>
+          <t>-33.36048, -70.80904</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/15 16:07:40</t>
+          <t>2026/07/15 15:29:09</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.3654, -70.6799283</t>
+          <t>-33.3895116, -70.6738666</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.36540, -70.67993</t>
+          <t>-33.38951, -70.67387</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>00:37:58</t>
+          <t>00:46:06</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3.65</v>
+        <v>17.34</v>
       </c>
       <c r="M113" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="N113" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,47 +7035,47 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/15 16:08:55</t>
+          <t>2026/07/15 15:29:42</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.3653549, -70.6799433</t>
+          <t>-33.3893049, -70.6740016</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.36535, -70.67994</t>
+          <t>-33.38930, -70.67400</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:15</t>
+          <t>2026/07/15 16:07:40</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.362085, -70.6701533</t>
+          <t>-33.3654, -70.6799283</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67015</t>
+          <t>-33.36540, -70.67993</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:50:20</t>
+          <t>00:37:58</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.66</v>
+        <v>3.65</v>
       </c>
       <c r="M114" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="N114" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,116 +7094,116 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:50</t>
+          <t>2026/07/15 16:08:55</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.3621033, -70.6702233</t>
+          <t>-33.3653549, -70.6799433</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67022</t>
+          <t>-33.36535, -70.67994</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:09</t>
+          <t>2026/07/15 16:59:15</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.3895, -70.6736916</t>
+          <t>-33.362085, -70.6701533</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.38950, -70.67369</t>
+          <t>-33.36209, -70.67015</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>03:07:19</t>
+          <t>00:50:20</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4.04</v>
+        <v>1.66</v>
       </c>
       <c r="M115" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="N115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/15 18:24:10</t>
+          <t>2026/07/15 16:59:50</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-33.0872466, -71.362245</t>
+          <t>-33.3621033, -70.6702233</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-33.08725, -71.36225</t>
+          <t>-33.36210, -70.67022</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/17 22:24:22</t>
+          <t>2026/07/15 20:07:09</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-33.0872466, -71.362245</t>
+          <t>-33.3895, -70.6736916</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-33.08725, -71.36225</t>
+          <t>-33.38950, -70.67369</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>52:00:12</t>
+          <t>03:07:19</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/15 18:32:49</t>
+          <t>2026/07/15 17:04:13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.840415, -70.960116</t>
+          <t>-33.482171, -70.764904</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.84042, -70.96012</t>
+          <t>-33.48217, -70.76490</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/15 19:09:21</t>
+          <t>2026/07/15 18:54:01</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-32.838369, -70.956136</t>
+          <t>-33.480734, -70.760036</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95614</t>
+          <t>-33.48073, -70.76004</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:36:32</t>
+          <t>01:49:48</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.97</v>
+        <v>0.51</v>
       </c>
       <c r="M117" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N117" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/07/15 18:38:03</t>
+          <t>2026/07/15 18:32:49</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-32.7917783, -70.872935</t>
+          <t>-32.840415, -70.960116</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-32.79178, -70.87293</t>
+          <t>-32.84042, -70.96012</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/15 19:19:22</t>
+          <t>2026/07/15 19:09:21</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.88742</t>
+          <t>-32.838369, -70.956136</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88742</t>
+          <t>-32.83837, -70.95614</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:41:19</t>
+          <t>00:36:32</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.7</v>
+        <v>0.97</v>
       </c>
       <c r="M118" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="N118" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,106 +7330,106 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/15 18:55:01</t>
+          <t>2026/07/15 18:38:03</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-33.479699, -70.758226</t>
+          <t>-32.7917783, -70.872935</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-33.47970, -70.75823</t>
+          <t>-32.79178, -70.87293</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/15 20:02:31</t>
+          <t>2026/07/15 19:19:22</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-32.838758, -70.954109</t>
+          <t>-32.7977149, -70.88742</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-32.83876, -70.95411</t>
+          <t>-32.79771, -70.88742</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>01:07:30</t>
+          <t>00:41:19</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>95.33</v>
+        <v>1.7</v>
       </c>
       <c r="M119" t="n">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="N119" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/15 19:03:40</t>
+          <t>2026/07/15 18:55:01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-32.87923, -70.6088166</t>
+          <t>-33.479699, -70.758226</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60882</t>
+          <t>-33.47970, -70.75823</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/17 23:12:02</t>
+          <t>2026/07/15 20:02:31</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-32.8792333, -70.608815</t>
+          <t>-32.838758, -70.954109</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60882</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>52:08:22</t>
+          <t>01:07:30</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.01</v>
+        <v>95.33</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="121">
@@ -7758,26 +7758,26 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/17 23:29:49</t>
+          <t>2026/07/18 22:32:46</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-32.7429883, -70.7298566</t>
+          <t>-32.7429766, -70.7298116</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-32.74299, -70.72986</t>
+          <t>-32.74298, -70.72981</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>50:12:55</t>
+          <t>73:15:52</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -7848,70 +7848,70 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/07/17 12:50:36</t>
+          <t>2026/07/17 16:51:20</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-32.79759, -70.8871066</t>
+          <t>-33.3665833, -70.6954649</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88711</t>
+          <t>-33.36658, -70.69546</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/17 22:50:36</t>
+          <t>2026/07/17 17:48:13</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-32.79759, -70.8871066</t>
+          <t>-33.4358716, -70.6300966</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88711</t>
+          <t>-33.43587, -70.63010</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>00:56:53</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>13.29</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,37 +7920,37 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/07/17 15:37:33</t>
+          <t>2026/07/17 17:49:25</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-32.841776, -70.936812</t>
+          <t>-33.43628, -70.629375</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-32.84178, -70.93681</t>
+          <t>-33.43628, -70.62937</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/17 23:40:40</t>
+          <t>2026/07/18 21:49:25</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-32.841776, -70.936812</t>
+          <t>-33.43628, -70.629375</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-32.84178, -70.93681</t>
+          <t>-33.43628, -70.62937</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>08:03:07</t>
+          <t>28:00:00</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -7966,11 +7966,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,57 +7979,57 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/07/17 16:51:20</t>
+          <t>2026/07/18 10:37:00</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-33.3665833, -70.6954649</t>
+          <t>-33.55173, -70.8447033</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69546</t>
+          <t>-33.55173, -70.84470</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/07/17 17:48:13</t>
+          <t>2026/07/18 11:41:27</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-33.4358716, -70.6300966</t>
+          <t>-33.3671116, -70.6954666</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-33.43587, -70.63010</t>
+          <t>-33.36711, -70.69547</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>00:56:53</t>
+          <t>01:04:27</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>13.29</v>
+        <v>35.8</v>
       </c>
       <c r="M130" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="N130" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8038,37 +8038,37 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/07/17 17:49:25</t>
+          <t>2026/07/18 11:42:39</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-33.43628, -70.629375</t>
+          <t>-33.3671433, -70.6958149</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62937</t>
+          <t>-33.36714, -70.69581</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/17 23:49:25</t>
+          <t>2026/07/18 21:42:39</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-33.43628, -70.629375</t>
+          <t>-33.3671433, -70.6958149</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62937</t>
+          <t>-33.36714, -70.69581</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -8084,11 +8084,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8097,41 +8097,41 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/07/17 18:52:06</t>
+          <t>2026/07/18 13:08:33</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-32.838358, -70.955537</t>
+          <t>-32.8792266, -70.6088966</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95554</t>
+          <t>-32.87923, -70.60890</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/17 23:49:37</t>
+          <t>2026/07/18 21:10:35</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-32.838358, -70.955537</t>
+          <t>-32.879245, -70.6087783</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95554</t>
+          <t>-32.87924, -70.60878</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>04:57:31</t>
+          <t>08:02:02</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -8143,11 +8143,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,46 +8156,282 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/07/17 21:10:52</t>
+          <t>2026/07/18 13:23:30</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-33.4761016, -70.6985316</t>
+          <t>-32.841653, -70.936835</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69853</t>
+          <t>-32.84165, -70.93684</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/17 23:13:07</t>
+          <t>2026/07/18 22:26:36</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-33.4761466, -70.6985149</t>
+          <t>-32.841653, -70.936835</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69851</t>
+          <t>-32.84165, -70.93684</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>02:02:15</t>
+          <t>09:03:06</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>8</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026/07/18 17:09:09</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-33.0873, -71.3623216</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-33.08730, -71.36232</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026/07/18 22:29:58</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-33.0872566, -71.3622533</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-33.08726, -71.36225</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>05:20:49</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TGPS-77</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026/07/18 19:04:34</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-32.7975833, -70.88705</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-32.79758, -70.88705</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026/07/18 21:04:34</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-32.7975833, -70.88705</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-32.79758, -70.88705</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>6</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026/07/18 19:54:58</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-33.5779366, -70.6311033</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-33.57794, -70.63110</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026/07/18 21:55:00</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-33.5779366, -70.6311033</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-33.57794, -70.63110</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>02:00:02</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026/07/18 20:19:14</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-32.840582, -70.995705</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-32.84058, -70.99571</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026/07/18 22:16:44</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-32.840582, -70.995705</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-32.84058, -70.99571</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>01:57:30</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8247,10 +8483,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1359.96</v>
+        <v>1318.61</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8266,10 +8502,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>621.08</v>
+        <v>576.0599999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -8285,10 +8521,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>661.3</v>
+        <v>648.12</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8304,7 +8540,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>580.88</v>
+        <v>580.87</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
@@ -8342,7 +8578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -8475,10 +8711,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>888.84</v>
+        <v>865.89</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -8513,16 +8749,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>77.44</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
@@ -8551,7 +8787,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
@@ -8570,10 +8806,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1040.45</v>
+        <v>944.34</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -8589,10 +8825,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>552.2</v>
+        <v>449.48</v>
       </c>
       <c r="C20" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/18 21:34:34</t>
+          <t>2026/07/18 23:34:36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>165:20:18</t>
+          <t>167:20:20</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/18 22:13:24</t>
+          <t>2026/07/18 23:13:38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>165:59:04</t>
+          <t>166:59:18</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/18 22:24:44</t>
+          <t>2026/07/18 23:24:07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:08:17</t>
+          <t>167:07:40</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/18 21:57:21</t>
+          <t>2026/07/18 23:57:22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>165:40:45</t>
+          <t>167:40:46</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/18 21:56:11</t>
+          <t>2026/07/18 23:56:11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>165:32:15</t>
+          <t>167:32:15</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/18 22:31:37</t>
+          <t>2026/07/18 23:31:38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:05:44</t>
+          <t>167:05:45</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/18 22:01:29</t>
+          <t>2026/07/18 23:01:38</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>164:00:01</t>
+          <t>165:00:10</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/18 22:11:21</t>
+          <t>2026/07/18 23:11:22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>163:59:07</t>
+          <t>164:59:08</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/18 21:40:20</t>
+          <t>2026/07/18 23:40:44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>161:01:02</t>
+          <t>163:01:26</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -7758,22 +7758,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/18 22:32:46</t>
+          <t>2026/07/18 23:59:01</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-32.7429766, -70.7298116</t>
+          <t>-32.7430016, -70.7298083</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-32.74298, -70.72981</t>
+          <t>-32.74300, -70.72981</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>73:15:52</t>
+          <t>74:42:07</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/18 21:49:25</t>
+          <t>2026/07/18 23:49:25</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>28:00:00</t>
+          <t>30:00:00</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/18 21:42:39</t>
+          <t>2026/07/18 23:42:39</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/18 21:10:35</t>
+          <t>2026/07/18 23:10:35</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>08:02:02</t>
+          <t>10:02:02</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/18 22:26:36</t>
+          <t>2026/07/18 23:26:36</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>09:03:06</t>
+          <t>10:03:06</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/07/18 21:04:34</t>
+          <t>2026/07/18 23:04:34</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/07/18 21:55:00</t>
+          <t>2026/07/18 23:55:00</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>02:00:02</t>
+          <t>04:00:02</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/18 22:16:44</t>
+          <t>2026/07/18 23:16:44</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>01:57:30</t>
+          <t>02:57:30</t>
         </is>
       </c>
       <c r="L137" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/12 04:00:00   Hasta : 2026/07/19 03:59:59</t>
+          <t>Desde : 2026/07/13 04:00:00   Hasta : 2026/07/20 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,62 +540,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/07/12 00:00:29</t>
+          <t>2026/07/13 00:01:34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.832254, -70.976477</t>
+          <t>-34.346035, -71.125736</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-32.83225, -70.97648</t>
+          <t>-34.34604, -71.12574</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/12 00:07:41</t>
+          <t>2026/07/19 23:01:38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-32.785516, -70.960409</t>
+          <t>-34.345949, -71.125868</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.78552, -70.96041</t>
+          <t>-34.34595, -71.12587</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>00:07:12</t>
+          <t>167:00:04</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.74</v>
+        <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -604,53 +604,53 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/07/12 00:08:25</t>
+          <t>2026/07/13 00:05:35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-32.785335, -70.960448</t>
+          <t>-33.476115, -70.6985383</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-32.78534, -70.96045</t>
+          <t>-33.47612, -70.69854</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/12 08:10:51</t>
+          <t>2026/07/13 09:32:34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.384799, -70.532819</t>
+          <t>-34.2048766, -70.6856249</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.38480, -70.53282</t>
+          <t>-34.20488, -70.68562</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>08:02:26</t>
+          <t>09:26:59</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>103.98</v>
+        <v>87.7</v>
       </c>
       <c r="M5" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="N5" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,37 +663,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/07/12 00:14:16</t>
+          <t>2026/07/13 00:12:19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.579544, -70.961407</t>
+          <t>-34.205228, -70.67741</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.57954, -70.96141</t>
+          <t>-34.20523, -70.67741</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/18 23:34:36</t>
+          <t>2026/07/19 23:11:38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.5796, -70.961366</t>
+          <t>-34.205402, -70.677263</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.57960, -70.96137</t>
+          <t>-34.20540, -70.67726</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>167:20:20</t>
+          <t>166:59:19</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -722,22 +722,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/07/12 00:14:20</t>
+          <t>2026/07/13 00:13:21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.360009, -70.807034</t>
+          <t>-33.359984, -70.807055</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80703</t>
+          <t>-33.35998, -70.80706</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/18 23:13:38</t>
+          <t>2026/07/19 23:13:21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>166:59:18</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,53 +781,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/07/12 00:14:39</t>
+          <t>2026/07/13 00:22:58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.346017, -71.125783</t>
+          <t>-34.876427, -71.127258</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.34602, -71.12578</t>
+          <t>-34.87643, -71.12726</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/12 01:04:03</t>
+          <t>2026/07/19 22:23:34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.346035, -71.125736</t>
+          <t>-34.876517, -71.127094</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.34604, -71.12574</t>
+          <t>-34.87652, -71.12709</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>00:49:24</t>
+          <t>166:00:36</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/07/12 00:15:09</t>
+          <t>2026/07/13 00:23:50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677325</t>
+          <t>-33.360092, -70.807118</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67732</t>
+          <t>-33.36009, -70.80712</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/12 01:14:34</t>
+          <t>2026/07/13 08:59:50</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-34.205228, -70.67741</t>
+          <t>-33.360023, -70.806713</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67741</t>
+          <t>-33.36002, -70.80671</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>00:59:25</t>
+          <t>08:36:00</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/07/12 00:16:27</t>
+          <t>2026/07/13 00:26:39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-34.876497, -71.127268</t>
+          <t>-32.7430583, -70.7297799</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-34.87650, -71.12727</t>
+          <t>-32.74306, -70.72978</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/18 23:24:07</t>
+          <t>2026/07/13 07:15:14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-34.876517, -71.127094</t>
+          <t>-32.8657616, -70.681495</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.87652, -71.12709</t>
+          <t>-32.86576, -70.68149</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>167:07:40</t>
+          <t>06:48:35</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.06</v>
+        <v>16.37</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -958,41 +958,41 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/07/12 00:16:36</t>
+          <t>2026/07/13 00:31:20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.042744, -70.681743</t>
+          <t>-33.899812, -71.429505</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.04274, -70.68174</t>
+          <t>-33.89981, -71.42951</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/18 23:57:22</t>
+          <t>2026/07/19 22:31:37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.042596, -70.681656</t>
+          <t>-33.89987, -71.429483</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.04260, -70.68166</t>
+          <t>-33.89987, -71.42948</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>167:40:46</t>
+          <t>166:00:17</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/07/12 00:18:15</t>
+          <t>2026/07/13 00:34:45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-32.7429983, -70.7298549</t>
+          <t>-34.579681, -70.961483</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-32.74300, -70.72985</t>
+          <t>-34.57968, -70.96148</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/12 18:03:39</t>
+          <t>2026/07/19 22:34:34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-32.748345, -70.6528216</t>
+          <t>-34.5796, -70.961366</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.74835, -70.65282</t>
+          <t>-34.57960, -70.96137</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17:45:24</t>
+          <t>165:59:49</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.050000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="M12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,58 +1071,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/07/12 00:23:56</t>
+          <t>2026/07/13 00:36:38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.8792216, -70.608875</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.87922, -70.60887</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/18 23:56:11</t>
+          <t>2026/07/13 08:58:40</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.2033433, -70.68859</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.20334, -70.68859</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>167:32:15</t>
+          <t>08:22:02</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>164.51</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/07/12 00:24:08</t>
+          <t>2026/07/13 00:37:05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.360092, -70.807118</t>
+          <t>-32.838343, -70.955543</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36009, -70.80712</t>
+          <t>-32.83834, -70.95554</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/13 08:59:50</t>
+          <t>2026/07/13 12:12:25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.360023, -70.806713</t>
+          <t>-32.839701, -70.954577</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80671</t>
+          <t>-32.83970, -70.95458</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>32:35:42</t>
+          <t>11:35:20</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.12</v>
+        <v>204.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,46 +1189,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/07/12 00:25:53</t>
+          <t>2026/07/13 00:39:37</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.899806, -71.429473</t>
+          <t>-33.3674, -70.696184</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.89981, -71.42947</t>
+          <t>-33.36740, -70.69618</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/18 23:31:38</t>
+          <t>2026/07/19 22:40:44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.89987, -71.429483</t>
+          <t>-33.36714, -70.696418</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.89987, -71.42948</t>
+          <t>-33.36714, -70.69642</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>167:05:45</t>
+          <t>166:01:07</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/07/12 00:28:02</t>
+          <t>2026/07/13 00:39:59</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.087215, -71.3622349</t>
+          <t>-33.0872483, -71.36224</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36223</t>
+          <t>-33.08725, -71.36224</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/12 11:16:46</t>
+          <t>2026/07/13 08:11:09</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.087305, -71.3623016</t>
+          <t>-33.087285, -71.36232</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36230</t>
+          <t>-33.08729, -71.36232</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10:48:44</t>
+          <t>07:31:10</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>0.01</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,53 +1312,53 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/07/12 00:28:31</t>
+          <t>2026/07/13 00:48:31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-32.841755, -70.936878</t>
+          <t>-33.4362783, -70.629345</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-32.84175, -70.93688</t>
+          <t>-33.43628, -70.62935</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/12 11:12:02</t>
+          <t>2026/07/13 07:06:26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-32.838851, -70.954161</t>
+          <t>-33.4449966, -70.61965</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-32.83885, -70.95416</t>
+          <t>-33.44500, -70.61965</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10:43:31</t>
+          <t>06:17:55</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="N17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/07/12 00:39:00</t>
+          <t>2026/07/13 00:55:01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.367062, -70.696335</t>
+          <t>-32.841676, -70.936803</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.36706, -70.69634</t>
+          <t>-32.84168, -70.93680</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/12 03:41:06</t>
+          <t>2026/07/13 09:51:07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.367377, -70.695938</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.36738, -70.69594</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03:02:06</t>
+          <t>08:56:06</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.04</v>
+        <v>76.92</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,58 +1425,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/07/12 00:47:44</t>
+          <t>2026/07/13 00:56:10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-32.7976, -70.8870766</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/12 11:01:08</t>
+          <t>2026/07/19 22:56:11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-32.7465733, -70.7223516</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.74657, -70.72235</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10:13:24</t>
+          <t>166:00:01</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>19.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1484,52 +1484,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/07/12 00:48:31</t>
+          <t>2026/07/13 00:57:51</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.4362783, -70.629345</t>
+          <t>-34.042641, -70.681549</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62935</t>
+          <t>-34.04264, -70.68155</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/13 07:06:26</t>
+          <t>2026/07/19 22:57:38</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.4449966, -70.61965</t>
+          <t>-34.042596, -70.681656</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.44500, -70.61965</t>
+          <t>-34.04260, -70.68166</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30:17:55</t>
+          <t>165:59:47</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.97</v>
+        <v>0.05</v>
       </c>
       <c r="M20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/07/12 01:02:21</t>
+          <t>2026/07/13 01:02:21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>152:56:59</t>
+          <t>128:56:59</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1594,7 +1594,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,57 +1607,57 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/07/12 01:13:18</t>
+          <t>2026/07/13 01:09:47</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-33.4761183, -70.6984916</t>
+          <t>-32.79757, -70.8870583</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69849</t>
+          <t>-32.79757, -70.88706</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/07/12 14:16:01</t>
+          <t>2026/07/13 07:47:17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.4762183, -70.6983649</t>
+          <t>-33.3672916, -70.696675</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69836</t>
+          <t>-33.36729, -70.69667</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13:02:43</t>
+          <t>06:37:30</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.02</v>
+        <v>92.58</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/07/12 01:23:12</t>
+          <t>2026/07/13 07:07:07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.6087933</t>
+          <t>-33.445475, -70.6204933</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-33.44548, -70.62049</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/07/12 11:16:04</t>
+          <t>2026/07/13 08:58:35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-32.8678316, -70.6224066</t>
+          <t>-33.43611, -70.6298416</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-32.86783, -70.62241</t>
+          <t>-33.43611, -70.62984</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>09:52:52</t>
+          <t>01:51:28</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.46</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="N23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1720,58 +1720,58 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/07/12 02:01:28</t>
+          <t>2026/07/13 07:16:29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-34.346035, -71.125736</t>
+          <t>-32.8702183, -70.6803383</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-34.34604, -71.12574</t>
+          <t>-32.87022, -70.68034</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/18 23:01:38</t>
+          <t>2026/07/13 08:18:53</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-34.345949, -71.125868</t>
+          <t>-33.3599333, -70.8071349</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12587</t>
+          <t>-33.35993, -70.80713</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>165:00:10</t>
+          <t>01:02:24</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.03</v>
+        <v>72.94</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1779,58 +1779,58 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/07/12 02:12:14</t>
+          <t>2026/07/13 07:48:32</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-34.205228, -70.67741</t>
+          <t>-33.3672533, -70.696775</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67741</t>
+          <t>-33.36725, -70.69678</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/18 23:11:22</t>
+          <t>2026/07/13 09:17:19</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.205402, -70.677263</t>
+          <t>-34.2051666, -70.6840649</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67726</t>
+          <t>-34.20517, -70.68406</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>164:59:08</t>
+          <t>01:28:47</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.05</v>
+        <v>101.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1843,53 +1843,53 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/07/12 04:39:18</t>
+          <t>2026/07/13 08:11:38</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.0873233, -71.3622866</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.08732, -71.36229</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/18 23:40:44</t>
+          <t>2026/07/13 10:16:24</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.36714, -70.696418</t>
+          <t>-33.3601966, -70.8090216</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.36714, -70.69642</t>
+          <t>-33.36020, -70.80902</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>163:01:26</t>
+          <t>02:04:46</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.29</v>
+        <v>114.82</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1902,57 +1902,57 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/07/12 08:11:36</t>
+          <t>2026/07/13 08:19:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.384819, -70.532828</t>
+          <t>-33.35994, -70.8071866</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.38482, -70.53283</t>
+          <t>-33.35994, -70.80719</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/07/12 19:16:21</t>
+          <t>2026/07/13 09:26:02</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-32.838361, -70.955691</t>
+          <t>-33.3599466, -70.807095</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95569</t>
+          <t>-33.35995, -70.80710</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11:04:45</t>
+          <t>01:07:02</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>94.56999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="M27" t="n">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,53 +1961,53 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/07/12 11:01:14</t>
+          <t>2026/07/13 08:58:50</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.7465633, -70.7223533</t>
+          <t>-33.4362533, -70.6295033</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.74656, -70.72235</t>
+          <t>-33.43625, -70.62950</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/07/12 11:16:51</t>
+          <t>2026/07/13 10:02:50</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.7547866, -70.7279983</t>
+          <t>-33.3672499, -70.6955516</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.75479, -70.72800</t>
+          <t>-33.36725, -70.69555</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:15:37</t>
+          <t>01:04:00</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>13.38</v>
       </c>
       <c r="M28" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2020,53 +2020,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/07/12 11:12:22</t>
+          <t>2026/07/13 08:59:55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-32.838852, -70.954163</t>
+          <t>-34.2050983, -70.6852199</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.83885, -70.95416</t>
+          <t>-34.20510, -70.68522</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/07/12 11:20:31</t>
+          <t>2026/07/13 09:14:45</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-32.838273, -70.954522</t>
+          <t>-34.2046433, -70.6796633</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-32.83827, -70.95452</t>
+          <t>-34.20464, -70.67966</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:08:09</t>
+          <t>00:14:50</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
       <c r="M29" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2079,47 +2079,47 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/07/12 11:17:03</t>
+          <t>2026/07/13 09:00:21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-33.0873483, -71.3622483</t>
+          <t>-33.36005, -70.806665</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36225</t>
+          <t>-33.36005, -70.80666</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/07/12 15:41:38</t>
+          <t>2026/07/13 09:23:53</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-33.0904616, -71.3605616</t>
+          <t>-33.359906, -70.807149</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-33.09046, -71.36056</t>
+          <t>-33.35991, -70.80715</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>04:24:35</t>
+          <t>00:23:32</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.61</v>
+        <v>0.14</v>
       </c>
       <c r="M30" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,47 +2138,47 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/07/12 11:17:19</t>
+          <t>2026/07/13 09:15:04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-32.866175, -70.624015</t>
+          <t>-34.2042933, -70.6790766</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-32.86617, -70.62401</t>
+          <t>-34.20429, -70.67908</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/07/12 12:11:20</t>
+          <t>2026/07/13 09:53:03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-32.69114, -70.7803549</t>
+          <t>-34.2053416, -70.6802733</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.69114, -70.78035</t>
+          <t>-34.20534, -70.68027</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:54:01</t>
+          <t>00:37:59</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>28.08</v>
+        <v>2.46</v>
       </c>
       <c r="M31" t="n">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -2197,53 +2197,53 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/07/12 11:17:57</t>
+          <t>2026/07/13 09:18:34</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-32.7549149, -70.7280916</t>
+          <t>-34.2053666, -70.6803766</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-32.75491, -70.72809</t>
+          <t>-34.20537, -70.68038</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/07/12 11:58:42</t>
+          <t>2026/07/13 11:21:38</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-32.757665, -70.7028433</t>
+          <t>-34.2055433, -70.6775583</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.75767, -70.70284</t>
+          <t>-34.20554, -70.67756</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:40:45</t>
+          <t>02:03:04</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="M32" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="N32" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2251,58 +2251,58 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/07/12 11:21:27</t>
+          <t>2026/07/13 09:23:56</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.837088, -70.954738</t>
+          <t>-33.359904, -70.807156</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.83709, -70.95474</t>
+          <t>-33.35990, -70.80716</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/07/12 13:24:49</t>
+          <t>2026/07/13 09:45:20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-32.841915, -70.936828</t>
+          <t>-33.360145, -70.80659</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.84192, -70.93683</t>
+          <t>-33.36015, -70.80659</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>02:03:22</t>
+          <t>00:21:24</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.73</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/07/12 11:59:57</t>
+          <t>2026/07/13 09:27:17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.7577416, -70.7025466</t>
+          <t>-33.3601216, -70.8066816</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.75774, -70.70255</t>
+          <t>-33.36012, -70.80668</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/07/12 13:04:51</t>
+          <t>2026/07/13 10:33:29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.797665, -70.8874083</t>
+          <t>-33.360125, -70.8067916</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.79767, -70.88741</t>
+          <t>-33.36012, -70.80679</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:04:54</t>
+          <t>01:06:12</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>22.46</v>
+        <v>0.01</v>
       </c>
       <c r="M34" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,53 +2374,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/07/12 12:12:35</t>
+          <t>2026/07/13 09:33:49</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.690825, -70.78046</t>
+          <t>-34.2051, -70.685155</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.69082, -70.78046</t>
+          <t>-34.20510, -70.68515</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/07/12 12:48:28</t>
+          <t>2026/07/13 10:55:27</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.7409383, -70.7324083</t>
+          <t>-34.2054883, -70.677505</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.74094, -70.73241</t>
+          <t>-34.20549, -70.67750</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:35:53</t>
+          <t>01:21:38</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>7.96</v>
+        <v>0.71</v>
       </c>
       <c r="M35" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="N35" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2428,62 +2428,62 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/07/12 12:49:43</t>
+          <t>2026/07/13 09:45:47</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.7436883, -70.7306733</t>
+          <t>-33.360123, -70.806616</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-32.74369, -70.73067</t>
+          <t>-33.36012, -70.80662</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/07/12 13:28:21</t>
+          <t>2026/07/13 10:36:19</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-32.865405, -70.638115</t>
+          <t>-33.360119, -70.806713</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-32.86541, -70.63811</t>
+          <t>-33.36012, -70.80671</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:38:38</t>
+          <t>00:50:32</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>19.87</v>
+        <v>0.01</v>
       </c>
       <c r="M36" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,53 +2492,53 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/07/12 13:06:06</t>
+          <t>2026/07/13 09:51:13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-32.79756, -70.8870783</t>
+          <t>-33.367361, -70.695931</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-32.79756, -70.88708</t>
+          <t>-33.36736, -70.69593</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/07/12 15:58:52</t>
+          <t>2026/07/13 10:52:55</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-32.7957266, -70.8201483</t>
+          <t>-33.364484, -70.784452</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-32.79573, -70.82015</t>
+          <t>-33.36448, -70.78445</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02:52:46</t>
+          <t>01:01:42</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9.869999999999999</v>
+        <v>11.52</v>
       </c>
       <c r="M37" t="n">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="N37" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/07/12 13:25:48</t>
+          <t>2026/07/13 09:53:25</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-32.841778, -70.936838</t>
+          <t>-34.2054416, -70.67916</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-32.84178, -70.93684</t>
+          <t>-34.20544, -70.67916</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/07/12 20:45:45</t>
+          <t>2026/07/13 10:56:55</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-32.838513, -70.95394</t>
+          <t>-34.2042116, -70.6790666</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-32.83851, -70.95394</t>
+          <t>-34.20421, -70.67907</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>07:19:57</t>
+          <t>01:03:30</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>0.26</v>
       </c>
       <c r="M38" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="N38" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/07/12 13:29:36</t>
+          <t>2026/07/13 10:03:12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-32.8660333, -70.6373499</t>
+          <t>-33.36728, -70.695735</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-32.86603, -70.63735</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/07/12 14:04:28</t>
+          <t>2026/07/13 18:48:27</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.608835</t>
+          <t>-33.4360999, -70.6298916</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60883</t>
+          <t>-33.43610, -70.62989</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:34:52</t>
+          <t>08:45:15</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>12.43</v>
+        <v>19.08</v>
       </c>
       <c r="M39" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="N39" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/07/12 14:04:34</t>
+          <t>2026/07/13 10:16:38</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-32.879205, -70.6087833</t>
+          <t>-33.360755, -70.8090433</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60878</t>
+          <t>-33.36075, -70.80904</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/07/12 15:10:32</t>
+          <t>2026/07/13 12:01:57</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-32.8911866, -70.62515</t>
+          <t>-33.3589366, -70.8089099</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-32.89119, -70.62515</t>
+          <t>-33.35894, -70.80891</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>01:05:58</t>
+          <t>01:45:19</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.08</v>
+        <v>0.23</v>
       </c>
       <c r="M40" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="N40" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,116 +2728,116 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/07/12 14:16:36</t>
+          <t>2026/07/13 10:33:43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.4763283, -70.6983683</t>
+          <t>-33.3600066, -70.8068483</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.47633, -70.69837</t>
+          <t>-33.36001, -70.80685</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/07/12 15:27:20</t>
+          <t>2026/07/13 14:27:08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.451265, -70.59669</t>
+          <t>-33.359985, -70.8070316</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.45126, -70.59669</t>
+          <t>-33.35999, -70.80703</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>01:10:44</t>
+          <t>03:53:25</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>13.33</v>
+        <v>0.04</v>
       </c>
       <c r="M41" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/07/12 15:11:47</t>
+          <t>2026/07/13 10:36:41</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-32.891345, -70.624735</t>
+          <t>-33.360039, -70.806789</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-32.89135, -70.62474</t>
+          <t>-33.36004, -70.80679</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/07/12 15:25:22</t>
+          <t>2026/07/13 10:48:50</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-32.8793, -70.6088716</t>
+          <t>-33.360072, -70.806802</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-32.87930, -70.60887</t>
+          <t>-33.36007, -70.80680</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:13:35</t>
+          <t>00:12:09</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,53 +2846,53 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/07/12 15:26:03</t>
+          <t>2026/07/13 10:49:00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.6088633</t>
+          <t>-33.360103, -70.806819</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60886</t>
+          <t>-33.36010, -70.80682</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/07/12 16:09:05</t>
+          <t>2026/07/13 12:24:43</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-32.8299833, -70.5961333</t>
+          <t>-33.359879, -70.807133</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-32.82998, -70.59613</t>
+          <t>-33.35988, -70.80713</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:43:02</t>
+          <t>01:35:43</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9.4</v>
+        <v>0.45</v>
       </c>
       <c r="M43" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2905,53 +2905,53 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/07/12 15:28:35</t>
+          <t>2026/07/13 10:53:55</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.451405, -70.5962799</t>
+          <t>-33.359356, -70.791177</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.45141, -70.59628</t>
+          <t>-33.35936, -70.79118</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/07/12 16:17:13</t>
+          <t>2026/07/13 11:09:07</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.4648449, -70.5975416</t>
+          <t>-33.359937, -70.806859</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.46484, -70.59754</t>
+          <t>-33.35994, -70.80686</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:48:38</t>
+          <t>00:15:12</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="M44" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N44" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2964,44 +2964,44 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/07/12 15:42:53</t>
+          <t>2026/07/13 10:56:34</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-33.09078, -71.3609549</t>
+          <t>-34.2052333, -70.6774933</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-33.09078, -71.36095</t>
+          <t>-34.20523, -70.67749</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/07/12 15:52:13</t>
+          <t>2026/07/13 11:45:44</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.0869333, -71.36188</t>
+          <t>-34.2057283, -70.6761133</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.08693, -71.36188</t>
+          <t>-34.20573, -70.67611</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:09:20</t>
+          <t>00:49:10</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.58</v>
+        <v>0.15</v>
       </c>
       <c r="M45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N45" t="n">
         <v>12</v>
@@ -3010,11 +3010,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/07/12 15:53:12</t>
+          <t>2026/07/13 10:58:10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-33.0873099, -71.3623416</t>
+          <t>-34.2042299, -70.6790299</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36234</t>
+          <t>-34.20423, -70.67903</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/07/13 08:11:09</t>
+          <t>2026/07/13 11:18:43</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-33.087285, -71.36232</t>
+          <t>-34.2054883, -70.6781033</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36232</t>
+          <t>-34.20549, -70.67810</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>16:17:57</t>
+          <t>00:20:33</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="M46" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" t="n">
         <v>8</v>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,47 +3082,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/07/12 15:59:04</t>
+          <t>2026/07/13 11:09:25</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-32.7958466, -70.8200833</t>
+          <t>-33.359996, -70.806786</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-32.79585, -70.82008</t>
+          <t>-33.36000, -70.80679</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/07/12 17:08:26</t>
+          <t>2026/07/13 12:42:52</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.887415</t>
+          <t>-33.351878, -70.801367</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88742</t>
+          <t>-33.35188, -70.80137</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>01:09:22</t>
+          <t>01:33:27</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.56</v>
+        <v>1.17</v>
       </c>
       <c r="M47" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="N47" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,53 +3141,53 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/07/12 16:09:37</t>
+          <t>2026/07/13 11:19:47</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-32.8295983, -70.597325</t>
+          <t>-34.2054183, -70.678095</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-32.82960, -70.59732</t>
+          <t>-34.20542, -70.67809</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/07/12 18:40:20</t>
+          <t>2026/07/13 11:32:07</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-32.8792083, -70.6088483</t>
+          <t>-34.2055099, -70.6784433</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60885</t>
+          <t>-34.20551, -70.67844</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>02:30:43</t>
+          <t>00:12:20</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>8.18</v>
+        <v>0.03</v>
       </c>
       <c r="M48" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="N48" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/07/12 16:18:28</t>
+          <t>2026/07/13 11:21:48</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-33.4649216, -70.5971233</t>
+          <t>-34.2053583, -70.6774883</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-33.46492, -70.59712</t>
+          <t>-34.20536, -70.67749</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/07/12 16:37:12</t>
+          <t>2026/07/13 11:47:23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-33.4508833, -70.5960266</t>
+          <t>-34.2070016, -70.6769283</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-33.45088, -70.59603</t>
+          <t>-34.20700, -70.67693</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:18:44</t>
+          <t>00:25:35</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.02</v>
+        <v>0.32</v>
       </c>
       <c r="M49" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/07/12 16:37:37</t>
+          <t>2026/07/13 11:33:16</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.45125, -70.5959933</t>
+          <t>-34.205415, -70.6790116</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.45125, -70.59599</t>
+          <t>-34.20542, -70.67901</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/07/12 17:12:43</t>
+          <t>2026/07/13 12:38:52</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.4549116, -70.6270566</t>
+          <t>-34.190015, -70.709305</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.45491, -70.62706</t>
+          <t>-34.19002, -70.70931</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:35:06</t>
+          <t>01:05:36</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.87</v>
+        <v>4.86</v>
       </c>
       <c r="M50" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="N50" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/07/12 17:09:41</t>
+          <t>2026/07/13 11:46:48</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-32.79757, -70.8870583</t>
+          <t>-34.2073166, -70.6769149</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-32.79757, -70.88706</t>
+          <t>-34.20732, -70.67691</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/07/13 07:47:17</t>
+          <t>2026/07/13 12:55:52</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.3672916, -70.696675</t>
+          <t>-34.2053433, -70.6803133</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.36729, -70.69667</t>
+          <t>-34.20534, -70.68031</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>14:37:36</t>
+          <t>01:09:04</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>92.58</v>
+        <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="N51" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/07/12 17:12:58</t>
+          <t>2026/07/13 11:48:38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.4549566, -70.6270666</t>
+          <t>-34.2071999, -70.6769116</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.45496, -70.62707</t>
+          <t>-34.20720, -70.67691</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/07/12 17:39:59</t>
+          <t>2026/07/13 12:35:51</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.4762766, -70.69834</t>
+          <t>-34.1900799, -70.709435</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69834</t>
+          <t>-34.19008, -70.70943</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:27:01</t>
+          <t>00:47:13</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>8.73</v>
+        <v>4.21</v>
       </c>
       <c r="M52" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="N52" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,53 +3436,53 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/07/12 17:40:07</t>
+          <t>2026/07/13 12:03:12</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-33.4763166, -70.6983783</t>
+          <t>-33.35947, -70.8089749</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69838</t>
+          <t>-33.35947, -70.80897</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/07/12 21:07:31</t>
+          <t>2026/07/13 12:42:09</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.3895299, -70.6739</t>
+          <t>-33.3518616, -70.8012866</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.38953, -70.67390</t>
+          <t>-33.35186, -70.80129</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>03:27:24</t>
+          <t>00:38:57</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>23.37</v>
+        <v>1.46</v>
       </c>
       <c r="M53" t="n">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="N53" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3495,116 +3495,116 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/07/12 18:03:54</t>
+          <t>2026/07/13 12:13:15</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-32.7483666, -70.6526849</t>
+          <t>-32.838747, -70.954109</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-32.74837, -70.65268</t>
+          <t>-32.83875, -70.95411</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/07/12 18:42:42</t>
+          <t>2026/07/13 12:36:18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-32.7434416, -70.7326933</t>
+          <t>-32.838358, -70.956156</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-32.74344, -70.73269</t>
+          <t>-32.83836, -70.95616</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:38:48</t>
+          <t>00:23:03</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>8.51</v>
+        <v>0.43</v>
       </c>
       <c r="M54" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="N54" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/07/12 18:41:35</t>
+          <t>2026/07/13 12:25:07</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-32.8791383, -70.608845</t>
+          <t>-33.359881, -70.807152</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-32.87914, -70.60885</t>
+          <t>-33.35988, -70.80715</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/07/12 20:07:16</t>
+          <t>2026/07/13 14:25:09</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-32.8792099, -70.6089083</t>
+          <t>-33.360174, -70.806587</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60891</t>
+          <t>-33.36017, -70.80659</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>01:25:41</t>
+          <t>02:00:02</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>11.39</v>
+        <v>0.06</v>
       </c>
       <c r="M55" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,57 +3613,57 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/07/12 18:43:14</t>
+          <t>2026/07/13 12:36:23</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-32.7435066, -70.7327433</t>
+          <t>-34.1899083, -70.7092533</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-32.74351, -70.73274</t>
+          <t>-34.18991, -70.70925</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/07/12 19:12:44</t>
+          <t>2026/07/13 13:14:12</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-32.7435616, -70.736105</t>
+          <t>-34.2052566, -70.6828083</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-32.74356, -70.73610</t>
+          <t>-34.20526, -70.68281</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:29:30</t>
+          <t>00:37:49</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.77</v>
+        <v>3.16</v>
       </c>
       <c r="M56" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N56" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/07/12 19:13:42</t>
+          <t>2026/07/13 12:37:09</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-32.743345, -70.7326616</t>
+          <t>-32.838374, -70.955502</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-32.74334, -70.73266</t>
+          <t>-32.83837, -70.95550</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/07/12 20:25:18</t>
+          <t>2026/07/13 17:30:47</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-32.74317, -70.729675</t>
+          <t>-32.840952, -70.957275</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72968</t>
+          <t>-32.84095, -70.95727</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01:11:36</t>
+          <t>04:53:38</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.07</v>
+        <v>0.66</v>
       </c>
       <c r="M57" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/07/12 19:16:43</t>
+          <t>2026/07/13 12:39:05</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.838355, -70.955537</t>
+          <t>-34.1899449, -70.7092716</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.83835, -70.95554</t>
+          <t>-34.18994, -70.70927</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/07/12 20:54:06</t>
+          <t>2026/07/13 13:16:35</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.785477, -70.960406</t>
+          <t>-34.20424, -70.67912</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.78548, -70.96041</t>
+          <t>-34.20424, -70.67912</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:37:30</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>9.66</v>
+        <v>3.56</v>
       </c>
       <c r="M58" t="n">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="N58" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,53 +3790,53 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/07/12 20:08:31</t>
+          <t>2026/07/13 12:43:24</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.608875</t>
+          <t>-33.3553366, -70.796635</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60887</t>
+          <t>-33.35534, -70.79663</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/07/13 08:58:40</t>
+          <t>2026/07/13 13:05:20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-34.2033433, -70.68859</t>
+          <t>-33.40161, -70.7492849</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-34.20334, -70.68859</t>
+          <t>-33.40161, -70.74928</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>12:50:09</t>
+          <t>00:21:56</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>164.51</v>
+        <v>8.18</v>
       </c>
       <c r="M59" t="n">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="N59" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3849,53 +3849,53 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/07/12 20:26:33</t>
+          <t>2026/07/13 12:43:46</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-32.7430583, -70.7297799</t>
+          <t>-33.354838, -70.797277</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-32.74306, -70.72978</t>
+          <t>-33.35484, -70.79728</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/07/13 07:15:14</t>
+          <t>2026/07/13 13:05:22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-32.8657616, -70.681495</t>
+          <t>-33.401431, -70.749801</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-32.86576, -70.68149</t>
+          <t>-33.40143, -70.74980</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>10:48:41</t>
+          <t>00:21:36</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>16.37</v>
+        <v>8.33</v>
       </c>
       <c r="M60" t="n">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="N60" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/07/12 20:46:45</t>
+          <t>2026/07/13 12:55:58</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-32.838826, -70.954145</t>
+          <t>-34.20534, -70.6801749</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-32.83883, -70.95414</t>
+          <t>-34.20534, -70.68017</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/07/12 21:29:28</t>
+          <t>2026/07/13 13:34:17</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.837137, -70.967133</t>
+          <t>-34.2057549, -70.6761633</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.83714, -70.96713</t>
+          <t>-34.20575, -70.67616</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:42:43</t>
+          <t>00:38:19</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.49</v>
+        <v>0.73</v>
       </c>
       <c r="M61" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N61" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/07/12 20:54:32</t>
+          <t>2026/07/13 13:06:01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-32.785335, -70.960431</t>
+          <t>-33.401182, -70.750379</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-32.78534, -70.96043</t>
+          <t>-33.40118, -70.75038</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/07/12 22:21:16</t>
+          <t>2026/07/13 14:21:28</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-32.840285, -70.960044</t>
+          <t>-33.361524, -70.809105</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-32.84029, -70.96004</t>
+          <t>-33.36152, -70.80911</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>01:26:44</t>
+          <t>01:15:27</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>13.09</v>
+        <v>10.12</v>
       </c>
       <c r="M62" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N62" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,57 +4026,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/07/12 21:07:56</t>
+          <t>2026/07/13 13:06:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-33.3893316, -70.6740566</t>
+          <t>-33.401135, -70.7505233</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-33.38933, -70.67406</t>
+          <t>-33.40113, -70.75052</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/07/12 22:04:25</t>
+          <t>2026/07/13 14:10:37</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-33.4762683, -70.6983366</t>
+          <t>-33.360195, -70.8090133</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69834</t>
+          <t>-33.36019, -70.80901</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:56:29</t>
+          <t>01:04:34</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>13.52</v>
+        <v>10.86</v>
       </c>
       <c r="M63" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="N63" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/07/12 21:29:55</t>
+          <t>2026/07/13 13:14:48</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-32.837103, -70.967171</t>
+          <t>-34.2053583, -70.6801916</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-32.83710, -70.96717</t>
+          <t>-34.20536, -70.68019</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/07/12 21:51:25</t>
+          <t>2026/07/13 17:31:43</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-32.841867, -70.936848</t>
+          <t>-32.7576883, -70.7029933</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-32.84187, -70.93685</t>
+          <t>-32.75769, -70.70299</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:21:30</t>
+          <t>04:16:55</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.52</v>
+        <v>173.31</v>
       </c>
       <c r="M64" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="N64" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/07/12 21:52:01</t>
+          <t>2026/07/13 13:17:50</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-32.841676, -70.936803</t>
+          <t>-34.2042583, -70.6790549</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-32.84168, -70.93680</t>
+          <t>-34.20426, -70.67905</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/07/13 09:51:07</t>
+          <t>2026/07/13 13:25:34</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.367377, -70.695938</t>
+          <t>-34.2055533, -70.6781966</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.36738, -70.69594</t>
+          <t>-34.20555, -70.67820</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>11:59:06</t>
+          <t>00:07:44</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>76.92</v>
+        <v>0.2</v>
       </c>
       <c r="M65" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,53 +4203,53 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/07/12 22:05:35</t>
+          <t>2026/07/13 13:25:51</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-33.476115, -70.6985383</t>
+          <t>-34.2055266, -70.67827</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69854</t>
+          <t>-34.20553, -70.67827</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/07/13 09:32:34</t>
+          <t>2026/07/13 13:49:50</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.2048766, -70.6856249</t>
+          <t>-34.2055516, -70.6781983</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.20488, -70.68562</t>
+          <t>-34.20555, -70.67820</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>11:26:59</t>
+          <t>00:23:59</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>87.7</v>
+        <v>0.01</v>
       </c>
       <c r="M66" t="n">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="N66" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4262,57 +4262,57 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/07/12 22:21:24</t>
+          <t>2026/07/13 13:35:21</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-32.840256, -70.960131</t>
+          <t>-34.2079316, -70.6771533</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-32.84026, -70.96013</t>
+          <t>-34.20793, -70.67715</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/07/12 22:39:06</t>
+          <t>2026/07/13 14:24:46</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-32.838368, -70.955964</t>
+          <t>-34.2055666, -70.676895</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95596</t>
+          <t>-34.20557, -70.67690</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>00:17:42</t>
+          <t>00:49:25</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.16</v>
+        <v>0.36</v>
       </c>
       <c r="M67" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N67" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/07/12 22:39:34</t>
+          <t>2026/07/13 13:50:07</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-32.838343, -70.955543</t>
+          <t>-34.2055566, -70.6777866</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-32.83834, -70.95554</t>
+          <t>-34.20556, -70.67779</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/07/13 12:12:25</t>
+          <t>2026/07/13 13:58:22</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-32.839701, -70.954577</t>
+          <t>-34.2054733, -70.6781233</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-32.83970, -70.95458</t>
+          <t>-34.20547, -70.67812</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>13:32:51</t>
+          <t>00:08:15</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>204.05</v>
+        <v>0.03</v>
       </c>
       <c r="M68" t="n">
-        <v>138</v>
+        <v>6</v>
       </c>
       <c r="N68" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,175 +4380,175 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/07/13 08:58:50</t>
+          <t>2026/07/13 13:58:54</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-33.4362533, -70.6295033</t>
+          <t>-34.2049483, -70.6781299</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-33.43625, -70.62950</t>
+          <t>-34.20495, -70.67813</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/07/13 10:02:50</t>
+          <t>2026/07/13 14:08:05</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-33.3672499, -70.6955516</t>
+          <t>-34.204985, -70.6782233</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69555</t>
+          <t>-34.20499, -70.67822</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>01:04:00</t>
+          <t>00:09:11</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>13.38</v>
+        <v>0.01</v>
       </c>
       <c r="M69" t="n">
-        <v>114</v>
+        <v>6</v>
       </c>
       <c r="N69" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/07/13 09:23:56</t>
+          <t>2026/07/13 14:08:38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-33.359904, -70.807156</t>
+          <t>-34.2055233, -70.6782049</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80716</t>
+          <t>-34.20552, -70.67820</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:20</t>
+          <t>2026/07/13 14:21:45</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-33.360145, -70.80659</t>
+          <t>-34.20556, -70.6782116</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80659</t>
+          <t>-34.20556, -70.67821</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:21:24</t>
+          <t>00:13:07</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:47</t>
+          <t>2026/07/13 14:11:52</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-33.360123, -70.806616</t>
+          <t>-33.36071, -70.809025</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80662</t>
+          <t>-33.36071, -70.80903</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/07/13 10:36:19</t>
+          <t>2026/07/13 14:19:52</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.360119, -70.806713</t>
+          <t>-33.3605066, -70.8091083</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80671</t>
+          <t>-33.36051, -70.80911</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:50:32</t>
+          <t>00:08:00</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,116 +4557,116 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/07/13 10:03:12</t>
+          <t>2026/07/13 14:20:10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.36728, -70.695735</t>
+          <t>-33.360525, -70.8092616</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-33.36053, -70.80926</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/07/13 18:48:27</t>
+          <t>2026/07/13 16:09:51</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.4360999, -70.6298916</t>
+          <t>-33.1345899, -71.5636699</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.43610, -70.62989</t>
+          <t>-33.13459, -71.56367</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>08:45:15</t>
+          <t>01:49:41</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>19.08</v>
+        <v>104.92</v>
       </c>
       <c r="M72" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="N72" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/07/13 10:36:41</t>
+          <t>2026/07/13 14:21:49</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-33.360039, -70.806789</t>
+          <t>-33.361521, -70.80911</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80679</t>
+          <t>-33.36152, -70.80911</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/07/13 10:48:50</t>
+          <t>2026/07/13 14:59:25</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.360072, -70.806802</t>
+          <t>-33.360153, -70.806693</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80680</t>
+          <t>-33.36015, -70.80669</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:12:09</t>
+          <t>00:37:36</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,47 +4675,47 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/07/13 10:49:00</t>
+          <t>2026/07/13 14:22:11</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.360103, -70.806819</t>
+          <t>-34.2055566, -70.6783433</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80682</t>
+          <t>-34.20556, -70.67834</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/07/13 12:24:43</t>
+          <t>2026/07/13 16:00:08</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.359879, -70.807133</t>
+          <t>-33.744805, -70.7382516</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.35988, -70.80713</t>
+          <t>-33.74480, -70.73825</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>01:35:43</t>
+          <t>01:37:57</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.45</v>
+        <v>56.03</v>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,44 +4734,44 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/07/13 12:25:07</t>
+          <t>2026/07/13 14:25:31</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.359881, -70.807152</t>
+          <t>-33.360108, -70.806563</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.35988, -70.80715</t>
+          <t>-33.36011, -70.80656</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:09</t>
+          <t>2026/07/13 15:19:07</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.360174, -70.806587</t>
+          <t>-33.360027, -70.807117</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80659</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>02:00:02</t>
+          <t>00:53:36</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
         <v>3</v>
@@ -4780,11 +4780,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/07/13 13:06:03</t>
+          <t>2026/07/13 14:26:01</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.401135, -70.7505233</t>
+          <t>-34.2055366, -70.6783316</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.40113, -70.75052</t>
+          <t>-34.20554, -70.67833</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/07/13 14:10:37</t>
+          <t>2026/07/13 15:48:26</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.360195, -70.8090133</t>
+          <t>-33.476305, -70.698345</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.36019, -70.80901</t>
+          <t>-33.47631, -70.69835</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01:04:34</t>
+          <t>01:22:25</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>10.86</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="N76" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/07/13 14:08:38</t>
+          <t>2026/07/13 14:27:42</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-34.2055233, -70.6782049</t>
+          <t>-33.3601166, -70.8064883</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-34.20552, -70.67820</t>
+          <t>-33.36012, -70.80649</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/07/13 14:21:45</t>
+          <t>2026/07/13 15:17:08</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-34.20556, -70.6782116</t>
+          <t>-33.36016, -70.8067916</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67821</t>
+          <t>-33.36016, -70.80679</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:13:07</t>
+          <t>00:49:26</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,53 +4911,53 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/07/13 14:11:52</t>
+          <t>2026/07/13 15:00:25</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.36071, -70.809025</t>
+          <t>-33.360152, -70.806692</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.36071, -70.80903</t>
+          <t>-33.36015, -70.80669</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/07/13 14:19:52</t>
+          <t>2026/07/13 17:44:58</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.3605066, -70.8091083</t>
+          <t>-33.482168, -70.764932</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.36051, -70.80911</t>
+          <t>-33.48217, -70.76493</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:08:00</t>
+          <t>02:44:33</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.02</v>
+        <v>21.45</v>
       </c>
       <c r="M78" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4970,175 +4970,175 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/07/13 14:20:10</t>
+          <t>2026/07/13 15:18:23</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.360525, -70.8092616</t>
+          <t>-33.359985, -70.80697</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.36053, -70.80926</t>
+          <t>-33.35999, -70.80697</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/07/13 16:09:51</t>
+          <t>2026/07/13 15:39:55</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.1345899, -71.5636699</t>
+          <t>-33.3797383, -70.7528033</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.13459, -71.56367</t>
+          <t>-33.37974, -70.75280</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>01:49:41</t>
+          <t>00:21:32</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>104.92</v>
+        <v>7.56</v>
       </c>
       <c r="M79" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="N79" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/07/13 14:22:11</t>
+          <t>2026/07/13 15:19:48</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-34.2055566, -70.6783433</t>
+          <t>-33.360031, -70.807117</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67834</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/07/13 16:00:08</t>
+          <t>2026/07/13 16:32:46</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.744805, -70.7382516</t>
+          <t>-33.35997, -70.807061</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.74480, -70.73825</t>
+          <t>-33.35997, -70.80706</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>01:37:57</t>
+          <t>01:12:58</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>56.03</v>
+        <v>0.1</v>
       </c>
       <c r="M80" t="n">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:31</t>
+          <t>2026/07/13 15:40:13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.360108, -70.806563</t>
+          <t>-33.3797466, -70.7528116</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.36011, -70.80656</t>
+          <t>-33.37975, -70.75281</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:07</t>
+          <t>2026/07/13 16:14:59</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.360027, -70.807117</t>
+          <t>-33.3599716, -70.8070499</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:53:36</t>
+          <t>00:34:46</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.07000000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,116 +5147,116 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/07/13 15:18:23</t>
+          <t>2026/07/13 15:48:32</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-33.359985, -70.80697</t>
+          <t>-33.476335, -70.6983783</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80697</t>
+          <t>-33.47633, -70.69838</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/07/13 15:39:55</t>
+          <t>2026/07/13 18:25:18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-33.3797383, -70.7528033</t>
+          <t>-33.3893033, -70.674025</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-33.37974, -70.75280</t>
+          <t>-33.38930, -70.67403</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:21:32</t>
+          <t>02:36:46</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>7.56</v>
+        <v>14.95</v>
       </c>
       <c r="M82" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="N82" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:48</t>
+          <t>2026/07/13 16:01:23</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.360031, -70.807117</t>
+          <t>-33.7441016, -70.738085</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-33.74410, -70.73808</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/07/13 16:32:46</t>
+          <t>2026/07/13 16:46:22</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.35997, -70.807061</t>
+          <t>-33.501845, -70.7686866</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80706</t>
+          <t>-33.50185, -70.76869</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>01:12:58</t>
+          <t>00:44:59</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.1</v>
+        <v>35</v>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/07/13 15:40:13</t>
+          <t>2026/07/13 16:11:06</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.3797466, -70.7528116</t>
+          <t>-33.1347083, -71.5636116</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.37975, -70.75281</t>
+          <t>-33.13471, -71.56361</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/07/13 16:14:59</t>
+          <t>2026/07/13 17:07:54</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.3599716, -70.8070499</t>
+          <t>-33.0873133, -71.3622983</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:34:46</t>
+          <t>00:56:48</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>7.79</v>
+        <v>43.75</v>
       </c>
       <c r="M84" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="N84" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,116 +5324,116 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/07/13 16:01:23</t>
+          <t>2026/07/13 16:15:08</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-33.7441016, -70.738085</t>
+          <t>-33.3599866, -70.8071883</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-33.74410, -70.73808</t>
+          <t>-33.35999, -70.80719</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/07/13 16:46:22</t>
+          <t>2026/07/13 18:54:29</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.501845, -70.7686866</t>
+          <t>-32.7431899, -70.733085</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.50185, -70.76869</t>
+          <t>-32.74319, -70.73309</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>00:44:59</t>
+          <t>02:39:21</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>35</v>
+        <v>90.23</v>
       </c>
       <c r="M85" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="N85" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/07/13 16:11:06</t>
+          <t>2026/07/13 16:33:02</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.1347083, -71.5636116</t>
+          <t>-33.360044, -70.807116</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.13471, -71.56361</t>
+          <t>-33.36004, -70.80712</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/13 17:07:54</t>
+          <t>2026/07/14 11:24:00</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.0873133, -71.3622983</t>
+          <t>-33.359965, -70.807053</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36230</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:56:48</t>
+          <t>18:50:58</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>43.75</v>
+        <v>0.05</v>
       </c>
       <c r="M86" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="N86" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,116 +5442,116 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/07/13 16:15:08</t>
+          <t>2026/07/13 16:46:32</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.3599866, -70.8071883</t>
+          <t>-33.501865, -70.76861</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80719</t>
+          <t>-33.50187, -70.76861</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/07/13 18:54:29</t>
+          <t>2026/07/13 18:38:20</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-32.7431899, -70.733085</t>
+          <t>-32.8823216, -70.6119916</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73309</t>
+          <t>-32.88232, -70.61199</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>02:39:21</t>
+          <t>01:51:48</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>90.23</v>
+        <v>88.83</v>
       </c>
       <c r="M87" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="N87" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/07/13 16:33:02</t>
+          <t>2026/07/13 17:09:09</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.360044, -70.807116</t>
+          <t>-33.0872883, -71.36232</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-33.08729, -71.36232</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:00</t>
+          <t>2026/07/13 17:47:39</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.359965, -70.807053</t>
+          <t>-33.0872316, -71.3622516</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-33.08723, -71.36225</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>18:50:58</t>
+          <t>00:38:30</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,57 +5560,57 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/13 16:46:32</t>
+          <t>2026/07/13 17:31:20</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-33.501865, -70.76861</t>
+          <t>-32.840668, -70.958633</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-33.50187, -70.76861</t>
+          <t>-32.84067, -70.95863</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/13 18:38:20</t>
+          <t>2026/07/13 18:50:54</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-32.8823216, -70.6119916</t>
+          <t>-32.838368, -70.955637</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-32.88232, -70.61199</t>
+          <t>-32.83837, -70.95564</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>01:51:48</t>
+          <t>01:19:34</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>88.83</v>
+        <v>1.37</v>
       </c>
       <c r="M89" t="n">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="N89" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,47 +5619,47 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/07/13 17:09:09</t>
+          <t>2026/07/13 17:32:57</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.0872883, -71.36232</t>
+          <t>-32.7580216, -70.7024383</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36232</t>
+          <t>-32.75802, -70.70244</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/07/13 17:47:39</t>
+          <t>2026/07/13 18:39:30</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.0872316, -71.3622516</t>
+          <t>-32.7977099, -70.8874433</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.08723, -71.36225</t>
+          <t>-32.79771, -70.88744</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>00:38:30</t>
+          <t>01:06:33</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.01</v>
+        <v>27.99</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="N90" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5783,11 +5783,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/13 18:39:35</t>
+          <t>2026/07/13 18:25:37</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-32.8794099, -70.6088433</t>
+          <t>-33.3893, -70.6740366</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-32.87941, -70.60884</t>
+          <t>-33.38930, -70.67404</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/13 19:14:47</t>
+          <t>2026/07/13 19:12:56</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-32.8791466, -70.6092666</t>
+          <t>-33.476265, -70.6983516</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-32.87915, -70.60927</t>
+          <t>-33.47626, -70.69835</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:35:12</t>
+          <t>00:47:19</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.09</v>
+        <v>13.57</v>
       </c>
       <c r="M93" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/13 18:40:01</t>
+          <t>2026/07/13 18:39:35</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8871099</t>
+          <t>-32.8794099, -70.6088433</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88711</t>
+          <t>-32.87941, -70.60884</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/13 19:35:24</t>
+          <t>2026/07/13 19:14:47</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-32.7832683, -70.8549766</t>
+          <t>-32.8791466, -70.6092666</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-32.78327, -70.85498</t>
+          <t>-32.87915, -70.60927</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>00:55:23</t>
+          <t>00:35:12</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.86</v>
+        <v>0.09</v>
       </c>
       <c r="M94" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="N94" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/13 18:48:42</t>
+          <t>2026/07/13 18:40:01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-33.436315, -70.6293299</t>
+          <t>-32.79761, -70.8871099</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-33.43632, -70.62933</t>
+          <t>-32.79761, -70.88711</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/13 19:31:57</t>
+          <t>2026/07/13 19:35:24</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-33.466985, -70.6068116</t>
+          <t>-32.7832683, -70.8549766</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-33.46699, -70.60681</t>
+          <t>-32.78327, -70.85498</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:43:15</t>
+          <t>00:55:23</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>5.39</v>
+        <v>3.86</v>
       </c>
       <c r="M95" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="N95" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/13 18:54:41</t>
+          <t>2026/07/13 18:48:42</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-32.7433, -70.7327583</t>
+          <t>-33.436315, -70.6293299</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-32.74330, -70.73276</t>
+          <t>-33.43632, -70.62933</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/13 19:59:23</t>
+          <t>2026/07/13 19:31:57</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-32.7430866, -70.7297566</t>
+          <t>-33.466985, -70.6068116</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-32.74309, -70.72976</t>
+          <t>-33.46699, -70.60681</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>01:04:42</t>
+          <t>00:43:15</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.38</v>
+        <v>5.39</v>
       </c>
       <c r="M96" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="N96" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/07/13 19:15:19</t>
+          <t>2026/07/13 18:51:42</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088066</t>
+          <t>-32.838369, -70.955496</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-32.83837, -70.95550</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/07/14 09:00:09</t>
+          <t>2026/07/13 19:55:29</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-34.2055083, -70.6783166</t>
+          <t>-32.839555, -70.954478</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67832</t>
+          <t>-32.83955, -70.95448</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>13:44:50</t>
+          <t>01:03:47</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>164.8</v>
+        <v>21.01</v>
       </c>
       <c r="M97" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N97" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,57 +6091,57 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/13 19:33:12</t>
+          <t>2026/07/13 18:54:41</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.4670566, -70.6068533</t>
+          <t>-32.7433, -70.7327583</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.46706, -70.60685</t>
+          <t>-32.74330, -70.73276</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/13 21:01:57</t>
+          <t>2026/07/13 19:59:23</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-33.44084, -70.6303416</t>
+          <t>-32.7430866, -70.7297566</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-33.44084, -70.63034</t>
+          <t>-32.74309, -70.72976</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>01:28:45</t>
+          <t>01:04:42</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>4.58</v>
+        <v>1.38</v>
       </c>
       <c r="M98" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N98" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/13 19:35:28</t>
+          <t>2026/07/13 19:14:11</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.7832333, -70.85493</t>
+          <t>-33.4761233, -70.6985316</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.78323, -70.85493</t>
+          <t>-33.47612, -70.69853</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:29</t>
+          <t>2026/07/14 10:54:23</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871633</t>
+          <t>-34.2054066, -70.67967</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88716</t>
+          <t>-34.20541, -70.67967</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:20:01</t>
+          <t>15:40:12</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.72</v>
+        <v>126.75</v>
       </c>
       <c r="M99" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="N99" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/13 19:49:28</t>
+          <t>2026/07/13 19:15:19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-33.0461283, -71.4200833</t>
+          <t>-32.8792316, -70.6088066</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-33.04613, -71.42008</t>
+          <t>-32.87923, -70.60881</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/13 20:28:02</t>
+          <t>2026/07/14 09:00:09</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-33.08734, -71.3622683</t>
+          <t>-34.2055083, -70.6783166</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36227</t>
+          <t>-34.20551, -70.67832</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:38:34</t>
+          <t>13:44:50</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>10.28</v>
+        <v>164.8</v>
       </c>
       <c r="M100" t="n">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="N100" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,53 +6268,53 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:48</t>
+          <t>2026/07/13 19:33:12</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-32.7976016, -70.887115</t>
+          <t>-33.4670566, -70.6068533</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88711</t>
+          <t>-33.46706, -70.60685</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/14 08:40:37</t>
+          <t>2026/07/13 21:01:57</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.682345</t>
+          <t>-33.44084, -70.6303416</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68234</t>
+          <t>-33.44084, -70.63034</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>12:44:49</t>
+          <t>01:28:45</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>190.85</v>
+        <v>4.58</v>
       </c>
       <c r="M101" t="n">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="N101" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6327,47 +6327,47 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/13 19:59:32</t>
+          <t>2026/07/13 19:35:28</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.7430283, -70.7297866</t>
+          <t>-32.7832333, -70.85493</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72979</t>
+          <t>-32.78323, -70.85493</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/14 08:15:13</t>
+          <t>2026/07/13 19:55:29</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-33.3598283, -70.806785</t>
+          <t>-32.7976249, -70.8871633</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-33.35983, -70.80679</t>
+          <t>-32.79762, -70.88716</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>12:15:41</t>
+          <t>00:20:01</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>90</v>
+        <v>3.72</v>
       </c>
       <c r="M102" t="n">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="N102" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/13 20:29:15</t>
+          <t>2026/07/13 19:49:28</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.0873083, -71.3623783</t>
+          <t>-33.0461283, -71.4200833</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36238</t>
+          <t>-33.04613, -71.42008</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/14 07:46:35</t>
+          <t>2026/07/13 20:28:02</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.0868883, -71.3619016</t>
+          <t>-33.08734, -71.3622683</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.08689, -71.36190</t>
+          <t>-33.08734, -71.36227</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>11:17:20</t>
+          <t>00:38:34</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>14</v>
+        <v>10.28</v>
       </c>
       <c r="M103" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N103" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/13 21:02:13</t>
+          <t>2026/07/13 19:55:48</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-33.440555, -70.63033</t>
+          <t>-32.7976016, -70.887115</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-33.44056, -70.63033</t>
+          <t>-32.79760, -70.88711</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/13 21:24:44</t>
+          <t>2026/07/14 08:40:37</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.4362516, -70.629595</t>
+          <t>-34.2052916, -70.682345</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.43625, -70.62959</t>
+          <t>-34.20529, -70.68234</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>00:22:31</t>
+          <t>12:44:49</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.72</v>
+        <v>190.85</v>
       </c>
       <c r="M104" t="n">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="N104" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,116 +6504,116 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/13 21:25:42</t>
+          <t>2026/07/13 19:56:09</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-33.4364766, -70.6295866</t>
+          <t>-32.838872, -70.954156</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-33.43648, -70.62959</t>
+          <t>-32.83887, -70.95416</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/14 10:57:49</t>
+          <t>2026/07/13 20:25:16</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.3661216, -70.6955083</t>
+          <t>-32.838364, -70.955496</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.36612, -70.69551</t>
+          <t>-32.83836, -70.95550</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>13:32:07</t>
+          <t>00:29:07</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>13.47</v>
+        <v>0.51</v>
       </c>
       <c r="M105" t="n">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="N105" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:17</t>
+          <t>2026/07/13 19:59:32</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-33.359942, -70.807084</t>
+          <t>-32.7430283, -70.7297866</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80708</t>
+          <t>-32.74303, -70.72979</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/14 12:02:22</t>
+          <t>2026/07/14 08:15:13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.360005, -70.806977</t>
+          <t>-33.3598283, -70.806785</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80698</t>
+          <t>-33.35983, -70.80679</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>00:38:05</t>
+          <t>12:15:41</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.04</v>
+        <v>90</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/14 12:03:21</t>
+          <t>2026/07/13 20:25:42</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-33.360075, -70.806905</t>
+          <t>-32.838362, -70.955504</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80691</t>
+          <t>-32.83836, -70.95550</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/14 12:25:04</t>
+          <t>2026/07/14 08:45:39</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-33.360001, -70.807087</t>
+          <t>-32.838372, -70.955582</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80709</t>
+          <t>-32.83837, -70.95558</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:21:43</t>
+          <t>12:19:57</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.19</v>
+        <v>1.36</v>
       </c>
       <c r="M107" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,57 +6681,57 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/14 14:09:00</t>
+          <t>2026/07/13 20:29:15</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-33.360079, -70.806683</t>
+          <t>-33.0873083, -71.3623783</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80668</t>
+          <t>-33.08731, -71.36238</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/14 15:09:39</t>
+          <t>2026/07/14 07:46:35</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-33.36007, -70.808767</t>
+          <t>-33.0868883, -71.3619016</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80877</t>
+          <t>-33.08689, -71.36190</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>01:00:39</t>
+          <t>11:17:20</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="M108" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="N108" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,57 +6740,57 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/14 15:10:31</t>
+          <t>2026/07/13 21:02:13</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-33.360105, -70.806689</t>
+          <t>-33.440555, -70.63033</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80669</t>
+          <t>-33.44056, -70.63033</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/14 18:47:39</t>
+          <t>2026/07/13 21:24:44</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-33.482123, -70.765334</t>
+          <t>-33.4362516, -70.629595</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-33.48212, -70.76533</t>
+          <t>-33.43625, -70.62959</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>03:37:08</t>
+          <t>00:22:31</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>19.34</v>
+        <v>0.72</v>
       </c>
       <c r="M109" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="N109" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,112 +6799,112 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/14 18:23:10</t>
+          <t>2026/07/13 21:25:42</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-33.087325, -71.3623016</t>
+          <t>-33.4364766, -70.6295866</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36230</t>
+          <t>-33.43648, -70.62959</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/15 08:27:37</t>
+          <t>2026/07/14 10:57:49</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-33.0872683, -71.3623066</t>
+          <t>-33.3661216, -70.6955083</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36231</t>
+          <t>-33.36612, -70.69551</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14:04:27</t>
+          <t>13:32:07</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.04</v>
+        <v>13.47</v>
       </c>
       <c r="M110" t="n">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="N110" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/14 18:48:33</t>
+          <t>2026/07/14 11:24:17</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.482178, -70.764895</t>
+          <t>-33.359942, -70.807084</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76489</t>
+          <t>-33.35994, -70.80708</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/15 08:54:52</t>
+          <t>2026/07/14 12:02:22</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-33.359961, -70.806992</t>
+          <t>-33.360005, -70.806977</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80699</t>
+          <t>-33.36001, -70.80698</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>14:06:19</t>
+          <t>00:38:05</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>22.72</v>
+        <v>0.04</v>
       </c>
       <c r="M111" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="N111" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6917,53 +6917,53 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/15 13:46:36</t>
+          <t>2026/07/14 15:10:31</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-33.3604683, -70.8083033</t>
+          <t>-33.360105, -70.806689</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-33.36047, -70.80830</t>
+          <t>-33.36010, -70.80669</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/15 14:41:48</t>
+          <t>2026/07/14 18:47:39</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-33.3612533, -70.8090166</t>
+          <t>-33.482123, -70.765334</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-33.36125, -70.80902</t>
+          <t>-33.48212, -70.76533</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:55:12</t>
+          <t>03:37:08</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.15</v>
+        <v>19.34</v>
       </c>
       <c r="M112" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="N112" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6976,106 +6976,106 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/07/15 14:43:03</t>
+          <t>2026/07/14 18:48:33</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.3604783, -70.8090416</t>
+          <t>-33.482178, -70.764895</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.36048, -70.80904</t>
+          <t>-33.48218, -70.76489</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:09</t>
+          <t>2026/07/15 08:54:52</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.3895116, -70.6738666</t>
+          <t>-33.359961, -70.806992</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.38951, -70.67387</t>
+          <t>-33.35996, -70.80699</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>00:46:06</t>
+          <t>14:06:19</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>17.34</v>
+        <v>22.72</v>
       </c>
       <c r="M113" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N113" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:42</t>
+          <t>2026/07/15 12:52:32</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.3893049, -70.6740016</t>
+          <t>-33.360034, -70.807127</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.38930, -70.67400</t>
+          <t>-33.36003, -70.80713</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/15 16:07:40</t>
+          <t>2026/07/15 15:16:50</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.3654, -70.6799283</t>
+          <t>-33.360008, -70.807123</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.36540, -70.67993</t>
+          <t>-33.36001, -70.80712</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:37:58</t>
+          <t>02:24:18</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.65</v>
+        <v>0.03</v>
       </c>
       <c r="M114" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/15 16:08:55</t>
+          <t>2026/07/15 14:43:03</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.3653549, -70.6799433</t>
+          <t>-33.3604783, -70.8090416</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.36535, -70.67994</t>
+          <t>-33.36048, -70.80904</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:15</t>
+          <t>2026/07/15 15:29:09</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.362085, -70.6701533</t>
+          <t>-33.3895116, -70.6738666</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67015</t>
+          <t>-33.38951, -70.67387</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:50:20</t>
+          <t>00:46:06</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.66</v>
+        <v>17.34</v>
       </c>
       <c r="M115" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="N115" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,53 +7153,53 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:50</t>
+          <t>2026/07/15 15:16:58</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-33.3621033, -70.6702233</t>
+          <t>-33.36003, -70.807124</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67022</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:09</t>
+          <t>2026/07/19 11:57:32</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-33.3895, -70.6736916</t>
+          <t>-33.360197, -70.807434</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-33.38950, -70.67369</t>
+          <t>-33.36020, -70.80743</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>03:07:19</t>
+          <t>92:40:34</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M116" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="N116" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/15 17:04:13</t>
+          <t>2026/07/15 15:29:42</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-33.482171, -70.764904</t>
+          <t>-33.3893049, -70.6740016</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-33.48217, -70.76490</t>
+          <t>-33.38930, -70.67400</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/15 18:54:01</t>
+          <t>2026/07/15 16:07:40</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-33.480734, -70.760036</t>
+          <t>-33.3654, -70.6799283</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-33.48073, -70.76004</t>
+          <t>-33.36540, -70.67993</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>01:49:48</t>
+          <t>00:37:58</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.51</v>
+        <v>3.65</v>
       </c>
       <c r="M117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/07/15 18:32:49</t>
+          <t>2026/07/15 16:08:55</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-32.840415, -70.960116</t>
+          <t>-33.3653549, -70.6799433</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-32.84042, -70.96012</t>
+          <t>-33.36535, -70.67994</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/15 19:09:21</t>
+          <t>2026/07/15 16:59:15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-32.838369, -70.956136</t>
+          <t>-33.362085, -70.6701533</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95614</t>
+          <t>-33.36209, -70.67015</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:36:32</t>
+          <t>00:50:20</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.97</v>
+        <v>1.66</v>
       </c>
       <c r="M118" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,47 +7330,47 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/15 18:38:03</t>
+          <t>2026/07/15 16:59:50</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-32.7917783, -70.872935</t>
+          <t>-33.3621033, -70.6702233</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-32.79178, -70.87293</t>
+          <t>-33.36210, -70.67022</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/15 19:19:22</t>
+          <t>2026/07/15 20:07:09</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.88742</t>
+          <t>-33.3895, -70.6736916</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88742</t>
+          <t>-33.38950, -70.67369</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:41:19</t>
+          <t>03:07:19</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.7</v>
+        <v>4.04</v>
       </c>
       <c r="M119" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N119" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7389,47 +7389,47 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/15 18:55:01</t>
+          <t>2026/07/15 17:04:13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.479699, -70.758226</t>
+          <t>-33.482171, -70.764904</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.47970, -70.75823</t>
+          <t>-33.48217, -70.76490</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/15 20:02:31</t>
+          <t>2026/07/15 18:54:01</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-32.838758, -70.954109</t>
+          <t>-33.480734, -70.760036</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-32.83876, -70.95411</t>
+          <t>-33.48073, -70.76004</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>01:07:30</t>
+          <t>01:49:48</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>95.33</v>
+        <v>0.51</v>
       </c>
       <c r="M120" t="n">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="N120" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121">
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,57 +7448,57 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/15 19:10:01</t>
+          <t>2026/07/15 18:32:49</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-32.838366, -70.955481</t>
+          <t>-32.840415, -70.960116</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95548</t>
+          <t>-32.84042, -70.96012</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/16 14:53:29</t>
+          <t>2026/07/15 19:09:21</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-32.840584, -70.99572</t>
+          <t>-32.838369, -70.956136</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-32.84058, -70.99572</t>
+          <t>-32.83837, -70.95614</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>19:43:28</t>
+          <t>00:36:32</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>8.380000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="M121" t="n">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="N121" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,57 +7507,57 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/07/15 19:20:18</t>
+          <t>2026/07/15 18:55:01</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870916</t>
+          <t>-33.479699, -70.758226</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88709</t>
+          <t>-33.47970, -70.75823</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/16 10:28:18</t>
+          <t>2026/07/15 20:02:31</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.7976766, -70.88739</t>
+          <t>-32.838758, -70.954109</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.79768, -70.88739</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>15:08:00</t>
+          <t>01:07:30</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>13.03</v>
+        <v>95.33</v>
       </c>
       <c r="M122" t="n">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="N122" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,57 +7566,57 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/15 20:02:41</t>
+          <t>2026/07/15 19:10:01</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.838757, -70.954109</t>
+          <t>-32.838366, -70.955481</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.83876, -70.95411</t>
+          <t>-32.83837, -70.95548</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/15 21:31:52</t>
+          <t>2026/07/16 14:53:29</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.841759, -70.936896</t>
+          <t>-32.840584, -70.99572</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.84176, -70.93690</t>
+          <t>-32.84058, -70.99572</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>01:29:11</t>
+          <t>19:43:28</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.27</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M123" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="N123" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,57 +7625,57 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:32</t>
+          <t>2026/07/15 19:20:18</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-33.38955, -70.6736383</t>
+          <t>-32.797605, -70.8870916</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-33.38955, -70.67364</t>
+          <t>-32.79760, -70.88709</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/15 20:50:24</t>
+          <t>2026/07/16 10:28:18</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-33.476245, -70.6983</t>
+          <t>-32.7976766, -70.88739</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69830</t>
+          <t>-32.79768, -70.88739</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>00:42:52</t>
+          <t>15:08:00</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>13.57</v>
+        <v>13.03</v>
       </c>
       <c r="M124" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="N124" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,116 +7684,116 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/15 20:51:39</t>
+          <t>2026/07/15 20:02:41</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.4761616, -70.698455</t>
+          <t>-32.838757, -70.954109</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69845</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/17 10:16:04</t>
+          <t>2026/07/15 21:31:52</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.3621016, -70.67012</t>
+          <t>-32.841759, -70.936896</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67012</t>
+          <t>-32.84176, -70.93690</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>37:24:25</t>
+          <t>01:29:11</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>18.78</v>
+        <v>2.27</v>
       </c>
       <c r="M125" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="N125" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/15 21:16:54</t>
+          <t>2026/07/15 20:07:32</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-32.743215, -70.7296266</t>
+          <t>-33.38955, -70.6736383</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-32.74321, -70.72963</t>
+          <t>-33.38955, -70.67364</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/18 23:59:01</t>
+          <t>2026/07/15 20:50:24</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-32.7430016, -70.7298083</t>
+          <t>-33.476245, -70.6983</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-32.74300, -70.72981</t>
+          <t>-33.47624, -70.69830</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>74:42:07</t>
+          <t>00:42:52</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.04</v>
+        <v>13.57</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -7802,57 +7802,57 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/07/15 21:32:18</t>
+          <t>2026/07/15 20:51:39</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-32.841741, -70.936882</t>
+          <t>-33.4761616, -70.698455</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-32.84174, -70.93688</t>
+          <t>-33.47616, -70.69845</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/16 11:02:40</t>
+          <t>2026/07/17 10:16:04</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-32.840636, -70.958522</t>
+          <t>-33.3621016, -70.67012</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-32.84064, -70.95852</t>
+          <t>-33.36210, -70.67012</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>13:30:22</t>
+          <t>37:24:25</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.86</v>
+        <v>18.78</v>
       </c>
       <c r="M127" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="N127" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7861,47 +7861,47 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/07/17 16:51:20</t>
+          <t>2026/07/15 21:32:18</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-33.3665833, -70.6954649</t>
+          <t>-32.841741, -70.936882</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69546</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/07/17 17:48:13</t>
+          <t>2026/07/16 11:02:40</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-33.4358716, -70.6300966</t>
+          <t>-32.840636, -70.958522</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-33.43587, -70.63010</t>
+          <t>-32.84064, -70.95852</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>00:56:53</t>
+          <t>13:30:22</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>13.29</v>
+        <v>2.86</v>
       </c>
       <c r="M128" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="N128" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7935,32 +7935,32 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/07/18 23:49:25</t>
+          <t>2026/07/19 15:13:00</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-33.43628, -70.629375</t>
+          <t>-33.4296566, -70.6486349</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62937</t>
+          <t>-33.42966, -70.64863</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>30:00:00</t>
+          <t>45:23:35</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/18 23:42:39</t>
+          <t>2026/07/19 21:42:39</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>34:00:00</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -8084,7 +8084,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -8097,37 +8097,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/07/18 13:08:33</t>
+          <t>2026/07/19 14:16:44</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-32.8792266, -70.6088966</t>
+          <t>-32.7430883, -70.7297416</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60890</t>
+          <t>-32.74309, -70.72974</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/07/18 23:10:35</t>
+          <t>2026/07/19 22:22:46</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-32.879245, -70.6087783</t>
+          <t>-32.7430183, -70.7298083</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60878</t>
+          <t>-32.74302, -70.72981</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10:02:02</t>
+          <t>08:06:02</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -8143,11 +8143,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,41 +8156,41 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/07/18 13:23:30</t>
+          <t>2026/07/19 15:52:39</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-32.841653, -70.936835</t>
+          <t>-33.4362749, -70.6294183</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-32.84165, -70.93684</t>
+          <t>-33.43627, -70.62942</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/18 23:26:36</t>
+          <t>2026/07/19 21:55:08</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-32.841653, -70.936835</t>
+          <t>-33.4363066, -70.62936</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-32.84165, -70.93684</t>
+          <t>-33.43631, -70.62936</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>10:03:06</t>
+          <t>06:02:29</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8215,41 +8215,41 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/07/18 17:09:09</t>
+          <t>2026/07/19 19:23:15</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-33.0873, -71.3623216</t>
+          <t>-33.08722, -71.3622533</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36232</t>
+          <t>-33.08722, -71.36225</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/18 22:29:58</t>
+          <t>2026/07/19 21:24:58</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-33.0872566, -71.3622533</t>
+          <t>-33.08722, -71.3622533</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-33.08726, -71.36225</t>
+          <t>-33.08722, -71.36225</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>05:20:49</t>
+          <t>02:01:43</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -8261,11 +8261,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8274,37 +8274,37 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/07/18 19:04:34</t>
+          <t>2026/07/19 20:08:51</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-32.7975833, -70.88705</t>
+          <t>-33.47616, -70.6984166</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88705</t>
+          <t>-33.47616, -70.69842</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/07/18 23:04:34</t>
+          <t>2026/07/19 22:08:51</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-32.7975833, -70.88705</t>
+          <t>-33.47616, -70.6984166</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-32.79758, -70.88705</t>
+          <t>-33.47616, -70.69842</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -8320,11 +8320,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8333,37 +8333,37 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/07/18 19:54:58</t>
+          <t>2026/07/19 20:10:55</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-33.5779366, -70.6311033</t>
+          <t>-32.797605, -70.8871183</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-33.57794, -70.63110</t>
+          <t>-32.79760, -70.88712</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/07/18 23:55:00</t>
+          <t>2026/07/19 22:10:55</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-33.5779366, -70.6311033</t>
+          <t>-32.797605, -70.8871183</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-33.57794, -70.63110</t>
+          <t>-32.79760, -70.88712</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>04:00:02</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8392,37 +8392,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026/07/18 20:19:14</t>
+          <t>2026/07/19 21:07:02</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-32.840582, -70.995705</t>
+          <t>-32.838361, -70.955532</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-32.84058, -70.99571</t>
+          <t>-32.83836, -70.95553</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/07/18 23:16:44</t>
+          <t>2026/07/19 23:04:41</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-32.840582, -70.995705</t>
+          <t>-32.838361, -70.955532</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>-32.84058, -70.99571</t>
+          <t>-32.83836, -70.95553</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>02:57:30</t>
+          <t>01:57:39</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8432,6 +8432,65 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>6</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026/07/19 22:06:31</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-32.841676, -70.936812</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-32.84168, -70.93681</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026/07/19 23:09:32</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-32.841676, -70.936812</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-32.84168, -70.93681</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>01:03:01</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8483,10 +8542,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1318.61</v>
+        <v>1301.72</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8502,10 +8561,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>576.0599999999999</v>
+        <v>381.35</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -8521,10 +8580,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>648.12</v>
+        <v>659.99</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8540,10 +8599,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>580.87</v>
+        <v>559.9400000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -8565,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -8584,7 +8643,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -8622,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -8711,10 +8770,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>865.89</v>
+        <v>843.55</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -8730,10 +8789,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>213.73</v>
+        <v>220.43</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -8787,10 +8846,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
@@ -8806,13 +8865,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>944.34</v>
+        <v>853.47</v>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>141</v>
@@ -8825,7 +8884,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>449.48</v>
+        <v>452.86</v>
       </c>
       <c r="C20" t="n">
         <v>54</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/19 22:23:34</t>
+          <t>2026/07/19 23:23:39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:00:36</t>
+          <t>167:00:41</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/19 22:31:37</t>
+          <t>2026/07/19 23:31:38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>166:00:17</t>
+          <t>167:00:18</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/19 22:34:34</t>
+          <t>2026/07/19 23:34:30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>165:59:49</t>
+          <t>166:59:45</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/19 22:40:44</t>
+          <t>2026/07/19 23:40:44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:01:07</t>
+          <t>167:01:07</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/19 22:56:11</t>
+          <t>2026/07/19 23:56:11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>166:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/19 22:57:38</t>
+          <t>2026/07/19 23:57:22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>165:59:47</t>
+          <t>166:59:31</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/07/19 21:42:39</t>
+          <t>2026/07/19 23:42:39</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>34:00:00</t>
+          <t>36:00:00</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/07/19 21:55:08</t>
+          <t>2026/07/19 23:55:08</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>06:02:29</t>
+          <t>08:02:29</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/07/19 21:24:58</t>
+          <t>2026/07/19 23:24:58</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>02:01:43</t>
+          <t>04:01:43</t>
         </is>
       </c>
       <c r="L134" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 04:00:00   Hasta : 2026/07/20 03:59:59</t>
+          <t>Desde : 2026/07/14 04:00:00   Hasta : 2026/07/21 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/07/13 00:01:34</t>
+          <t>2026/07/14 00:02:23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,26 +560,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/19 23:01:38</t>
+          <t>2026/07/20 22:01:40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-34.345949, -71.125868</t>
+          <t>-34.345929, -71.125846</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12587</t>
+          <t>-34.34593, -71.12585</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>167:00:04</t>
+          <t>165:59:17</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,58 +599,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/07/13 00:05:35</t>
+          <t>2026/07/14 00:12:26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.476115, -70.6985383</t>
+          <t>-34.205228, -70.67741</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69854</t>
+          <t>-34.20523, -70.67741</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/13 09:32:34</t>
+          <t>2026/07/20 22:11:25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.2048766, -70.6856249</t>
+          <t>-34.205371, -70.677398</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.20488, -70.68562</t>
+          <t>-34.20537, -70.67740</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>09:26:59</t>
+          <t>165:58:59</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>87.7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,41 +663,41 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/07/13 00:12:19</t>
+          <t>2026/07/14 00:13:21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.205228, -70.67741</t>
+          <t>-33.359984, -70.807055</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67741</t>
+          <t>-33.35998, -70.80706</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/19 23:11:38</t>
+          <t>2026/07/20 22:13:14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.205402, -70.677263</t>
+          <t>-33.360034, -70.807056</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67726</t>
+          <t>-33.36003, -70.80706</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>166:59:19</t>
+          <t>165:59:53</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -722,47 +722,47 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/07/13 00:13:21</t>
+          <t>2026/07/14 00:19:47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.359984, -70.807055</t>
+          <t>-33.360054, -70.807138</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80706</t>
+          <t>-33.36005, -70.80714</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/19 23:13:21</t>
+          <t>2026/07/14 11:24:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.360021, -70.807061</t>
+          <t>-33.359965, -70.807053</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80706</t>
+          <t>-33.35997, -70.80705</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>167:00:00</t>
+          <t>11:04:13</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -781,7 +781,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/07/13 00:22:58</t>
+          <t>2026/07/14 00:23:08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -796,26 +796,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/19 23:23:39</t>
+          <t>2026/07/20 22:24:57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.876517, -71.127094</t>
+          <t>-34.876573, -71.127266</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.87652, -71.12709</t>
+          <t>-34.87657, -71.12727</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>167:00:41</t>
+          <t>166:01:49</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/07/13 00:23:50</t>
+          <t>2026/07/14 00:23:12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.360092, -70.807118</t>
+          <t>-32.838362, -70.955504</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.36009, -70.80712</t>
+          <t>-32.83836, -70.95550</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/13 08:59:50</t>
+          <t>2026/07/14 08:45:39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.360023, -70.806713</t>
+          <t>-32.838372, -70.955582</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80671</t>
+          <t>-32.83837, -70.95558</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>08:36:00</t>
+          <t>08:22:27</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.12</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -899,47 +899,47 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/07/13 00:26:39</t>
+          <t>2026/07/14 00:29:15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-32.7430583, -70.7297799</t>
+          <t>-33.0873083, -71.3623783</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-32.74306, -70.72978</t>
+          <t>-33.08731, -71.36238</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/13 07:15:14</t>
+          <t>2026/07/14 07:46:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-32.8657616, -70.681495</t>
+          <t>-33.0868883, -71.3619016</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.86576, -70.68149</t>
+          <t>-33.08689, -71.36190</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>06:48:35</t>
+          <t>07:17:20</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>16.37</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N10" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -958,7 +958,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/07/13 00:31:20</t>
+          <t>2026/07/14 00:31:38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -973,26 +973,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/19 23:31:38</t>
+          <t>2026/07/20 21:31:51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.89987, -71.429483</t>
+          <t>-33.899813, -71.429474</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.89987, -71.42948</t>
+          <t>-33.89981, -71.42947</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>167:00:18</t>
+          <t>165:00:13</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/07/13 00:34:45</t>
+          <t>2026/07/14 00:34:52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1032,26 +1032,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/19 23:34:30</t>
+          <t>2026/07/20 21:34:24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-34.5796, -70.961366</t>
+          <t>-34.57967, -70.96146</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.57960, -70.96137</t>
+          <t>-34.57967, -70.96146</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>166:59:45</t>
+          <t>164:59:32</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/07/13 00:36:38</t>
+          <t>2026/07/14 00:41:06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.608875</t>
+          <t>-33.3674, -70.696184</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60887</t>
+          <t>-33.36740, -70.69618</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/13 08:58:40</t>
+          <t>2026/07/20 01:41:36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.2033433, -70.68859</t>
+          <t>-33.367076, -70.696346</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.20334, -70.68859</t>
+          <t>-33.36708, -70.69635</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>08:22:02</t>
+          <t>145:00:30</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>164.51</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>137</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/07/13 00:37:05</t>
+          <t>2026/07/14 00:48:22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-32.838343, -70.955543</t>
+          <t>-33.482188, -70.764925</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-32.83834, -70.95554</t>
+          <t>-33.48219, -70.76493</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/13 12:12:25</t>
+          <t>2026/07/14 09:05:33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-32.839701, -70.954577</t>
+          <t>-33.359932, -70.806898</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-32.83970, -70.95458</t>
+          <t>-33.35993, -70.80690</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11:35:20</t>
+          <t>08:17:11</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>204.05</v>
+        <v>25.07</v>
       </c>
       <c r="M14" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="N14" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,46 +1189,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/07/13 00:39:37</t>
+          <t>2026/07/14 00:56:10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/19 23:40:44</t>
+          <t>2026/07/20 21:56:10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.36714, -70.696418</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36714, -70.69642</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>167:01:07</t>
+          <t>165:00:00</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,58 +1248,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/07/13 00:39:59</t>
+          <t>2026/07/14 00:59:09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.0872483, -71.36224</t>
+          <t>-34.042641, -70.681549</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.08725, -71.36224</t>
+          <t>-34.04264, -70.68155</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/13 08:11:09</t>
+          <t>2026/07/20 21:57:31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.087285, -71.36232</t>
+          <t>-34.042665, -70.681704</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36232</t>
+          <t>-34.04266, -70.68170</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>07:31:10</t>
+          <t>164:58:22</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,53 +1312,53 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/07/13 00:48:31</t>
+          <t>2026/07/14 01:02:21</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.4362783, -70.629345</t>
+          <t>-33.3672816, -70.69573</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62935</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/13 07:06:26</t>
+          <t>2026/07/18 09:59:20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.4449966, -70.61965</t>
+          <t>-33.4640433, -70.6511716</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.44500, -70.61965</t>
+          <t>-33.46404, -70.65117</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>06:17:55</t>
+          <t>104:56:59</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>16.4</v>
       </c>
       <c r="M17" t="n">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="N17" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,53 +1371,53 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/07/13 00:55:01</t>
+          <t>2026/07/14 01:14:34</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-32.841676, -70.936803</t>
+          <t>-33.4761233, -70.6985316</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-32.84168, -70.93680</t>
+          <t>-33.47612, -70.69853</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/13 09:51:07</t>
+          <t>2026/07/14 10:54:23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.367377, -70.695938</t>
+          <t>-34.2054066, -70.67967</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.36738, -70.69594</t>
+          <t>-34.20541, -70.67967</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>08:56:06</t>
+          <t>09:39:49</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>76.92</v>
+        <v>126.75</v>
       </c>
       <c r="M18" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="N18" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,58 +1425,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/07/13 00:56:10</t>
+          <t>2026/07/14 01:15:19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.8792316, -70.6088066</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.87923, -70.60881</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/19 23:56:11</t>
+          <t>2026/07/14 09:00:09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.2055083, -70.6783166</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.20551, -70.67832</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>167:00:01</t>
+          <t>07:44:50</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>164.8</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1484,58 +1484,58 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/07/13 00:57:51</t>
+          <t>2026/07/14 01:25:42</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-34.042641, -70.681549</t>
+          <t>-33.4364766, -70.6295866</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-34.04264, -70.68155</t>
+          <t>-33.43648, -70.62959</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/19 23:57:22</t>
+          <t>2026/07/14 10:57:49</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-34.042596, -70.681656</t>
+          <t>-33.3661216, -70.6955083</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-34.04260, -70.68166</t>
+          <t>-33.36612, -70.69551</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>166:59:31</t>
+          <t>09:32:07</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.05</v>
+        <v>13.47</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/07/13 01:02:21</t>
+          <t>2026/07/14 01:55:48</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.69573</t>
+          <t>-32.7976016, -70.887115</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-32.79760, -70.88711</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/07/18 09:59:20</t>
+          <t>2026/07/14 08:40:37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.4640433, -70.6511716</t>
+          <t>-34.2052916, -70.682345</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.46404, -70.65117</t>
+          <t>-34.20529, -70.68234</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>128:56:59</t>
+          <t>06:44:49</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>16.4</v>
+        <v>190.85</v>
       </c>
       <c r="M21" t="n">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="N21" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,53 +1607,53 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/07/13 01:09:47</t>
+          <t>2026/07/14 01:59:32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-32.79757, -70.8870583</t>
+          <t>-32.7430283, -70.7297866</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-32.79757, -70.88706</t>
+          <t>-32.74303, -70.72979</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/07/13 07:47:17</t>
+          <t>2026/07/14 08:15:13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.3672916, -70.696675</t>
+          <t>-33.3598283, -70.806785</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.36729, -70.69667</t>
+          <t>-33.35983, -70.80679</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06:37:30</t>
+          <t>06:15:41</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>92.58</v>
+        <v>90</v>
       </c>
       <c r="M22" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="N22" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1666,47 +1666,47 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/07/13 07:07:07</t>
+          <t>2026/07/14 07:47:11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.445475, -70.6204933</t>
+          <t>-33.0872933, -71.3623533</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.44548, -70.62049</t>
+          <t>-33.08729, -71.36235</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/07/13 08:58:35</t>
+          <t>2026/07/14 09:08:37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.43611, -70.6298416</t>
+          <t>-33.0977283, -71.3297633</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.43611, -70.62984</t>
+          <t>-33.09773, -71.32976</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>01:51:28</t>
+          <t>01:21:26</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>4.14</v>
       </c>
       <c r="M23" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1725,47 +1725,47 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/07/13 07:16:29</t>
+          <t>2026/07/14 08:15:28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.8702183, -70.6803383</t>
+          <t>-33.3599533, -70.8071933</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.87022, -70.68034</t>
+          <t>-33.35995, -70.80719</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/13 08:18:53</t>
+          <t>2026/07/14 12:08:28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.3599333, -70.8071349</t>
+          <t>-33.3613949, -70.8066633</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.35993, -70.80713</t>
+          <t>-33.36139, -70.80666</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>01:02:24</t>
+          <t>03:53:00</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>72.94</v>
+        <v>0.2</v>
       </c>
       <c r="M24" t="n">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1784,53 +1784,53 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/07/13 07:48:32</t>
+          <t>2026/07/14 08:41:52</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.3672533, -70.696775</t>
+          <t>-34.20538, -70.680535</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69678</t>
+          <t>-34.20538, -70.68054</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/13 09:17:19</t>
+          <t>2026/07/14 09:11:06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.2051666, -70.6840649</t>
+          <t>-34.2053583, -70.6805233</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.20517, -70.68406</t>
+          <t>-34.20536, -70.68052</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01:28:47</t>
+          <t>00:29:14</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>101.25</v>
+        <v>0.93</v>
       </c>
       <c r="M25" t="n">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/07/13 08:11:38</t>
+          <t>2026/07/14 08:45:59</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.0873233, -71.3622866</t>
+          <t>-32.838375, -70.955504</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36229</t>
+          <t>-32.83837, -70.95550</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/13 10:16:24</t>
+          <t>2026/07/14 20:09:49</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.3601966, -70.8090216</t>
+          <t>-32.838789, -70.954119</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.36020, -70.80902</t>
+          <t>-32.83879, -70.95412</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>02:04:46</t>
+          <t>11:23:50</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>114.82</v>
+        <v>0.36</v>
       </c>
       <c r="M26" t="n">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="N26" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,41 +1902,41 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/07/13 08:19:00</t>
+          <t>2026/07/14 09:00:25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.35994, -70.8071866</t>
+          <t>-34.205505, -70.67842</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80719</t>
+          <t>-34.20551, -70.67842</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/07/13 09:26:02</t>
+          <t>2026/07/14 09:29:20</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.3599466, -70.807095</t>
+          <t>-34.205345, -70.6786333</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80710</t>
+          <t>-34.20535, -70.67863</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01:07:02</t>
+          <t>00:28:55</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
@@ -1948,11 +1948,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/07/13 08:58:50</t>
+          <t>2026/07/14 09:06:04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.4362533, -70.6295033</t>
+          <t>-33.359961, -70.8071</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.43625, -70.62950</t>
+          <t>-33.35996, -70.80710</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/07/13 10:02:50</t>
+          <t>2026/07/14 09:39:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.3672499, -70.6955516</t>
+          <t>-33.356611, -70.794937</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69555</t>
+          <t>-33.35661, -70.79494</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>01:04:00</t>
+          <t>00:32:56</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13.38</v>
+        <v>1.99</v>
       </c>
       <c r="M28" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="N28" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,57 +2020,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/07/13 08:59:55</t>
+          <t>2026/07/14 09:08:48</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-34.2050983, -70.6852199</t>
+          <t>-33.0976883, -71.329775</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-34.20510, -70.68522</t>
+          <t>-33.09769, -71.32977</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/07/13 09:14:45</t>
+          <t>2026/07/14 10:14:47</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.2046433, -70.6796633</t>
+          <t>-33.0878933, -71.362315</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.20464, -70.67966</t>
+          <t>-33.08789, -71.36231</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:14:50</t>
+          <t>01:05:59</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.55</v>
+        <v>3.92</v>
       </c>
       <c r="M29" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="N29" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/07/13 09:00:21</t>
+          <t>2026/07/14 09:12:21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-33.36005, -70.806665</t>
+          <t>-34.205505, -70.6783983</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80666</t>
+          <t>-34.20551, -70.67840</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/07/13 09:23:53</t>
+          <t>2026/07/14 11:38:27</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-33.359906, -70.807149</t>
+          <t>-34.20494, -70.6779266</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-33.35991, -70.80715</t>
+          <t>-34.20494, -70.67793</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:23:32</t>
+          <t>02:26:06</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -2138,53 +2138,53 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/07/13 09:15:04</t>
+          <t>2026/07/14 09:30:11</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-34.2042933, -70.6790766</t>
+          <t>-34.2048833, -70.67869</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-34.20429, -70.67908</t>
+          <t>-34.20488, -70.67869</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/07/13 09:53:03</t>
+          <t>2026/07/14 09:43:04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-34.2053416, -70.6802733</t>
+          <t>-34.20538, -70.6801349</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68027</t>
+          <t>-34.20538, -70.68013</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:37:59</t>
+          <t>00:12:53</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.46</v>
+        <v>0.2</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2197,116 +2197,116 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/07/13 09:18:34</t>
+          <t>2026/07/14 09:39:15</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-34.2053666, -70.6803766</t>
+          <t>-33.356611, -70.794936</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-34.20537, -70.68038</t>
+          <t>-33.35661, -70.79494</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/07/13 11:21:38</t>
+          <t>2026/07/14 10:11:18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-34.2055433, -70.6775583</t>
+          <t>-33.367269, -70.695886</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67756</t>
+          <t>-33.36727, -70.69589</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>02:03:04</t>
+          <t>00:32:03</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.7</v>
+        <v>10.48</v>
       </c>
       <c r="M32" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="N32" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/07/13 09:23:56</t>
+          <t>2026/07/14 09:44:19</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-33.359904, -70.807156</t>
+          <t>-34.2054733, -70.6784083</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80716</t>
+          <t>-34.20547, -70.67841</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:20</t>
+          <t>2026/07/14 10:01:17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-33.360145, -70.80659</t>
+          <t>-34.2049233, -70.6780999</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80659</t>
+          <t>-34.20492, -70.67810</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:21:24</t>
+          <t>00:16:58</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/07/13 09:27:17</t>
+          <t>2026/07/14 10:01:46</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-33.3601216, -70.8066816</t>
+          <t>-34.20488, -70.6787116</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80668</t>
+          <t>-34.20488, -70.67871</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/07/13 10:33:29</t>
+          <t>2026/07/14 11:29:22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-33.360125, -70.8067916</t>
+          <t>-34.2044666, -70.6794183</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80679</t>
+          <t>-34.20447, -70.67942</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:06:12</t>
+          <t>01:27:36</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,53 +2374,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/07/13 09:33:49</t>
+          <t>2026/07/14 10:12:15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-34.2051, -70.685155</t>
+          <t>-33.367257, -70.695904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-34.20510, -70.68515</t>
+          <t>-33.36726, -70.69590</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/07/13 10:55:27</t>
+          <t>2026/07/14 10:50:21</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-34.2054883, -70.677505</t>
+          <t>-33.37887, -70.68308</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-34.20549, -70.67750</t>
+          <t>-33.37887, -70.68308</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01:21:38</t>
+          <t>00:38:06</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.71</v>
+        <v>2.82</v>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="N35" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2428,62 +2428,62 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/07/13 09:45:47</t>
+          <t>2026/07/14 10:15:23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.360123, -70.806616</t>
+          <t>-33.0878966, -71.3623366</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80662</t>
+          <t>-33.08790, -71.36234</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/07/13 10:36:19</t>
+          <t>2026/07/14 10:47:01</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.360119, -70.806713</t>
+          <t>-33.0977366, -71.3297433</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80671</t>
+          <t>-33.09774, -71.32974</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:50:32</t>
+          <t>00:31:38</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.01</v>
+        <v>3.94</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/07/13 09:51:13</t>
+          <t>2026/07/14 10:47:28</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.367361, -70.695931</t>
+          <t>-33.0977533, -71.3297149</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.36736, -70.69593</t>
+          <t>-33.09775, -71.32971</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/07/13 10:52:55</t>
+          <t>2026/07/14 11:30:29</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.364484, -70.784452</t>
+          <t>-33.0885183, -71.3613133</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.36448, -70.78445</t>
+          <t>-33.08852, -71.36131</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>01:01:42</t>
+          <t>00:43:01</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>11.52</v>
+        <v>3.87</v>
       </c>
       <c r="M37" t="n">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="N37" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/07/13 09:53:25</t>
+          <t>2026/07/14 10:50:41</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-34.2054416, -70.67916</t>
+          <t>-33.37885, -70.682995</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67916</t>
+          <t>-33.37885, -70.68300</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/07/13 10:56:55</t>
+          <t>2026/07/14 11:48:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-34.2042116, -70.6790666</t>
+          <t>-33.367297, -70.69598</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-34.20421, -70.67907</t>
+          <t>-33.36730, -70.69598</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01:03:30</t>
+          <t>00:57:19</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.26</v>
+        <v>2.68</v>
       </c>
       <c r="M38" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="N38" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/07/13 10:03:12</t>
+          <t>2026/07/14 10:54:42</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.36728, -70.695735</t>
+          <t>-34.205495, -70.6784683</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-34.20549, -70.67847</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/07/13 18:48:27</t>
+          <t>2026/07/14 11:47:27</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.4360999, -70.6298916</t>
+          <t>-34.2048816, -70.6785466</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.43610, -70.62989</t>
+          <t>-34.20488, -70.67855</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>08:45:15</t>
+          <t>00:52:45</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19.08</v>
+        <v>0.08</v>
       </c>
       <c r="M39" t="n">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="N39" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,171 +2669,171 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/07/13 10:16:38</t>
+          <t>2026/07/14 10:58:45</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-33.360755, -70.8090433</t>
+          <t>-33.3669933, -70.6955383</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-33.36075, -70.80904</t>
+          <t>-33.36699, -70.69554</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/07/13 12:01:57</t>
+          <t>2026/07/14 19:26:41</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-33.3589366, -70.8089099</t>
+          <t>-33.4358749, -70.6300383</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-33.35894, -70.80891</t>
+          <t>-33.43587, -70.63004</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>01:45:19</t>
+          <t>08:27:56</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.23</v>
+        <v>23.39</v>
       </c>
       <c r="M40" t="n">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/07/13 10:33:43</t>
+          <t>2026/07/14 11:24:17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.3600066, -70.8068483</t>
+          <t>-33.359942, -70.807084</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80685</t>
+          <t>-33.35994, -70.80708</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/07/13 14:27:08</t>
+          <t>2026/07/14 12:02:22</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.359985, -70.8070316</t>
+          <t>-33.360005, -70.806977</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80703</t>
+          <t>-33.36001, -70.80698</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03:53:25</t>
+          <t>00:38:05</t>
         </is>
       </c>
       <c r="L41" t="n">
         <v>0.04</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/07/13 10:36:41</t>
+          <t>2026/07/14 11:29:26</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-33.360039, -70.806789</t>
+          <t>-34.2044466, -70.6793866</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80679</t>
+          <t>-34.20445, -70.67939</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/07/13 10:48:50</t>
+          <t>2026/07/14 11:44:44</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-33.360072, -70.806802</t>
+          <t>-34.204775, -70.6780999</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80680</t>
+          <t>-34.20477, -70.67810</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:12:09</t>
+          <t>00:15:18</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/07/13 10:49:00</t>
+          <t>2026/07/14 11:31:44</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-33.360103, -70.806819</t>
+          <t>-33.0879133, -71.3622983</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80682</t>
+          <t>-33.08791, -71.36230</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/07/13 12:24:43</t>
+          <t>2026/07/14 11:50:32</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-33.359879, -70.807133</t>
+          <t>-33.044255, -71.3752933</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-33.35988, -70.80713</t>
+          <t>-33.04425, -71.37529</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>01:35:43</t>
+          <t>00:18:48</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.45</v>
+        <v>5.54</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/07/13 10:53:55</t>
+          <t>2026/07/14 11:38:36</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.359356, -70.791177</t>
+          <t>-34.2049466, -70.6780933</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.35936, -70.79118</t>
+          <t>-34.20495, -70.67809</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/07/13 11:09:07</t>
+          <t>2026/07/14 11:46:48</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.359937, -70.806859</t>
+          <t>-34.2048916, -70.6783983</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80686</t>
+          <t>-34.20489, -70.67840</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:15:12</t>
+          <t>00:08:12</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.44</v>
+        <v>0.03</v>
       </c>
       <c r="M44" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,53 +2964,53 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/07/13 10:56:34</t>
+          <t>2026/07/14 11:44:59</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-34.2052333, -70.6774933</t>
+          <t>-34.205015, -70.6780983</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67749</t>
+          <t>-34.20502, -70.67810</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/07/13 11:45:44</t>
+          <t>2026/07/14 12:32:31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-34.2057283, -70.6761133</t>
+          <t>-34.2049566, -70.6781216</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-34.20573, -70.67611</t>
+          <t>-34.20496, -70.67812</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:49:10</t>
+          <t>00:47:32</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="M45" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N45" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/07/13 10:58:10</t>
+          <t>2026/07/14 11:47:54</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-34.2042299, -70.6790299</t>
+          <t>-34.2048716, -70.67926</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-34.20423, -70.67903</t>
+          <t>-34.20487, -70.67926</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/07/13 11:18:43</t>
+          <t>2026/07/14 13:32:36</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-34.2054883, -70.6781033</t>
+          <t>-34.190165, -70.7093666</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-34.20549, -70.67810</t>
+          <t>-34.19017, -70.70937</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:20:33</t>
+          <t>01:44:42</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.37</v>
+        <v>3.48</v>
       </c>
       <c r="M46" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="N46" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,53 +3082,53 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/07/13 11:09:25</t>
+          <t>2026/07/14 11:47:57</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.359996, -70.806786</t>
+          <t>-34.2048699, -70.67917</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80679</t>
+          <t>-34.20487, -70.67917</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/07/13 12:42:52</t>
+          <t>2026/07/14 13:32:42</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.351878, -70.801367</t>
+          <t>-34.1901233, -70.7093333</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.35188, -70.80137</t>
+          <t>-34.19012, -70.70933</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>01:33:27</t>
+          <t>01:44:45</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="M47" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="N47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3141,57 +3141,57 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/07/13 11:19:47</t>
+          <t>2026/07/14 11:48:13</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-34.2054183, -70.678095</t>
+          <t>-33.367289, -70.695964</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67809</t>
+          <t>-33.36729, -70.69596</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/07/13 11:32:07</t>
+          <t>2026/07/14 12:20:12</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-34.2055099, -70.6784433</t>
+          <t>-33.359933, -70.806779</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67844</t>
+          <t>-33.35993, -70.80678</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:12:20</t>
+          <t>00:31:59</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.03</v>
+        <v>14.81</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,116 +3200,116 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/07/13 11:21:48</t>
+          <t>2026/07/14 11:51:47</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-34.2053583, -70.6774883</t>
+          <t>-33.0438766, -71.37526</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-34.20536, -70.67749</t>
+          <t>-33.04388, -71.37526</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/07/13 11:47:23</t>
+          <t>2026/07/14 12:31:45</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-34.2070016, -70.6769283</t>
+          <t>-33.0436233, -71.4166216</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-34.20700, -70.67693</t>
+          <t>-33.04362, -71.41662</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:25:35</t>
+          <t>00:39:58</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.32</v>
+        <v>4.19</v>
       </c>
       <c r="M49" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026/07/14 12:03:21</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-33.360075, -70.806905</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-33.36008, -70.80691</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026/07/14 12:25:04</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-33.360001, -70.807087</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-33.36000, -70.80709</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>00:21:43</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M50" t="n">
         <v>7</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026/07/13 11:33:16</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-34.205415, -70.6790116</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-34.20542, -70.67901</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026/07/13 12:38:52</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-34.190015, -70.709305</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-34.19002, -70.70931</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>01:05:36</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="M50" t="n">
-        <v>39</v>
-      </c>
       <c r="N50" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/07/13 11:46:48</t>
+          <t>2026/07/14 12:08:39</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-34.2073166, -70.6769149</t>
+          <t>-33.3615533, -70.80668</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-34.20732, -70.67691</t>
+          <t>-33.36155, -70.80668</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/07/13 12:55:52</t>
+          <t>2026/07/14 12:16:57</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-34.2053433, -70.6803133</t>
+          <t>-33.36014, -70.8064633</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68031</t>
+          <t>-33.36014, -70.80646</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>01:09:04</t>
+          <t>00:08:18</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.58</v>
+        <v>0.26</v>
       </c>
       <c r="M51" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="N51" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/07/13 11:48:38</t>
+          <t>2026/07/14 12:17:14</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-34.2071999, -70.6769116</t>
+          <t>-33.3600349, -70.8066783</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-34.20720, -70.67691</t>
+          <t>-33.36003, -70.80668</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/07/13 12:35:51</t>
+          <t>2026/07/14 14:49:58</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-34.1900799, -70.709435</t>
+          <t>-33.361315, -70.8068249</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-34.19008, -70.70943</t>
+          <t>-33.36131, -70.80682</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:47:13</t>
+          <t>02:32:44</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.21</v>
+        <v>0.34</v>
       </c>
       <c r="M52" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="N52" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,175 +3436,175 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/07/13 12:03:12</t>
+          <t>2026/07/14 12:21:06</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-33.35947, -70.8089749</t>
+          <t>-33.360073, -70.806914</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-33.35947, -70.80897</t>
+          <t>-33.36007, -70.80691</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/07/13 12:42:09</t>
+          <t>2026/07/14 12:46:36</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.3518616, -70.8012866</t>
+          <t>-33.353327, -70.799399</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.35186, -70.80129</t>
+          <t>-33.35333, -70.79940</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:38:57</t>
+          <t>00:25:30</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.46</v>
+        <v>2.89</v>
       </c>
       <c r="M53" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="N53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/07/13 12:13:15</t>
+          <t>2026/07/14 12:25:25</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-32.838747, -70.954109</t>
+          <t>-33.360082, -70.807131</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-32.83875, -70.95411</t>
+          <t>-33.36008, -70.80713</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/07/13 12:36:18</t>
+          <t>2026/07/15 09:10:23</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-32.838358, -70.956156</t>
+          <t>-33.360117, -70.806631</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95616</t>
+          <t>-33.36012, -70.80663</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:23:03</t>
+          <t>20:44:58</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.43</v>
+        <v>0.09</v>
       </c>
       <c r="M54" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/07/13 12:25:07</t>
+          <t>2026/07/14 12:33:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.359881, -70.807152</t>
+          <t>-33.04356, -71.4166366</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.35988, -70.80715</t>
+          <t>-33.04356, -71.41664</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:09</t>
+          <t>2026/07/14 13:02:22</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.360174, -70.806587</t>
+          <t>-33.044495, -71.42038</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80659</t>
+          <t>-33.04449, -71.42038</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>02:00:02</t>
+          <t>00:29:22</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.06</v>
+        <v>0.89</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,57 +3613,57 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/07/13 12:36:23</t>
+          <t>2026/07/14 12:33:04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-34.1899083, -70.7092533</t>
+          <t>-34.2049416, -70.6788416</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-34.18991, -70.70925</t>
+          <t>-34.20494, -70.67884</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/07/13 13:14:12</t>
+          <t>2026/07/14 13:35:11</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-34.2052566, -70.6828083</t>
+          <t>-34.1900849, -70.70941</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68281</t>
+          <t>-34.19008, -70.70941</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:37:49</t>
+          <t>01:02:07</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.16</v>
+        <v>3.53</v>
       </c>
       <c r="M56" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="N56" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/07/13 12:37:09</t>
+          <t>2026/07/14 12:47:39</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-32.838374, -70.955502</t>
+          <t>-33.35716, -70.79427</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95550</t>
+          <t>-33.35716, -70.79427</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/07/13 17:30:47</t>
+          <t>2026/07/14 13:05:42</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-32.840952, -70.957275</t>
+          <t>-33.401738, -70.749146</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-32.84095, -70.95727</t>
+          <t>-33.40174, -70.74915</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>04:53:38</t>
+          <t>00:18:03</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.66</v>
+        <v>7.87</v>
       </c>
       <c r="M57" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="N57" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/07/13 12:39:05</t>
+          <t>2026/07/14 13:03:13</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-34.1899449, -70.7092716</t>
+          <t>-33.0444983, -71.42037</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-34.18994, -70.70927</t>
+          <t>-33.04450, -71.42037</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/07/13 13:16:35</t>
+          <t>2026/07/14 13:21:09</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-34.20424, -70.67912</t>
+          <t>-33.0560066, -71.4270166</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-34.20424, -70.67912</t>
+          <t>-33.05601, -71.42702</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:37:30</t>
+          <t>00:17:56</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.56</v>
+        <v>2.11</v>
       </c>
       <c r="M58" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N58" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/07/13 12:43:24</t>
+          <t>2026/07/14 13:06:40</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.3553366, -70.796635</t>
+          <t>-33.401249, -70.750322</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.35534, -70.79663</t>
+          <t>-33.40125, -70.75032</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/07/13 13:05:20</t>
+          <t>2026/07/14 14:08:30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.40161, -70.7492849</t>
+          <t>-33.359998, -70.806774</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.40161, -70.74928</t>
+          <t>-33.36000, -70.80677</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:21:56</t>
+          <t>01:01:50</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>8.18</v>
+        <v>9.76</v>
       </c>
       <c r="M59" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="N59" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/07/13 12:43:46</t>
+          <t>2026/07/14 13:22:24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-33.354838, -70.797277</t>
+          <t>-33.0559483, -71.4270616</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-33.35484, -70.79728</t>
+          <t>-33.05595, -71.42706</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/07/13 13:05:22</t>
+          <t>2026/07/14 13:44:34</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-33.401431, -70.749801</t>
+          <t>-33.0873466, -71.3623049</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-33.40143, -70.74980</t>
+          <t>-33.08735, -71.36230</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:21:36</t>
+          <t>00:22:10</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>8.33</v>
+        <v>8.44</v>
       </c>
       <c r="M60" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N60" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/07/13 12:55:58</t>
+          <t>2026/07/14 13:32:42</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-34.20534, -70.6801749</t>
+          <t>-34.1902183, -70.7094083</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68017</t>
+          <t>-34.19022, -70.70941</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/07/13 13:34:17</t>
+          <t>2026/07/14 14:18:31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-34.2057549, -70.6761633</t>
+          <t>-34.20485, -70.6798033</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-34.20575, -70.67616</t>
+          <t>-34.20485, -70.67980</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:38:19</t>
+          <t>00:45:49</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.73</v>
+        <v>3.42</v>
       </c>
       <c r="M61" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="N61" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/07/13 13:06:01</t>
+          <t>2026/07/14 13:32:59</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-33.401182, -70.750379</t>
+          <t>-34.1902116, -70.7094066</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-33.40118, -70.75038</t>
+          <t>-34.19021, -70.70941</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/07/13 14:21:28</t>
+          <t>2026/07/14 14:19:11</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-33.361524, -70.809105</t>
+          <t>-34.2053366, -70.6803249</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-33.36152, -70.80911</t>
+          <t>-34.20534, -70.68032</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>01:15:27</t>
+          <t>00:46:12</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>10.12</v>
+        <v>3.35</v>
       </c>
       <c r="M62" t="n">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="N62" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,57 +4026,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/07/13 13:06:03</t>
+          <t>2026/07/14 13:35:25</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-33.401135, -70.7505233</t>
+          <t>-34.1902449, -70.7093483</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-33.40113, -70.75052</t>
+          <t>-34.19024, -70.70935</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/07/13 14:10:37</t>
+          <t>2026/07/14 14:25:10</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-33.360195, -70.8090133</t>
+          <t>-34.2044049, -70.679025</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-33.36019, -70.80901</t>
+          <t>-34.20440, -70.67902</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>01:04:34</t>
+          <t>00:49:45</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>10.86</v>
+        <v>3.56</v>
       </c>
       <c r="M63" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="N63" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/07/13 13:14:48</t>
+          <t>2026/07/14 13:44:48</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.2053583, -70.6801916</t>
+          <t>-33.0873283, -71.3623283</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.20536, -70.68019</t>
+          <t>-33.08733, -71.36233</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/07/13 17:31:43</t>
+          <t>2026/07/14 16:06:26</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-32.7576883, -70.7029933</t>
+          <t>-33.087325, -71.3622866</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-32.75769, -70.70299</t>
+          <t>-33.08732, -71.36229</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>04:16:55</t>
+          <t>02:21:38</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>173.31</v>
+        <v>11.87</v>
       </c>
       <c r="M64" t="n">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="N64" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/07/13 13:17:50</t>
+          <t>2026/07/14 14:09:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-34.2042583, -70.6790549</t>
+          <t>-33.360079, -70.806683</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-34.20426, -70.67905</t>
+          <t>-33.36008, -70.80668</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/07/13 13:25:34</t>
+          <t>2026/07/14 15:09:39</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.2055533, -70.6781966</t>
+          <t>-33.36007, -70.808767</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67820</t>
+          <t>-33.36007, -70.80877</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:07:44</t>
+          <t>01:00:39</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M65" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,47 +4203,47 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/07/13 13:25:51</t>
+          <t>2026/07/14 14:18:51</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.2055266, -70.67827</t>
+          <t>-34.2049233, -70.6791316</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.20553, -70.67827</t>
+          <t>-34.20492, -70.67913</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/07/13 13:49:50</t>
+          <t>2026/07/14 19:16:49</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.2055516, -70.6781983</t>
+          <t>-32.7918949, -70.8294333</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67820</t>
+          <t>-32.79189, -70.82943</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>00:23:59</t>
+          <t>04:57:58</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.01</v>
+        <v>188.22</v>
       </c>
       <c r="M66" t="n">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,44 +4262,44 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/07/13 13:35:21</t>
+          <t>2026/07/14 14:20:26</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-34.2079316, -70.6771533</t>
+          <t>-34.2042266, -70.6791133</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-34.20793, -70.67715</t>
+          <t>-34.20423, -70.67911</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/07/13 14:24:46</t>
+          <t>2026/07/14 14:58:07</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-34.2055666, -70.676895</t>
+          <t>-34.2044166, -70.67878</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-34.20557, -70.67690</t>
+          <t>-34.20442, -70.67878</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>00:49:25</t>
+          <t>00:37:41</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="M67" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N67" t="n">
         <v>10</v>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/07/13 13:50:07</t>
+          <t>2026/07/14 14:26:25</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.2055566, -70.6777866</t>
+          <t>-34.2046383, -70.67904</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67779</t>
+          <t>-34.20464, -70.67904</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/07/13 13:58:22</t>
+          <t>2026/07/14 14:51:49</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-34.2054733, -70.6781233</t>
+          <t>-34.2044049, -70.6790233</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67812</t>
+          <t>-34.20440, -70.67902</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:08:15</t>
+          <t>00:25:24</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.03</v>
+        <v>1.36</v>
       </c>
       <c r="M68" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,47 +4380,47 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/07/13 13:58:54</t>
+          <t>2026/07/14 14:50:54</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.2049483, -70.6781299</t>
+          <t>-33.360025, -70.8067666</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.20495, -70.67813</t>
+          <t>-33.36003, -70.80677</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/07/13 14:08:05</t>
+          <t>2026/07/14 15:43:59</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.204985, -70.6782233</t>
+          <t>-33.3599616, -70.806995</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.20499, -70.67822</t>
+          <t>-33.35996, -70.80700</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:09:11</t>
+          <t>00:53:05</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.01</v>
+        <v>0.58</v>
       </c>
       <c r="M69" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,41 +4439,41 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/07/13 14:08:38</t>
+          <t>2026/07/14 14:52:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-34.2055233, -70.6782049</t>
+          <t>-34.204845, -70.6790533</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-34.20552, -70.67820</t>
+          <t>-34.20484, -70.67905</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/07/13 14:21:45</t>
+          <t>2026/07/14 15:20:37</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-34.20556, -70.6782116</t>
+          <t>-34.205435, -70.6790266</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67821</t>
+          <t>-34.20544, -70.67903</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:13:07</t>
+          <t>00:28:14</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M70" t="n">
         <v>6</v>
@@ -4485,11 +4485,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/07/13 14:11:52</t>
+          <t>2026/07/14 14:59:22</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-33.36071, -70.809025</t>
+          <t>-34.2050133, -70.6788466</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-33.36071, -70.80903</t>
+          <t>-34.20501, -70.67885</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/07/13 14:19:52</t>
+          <t>2026/07/14 18:03:44</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.3605066, -70.8091083</t>
+          <t>-33.3895483, -70.6738716</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.36051, -70.80911</t>
+          <t>-33.38955, -70.67387</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:08:00</t>
+          <t>03:04:22</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.02</v>
+        <v>101.81</v>
       </c>
       <c r="M71" t="n">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/07/13 14:20:10</t>
+          <t>2026/07/14 15:10:31</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.360525, -70.8092616</t>
+          <t>-33.360105, -70.806689</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.36053, -70.80926</t>
+          <t>-33.36010, -70.80669</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/07/13 16:09:51</t>
+          <t>2026/07/14 18:47:39</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.1345899, -71.5636699</t>
+          <t>-33.482123, -70.765334</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.13459, -71.56367</t>
+          <t>-33.48212, -70.76533</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>01:49:41</t>
+          <t>03:37:08</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>104.92</v>
+        <v>19.34</v>
       </c>
       <c r="M72" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="N72" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,47 +4616,47 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/07/13 14:21:49</t>
+          <t>2026/07/14 15:21:52</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-33.361521, -70.80911</t>
+          <t>-34.2054733, -70.67876</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-33.36152, -70.80911</t>
+          <t>-34.20547, -70.67876</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/07/13 14:59:25</t>
+          <t>2026/07/14 15:32:47</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.360153, -70.806693</t>
+          <t>-34.2049683, -70.6778549</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80669</t>
+          <t>-34.20497, -70.67785</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:37:36</t>
+          <t>00:10:55</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="M73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,116 +4675,116 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/07/13 14:22:11</t>
+          <t>2026/07/14 15:33:24</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-34.2055566, -70.6783433</t>
+          <t>-34.2049233, -70.6788583</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67834</t>
+          <t>-34.20492, -70.67886</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/07/13 16:00:08</t>
+          <t>2026/07/14 15:52:45</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.744805, -70.7382516</t>
+          <t>-34.2048683, -70.6792583</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.74480, -70.73825</t>
+          <t>-34.20487, -70.67926</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>01:37:57</t>
+          <t>00:19:21</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>56.03</v>
+        <v>0.04</v>
       </c>
       <c r="M74" t="n">
-        <v>131</v>
+        <v>6</v>
       </c>
       <c r="N74" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/07/13 14:25:31</t>
+          <t>2026/07/14 15:44:07</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.360108, -70.806563</t>
+          <t>-33.3599966, -70.807145</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.36011, -70.80656</t>
+          <t>-33.36000, -70.80715</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/13 15:19:07</t>
+          <t>2026/07/14 19:02:41</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.360027, -70.807117</t>
+          <t>-32.7431749, -70.7330116</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-32.74317, -70.73301</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:53:36</t>
+          <t>03:18:34</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.07000000000000001</v>
+        <v>90</v>
       </c>
       <c r="M75" t="n">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,116 +4793,116 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/07/13 14:26:01</t>
+          <t>2026/07/14 15:54:00</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-34.2055366, -70.6783316</t>
+          <t>-34.204815, -70.67926</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67833</t>
+          <t>-34.20482, -70.67926</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/07/13 15:48:26</t>
+          <t>2026/07/14 18:42:47</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.476305, -70.698345</t>
+          <t>-32.8791066, -70.6092816</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69835</t>
+          <t>-32.87911, -70.60928</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01:22:25</t>
+          <t>02:48:47</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>87.73999999999999</v>
+        <v>163.64</v>
       </c>
       <c r="M76" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="N76" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>12</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026/07/14 16:07:41</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-33.0872966, -71.3623166</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-33.08730, -71.36232</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026/07/14 16:48:59</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-33.0872966, -71.3623166</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-33.08730, -71.36232</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>00:41:18</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
         <v>6</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2026/07/13 14:27:42</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-33.3601166, -70.8064883</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-33.36012, -70.80649</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2026/07/13 15:17:08</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-33.36016, -70.8067916</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>-33.36016, -70.80679</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>00:49:26</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M77" t="n">
-        <v>7</v>
-      </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,53 +4911,53 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/07/13 15:00:25</t>
+          <t>2026/07/14 16:49:53</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.360152, -70.806692</t>
+          <t>-33.0872083, -71.362245</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80669</t>
+          <t>-33.08721, -71.36225</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/07/13 17:44:58</t>
+          <t>2026/07/14 18:21:55</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.482168, -70.764932</t>
+          <t>-33.087265, -71.3622383</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.48217, -70.76493</t>
+          <t>-33.08727, -71.36224</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>02:44:33</t>
+          <t>01:32:02</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>21.45</v>
+        <v>0.01</v>
       </c>
       <c r="M78" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="N78" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4970,116 +4970,116 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/07/13 15:18:23</t>
+          <t>2026/07/14 18:04:21</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.359985, -70.80697</t>
+          <t>-33.3893283, -70.6740666</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80697</t>
+          <t>-33.38933, -70.67407</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/07/13 15:39:55</t>
+          <t>2026/07/14 18:44:56</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.3797383, -70.7528033</t>
+          <t>-33.3754316, -70.6714666</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.37974, -70.75280</t>
+          <t>-33.37543, -70.67147</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:21:32</t>
+          <t>00:40:35</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>7.56</v>
+        <v>2.04</v>
       </c>
       <c r="M79" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N79" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>14</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026/07/14 18:23:10</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-33.087325, -71.3623016</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-33.08732, -71.36230</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026/07/15 08:27:37</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-33.0872683, -71.3623066</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-33.08727, -71.36231</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>14:04:27</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M80" t="n">
         <v>9</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026/07/13 15:19:48</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-33.360031, -70.807117</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-33.36003, -70.80712</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2026/07/13 16:32:46</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-33.35997, -70.807061</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-33.35997, -70.80706</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>01:12:58</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4</v>
-      </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,47 +5088,47 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/07/13 15:40:13</t>
+          <t>2026/07/14 18:43:26</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.3797466, -70.7528116</t>
+          <t>-32.8792233, -70.6087466</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.37975, -70.75281</t>
+          <t>-32.87922, -70.60875</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/07/13 16:14:59</t>
+          <t>2026/07/15 09:00:26</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.3599716, -70.8070499</t>
+          <t>-33.36727, -70.6965783</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-33.36727, -70.69658</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:34:46</t>
+          <t>14:17:00</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>7.79</v>
+        <v>72.78</v>
       </c>
       <c r="M81" t="n">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="N81" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82">
@@ -5147,57 +5147,57 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/07/13 15:48:32</t>
+          <t>2026/07/14 18:46:11</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-33.476335, -70.6983783</t>
+          <t>-33.3729483, -70.6710666</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-33.47633, -70.69838</t>
+          <t>-33.37295, -70.67107</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/07/13 18:25:18</t>
+          <t>2026/07/14 18:57:43</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-33.3893033, -70.674025</t>
+          <t>-33.3623666, -70.6701466</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-33.38930, -70.67403</t>
+          <t>-33.36237, -70.67015</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>02:36:46</t>
+          <t>00:11:32</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>14.95</v>
+        <v>1.38</v>
       </c>
       <c r="M82" t="n">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="N82" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,53 +5206,53 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/07/13 16:01:23</t>
+          <t>2026/07/14 18:48:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.7441016, -70.738085</t>
+          <t>-33.482178, -70.764895</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.74410, -70.73808</t>
+          <t>-33.48218, -70.76489</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/07/13 16:46:22</t>
+          <t>2026/07/15 08:54:52</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.501845, -70.7686866</t>
+          <t>-33.359961, -70.806992</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.50185, -70.76869</t>
+          <t>-33.35996, -70.80699</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>00:44:59</t>
+          <t>14:06:19</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>35</v>
+        <v>22.72</v>
       </c>
       <c r="M83" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="N83" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -5265,47 +5265,47 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/07/13 16:11:06</t>
+          <t>2026/07/14 18:58:31</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.1347083, -71.5636116</t>
+          <t>-33.3622, -70.67015</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.13471, -71.56361</t>
+          <t>-33.36220, -70.67015</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/07/13 17:07:54</t>
+          <t>2026/07/14 20:02:28</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.0873133, -71.3622983</t>
+          <t>-33.4761199, -70.69851</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36230</t>
+          <t>-33.47612, -70.69851</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:56:48</t>
+          <t>01:03:57</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>43.75</v>
+        <v>18.12</v>
       </c>
       <c r="M84" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="N84" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
@@ -5315,125 +5315,125 @@
         </is>
       </c>
       <c r="C85" t="n">
+        <v>7</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026/07/14 19:03:15</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-32.7432716, -70.73279</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-32.74327, -70.73279</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026/07/14 19:28:01</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-32.7431599, -70.7296533</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-32.74316, -70.72965</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>00:24:46</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M85" t="n">
+        <v>13</v>
+      </c>
+      <c r="N85" t="n">
         <v>9</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026/07/13 16:15:08</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-33.3599866, -70.8071883</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-33.35999, -70.80719</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2026/07/13 18:54:29</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-32.7431899, -70.733085</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>-32.74319, -70.73309</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>02:39:21</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>90.23</v>
-      </c>
-      <c r="M85" t="n">
-        <v>130</v>
-      </c>
-      <c r="N85" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/07/13 16:33:02</t>
+          <t>2026/07/14 19:18:04</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.360044, -70.807116</t>
+          <t>-32.7853633, -70.8316833</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80712</t>
+          <t>-32.78536, -70.83168</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:00</t>
+          <t>2026/07/14 19:28:42</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.359965, -70.807053</t>
+          <t>-32.7832333, -70.8550033</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-32.78323, -70.85500</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>18:50:58</t>
+          <t>00:10:38</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.05</v>
+        <v>3.85</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/07/13 16:46:32</t>
+          <t>2026/07/14 19:27:56</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.501865, -70.76861</t>
+          <t>-33.4363716, -70.6292483</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.50187, -70.76861</t>
+          <t>-33.43637, -70.62925</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/07/13 18:38:20</t>
+          <t>2026/07/15 13:52:20</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-32.8823216, -70.6119916</t>
+          <t>-33.36227, -70.8072283</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-32.88232, -70.61199</t>
+          <t>-33.36227, -70.80723</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01:51:48</t>
+          <t>18:24:24</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>88.83</v>
+        <v>30.19</v>
       </c>
       <c r="M87" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N87" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/07/13 17:09:09</t>
+          <t>2026/07/14 19:29:05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.0872883, -71.36232</t>
+          <t>-32.7832299, -70.8549183</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36232</t>
+          <t>-32.78323, -70.85492</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/13 17:47:39</t>
+          <t>2026/07/14 19:42:48</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.0872316, -71.3622516</t>
+          <t>-32.7977166, -70.8874216</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.08723, -71.36225</t>
+          <t>-32.79772, -70.88742</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:38:30</t>
+          <t>00:13:43</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.01</v>
+        <v>3.69</v>
       </c>
       <c r="M88" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,47 +5560,47 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/13 17:31:20</t>
+          <t>2026/07/14 19:29:16</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-32.840668, -70.958633</t>
+          <t>-32.7430316, -70.72976</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-32.84067, -70.95863</t>
+          <t>-32.74303, -70.72976</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/13 18:50:54</t>
+          <t>2026/07/15 08:20:18</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-32.838368, -70.955637</t>
+          <t>-33.3599466, -70.8069716</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95564</t>
+          <t>-33.35995, -70.80697</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>01:19:34</t>
+          <t>12:51:02</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.37</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="N89" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/07/13 17:32:57</t>
+          <t>2026/07/14 19:43:30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-32.7580216, -70.7024383</t>
+          <t>-32.7976083, -70.8870733</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-32.75802, -70.70244</t>
+          <t>-32.79761, -70.88707</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/07/13 18:39:30</t>
+          <t>2026/07/15 08:48:07</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-32.7977099, -70.8874433</t>
+          <t>-33.3672366, -70.69658</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88744</t>
+          <t>-33.36724, -70.69658</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>01:06:33</t>
+          <t>13:04:37</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>27.99</v>
+        <v>100.46</v>
       </c>
       <c r="M90" t="n">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="N90" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/07/13 17:45:19</t>
+          <t>2026/07/14 20:03:43</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-33.482188, -70.764925</t>
+          <t>-33.4761049, -70.6985133</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-33.48219, -70.76493</t>
+          <t>-33.47610, -70.69851</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/07/14 09:05:33</t>
+          <t>2026/07/15 09:20:02</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.359932, -70.806898</t>
+          <t>-33.4762616, -70.6983149</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.35993, -70.80690</t>
+          <t>-33.47626, -70.69831</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>15:20:14</t>
+          <t>13:16:19</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>25.07</v>
+        <v>0.03</v>
       </c>
       <c r="M91" t="n">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="N91" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,57 +5737,57 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/07/13 17:48:54</t>
+          <t>2026/07/14 20:10:17</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-33.08732, -71.3622916</t>
+          <t>-32.838711, -70.954084</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36229</t>
+          <t>-32.83871, -70.95408</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/07/13 19:49:19</t>
+          <t>2026/07/14 20:50:25</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-33.0461516, -71.4201666</t>
+          <t>-32.838367, -70.955739</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-33.04615, -71.42017</t>
+          <t>-32.83837, -70.95574</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>02:00:25</t>
+          <t>00:40:08</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>10.39</v>
+        <v>6.25</v>
       </c>
       <c r="M92" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N92" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/13 18:25:37</t>
+          <t>2026/07/14 20:50:47</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.3893, -70.6740366</t>
+          <t>-32.838363, -70.95554</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.38930, -70.67404</t>
+          <t>-32.83836, -70.95554</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/13 19:12:56</t>
+          <t>2026/07/15 08:50:12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.476265, -70.6983516</t>
+          <t>-32.838373, -70.955507</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69835</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:47:19</t>
+          <t>11:59:25</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>13.57</v>
+        <v>1.34</v>
       </c>
       <c r="M93" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="N93" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/13 18:39:35</t>
+          <t>2026/07/15 09:10:55</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-32.8794099, -70.6088433</t>
+          <t>-33.360084, -70.806489</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-32.87941, -70.60884</t>
+          <t>-33.36008, -70.80649</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/13 19:14:47</t>
+          <t>2026/07/15 12:52:16</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-32.8791466, -70.6092666</t>
+          <t>-33.360003, -70.807175</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-32.87915, -70.60927</t>
+          <t>-33.36000, -70.80718</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>00:35:12</t>
+          <t>03:41:21</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="M94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/13 18:40:01</t>
+          <t>2026/07/15 13:53:23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8871099</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88711</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/13 19:35:24</t>
+          <t>2026/07/15 17:34:48</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-32.7832683, -70.8549766</t>
+          <t>-32.840932, -70.957233</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-32.78327, -70.85498</t>
+          <t>-32.84093, -70.95723</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:55:23</t>
+          <t>03:41:25</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.86</v>
+        <v>0.5</v>
       </c>
       <c r="M95" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="N95" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/13 18:48:42</t>
+          <t>2026/07/15 14:43:03</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-33.436315, -70.6293299</t>
+          <t>-33.3604783, -70.8090416</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-33.43632, -70.62933</t>
+          <t>-33.36048, -70.80904</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/13 19:31:57</t>
+          <t>2026/07/15 15:29:09</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-33.466985, -70.6068116</t>
+          <t>-33.3895116, -70.6738666</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-33.46699, -70.60681</t>
+          <t>-33.38951, -70.67387</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:43:15</t>
+          <t>00:46:06</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>5.39</v>
+        <v>17.34</v>
       </c>
       <c r="M96" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="N96" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/07/13 18:51:42</t>
+          <t>2026/07/15 15:29:42</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-32.838369, -70.955496</t>
+          <t>-33.3893049, -70.6740016</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95550</t>
+          <t>-33.38930, -70.67400</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:29</t>
+          <t>2026/07/15 16:07:40</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-32.839555, -70.954478</t>
+          <t>-33.3654, -70.6799283</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-32.83955, -70.95448</t>
+          <t>-33.36540, -70.67993</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>01:03:47</t>
+          <t>00:37:58</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>21.01</v>
+        <v>3.65</v>
       </c>
       <c r="M97" t="n">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="N97" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,44 +6091,44 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/13 18:54:41</t>
+          <t>2026/07/15 16:08:55</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-32.7433, -70.7327583</t>
+          <t>-33.3653549, -70.6799433</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-32.74330, -70.73276</t>
+          <t>-33.36535, -70.67994</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/13 19:59:23</t>
+          <t>2026/07/15 16:59:15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.7430866, -70.7297566</t>
+          <t>-33.362085, -70.6701533</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.74309, -70.72976</t>
+          <t>-33.36209, -70.67015</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>01:04:42</t>
+          <t>00:50:20</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="M98" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N98" t="n">
         <v>15</v>
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/13 19:14:11</t>
+          <t>2026/07/15 16:59:50</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-33.4761233, -70.6985316</t>
+          <t>-33.3621033, -70.6702233</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69853</t>
+          <t>-33.36210, -70.67022</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/14 10:54:23</t>
+          <t>2026/07/15 20:07:09</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-34.2054066, -70.67967</t>
+          <t>-33.3895, -70.6736916</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67967</t>
+          <t>-33.38950, -70.67369</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>15:40:12</t>
+          <t>03:07:19</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>126.75</v>
+        <v>4.04</v>
       </c>
       <c r="M99" t="n">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="N99" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/13 19:15:19</t>
+          <t>2026/07/15 17:35:34</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088066</t>
+          <t>-32.840585, -70.958909</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-32.84058, -70.95891</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/14 09:00:09</t>
+          <t>2026/07/15 17:50:02</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-34.2055083, -70.6783166</t>
+          <t>-32.840682, -70.959202</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67832</t>
+          <t>-32.84068, -70.95920</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>13:44:50</t>
+          <t>00:14:28</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>164.8</v>
+        <v>0.39</v>
       </c>
       <c r="M100" t="n">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="N100" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/13 19:33:12</t>
+          <t>2026/07/15 17:50:15</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.4670566, -70.6068533</t>
+          <t>-32.84104, -70.959322</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.46706, -70.60685</t>
+          <t>-32.84104, -70.95932</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/13 21:01:57</t>
+          <t>2026/07/15 18:32:27</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.44084, -70.6303416</t>
+          <t>-32.84017, -70.960969</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.44084, -70.63034</t>
+          <t>-32.84017, -70.96097</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>01:28:45</t>
+          <t>00:42:12</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.58</v>
+        <v>21.07</v>
       </c>
       <c r="M101" t="n">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="N101" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/13 19:35:28</t>
+          <t>2026/07/15 18:32:49</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.7832333, -70.85493</t>
+          <t>-32.840415, -70.960116</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.78323, -70.85493</t>
+          <t>-32.84042, -70.96012</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:29</t>
+          <t>2026/07/15 19:09:21</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871633</t>
+          <t>-32.838369, -70.956136</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88716</t>
+          <t>-32.83837, -70.95614</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:20:01</t>
+          <t>00:36:32</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.72</v>
+        <v>0.97</v>
       </c>
       <c r="M102" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="N102" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/13 19:49:28</t>
+          <t>2026/07/15 18:38:03</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.0461283, -71.4200833</t>
+          <t>-32.7917783, -70.872935</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.04613, -71.42008</t>
+          <t>-32.79178, -70.87293</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/13 20:28:02</t>
+          <t>2026/07/15 19:19:22</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.08734, -71.3622683</t>
+          <t>-32.7977149, -70.88742</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36227</t>
+          <t>-32.79771, -70.88742</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:38:34</t>
+          <t>00:41:19</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>10.28</v>
+        <v>1.7</v>
       </c>
       <c r="M103" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="N103" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,47 +6445,47 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/13 19:55:48</t>
+          <t>2026/07/15 18:55:01</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.7976016, -70.887115</t>
+          <t>-33.479699, -70.758226</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88711</t>
+          <t>-33.47970, -70.75823</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/14 08:40:37</t>
+          <t>2026/07/15 20:02:31</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.682345</t>
+          <t>-32.838758, -70.954109</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68234</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>12:44:49</t>
+          <t>01:07:30</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>190.85</v>
+        <v>95.33</v>
       </c>
       <c r="M104" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="N104" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="105">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/13 19:56:09</t>
+          <t>2026/07/15 19:10:01</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.838872, -70.954156</t>
+          <t>-32.838366, -70.955481</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.83887, -70.95416</t>
+          <t>-32.83837, -70.95548</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/13 20:25:16</t>
+          <t>2026/07/16 14:53:29</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.838364, -70.955496</t>
+          <t>-32.840584, -70.99572</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95550</t>
+          <t>-32.84058, -70.99572</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>00:29:07</t>
+          <t>19:43:28</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0.51</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M105" t="n">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="N105" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/13 19:59:32</t>
+          <t>2026/07/15 19:20:18</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.7430283, -70.7297866</t>
+          <t>-32.797605, -70.8870916</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72979</t>
+          <t>-32.79760, -70.88709</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/14 08:15:13</t>
+          <t>2026/07/16 10:28:18</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.3598283, -70.806785</t>
+          <t>-32.7976766, -70.88739</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.35983, -70.80679</t>
+          <t>-32.79768, -70.88739</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>12:15:41</t>
+          <t>15:08:00</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>90</v>
+        <v>13.03</v>
       </c>
       <c r="M106" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="N106" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/13 20:25:42</t>
+          <t>2026/07/15 19:46:53</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.838362, -70.955504</t>
+          <t>-33.4643833, -70.60761</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95550</t>
+          <t>-33.46438, -70.60761</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/14 08:45:39</t>
+          <t>2026/07/15 21:21:21</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.838372, -70.955582</t>
+          <t>-33.44062, -70.6302983</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95558</t>
+          <t>-33.44062, -70.63030</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>12:19:57</t>
+          <t>01:34:28</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.36</v>
+        <v>4.5</v>
       </c>
       <c r="M107" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="N107" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,57 +6681,57 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/13 20:29:15</t>
+          <t>2026/07/15 20:02:41</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-33.0873083, -71.3623783</t>
+          <t>-32.838757, -70.954109</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36238</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/14 07:46:35</t>
+          <t>2026/07/15 21:31:52</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-33.0868883, -71.3619016</t>
+          <t>-32.841759, -70.936896</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-33.08689, -71.36190</t>
+          <t>-32.84176, -70.93690</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>11:17:20</t>
+          <t>01:29:11</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>14</v>
+        <v>2.27</v>
       </c>
       <c r="M108" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="N108" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,57 +6740,57 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/13 21:02:13</t>
+          <t>2026/07/15 20:07:32</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-33.440555, -70.63033</t>
+          <t>-33.38955, -70.6736383</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-33.44056, -70.63033</t>
+          <t>-33.38955, -70.67364</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/13 21:24:44</t>
+          <t>2026/07/15 20:50:24</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-33.4362516, -70.629595</t>
+          <t>-33.476245, -70.6983</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-33.43625, -70.62959</t>
+          <t>-33.47624, -70.69830</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:22:31</t>
+          <t>00:42:52</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.72</v>
+        <v>13.57</v>
       </c>
       <c r="M109" t="n">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="N109" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,106 +6799,106 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/13 21:25:42</t>
+          <t>2026/07/15 20:51:39</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-33.4364766, -70.6295866</t>
+          <t>-33.4761616, -70.698455</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-33.43648, -70.62959</t>
+          <t>-33.47616, -70.69845</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/14 10:57:49</t>
+          <t>2026/07/17 10:16:04</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-33.3661216, -70.6955083</t>
+          <t>-33.3621016, -70.67012</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-33.36612, -70.69551</t>
+          <t>-33.36210, -70.67012</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>13:32:07</t>
+          <t>37:24:25</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>13.47</v>
+        <v>18.78</v>
       </c>
       <c r="M110" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="N110" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:17</t>
+          <t>2026/07/15 21:21:52</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.359942, -70.807084</t>
+          <t>-33.4406216, -70.6302316</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80708</t>
+          <t>-33.44062, -70.63023</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/14 12:02:22</t>
+          <t>2026/07/15 21:40:14</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-33.360005, -70.806977</t>
+          <t>-33.43623, -70.6295066</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80698</t>
+          <t>-33.43623, -70.62951</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:38:05</t>
+          <t>00:18:22</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.04</v>
+        <v>0.74</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="N111" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112">
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,57 +6917,57 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/14 15:10:31</t>
+          <t>2026/07/15 21:32:18</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-33.360105, -70.806689</t>
+          <t>-32.841741, -70.936882</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80669</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/14 18:47:39</t>
+          <t>2026/07/16 11:02:40</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-33.482123, -70.765334</t>
+          <t>-32.840636, -70.958522</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-33.48212, -70.76533</t>
+          <t>-32.84064, -70.95852</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>03:37:08</t>
+          <t>13:30:22</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>19.34</v>
+        <v>2.86</v>
       </c>
       <c r="M112" t="n">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="N112" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6976,116 +6976,116 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/07/14 18:48:33</t>
+          <t>2026/07/15 21:41:29</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.482178, -70.764895</t>
+          <t>-33.4364349, -70.6291566</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76489</t>
+          <t>-33.43643, -70.62916</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/15 08:54:52</t>
+          <t>2026/07/17 13:33:27</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.359961, -70.806992</t>
+          <t>-33.428385, -70.6207366</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80699</t>
+          <t>-33.42838, -70.62074</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>14:06:19</t>
+          <t>39:51:58</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>22.72</v>
+        <v>1.5</v>
       </c>
       <c r="M113" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="N113" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/15 12:52:32</t>
+          <t>2026/07/17 16:21:04</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.360034, -70.807127</t>
+          <t>-33.3671066, -70.6958466</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80713</t>
+          <t>-33.36711, -70.69585</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/15 15:16:50</t>
+          <t>2026/07/17 16:50:18</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.360008, -70.807123</t>
+          <t>-33.368485, -70.6971799</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80712</t>
+          <t>-33.36848, -70.69718</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>02:24:18</t>
+          <t>00:29:14</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/15 14:43:03</t>
+          <t>2026/07/17 16:51:20</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.3604783, -70.8090416</t>
+          <t>-33.3665833, -70.6954649</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.36048, -70.80904</t>
+          <t>-33.36658, -70.69546</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:09</t>
+          <t>2026/07/17 17:48:13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.3895116, -70.6738666</t>
+          <t>-33.4358716, -70.6300966</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.38951, -70.67387</t>
+          <t>-33.43587, -70.63010</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:46:06</t>
+          <t>00:56:53</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>17.34</v>
+        <v>13.29</v>
       </c>
       <c r="M115" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="N115" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,57 +7153,57 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/15 15:16:58</t>
+          <t>2026/07/17 17:49:25</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-33.36003, -70.807124</t>
+          <t>-33.43628, -70.629375</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80712</t>
+          <t>-33.43628, -70.62937</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/19 11:57:32</t>
+          <t>2026/07/19 15:13:00</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-33.360197, -70.807434</t>
+          <t>-33.4296566, -70.6486349</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-33.36020, -70.80743</t>
+          <t>-33.42966, -70.64863</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>92:40:34</t>
+          <t>45:23:35</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.21</v>
       </c>
       <c r="M116" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="N116" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,470 +7212,470 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:42</t>
+          <t>2026/07/18 10:37:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-33.3893049, -70.6740016</t>
+          <t>-33.55173, -70.8447033</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-33.38930, -70.67400</t>
+          <t>-33.55173, -70.84470</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/15 16:07:40</t>
+          <t>2026/07/18 11:41:27</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-33.3654, -70.6799283</t>
+          <t>-33.3671116, -70.6954666</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-33.36540, -70.67993</t>
+          <t>-33.36711, -70.69547</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:37:58</t>
+          <t>01:04:27</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.65</v>
+        <v>35.8</v>
       </c>
       <c r="M117" t="n">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="N117" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/07/15 16:08:55</t>
+          <t>2026/07/18 11:42:39</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-33.3653549, -70.6799433</t>
+          <t>-33.3671433, -70.6958149</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-33.36535, -70.67994</t>
+          <t>-33.36714, -70.69581</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:15</t>
+          <t>2026/07/20 21:42:39</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-33.362085, -70.6701533</t>
+          <t>-33.3671433, -70.6958149</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67015</t>
+          <t>-33.36714, -70.69581</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:50:20</t>
+          <t>58:00:00</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:50</t>
+          <t>2026/07/20 02:39:25</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-33.3621033, -70.6702233</t>
+          <t>-33.367076, -70.696346</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67022</t>
+          <t>-33.36708, -70.69635</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:09</t>
+          <t>2026/07/20 21:39:03</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.3895, -70.6736916</t>
+          <t>-33.367076, -70.696346</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.38950, -70.67369</t>
+          <t>-33.36708, -70.69635</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>03:07:19</t>
+          <t>18:59:38</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/15 17:04:13</t>
+          <t>2026/07/20 13:58:00</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.482171, -70.764904</t>
+          <t>-33.087305, -71.362325</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.48217, -70.76490</t>
+          <t>-33.08731, -71.36232</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/15 18:54:01</t>
+          <t>2026/07/20 21:28:49</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.480734, -70.760036</t>
+          <t>-33.0872533, -71.36223</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.48073, -70.76004</t>
+          <t>-33.08725, -71.36223</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>01:49:48</t>
+          <t>07:30:49</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.51</v>
+        <v>0.01</v>
       </c>
       <c r="M120" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/15 18:32:49</t>
+          <t>2026/07/20 14:02:11</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-32.840415, -70.960116</t>
+          <t>-32.7976249, -70.8870866</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-32.84042, -70.96012</t>
+          <t>-32.79762, -70.88709</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/15 19:09:21</t>
+          <t>2026/07/20 22:02:11</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-32.838369, -70.956136</t>
+          <t>-32.7976249, -70.8870866</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95614</t>
+          <t>-32.79762, -70.88709</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:36:32</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C122" t="n">
+        <v>9</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026/07/20 16:17:45</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-32.7432399, -70.7296166</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-32.74324, -70.72962</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026/07/20 17:05:10</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-32.7443383, -70.7300983</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-32.74434, -70.73010</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>00:47:25</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M122" t="n">
+        <v>24</v>
+      </c>
+      <c r="N122" t="n">
         <v>13</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2026/07/15 18:55:01</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-33.479699, -70.758226</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-33.47970, -70.75823</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2026/07/15 20:02:31</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-32.838758, -70.954109</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-32.83876, -70.95411</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>01:07:30</t>
-        </is>
-      </c>
-      <c r="L122" t="n">
-        <v>95.33</v>
-      </c>
-      <c r="M122" t="n">
-        <v>136</v>
-      </c>
-      <c r="N122" t="n">
-        <v>86</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/15 19:10:01</t>
+          <t>2026/07/20 16:30:53</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.838366, -70.955481</t>
+          <t>-33.4761683, -70.6984416</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95548</t>
+          <t>-33.47617, -70.69844</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/16 14:53:29</t>
+          <t>2026/07/20 22:31:00</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.840584, -70.99572</t>
+          <t>-33.4761683, -70.6984416</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.84058, -70.99572</t>
+          <t>-33.47617, -70.69844</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>19:43:28</t>
+          <t>06:00:07</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>8.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/15 19:20:18</t>
+          <t>2026/07/20 16:56:39</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870916</t>
+          <t>-33.482176, -70.764889</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88709</t>
+          <t>-33.48218, -70.76489</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/16 10:28:18</t>
+          <t>2026/07/20 22:00:00</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.7976766, -70.88739</t>
+          <t>-33.482176, -70.764889</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.79768, -70.88739</t>
+          <t>-33.48218, -70.76489</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>15:08:00</t>
+          <t>05:03:21</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>13.03</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,813 +7684,164 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/15 20:02:41</t>
+          <t>2026/07/20 17:05:47</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-32.838757, -70.954109</t>
+          <t>-32.7432966, -70.7327783</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-32.83876, -70.95411</t>
+          <t>-32.74330, -70.73278</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/15 21:31:52</t>
+          <t>2026/07/20 19:38:49</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-32.841759, -70.936896</t>
+          <t>-32.7431749, -70.72968</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-32.84176, -70.93690</t>
+          <t>-32.74317, -70.72968</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>01:29:11</t>
+          <t>02:33:02</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.27</v>
+        <v>0.44</v>
       </c>
       <c r="M125" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N125" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:32</t>
+          <t>2026/07/20 19:40:04</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.38955, -70.6736383</t>
+          <t>-32.7431333, -70.72971</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.38955, -70.67364</t>
+          <t>-32.74313, -70.72971</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/15 20:50:24</t>
+          <t>2026/07/20 21:40:29</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.476245, -70.6983</t>
+          <t>-32.743045, -70.7297683</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69830</t>
+          <t>-32.74305, -70.72977</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>00:42:52</t>
+          <t>02:00:25</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>13.57</v>
+        <v>0.01</v>
       </c>
       <c r="M126" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/07/15 20:51:39</t>
+          <t>2026/07/20 20:16:20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-33.4761616, -70.698455</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69845</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/17 10:16:04</t>
+          <t>2026/07/20 22:16:20</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-33.3621016, -70.67012</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67012</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>37:24:25</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>18.78</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>15</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026/07/15 21:32:18</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-32.841741, -70.936882</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-32.84174, -70.93688</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2026/07/16 11:02:40</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-32.840636, -70.958522</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-32.84064, -70.95852</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>13:30:22</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M128" t="n">
-        <v>33</v>
-      </c>
-      <c r="N128" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>9</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026/07/17 17:49:25</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.629375</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-33.43628, -70.62937</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2026/07/19 15:13:00</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-33.4296566, -70.6486349</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-33.42966, -70.64863</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>45:23:35</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="M129" t="n">
-        <v>60</v>
-      </c>
-      <c r="N129" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>OPEL COMBO</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>2</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2026/07/18 10:37:00</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-33.55173, -70.8447033</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-33.55173, -70.84470</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>2026/07/18 11:41:27</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-33.3671116, -70.6954666</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>-33.36711, -70.69547</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>01:04:27</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="M130" t="n">
-        <v>127</v>
-      </c>
-      <c r="N130" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>OPEL COMBO</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>3</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026/07/18 11:42:39</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-33.3671433, -70.6958149</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-33.36714, -70.69581</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>2026/07/19 23:42:39</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-33.3671433, -70.6958149</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-33.36714, -70.69581</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>36:00:00</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2026/07/19 14:16:44</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-32.7430883, -70.7297416</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-32.74309, -70.72974</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>2026/07/19 22:22:46</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-32.7430183, -70.7298083</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>-32.74302, -70.72981</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>08:06:02</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>2</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026/07/19 15:52:39</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-33.4362749, -70.6294183</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-33.43627, -70.62942</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>2026/07/19 23:55:08</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-33.4363066, -70.62936</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>-33.43631, -70.62936</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>08:02:29</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>2</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026/07/19 19:23:15</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-33.08722, -71.3622533</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-33.08722, -71.36225</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2026/07/19 23:24:58</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-33.08722, -71.3622533</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-33.08722, -71.36225</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>04:01:43</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>4</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026/07/19 20:08:51</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-33.47616, -70.6984166</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-33.47616, -70.69842</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2026/07/19 22:08:51</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-33.47616, -70.6984166</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-33.47616, -70.69842</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>4</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026/07/19 20:10:55</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-32.797605, -70.8871183</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-32.79760, -70.88712</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2026/07/19 22:10:55</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-32.797605, -70.8871183</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-32.79760, -70.88712</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>3</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026/07/19 21:07:02</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-32.838361, -70.955532</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-32.83836, -70.95553</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2026/07/19 23:04:41</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-32.838361, -70.955532</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-32.83836, -70.95553</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>01:57:39</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>6</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026/07/19 22:06:31</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-32.841676, -70.936812</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-32.84168, -70.93681</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2026/07/19 23:09:32</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-32.841676, -70.936812</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-32.84168, -70.93681</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>01:03:01</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8542,10 +7893,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1301.72</v>
+        <v>1187.64</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8561,16 +7912,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>381.35</v>
+        <v>325.5</v>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
@@ -8580,10 +7931,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>659.99</v>
+        <v>410.86</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8599,10 +7950,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>559.9400000000001</v>
+        <v>592.24</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -8637,16 +7988,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -8770,16 +8121,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>843.55</v>
+        <v>691.37</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
@@ -8789,16 +8140,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>220.43</v>
+        <v>235.3</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -8846,13 +8197,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.09</v>
+        <v>0.38</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
@@ -8865,13 +8216,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>853.47</v>
+        <v>535.0599999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>141</v>
@@ -8884,10 +8235,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>452.86</v>
+        <v>466.87</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/20 22:01:40</t>
+          <t>2026/07/20 23:01:20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>165:59:17</t>
+          <t>166:58:57</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/20 22:11:25</t>
+          <t>2026/07/20 23:11:39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>165:58:59</t>
+          <t>166:59:13</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/20 22:13:14</t>
+          <t>2026/07/20 23:13:31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>165:59:53</t>
+          <t>167:00:10</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/20 22:24:57</t>
+          <t>2026/07/20 23:24:01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:01:49</t>
+          <t>167:00:53</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/20 21:31:51</t>
+          <t>2026/07/20 23:32:12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>165:00:13</t>
+          <t>167:00:34</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/20 21:34:24</t>
+          <t>2026/07/20 23:34:52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>164:59:32</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/20 21:56:10</t>
+          <t>2026/07/20 23:56:10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>165:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/20 21:57:31</t>
+          <t>2026/07/20 23:57:38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>164:58:22</t>
+          <t>166:58:29</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/20 21:42:39</t>
+          <t>2026/07/20 23:42:39</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>58:00:00</t>
+          <t>60:00:00</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/20 21:39:03</t>
+          <t>2026/07/20 23:39:23</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18:59:38</t>
+          <t>20:59:58</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/20 21:28:49</t>
+          <t>2026/07/20 23:28:49</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>07:30:49</t>
+          <t>09:30:49</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/20 22:00:00</t>
+          <t>2026/07/20 23:00:03</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>05:03:21</t>
+          <t>06:03:24</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/20 21:40:29</t>
+          <t>2026/07/20 23:40:29</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>02:00:25</t>
+          <t>04:00:25</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7842,6 +7842,65 @@
         <v>0</v>
       </c>
       <c r="N127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>5</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026/07/20 20:35:17</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-33.4371483, -70.6294466</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-33.43715, -70.62945</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026/07/20 22:36:07</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-33.43715, -70.629445</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-33.43715, -70.62945</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>02:00:50</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7912,7 +7971,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>325.5</v>
+        <v>339.69</v>
       </c>
       <c r="C3" t="n">
         <v>34</v>
@@ -8140,13 +8199,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235.3</v>
+        <v>235.14</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>120</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/14 04:00:00   Hasta : 2026/07/21 03:59:59</t>
+          <t>Desde : 2026/07/15 04:00:00   Hasta : 2026/07/22 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/07/14 00:02:23</t>
+          <t>2026/07/15 00:01:37</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.346035, -71.125736</t>
+          <t>-34.345993, -71.125803</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-34.34604, -71.12574</t>
+          <t>-34.34599, -71.12580</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/20 23:01:20</t>
+          <t>2026/07/21 22:01:21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,11 +575,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>166:58:57</t>
+          <t>165:59:44</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,58 +599,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/07/14 00:12:26</t>
+          <t>2026/07/15 00:03:55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.205228, -70.67741</t>
+          <t>-33.4761049, -70.6985133</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.20523, -70.67741</t>
+          <t>-33.47610, -70.69851</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/20 23:11:39</t>
+          <t>2026/07/15 09:20:02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.205371, -70.677398</t>
+          <t>-33.4762616, -70.6983149</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67740</t>
+          <t>-33.47626, -70.69831</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>166:59:13</t>
+          <t>09:16:07</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,41 +663,41 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/07/14 00:13:21</t>
+          <t>2026/07/15 00:11:28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-33.359984, -70.807055</t>
+          <t>-34.205492, -70.677259</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80706</t>
+          <t>-34.20549, -70.67726</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/20 23:13:31</t>
+          <t>2026/07/21 22:11:23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.360034, -70.807056</t>
+          <t>-34.205371, -70.677398</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80706</t>
+          <t>-34.20537, -70.67740</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>167:00:10</t>
+          <t>165:59:55</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -722,47 +722,47 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/07/14 00:19:47</t>
+          <t>2026/07/15 00:13:21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.360054, -70.807138</t>
+          <t>-33.360017, -70.807084</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80714</t>
+          <t>-33.36002, -70.80708</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:00</t>
+          <t>2026/07/21 22:13:39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.359965, -70.807053</t>
+          <t>-33.360034, -70.807056</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.35997, -70.80705</t>
+          <t>-33.36003, -70.80706</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11:04:13</t>
+          <t>166:00:18</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -781,22 +781,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/07/14 00:23:08</t>
+          <t>2026/07/15 00:26:12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.876427, -71.127258</t>
+          <t>-34.87625, -71.127289</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12726</t>
+          <t>-34.87625, -71.12729</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/20 23:24:01</t>
+          <t>2026/07/21 22:24:37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>167:00:53</t>
+          <t>165:58:25</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/07/14 00:23:12</t>
+          <t>2026/07/15 00:26:27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-32.838362, -70.955504</t>
+          <t>-33.3601, -70.807159</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95550</t>
+          <t>-33.36010, -70.80716</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/14 08:45:39</t>
+          <t>2026/07/15 09:10:23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-32.838372, -70.955582</t>
+          <t>-33.360117, -70.806631</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95558</t>
+          <t>-33.36012, -70.80663</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>08:22:27</t>
+          <t>08:43:56</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/07/14 00:29:15</t>
+          <t>2026/07/15 00:31:21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.0873083, -71.3623783</t>
+          <t>-33.899781, -71.42949</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36238</t>
+          <t>-33.89978, -71.42949</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/14 07:46:35</t>
+          <t>2026/07/21 21:31:51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.0868883, -71.3619016</t>
+          <t>-33.899813, -71.429474</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.08689, -71.36190</t>
+          <t>-33.89981, -71.42947</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>07:17:20</t>
+          <t>165:00:30</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>0.02</v>
       </c>
       <c r="M10" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,52 +953,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/07/14 00:31:38</t>
+          <t>2026/07/15 00:33:04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-33.899812, -71.429505</t>
+          <t>-33.0872416, -71.3622349</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-33.89981, -71.42951</t>
+          <t>-33.08724, -71.36223</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/20 23:32:12</t>
+          <t>2026/07/15 08:27:37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.899813, -71.429474</t>
+          <t>-33.0872683, -71.3623066</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.89981, -71.42947</t>
+          <t>-33.08727, -71.36231</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>167:00:34</t>
+          <t>07:54:33</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>0.02</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/07/14 00:34:52</t>
+          <t>2026/07/15 00:35:04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-34.579681, -70.961483</t>
+          <t>-34.579616, -70.961324</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96148</t>
+          <t>-34.57962, -70.96132</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/20 23:34:52</t>
+          <t>2026/07/21 21:34:57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,11 +1047,11 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>167:00:00</t>
+          <t>164:59:53</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/07/14 00:41:06</t>
+          <t>2026/07/15 00:41:32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.3674, -70.696184</t>
+          <t>-33.365999, -70.696202</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69618</t>
+          <t>-33.36600, -70.69620</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1106,11 +1106,11 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>145:00:30</t>
+          <t>121:00:04</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
@@ -1122,7 +1122,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/07/14 00:48:22</t>
+          <t>2026/07/15 00:43:26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.482188, -70.764925</t>
+          <t>-32.8792233, -70.6087466</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.48219, -70.76493</t>
+          <t>-32.87922, -70.60875</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/14 09:05:33</t>
+          <t>2026/07/15 09:00:26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.359932, -70.806898</t>
+          <t>-33.36727, -70.6965783</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.35993, -70.80690</t>
+          <t>-33.36727, -70.69658</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>08:17:11</t>
+          <t>08:17:00</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>25.07</v>
+        <v>72.78</v>
       </c>
       <c r="M14" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="N14" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/07/14 00:56:10</t>
+          <t>2026/07/15 00:48:19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.838363, -70.95554</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.83836, -70.95554</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/20 23:56:10</t>
+          <t>2026/07/15 08:50:12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-32.838373, -70.955507</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>167:00:00</t>
+          <t>08:01:53</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,58 +1248,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/07/14 00:59:09</t>
+          <t>2026/07/15 00:51:39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-34.042641, -70.681549</t>
+          <t>-33.482178, -70.764895</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-34.04264, -70.68155</t>
+          <t>-33.48218, -70.76489</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/20 23:57:38</t>
+          <t>2026/07/15 08:54:52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.042665, -70.681704</t>
+          <t>-33.359961, -70.806992</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68170</t>
+          <t>-33.35996, -70.80699</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:58:29</t>
+          <t>08:03:13</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.05</v>
+        <v>22.72</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,58 +1307,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/07/14 01:02:21</t>
+          <t>2026/07/15 00:56:11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.3672816, -70.69573</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69573</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/18 09:59:20</t>
+          <t>2026/07/21 21:56:10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.4640433, -70.6511716</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.46404, -70.65117</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>104:56:59</t>
+          <t>164:59:59</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/07/14 01:14:34</t>
+          <t>2026/07/15 00:57:46</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.4761233, -70.6985316</t>
+          <t>-34.042558, -70.6817</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69853</t>
+          <t>-34.04256, -70.68170</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/14 10:54:23</t>
+          <t>2026/07/21 21:57:22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-34.2054066, -70.67967</t>
+          <t>-34.042665, -70.681704</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67967</t>
+          <t>-34.04266, -70.68170</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>09:39:49</t>
+          <t>164:59:36</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>126.75</v>
+        <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,47 +1430,47 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/07/14 01:15:19</t>
+          <t>2026/07/15 01:02:21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088066</t>
+          <t>-33.3672816, -70.69573</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/07/14 09:00:09</t>
+          <t>2026/07/18 09:59:20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-34.2055083, -70.6783166</t>
+          <t>-33.4640433, -70.6511716</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67832</t>
+          <t>-33.46404, -70.65117</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07:44:50</t>
+          <t>80:56:59</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>164.8</v>
+        <v>16.4</v>
       </c>
       <c r="M19" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="N19" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/07/14 01:25:42</t>
+          <t>2026/07/15 01:28:08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.4364766, -70.6295866</t>
+          <t>-33.4363716, -70.6292483</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.43648, -70.62959</t>
+          <t>-33.43637, -70.62925</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/07/14 10:57:49</t>
+          <t>2026/07/15 13:52:20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.3661216, -70.6955083</t>
+          <t>-33.36227, -70.8072283</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.36612, -70.69551</t>
+          <t>-33.36227, -70.80723</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>09:32:07</t>
+          <t>12:24:12</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>13.47</v>
+        <v>30.19</v>
       </c>
       <c r="M20" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N20" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/07/14 01:55:48</t>
+          <t>2026/07/15 01:29:22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-32.7976016, -70.887115</t>
+          <t>-32.7430316, -70.72976</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88711</t>
+          <t>-32.74303, -70.72976</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/07/14 08:40:37</t>
+          <t>2026/07/15 08:20:18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.682345</t>
+          <t>-33.3599466, -70.8069716</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68234</t>
+          <t>-33.35995, -70.80697</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06:44:49</t>
+          <t>06:50:56</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>190.85</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="N21" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,44 +1607,44 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/07/14 01:59:32</t>
+          <t>2026/07/15 01:43:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-32.7430283, -70.7297866</t>
+          <t>-32.7976083, -70.8870733</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72979</t>
+          <t>-32.79761, -70.88707</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/07/14 08:15:13</t>
+          <t>2026/07/15 08:48:07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.3598283, -70.806785</t>
+          <t>-33.3672366, -70.69658</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.35983, -70.80679</t>
+          <t>-33.36724, -70.69658</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06:15:41</t>
+          <t>07:04:37</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>90</v>
+        <v>100.46</v>
       </c>
       <c r="M22" t="n">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="N22" t="n">
         <v>59</v>
@@ -1653,7 +1653,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/07/14 07:47:11</t>
+          <t>2026/07/15 08:20:26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.0872933, -71.3623533</t>
+          <t>-33.3599416, -70.8071683</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36235</t>
+          <t>-33.35994, -70.80717</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/07/14 09:08:37</t>
+          <t>2026/07/15 15:29:07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.0977283, -71.3297633</t>
+          <t>-33.3604333, -70.8062016</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.09773, -71.32976</t>
+          <t>-33.36043, -70.80620</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>01:21:26</t>
+          <t>07:08:41</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.14</v>
+        <v>0.11</v>
       </c>
       <c r="M23" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="N23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1725,47 +1725,47 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/07/14 08:15:28</t>
+          <t>2026/07/15 08:27:55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.3599533, -70.8071933</t>
+          <t>-33.0872633, -71.3623216</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80719</t>
+          <t>-33.08726, -71.36232</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/07/14 12:08:28</t>
+          <t>2026/07/15 10:08:47</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.3613949, -70.8066633</t>
+          <t>-33.3631583, -70.78624</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.36139, -70.80666</t>
+          <t>-33.36316, -70.78624</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>03:53:00</t>
+          <t>01:40:52</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
+        <v>111.79</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
@@ -1784,47 +1784,47 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/07/14 08:41:52</t>
+          <t>2026/07/15 08:48:19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-34.20538, -70.680535</t>
+          <t>-33.3672116, -70.69669</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-34.20538, -70.68054</t>
+          <t>-33.36721, -70.69669</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/07/14 09:11:06</t>
+          <t>2026/07/15 10:22:48</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.2053583, -70.6805233</t>
+          <t>-33.40075, -70.9780633</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.20536, -70.68052</t>
+          <t>-33.40075, -70.97806</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>00:29:14</t>
+          <t>01:34:29</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.93</v>
+        <v>44.65</v>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="N25" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
@@ -1843,53 +1843,53 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/07/14 08:45:59</t>
+          <t>2026/07/15 08:50:48</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-32.838375, -70.955504</t>
+          <t>-32.838373, -70.955514</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95550</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/07/14 20:09:49</t>
+          <t>2026/07/15 12:05:12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-32.838789, -70.954119</t>
+          <t>-32.838511, -70.953947</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-32.83879, -70.95412</t>
+          <t>-32.83851, -70.95395</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11:23:50</t>
+          <t>03:14:24</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.36</v>
+        <v>1.32</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1902,53 +1902,53 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/07/14 09:00:25</t>
+          <t>2026/07/15 08:55:08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-34.205505, -70.67842</t>
+          <t>-33.359999, -70.807134</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67842</t>
+          <t>-33.36000, -70.80713</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/07/14 09:29:20</t>
+          <t>2026/07/15 10:58:55</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-34.205345, -70.6786333</t>
+          <t>-33.379708, -70.752618</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-34.20535, -70.67863</t>
+          <t>-33.37971, -70.75262</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:28:55</t>
+          <t>02:03:47</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.03</v>
+        <v>9.17</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1961,116 +1961,116 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/07/14 09:06:04</t>
+          <t>2026/07/15 09:00:40</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.359961, -70.8071</t>
+          <t>-33.3672566, -70.6967216</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80710</t>
+          <t>-33.36726, -70.69672</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/07/14 09:39:00</t>
+          <t>2026/07/15 15:10:17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.356611, -70.794937</t>
+          <t>-32.8792183, -70.6088933</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.35661, -70.79494</t>
+          <t>-32.87922, -70.60889</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:32:56</t>
+          <t>06:09:37</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.99</v>
+        <v>69.94</v>
       </c>
       <c r="M28" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="N28" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026/07/15 09:10:55</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-33.360084, -70.806489</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-33.36008, -70.80649</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026/07/15 12:52:16</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.360003, -70.807175</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-33.36000, -70.80718</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>03:41:21</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
         <v>3</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026/07/14 09:08:48</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-33.0976883, -71.329775</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-33.09769, -71.32977</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026/07/14 10:14:47</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-33.0878933, -71.362315</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-33.08789, -71.36231</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>01:05:59</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="M29" t="n">
-        <v>38</v>
-      </c>
-      <c r="N29" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,53 +2079,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/07/14 09:12:21</t>
+          <t>2026/07/15 09:20:13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-34.205505, -70.6783983</t>
+          <t>-33.4763183, -70.6983616</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67840</t>
+          <t>-33.47632, -70.69836</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/07/14 11:38:27</t>
+          <t>2026/07/15 10:10:47</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-34.20494, -70.6779266</t>
+          <t>-33.3673266, -70.6966966</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-34.20494, -70.67793</t>
+          <t>-33.36733, -70.69670</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02:26:06</t>
+          <t>00:50:34</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.17</v>
+        <v>25.81</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2138,53 +2138,53 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/07/14 09:30:11</t>
+          <t>2026/07/15 10:10:02</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-34.2048833, -70.67869</t>
+          <t>-33.3628299, -70.786655</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-34.20488, -70.67869</t>
+          <t>-33.36283, -70.78665</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/07/14 09:43:04</t>
+          <t>2026/07/15 10:34:20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-34.20538, -70.6801349</t>
+          <t>-33.3600333, -70.8068616</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-34.20538, -70.68013</t>
+          <t>-33.36003, -70.80686</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:12:53</t>
+          <t>00:24:18</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.2</v>
+        <v>3.04</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/07/14 09:39:15</t>
+          <t>2026/07/15 10:11:06</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.356611, -70.794936</t>
+          <t>-33.3672833, -70.6967016</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.35661, -70.79494</t>
+          <t>-33.36728, -70.69670</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/07/14 10:11:18</t>
+          <t>2026/07/15 10:48:20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.367269, -70.695886</t>
+          <t>-33.3601983, -70.8090583</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.36727, -70.69589</t>
+          <t>-33.36020, -70.80906</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:32:03</t>
+          <t>00:37:14</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10.48</v>
+        <v>15.06</v>
       </c>
       <c r="M32" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="N32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/07/14 09:44:19</t>
+          <t>2026/07/15 10:23:08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-34.2054733, -70.6784083</t>
+          <t>-33.4008216, -70.9785966</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67841</t>
+          <t>-33.40082, -70.97860</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/07/14 10:01:17</t>
+          <t>2026/07/15 12:35:36</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-34.2049233, -70.6780999</t>
+          <t>-33.4332916, -71.0299766</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-34.20492, -70.67810</t>
+          <t>-33.43329, -71.02998</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:16:58</t>
+          <t>02:12:28</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.19</v>
+        <v>7.12</v>
       </c>
       <c r="M33" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,53 +2315,53 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/07/14 10:01:46</t>
+          <t>2026/07/15 10:34:34</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-34.20488, -70.6787116</t>
+          <t>-33.360055, -70.8068033</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-34.20488, -70.67871</t>
+          <t>-33.36006, -70.80680</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/07/14 11:29:22</t>
+          <t>2026/07/15 10:49:08</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-34.2044666, -70.6794183</t>
+          <t>-33.3596316, -70.8089299</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-34.20447, -70.67942</t>
+          <t>-33.35963, -70.80893</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:27:36</t>
+          <t>00:14:34</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2374,47 +2374,47 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/07/14 10:12:15</t>
+          <t>2026/07/15 10:48:36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-33.367257, -70.695904</t>
+          <t>-33.3606066, -70.8091466</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-33.36726, -70.69590</t>
+          <t>-33.36061, -70.80915</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/07/14 10:50:21</t>
+          <t>2026/07/15 11:19:31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-33.37887, -70.68308</t>
+          <t>-33.360835, -70.80922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-33.37887, -70.68308</t>
+          <t>-33.36084, -70.80922</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:38:06</t>
+          <t>00:30:55</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.82</v>
+        <v>0.31</v>
       </c>
       <c r="M35" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N35" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/07/14 10:15:23</t>
+          <t>2026/07/15 10:50:23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.0878966, -71.3623366</t>
+          <t>-33.3607316, -70.8090416</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.08790, -71.36234</t>
+          <t>-33.36073, -70.80904</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/07/14 10:47:01</t>
+          <t>2026/07/15 11:42:56</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.0977366, -71.3297433</t>
+          <t>-33.3605233, -70.8088883</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.09774, -71.32974</t>
+          <t>-33.36052, -70.80889</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:31:38</t>
+          <t>00:52:33</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.94</v>
+        <v>0.04</v>
       </c>
       <c r="M36" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,53 +2492,53 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/07/14 10:47:28</t>
+          <t>2026/07/15 10:59:07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.0977533, -71.3297149</t>
+          <t>-33.379773, -70.752739</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.09775, -71.32971</t>
+          <t>-33.37977, -70.75274</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/07/14 11:30:29</t>
+          <t>2026/07/15 11:29:37</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.0885183, -71.3613133</t>
+          <t>-33.360122, -70.806601</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.08852, -71.36131</t>
+          <t>-33.36012, -70.80660</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:43:01</t>
+          <t>00:30:30</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.87</v>
+        <v>7.76</v>
       </c>
       <c r="M37" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="N37" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/07/14 10:50:41</t>
+          <t>2026/07/15 11:19:45</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-33.37885, -70.682995</t>
+          <t>-33.3608116, -70.8093016</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.37885, -70.68300</t>
+          <t>-33.36081, -70.80930</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/07/14 11:48:00</t>
+          <t>2026/07/15 11:47:33</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.367297, -70.69598</t>
+          <t>-33.3607833, -70.8091633</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69598</t>
+          <t>-33.36078, -70.80916</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:57:19</t>
+          <t>00:27:48</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.68</v>
+        <v>0.02</v>
       </c>
       <c r="M38" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="N38" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/07/14 10:54:42</t>
+          <t>2026/07/15 11:29:50</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-34.205495, -70.6784683</t>
+          <t>-33.360159, -70.806459</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-34.20549, -70.67847</t>
+          <t>-33.36016, -70.80646</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/07/14 11:47:27</t>
+          <t>2026/07/15 13:04:13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-34.2048816, -70.6785466</t>
+          <t>-33.353541, -70.799064</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-34.20488, -70.67855</t>
+          <t>-33.35354, -70.79906</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:52:45</t>
+          <t>01:34:23</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="N39" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,116 +2669,116 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/07/14 10:58:45</t>
+          <t>2026/07/15 11:43:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-33.3669933, -70.6955383</t>
+          <t>-33.3594333, -70.8091216</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-33.36699, -70.69554</t>
+          <t>-33.35943, -70.80912</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/07/14 19:26:41</t>
+          <t>2026/07/15 12:05:13</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-33.4358749, -70.6300383</t>
+          <t>-33.3594883, -70.8089766</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-33.43587, -70.63004</t>
+          <t>-33.35949, -70.80898</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>08:27:56</t>
+          <t>00:21:40</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>23.39</v>
+        <v>0.02</v>
       </c>
       <c r="M40" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/07/14 11:24:17</t>
+          <t>2026/07/15 11:48:48</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.359942, -70.807084</t>
+          <t>-33.3594116, -70.8090199</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80708</t>
+          <t>-33.35941, -70.80902</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/07/14 12:02:22</t>
+          <t>2026/07/15 11:54:06</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.360005, -70.806977</t>
+          <t>-33.3596266, -70.8091066</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.36001, -70.80698</t>
+          <t>-33.35963, -70.80911</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:38:05</t>
+          <t>00:05:18</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/07/14 11:29:26</t>
+          <t>2026/07/15 11:55:01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-34.2044466, -70.6793866</t>
+          <t>-33.3608416, -70.8092383</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-34.20445, -70.67939</t>
+          <t>-33.36084, -70.80924</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/07/14 11:44:44</t>
+          <t>2026/07/15 12:45:29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-34.204775, -70.6780999</t>
+          <t>-33.36081, -70.8091716</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-34.20477, -70.67810</t>
+          <t>-33.36081, -70.80917</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:15:18</t>
+          <t>00:50:28</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/07/14 11:31:44</t>
+          <t>2026/07/15 12:05:27</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-33.0879133, -71.3622983</t>
+          <t>-32.838742, -70.954083</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-33.08791, -71.36230</t>
+          <t>-32.83874, -70.95408</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/07/14 11:50:32</t>
+          <t>2026/07/15 12:27:51</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-33.044255, -71.3752933</t>
+          <t>-32.841076, -70.959164</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-33.04425, -71.37529</t>
+          <t>-32.84108, -70.95916</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:18:48</t>
+          <t>00:22:24</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5.54</v>
+        <v>1.97</v>
       </c>
       <c r="M43" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="N43" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/07/14 11:38:36</t>
+          <t>2026/07/15 12:06:28</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-34.2049466, -70.6780933</t>
+          <t>-33.3600683, -70.8090433</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-34.20495, -70.67809</t>
+          <t>-33.36007, -70.80904</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/07/14 11:46:48</t>
+          <t>2026/07/15 12:17:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-34.2048916, -70.6783983</t>
+          <t>-33.3612033, -70.8067766</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-34.20489, -70.67840</t>
+          <t>-33.36120, -70.80678</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:08:12</t>
+          <t>00:10:32</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="M44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/07/14 11:44:59</t>
+          <t>2026/07/15 12:17:39</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-34.205015, -70.6780983</t>
+          <t>-33.3600283, -70.8067983</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-34.20502, -70.67810</t>
+          <t>-33.36003, -70.80680</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/07/14 12:32:31</t>
+          <t>2026/07/15 13:09:17</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-34.2049566, -70.6781216</t>
+          <t>-33.4016883, -70.7491183</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-34.20496, -70.67812</t>
+          <t>-33.40169, -70.74912</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:47:32</t>
+          <t>00:51:38</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/07/14 11:47:54</t>
+          <t>2026/07/15 12:28:26</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-34.2048716, -70.67926</t>
+          <t>-32.841091, -70.959171</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-34.20487, -70.67926</t>
+          <t>-32.84109, -70.95917</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/07/14 13:32:36</t>
+          <t>2026/07/15 13:33:17</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-34.190165, -70.7093666</t>
+          <t>-32.840601, -70.958864</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-34.19017, -70.70937</t>
+          <t>-32.84060, -70.95886</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>01:44:42</t>
+          <t>01:04:51</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.48</v>
+        <v>1.65</v>
       </c>
       <c r="M46" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="N46" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/07/14 11:47:57</t>
+          <t>2026/07/15 12:36:51</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-34.2048699, -70.67917</t>
+          <t>-33.4314666, -71.0321216</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-34.20487, -70.67917</t>
+          <t>-33.43147, -71.03212</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/07/14 13:32:42</t>
+          <t>2026/07/15 12:56:35</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-34.1901233, -70.7093333</t>
+          <t>-33.4007449, -70.9780916</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-34.19012, -70.70933</t>
+          <t>-33.40074, -70.97809</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>01:44:45</t>
+          <t>00:19:44</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="M47" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="N47" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,116 +3141,116 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/07/14 11:48:13</t>
+          <t>2026/07/15 12:46:12</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.367289, -70.695964</t>
+          <t>-33.3594266, -70.8090983</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.36729, -70.69596</t>
+          <t>-33.35943, -70.80910</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/07/14 12:20:12</t>
+          <t>2026/07/15 13:17:25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.359933, -70.806779</t>
+          <t>-33.360825, -70.8092066</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.35993, -70.80678</t>
+          <t>-33.36082, -70.80921</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:31:59</t>
+          <t>00:31:13</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>14.81</v>
+        <v>0.17</v>
       </c>
       <c r="M48" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="N48" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/07/14 11:51:47</t>
+          <t>2026/07/15 12:52:32</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-33.0438766, -71.37526</t>
+          <t>-33.360034, -70.807127</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-33.04388, -71.37526</t>
+          <t>-33.36003, -70.80713</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/07/14 12:31:45</t>
+          <t>2026/07/15 15:16:50</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-33.0436233, -71.4166216</t>
+          <t>-33.360008, -70.807123</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-33.04362, -71.41662</t>
+          <t>-33.36001, -70.80712</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:39:58</t>
+          <t>02:24:18</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.19</v>
+        <v>0.03</v>
       </c>
       <c r="M49" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/07/14 12:03:21</t>
+          <t>2026/07/15 12:57:17</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.360075, -70.806905</t>
+          <t>-33.4008649, -70.9785866</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80691</t>
+          <t>-33.40086, -70.97859</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/07/14 12:25:04</t>
+          <t>2026/07/15 14:08:50</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.360001, -70.807087</t>
+          <t>-33.3672283, -70.6966383</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80709</t>
+          <t>-33.36723, -70.69664</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:21:43</t>
+          <t>01:11:33</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.19</v>
+        <v>47.39</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/07/14 12:08:39</t>
+          <t>2026/07/15 13:05:40</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-33.3615533, -70.80668</t>
+          <t>-33.35355, -70.799048</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-33.36155, -70.80668</t>
+          <t>-33.35355, -70.79905</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/07/14 12:16:57</t>
+          <t>2026/07/15 13:27:58</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.36014, -70.8064633</t>
+          <t>-33.401691, -70.749167</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.36014, -70.80646</t>
+          <t>-33.40169, -70.74917</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>00:08:18</t>
+          <t>00:22:18</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.26</v>
+        <v>8.4</v>
       </c>
       <c r="M51" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="N51" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/07/14 12:17:14</t>
+          <t>2026/07/15 13:09:57</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.3600349, -70.8066783</t>
+          <t>-33.4011416, -70.75044</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80668</t>
+          <t>-33.40114, -70.75044</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/07/14 14:49:58</t>
+          <t>2026/07/15 14:27:27</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.361315, -70.8068249</t>
+          <t>-33.3646816, -70.78415</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.36131, -70.80682</t>
+          <t>-33.36468, -70.78415</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>02:32:44</t>
+          <t>01:17:30</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.34</v>
+        <v>7.33</v>
       </c>
       <c r="M52" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,116 +3436,116 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/07/14 12:21:06</t>
+          <t>2026/07/15 13:18:40</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-33.360073, -70.806914</t>
+          <t>-33.3608049, -70.8092183</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80691</t>
+          <t>-33.36080, -70.80922</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/07/14 12:46:36</t>
+          <t>2026/07/15 13:37:32</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.353327, -70.799399</t>
+          <t>-33.3607883, -70.8091833</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.35333, -70.79940</t>
+          <t>-33.36079, -70.80918</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:25:30</t>
+          <t>00:18:52</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/07/14 12:25:25</t>
+          <t>2026/07/15 13:28:40</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.360082, -70.807131</t>
+          <t>-33.401191, -70.750368</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80713</t>
+          <t>-33.40119, -70.75037</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/07/15 09:10:23</t>
+          <t>2026/07/15 14:27:46</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.360117, -70.806631</t>
+          <t>-33.362488, -70.787099</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80663</t>
+          <t>-33.36249, -70.78710</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>20:44:58</t>
+          <t>00:59:06</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.09</v>
+        <v>8.75</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/07/14 12:33:00</t>
+          <t>2026/07/15 13:33:51</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.04356, -71.4166366</t>
+          <t>-32.84046, -70.959345</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.04356, -71.41664</t>
+          <t>-32.84046, -70.95934</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/07/14 13:02:22</t>
+          <t>2026/07/15 13:52:25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.044495, -71.42038</t>
+          <t>-32.838372, -70.955737</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.04449, -71.42038</t>
+          <t>-32.83837, -70.95574</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:29:22</t>
+          <t>00:18:34</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.89</v>
+        <v>2.71</v>
       </c>
       <c r="M55" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="N55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,57 +3613,57 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/07/14 12:33:04</t>
+          <t>2026/07/15 13:38:47</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-34.2049416, -70.6788416</t>
+          <t>-33.3594833, -70.8090233</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-34.20494, -70.67884</t>
+          <t>-33.35948, -70.80902</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/07/14 13:35:11</t>
+          <t>2026/07/15 13:45:21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-34.1900849, -70.70941</t>
+          <t>-33.3601616, -70.8083099</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-34.19008, -70.70941</t>
+          <t>-33.36016, -70.80831</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>01:02:07</t>
+          <t>00:06:34</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.53</v>
+        <v>0.13</v>
       </c>
       <c r="M56" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="N56" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/07/14 12:47:39</t>
+          <t>2026/07/15 13:46:36</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.35716, -70.79427</t>
+          <t>-33.3604683, -70.8083033</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.35716, -70.79427</t>
+          <t>-33.36047, -70.80830</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/07/14 13:05:42</t>
+          <t>2026/07/15 14:41:48</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.401738, -70.749146</t>
+          <t>-33.3612533, -70.8090166</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.40174, -70.74915</t>
+          <t>-33.36125, -70.80902</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:18:03</t>
+          <t>00:55:12</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.87</v>
+        <v>0.15</v>
       </c>
       <c r="M57" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="N57" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/07/14 13:03:13</t>
+          <t>2026/07/15 13:53:23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-33.0444983, -71.42037</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-33.04450, -71.42037</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/07/14 13:21:09</t>
+          <t>2026/07/15 17:34:48</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-33.0560066, -71.4270166</t>
+          <t>-32.840932, -70.957233</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-33.05601, -71.42702</t>
+          <t>-32.84093, -70.95723</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:17:56</t>
+          <t>03:41:25</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.11</v>
+        <v>0.5</v>
       </c>
       <c r="M58" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="N58" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/07/14 13:06:40</t>
+          <t>2026/07/15 13:53:35</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.401249, -70.750322</t>
+          <t>-33.3622516, -70.8075783</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.40125, -70.75032</t>
+          <t>-33.36225, -70.80758</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/07/14 14:08:30</t>
+          <t>2026/07/15 14:05:44</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.359998, -70.806774</t>
+          <t>-33.3601483, -70.80897</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80677</t>
+          <t>-33.36015, -70.80897</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>01:01:50</t>
+          <t>00:12:09</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>9.76</v>
+        <v>0.36</v>
       </c>
       <c r="M59" t="n">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="N59" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,47 +3849,47 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/07/14 13:22:24</t>
+          <t>2026/07/15 14:06:59</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-33.0559483, -71.4270616</t>
+          <t>-33.36011, -70.808885</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-33.05595, -71.42706</t>
+          <t>-33.36011, -70.80889</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/07/14 13:44:34</t>
+          <t>2026/07/15 15:10:46</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-33.0873466, -71.3623049</t>
+          <t>-33.3662733, -70.6955083</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36230</t>
+          <t>-33.36627, -70.69551</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:22:10</t>
+          <t>01:03:47</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>8.44</v>
+        <v>13.98</v>
       </c>
       <c r="M60" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="N60" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61">
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/07/14 13:32:42</t>
+          <t>2026/07/15 14:10:05</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-34.1902183, -70.7094083</t>
+          <t>-33.3672083, -70.69668</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-34.19022, -70.70941</t>
+          <t>-33.36721, -70.69668</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/07/14 14:18:31</t>
+          <t>2026/07/15 14:47:29</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-34.20485, -70.6798033</t>
+          <t>-33.23581, -70.7587866</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-34.20485, -70.67980</t>
+          <t>-33.23581, -70.75879</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:45:49</t>
+          <t>00:37:24</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.42</v>
+        <v>16.72</v>
       </c>
       <c r="M61" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="N61" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/07/14 13:32:59</t>
+          <t>2026/07/15 14:28:42</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-34.1902116, -70.7094066</t>
+          <t>-33.3626216, -70.786885</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-34.19021, -70.70941</t>
+          <t>-33.36262, -70.78688</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/07/14 14:19:11</t>
+          <t>2026/07/15 14:49:02</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-34.2053366, -70.6803249</t>
+          <t>-33.3598433, -70.806775</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68032</t>
+          <t>-33.35984, -70.80678</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:46:12</t>
+          <t>00:20:20</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="M62" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N62" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,57 +4026,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/07/14 13:35:25</t>
+          <t>2026/07/15 14:28:46</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.1902449, -70.7093483</t>
+          <t>-33.361863, -70.787873</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.19024, -70.70935</t>
+          <t>-33.36186, -70.78787</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/07/14 14:25:10</t>
+          <t>2026/07/15 14:47:14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.2044049, -70.679025</t>
+          <t>-33.359937, -70.807016</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.20440, -70.67902</t>
+          <t>-33.35994, -70.80702</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:49:45</t>
+          <t>00:18:28</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.56</v>
+        <v>2.87</v>
       </c>
       <c r="M63" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="N63" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,47 +4085,47 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/07/14 13:44:48</t>
+          <t>2026/07/15 14:43:03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.0873283, -71.3623283</t>
+          <t>-33.3604783, -70.8090416</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36233</t>
+          <t>-33.36048, -70.80904</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/07/14 16:06:26</t>
+          <t>2026/07/15 15:29:09</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.087325, -71.3622866</t>
+          <t>-33.3895116, -70.6738666</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36229</t>
+          <t>-33.38951, -70.67387</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>02:21:38</t>
+          <t>00:46:06</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>11.87</v>
+        <v>17.34</v>
       </c>
       <c r="M64" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="N64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,47 +4144,47 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/07/14 14:09:00</t>
+          <t>2026/07/15 14:47:43</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.360079, -70.806683</t>
+          <t>-33.359985, -70.807191</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80668</t>
+          <t>-33.35999, -70.80719</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/07/14 15:09:39</t>
+          <t>2026/07/15 15:35:35</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.36007, -70.808767</t>
+          <t>-33.359592, -70.810389</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.36007, -70.80877</t>
+          <t>-33.35959, -70.81039</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01:00:39</t>
+          <t>00:47:52</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.5</v>
+        <v>1.19</v>
       </c>
       <c r="M65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
@@ -4203,57 +4203,57 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/07/14 14:18:51</t>
+          <t>2026/07/15 14:48:44</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.2049233, -70.6791316</t>
+          <t>-33.2164483, -70.7670466</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.20492, -70.67913</t>
+          <t>-33.21645, -70.76705</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/07/14 19:16:49</t>
+          <t>2026/07/15 15:31:36</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-32.7918949, -70.8294333</t>
+          <t>-32.8826083, -70.6120516</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-32.79189, -70.82943</t>
+          <t>-32.88261, -70.61205</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>04:57:58</t>
+          <t>00:42:52</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>188.22</v>
+        <v>46.7</v>
       </c>
       <c r="M66" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="N66" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,47 +4262,47 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/07/14 14:20:26</t>
+          <t>2026/07/15 14:49:49</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-34.2042266, -70.6791133</t>
+          <t>-33.3600266, -70.8069683</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-34.20423, -70.67911</t>
+          <t>-33.36003, -70.80697</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/07/14 14:58:07</t>
+          <t>2026/07/15 16:19:51</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-34.2044166, -70.67878</t>
+          <t>-33.0595516, -71.3724283</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-34.20442, -70.67878</t>
+          <t>-33.05955, -71.37243</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>00:37:41</t>
+          <t>01:30:02</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.06</v>
+        <v>116.47</v>
       </c>
       <c r="M67" t="n">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/07/14 14:26:25</t>
+          <t>2026/07/15 15:10:31</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.2046383, -70.67904</t>
+          <t>-32.8792, -70.608815</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.20464, -70.67904</t>
+          <t>-32.87920, -70.60882</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/07/14 14:51:49</t>
+          <t>2026/07/15 19:02:25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-34.2044049, -70.6790233</t>
+          <t>-32.8792116, -70.6088816</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-34.20440, -70.67902</t>
+          <t>-32.87921, -70.60888</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:25:24</t>
+          <t>03:51:54</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.36</v>
+        <v>0.01</v>
       </c>
       <c r="M68" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,57 +4380,57 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/07/14 14:50:54</t>
+          <t>2026/07/15 15:11:51</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-33.360025, -70.8067666</t>
+          <t>-33.367045, -70.6955716</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80677</t>
+          <t>-33.36704, -70.69557</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/07/14 15:43:59</t>
+          <t>2026/07/15 19:46:07</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-33.3599616, -70.806995</t>
+          <t>-33.4647433, -70.607705</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80700</t>
+          <t>-33.46474, -70.60770</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:53:05</t>
+          <t>04:34:16</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.58</v>
+        <v>18.13</v>
       </c>
       <c r="M69" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,57 +4439,57 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/07/14 14:52:23</t>
+          <t>2026/07/15 15:16:58</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-34.204845, -70.6790533</t>
+          <t>-33.36003, -70.807124</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-34.20484, -70.67905</t>
+          <t>-33.36003, -70.80712</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/07/14 15:20:37</t>
+          <t>2026/07/19 11:57:32</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-34.205435, -70.6790266</t>
+          <t>-33.360197, -70.807434</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67903</t>
+          <t>-33.36020, -70.80743</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:28:14</t>
+          <t>92:40:34</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/07/14 14:59:22</t>
+          <t>2026/07/15 15:29:17</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.2050133, -70.6788466</t>
+          <t>-33.3606566, -70.8061333</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.20501, -70.67885</t>
+          <t>-33.36066, -70.80613</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/07/14 18:03:44</t>
+          <t>2026/07/15 15:49:42</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.3895483, -70.6738716</t>
+          <t>-33.3598533, -70.8071016</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.38955, -70.67387</t>
+          <t>-33.35985, -70.80710</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>03:04:22</t>
+          <t>00:20:25</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>101.81</v>
+        <v>0.88</v>
       </c>
       <c r="M71" t="n">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="N71" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/07/14 15:10:31</t>
+          <t>2026/07/15 15:29:42</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.360105, -70.806689</t>
+          <t>-33.3893049, -70.6740016</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80669</t>
+          <t>-33.38930, -70.67400</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/07/14 18:47:39</t>
+          <t>2026/07/15 16:07:40</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.482123, -70.765334</t>
+          <t>-33.3654, -70.6799283</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.48212, -70.76533</t>
+          <t>-33.36540, -70.67993</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>03:37:08</t>
+          <t>00:37:58</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>19.34</v>
+        <v>3.65</v>
       </c>
       <c r="M72" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N72" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/07/14 15:21:52</t>
+          <t>2026/07/15 15:32:51</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-34.2054733, -70.67876</t>
+          <t>-32.8831183, -70.6123816</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67876</t>
+          <t>-32.88312, -70.61238</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/07/14 15:32:47</t>
+          <t>2026/07/15 16:22:00</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-34.2049683, -70.6778549</t>
+          <t>-32.7584366, -70.72939</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-34.20497, -70.67785</t>
+          <t>-32.75844, -70.72939</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:10:55</t>
+          <t>00:49:09</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.2</v>
+        <v>25.08</v>
       </c>
       <c r="M73" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="N73" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,57 +4675,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/07/14 15:33:24</t>
+          <t>2026/07/15 15:36:35</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-34.2049233, -70.6788583</t>
+          <t>-33.359138, -70.809766</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-34.20492, -70.67886</t>
+          <t>-33.35914, -70.80977</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/07/14 15:52:45</t>
+          <t>2026/07/15 15:49:23</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-34.2048683, -70.6792583</t>
+          <t>-33.359963, -70.807099</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-34.20487, -70.67926</t>
+          <t>-33.35996, -70.80710</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:19:21</t>
+          <t>00:12:48</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.04</v>
+        <v>0.42</v>
       </c>
       <c r="M74" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,57 +4734,57 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/07/14 15:44:07</t>
+          <t>2026/07/15 15:49:35</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.3599966, -70.807145</t>
+          <t>-33.359968, -70.807124</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80715</t>
+          <t>-33.35997, -70.80712</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/07/14 19:02:41</t>
+          <t>2026/07/15 16:22:02</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-32.7431749, -70.7330116</t>
+          <t>-33.386261, -70.759307</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-32.74317, -70.73301</t>
+          <t>-33.38626, -70.75931</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>03:18:34</t>
+          <t>00:32:27</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>90</v>
+        <v>7.13</v>
       </c>
       <c r="M75" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="N75" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/07/14 15:54:00</t>
+          <t>2026/07/15 15:50:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-34.204815, -70.67926</t>
+          <t>-33.3598966, -70.807055</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-34.20482, -70.67926</t>
+          <t>-33.35990, -70.80706</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/07/14 18:42:47</t>
+          <t>2026/07/15 17:36:31</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-32.8791066, -70.6092816</t>
+          <t>-32.7431683, -70.733025</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-32.87911, -70.60928</t>
+          <t>-32.74317, -70.73302</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>02:48:47</t>
+          <t>01:46:28</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>163.64</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="N76" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,47 +4852,47 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/07/14 16:07:41</t>
+          <t>2026/07/15 16:08:55</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.0872966, -71.3623166</t>
+          <t>-33.3653549, -70.6799433</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36232</t>
+          <t>-33.36535, -70.67994</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/07/14 16:48:59</t>
+          <t>2026/07/15 16:59:15</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.0872966, -71.3623166</t>
+          <t>-33.362085, -70.6701533</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36232</t>
+          <t>-33.36209, -70.67015</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:41:18</t>
+          <t>00:50:20</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M77" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/07/14 16:49:53</t>
+          <t>2026/07/15 16:21:06</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.0872083, -71.362245</t>
+          <t>-33.0591449, -71.3723866</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.08721, -71.36225</t>
+          <t>-33.05914, -71.37239</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/07/14 18:21:55</t>
+          <t>2026/07/15 16:40:04</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.087265, -71.3622383</t>
+          <t>-33.08705, -71.3619983</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36224</t>
+          <t>-33.08705, -71.36200</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>01:32:02</t>
+          <t>00:18:58</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.01</v>
+        <v>5.14</v>
       </c>
       <c r="M78" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="N78" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,57 +4970,57 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/07/14 18:04:21</t>
+          <t>2026/07/15 16:22:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.3893283, -70.6740666</t>
+          <t>-32.7584766, -70.7293516</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.38933, -70.67407</t>
+          <t>-32.75848, -70.72935</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/07/14 18:44:56</t>
+          <t>2026/07/15 17:25:37</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.3754316, -70.6714666</t>
+          <t>-32.80567, -70.8247283</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.37543, -70.67147</t>
+          <t>-32.80567, -70.82473</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:40:35</t>
+          <t>01:03:24</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.04</v>
+        <v>17.67</v>
       </c>
       <c r="M79" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="N79" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/07/14 18:23:10</t>
+          <t>2026/07/15 16:22:56</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-33.087325, -71.3623016</t>
+          <t>-33.386285, -70.759129</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36230</t>
+          <t>-33.38629, -70.75913</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/07/15 08:27:37</t>
+          <t>2026/07/15 16:31:56</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.0872683, -71.3623066</t>
+          <t>-33.379676, -70.752524</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36231</t>
+          <t>-33.37968, -70.75252</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>14:04:27</t>
+          <t>00:09:00</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.04</v>
+        <v>2.08</v>
       </c>
       <c r="M80" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="N80" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,116 +5088,116 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/07/14 18:43:26</t>
+          <t>2026/07/15 16:32:18</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-32.8792233, -70.6087466</t>
+          <t>-33.379669, -70.752694</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60875</t>
+          <t>-33.37967, -70.75269</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/07/15 09:00:26</t>
+          <t>2026/07/15 17:03:16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.36727, -70.6965783</t>
+          <t>-33.482113, -70.765323</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.36727, -70.69658</t>
+          <t>-33.48211, -70.76532</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>14:17:00</t>
+          <t>00:30:58</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>72.78</v>
+        <v>13.68</v>
       </c>
       <c r="M81" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="N81" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C82" t="n">
+        <v>13</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026/07/15 16:40:42</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-33.0873466, -71.3622499</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-33.08735, -71.36225</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026/07/15 18:22:55</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-33.0873299, -71.3622566</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-33.08733, -71.36226</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>01:42:13</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
         <v>8</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2026/07/14 18:46:11</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-33.3729483, -70.6710666</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-33.37295, -70.67107</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2026/07/14 18:57:43</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-33.3623666, -70.6701466</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>-33.36237, -70.67015</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>00:11:32</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M82" t="n">
-        <v>22</v>
-      </c>
       <c r="N82" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/07/14 18:48:33</t>
+          <t>2026/07/15 16:59:50</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.482178, -70.764895</t>
+          <t>-33.3621033, -70.6702233</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76489</t>
+          <t>-33.36210, -70.67022</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/07/15 08:54:52</t>
+          <t>2026/07/15 20:07:09</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.359961, -70.806992</t>
+          <t>-33.3895, -70.6736916</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80699</t>
+          <t>-33.38950, -70.67369</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>14:06:19</t>
+          <t>03:07:19</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>22.72</v>
+        <v>4.04</v>
       </c>
       <c r="M83" t="n">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="N83" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/07/14 18:58:31</t>
+          <t>2026/07/15 17:04:13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.3622, -70.67015</t>
+          <t>-33.482171, -70.764904</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.36220, -70.67015</t>
+          <t>-33.48217, -70.76490</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/07/14 20:02:28</t>
+          <t>2026/07/15 18:54:01</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.4761199, -70.69851</t>
+          <t>-33.480734, -70.760036</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69851</t>
+          <t>-33.48073, -70.76004</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>01:03:57</t>
+          <t>01:49:48</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>18.12</v>
+        <v>0.51</v>
       </c>
       <c r="M84" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="N84" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/07/14 19:03:15</t>
+          <t>2026/07/15 17:26:52</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-32.7432716, -70.73279</t>
+          <t>-32.805665, -70.82468</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-32.74327, -70.73279</t>
+          <t>-32.80566, -70.82468</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/07/14 19:28:01</t>
+          <t>2026/07/15 17:52:13</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-32.7431599, -70.7296533</t>
+          <t>-32.797695, -70.8874099</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-32.74316, -70.72965</t>
+          <t>-32.79769, -70.88741</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>00:24:46</t>
+          <t>00:25:21</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.38</v>
+        <v>9.74</v>
       </c>
       <c r="M85" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="N85" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/07/14 19:18:04</t>
+          <t>2026/07/15 17:35:34</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-32.7853633, -70.8316833</t>
+          <t>-32.840585, -70.958909</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-32.78536, -70.83168</t>
+          <t>-32.84058, -70.95891</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/07/14 19:28:42</t>
+          <t>2026/07/15 17:50:02</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-32.7832333, -70.8550033</t>
+          <t>-32.840682, -70.959202</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-32.78323, -70.85500</t>
+          <t>-32.84068, -70.95920</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:10:38</t>
+          <t>00:14:28</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.85</v>
+        <v>0.39</v>
       </c>
       <c r="M86" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="N86" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/07/14 19:27:56</t>
+          <t>2026/07/15 17:36:49</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.4363716, -70.6292483</t>
+          <t>-32.7433316, -70.7327116</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.43637, -70.62925</t>
+          <t>-32.74333, -70.73271</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/07/15 13:52:20</t>
+          <t>2026/07/15 21:15:39</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.36227, -70.8072283</t>
+          <t>-32.7431783, -70.729675</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.36227, -70.80723</t>
+          <t>-32.74318, -70.72968</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>18:24:24</t>
+          <t>03:38:50</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>30.19</v>
+        <v>0.78</v>
       </c>
       <c r="M87" t="n">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="N87" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/07/14 19:29:05</t>
+          <t>2026/07/15 17:50:15</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-32.7832299, -70.8549183</t>
+          <t>-32.84104, -70.959322</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-32.78323, -70.85492</t>
+          <t>-32.84104, -70.95932</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/07/14 19:42:48</t>
+          <t>2026/07/15 18:32:27</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-32.7977166, -70.8874216</t>
+          <t>-32.84017, -70.960969</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88742</t>
+          <t>-32.84017, -70.96097</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:13:43</t>
+          <t>00:42:12</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.69</v>
+        <v>21.07</v>
       </c>
       <c r="M88" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="N88" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,57 +5560,57 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/07/14 19:29:16</t>
+          <t>2026/07/15 17:53:28</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-32.7430316, -70.72976</t>
+          <t>-32.7976116, -70.88712</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-32.74303, -70.72976</t>
+          <t>-32.79761, -70.88712</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/07/15 08:20:18</t>
+          <t>2026/07/15 18:37:47</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-33.3599466, -70.8069716</t>
+          <t>-32.7917066, -70.8727516</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80697</t>
+          <t>-32.79171, -70.87275</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>12:51:02</t>
+          <t>00:44:19</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>89.93000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="M89" t="n">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="N89" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/07/14 19:43:30</t>
+          <t>2026/07/15 18:24:10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870733</t>
+          <t>-33.0872466, -71.362245</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88707</t>
+          <t>-33.08725, -71.36225</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/07/15 08:48:07</t>
+          <t>2026/07/18 11:34:09</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.3672366, -70.69658</t>
+          <t>-33.0873266, -71.3622566</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69658</t>
+          <t>-33.08733, -71.36226</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>13:04:37</t>
+          <t>65:09:59</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>100.46</v>
+        <v>0.02</v>
       </c>
       <c r="M90" t="n">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="N90" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/07/14 20:03:43</t>
+          <t>2026/07/15 18:32:49</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-33.4761049, -70.6985133</t>
+          <t>-32.840415, -70.960116</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69851</t>
+          <t>-32.84042, -70.96012</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/07/15 09:20:02</t>
+          <t>2026/07/15 19:09:21</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.4762616, -70.6983149</t>
+          <t>-32.838369, -70.956136</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69831</t>
+          <t>-32.83837, -70.95614</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>13:16:19</t>
+          <t>00:36:32</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.03</v>
+        <v>0.97</v>
       </c>
       <c r="M91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,57 +5737,57 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/07/14 20:10:17</t>
+          <t>2026/07/15 18:38:03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-32.838711, -70.954084</t>
+          <t>-32.7917783, -70.872935</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-32.83871, -70.95408</t>
+          <t>-32.79178, -70.87293</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/07/14 20:50:25</t>
+          <t>2026/07/15 19:19:22</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-32.838367, -70.955739</t>
+          <t>-32.7977149, -70.88742</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95574</t>
+          <t>-32.79771, -70.88742</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>00:40:08</t>
+          <t>00:41:19</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>6.25</v>
+        <v>1.7</v>
       </c>
       <c r="M92" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N92" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/07/14 20:50:47</t>
+          <t>2026/07/15 18:55:01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-32.838363, -70.95554</t>
+          <t>-33.479699, -70.758226</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95554</t>
+          <t>-33.47970, -70.75823</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/07/15 08:50:12</t>
+          <t>2026/07/15 20:02:31</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-32.838373, -70.955507</t>
+          <t>-32.838758, -70.954109</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95551</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>11:59:25</t>
+          <t>01:07:30</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.34</v>
+        <v>95.33</v>
       </c>
       <c r="M93" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="N93" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,47 +5855,47 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/07/15 09:10:55</t>
+          <t>2026/07/15 19:03:40</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.360084, -70.806489</t>
+          <t>-32.87923, -70.6088166</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.36008, -70.80649</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/07/15 12:52:16</t>
+          <t>2026/07/18 13:07:18</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.360003, -70.807175</t>
+          <t>-32.8790916, -70.6093616</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80718</t>
+          <t>-32.87909, -70.60936</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>03:41:21</t>
+          <t>66:03:38</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>0.12</v>
       </c>
       <c r="M94" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/07/15 13:53:23</t>
+          <t>2026/07/15 19:10:01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95551</t>
+          <t>-32.838366, -70.955481</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95551</t>
+          <t>-32.83837, -70.95548</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/07/15 17:34:48</t>
+          <t>2026/07/16 14:53:29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-32.840932, -70.957233</t>
+          <t>-32.840584, -70.99572</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-32.84093, -70.95723</t>
+          <t>-32.84058, -70.99572</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>03:41:25</t>
+          <t>19:43:28</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M95" t="n">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="N95" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,44 +5973,44 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/07/15 14:43:03</t>
+          <t>2026/07/15 19:20:18</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-33.3604783, -70.8090416</t>
+          <t>-32.797605, -70.8870916</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-33.36048, -70.80904</t>
+          <t>-32.79760, -70.88709</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:09</t>
+          <t>2026/07/16 10:28:18</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-33.3895116, -70.6738666</t>
+          <t>-32.7976766, -70.88739</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-33.38951, -70.67387</t>
+          <t>-32.79768, -70.88739</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:46:06</t>
+          <t>15:08:00</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>17.34</v>
+        <v>13.03</v>
       </c>
       <c r="M96" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="N96" t="n">
         <v>26</v>
@@ -6019,11 +6019,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/07/15 15:29:42</t>
+          <t>2026/07/15 19:46:53</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-33.3893049, -70.6740016</t>
+          <t>-33.4643833, -70.60761</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-33.38930, -70.67400</t>
+          <t>-33.46438, -70.60761</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/07/15 16:07:40</t>
+          <t>2026/07/15 21:21:21</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-33.3654, -70.6799283</t>
+          <t>-33.44062, -70.6302983</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-33.36540, -70.67993</t>
+          <t>-33.44062, -70.63030</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:37:58</t>
+          <t>01:34:28</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="M97" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="N97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,47 +6091,47 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/07/15 16:08:55</t>
+          <t>2026/07/15 20:02:41</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.3653549, -70.6799433</t>
+          <t>-32.838757, -70.954109</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.36535, -70.67994</t>
+          <t>-32.83876, -70.95411</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:15</t>
+          <t>2026/07/15 21:31:52</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-33.362085, -70.6701533</t>
+          <t>-32.841759, -70.936896</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-33.36209, -70.67015</t>
+          <t>-32.84176, -70.93690</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:50:20</t>
+          <t>01:29:11</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="M98" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="N98" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/07/15 16:59:50</t>
+          <t>2026/07/15 20:07:32</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-33.3621033, -70.6702233</t>
+          <t>-33.38955, -70.6736383</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67022</t>
+          <t>-33.38955, -70.67364</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:09</t>
+          <t>2026/07/15 20:50:24</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-33.3895, -70.6736916</t>
+          <t>-33.476245, -70.6983</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-33.38950, -70.67369</t>
+          <t>-33.47624, -70.69830</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>03:07:19</t>
+          <t>00:42:52</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.04</v>
+        <v>13.57</v>
       </c>
       <c r="M99" t="n">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="N99" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/07/15 17:35:34</t>
+          <t>2026/07/15 20:51:39</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.840585, -70.958909</t>
+          <t>-33.4761616, -70.698455</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.84058, -70.95891</t>
+          <t>-33.47616, -70.69845</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/07/15 17:50:02</t>
+          <t>2026/07/17 10:16:04</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.840682, -70.959202</t>
+          <t>-33.3621016, -70.67012</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.84068, -70.95920</t>
+          <t>-33.36210, -70.67012</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:14:28</t>
+          <t>37:24:25</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.39</v>
+        <v>18.78</v>
       </c>
       <c r="M100" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="N100" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/07/15 17:50:15</t>
+          <t>2026/07/15 21:16:54</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-32.84104, -70.959322</t>
+          <t>-32.743215, -70.7296266</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-32.84104, -70.95932</t>
+          <t>-32.74321, -70.72963</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/07/15 18:32:27</t>
+          <t>2026/07/19 14:15:29</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-32.84017, -70.960969</t>
+          <t>-32.7431683, -70.729625</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-32.84017, -70.96097</t>
+          <t>-32.74317, -70.72962</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:42:12</t>
+          <t>88:58:35</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>21.07</v>
+        <v>0.48</v>
       </c>
       <c r="M101" t="n">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="N101" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/07/15 18:32:49</t>
+          <t>2026/07/15 21:21:52</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.840415, -70.960116</t>
+          <t>-33.4406216, -70.6302316</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.84042, -70.96012</t>
+          <t>-33.44062, -70.63023</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/07/15 19:09:21</t>
+          <t>2026/07/15 21:40:14</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.838369, -70.956136</t>
+          <t>-33.43623, -70.6295066</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95614</t>
+          <t>-33.43623, -70.62951</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:36:32</t>
+          <t>00:18:22</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="M102" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N102" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/07/15 18:38:03</t>
+          <t>2026/07/15 21:32:18</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.7917783, -70.872935</t>
+          <t>-32.841741, -70.936882</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.79178, -70.87293</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/07/15 19:19:22</t>
+          <t>2026/07/16 11:02:40</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.88742</t>
+          <t>-32.840636, -70.958522</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88742</t>
+          <t>-32.84064, -70.95852</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:41:19</t>
+          <t>13:30:22</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.7</v>
+        <v>2.86</v>
       </c>
       <c r="M103" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="N103" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/07/15 18:55:01</t>
+          <t>2026/07/15 21:41:29</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-33.479699, -70.758226</t>
+          <t>-33.4364349, -70.6291566</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-33.47970, -70.75823</t>
+          <t>-33.43643, -70.62916</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/07/15 20:02:31</t>
+          <t>2026/07/17 13:33:27</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-32.838758, -70.954109</t>
+          <t>-33.428385, -70.6207366</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-32.83876, -70.95411</t>
+          <t>-33.42838, -70.62074</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>01:07:30</t>
+          <t>39:51:58</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>95.33</v>
+        <v>1.5</v>
       </c>
       <c r="M104" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="N104" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/07/15 19:10:01</t>
+          <t>2026/07/17 16:51:20</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.838366, -70.955481</t>
+          <t>-33.3665833, -70.6954649</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95548</t>
+          <t>-33.36658, -70.69546</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/07/16 14:53:29</t>
+          <t>2026/07/17 17:48:13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.840584, -70.99572</t>
+          <t>-33.4358716, -70.6300966</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.84058, -70.99572</t>
+          <t>-33.43587, -70.63010</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>19:43:28</t>
+          <t>00:56:53</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>8.380000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="M105" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="N105" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/07/15 19:20:18</t>
+          <t>2026/07/17 17:49:25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.797605, -70.8870916</t>
+          <t>-33.43628, -70.629375</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88709</t>
+          <t>-33.43628, -70.62937</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/07/16 10:28:18</t>
+          <t>2026/07/19 15:13:00</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-32.7976766, -70.88739</t>
+          <t>-33.4296566, -70.6486349</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-32.79768, -70.88739</t>
+          <t>-33.42966, -70.64863</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>15:08:00</t>
+          <t>45:23:35</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>13.03</v>
+        <v>4.21</v>
       </c>
       <c r="M106" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N106" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/07/15 19:46:53</t>
+          <t>2026/07/18 10:37:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-33.4643833, -70.60761</t>
+          <t>-33.55173, -70.8447033</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-33.46438, -70.60761</t>
+          <t>-33.55173, -70.84470</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/07/15 21:21:21</t>
+          <t>2026/07/18 11:41:27</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-33.44062, -70.6302983</t>
+          <t>-33.3671116, -70.6954666</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-33.44062, -70.63030</t>
+          <t>-33.36711, -70.69547</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>01:34:28</t>
+          <t>01:04:27</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.5</v>
+        <v>35.8</v>
       </c>
       <c r="M107" t="n">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="N107" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,116 +6681,116 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/07/15 20:02:41</t>
+          <t>2026/07/18 11:42:39</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-32.838757, -70.954109</t>
+          <t>-33.3671433, -70.6958149</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-32.83876, -70.95411</t>
+          <t>-33.36714, -70.69581</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/07/15 21:31:52</t>
+          <t>2026/07/21 13:26:50</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-32.841759, -70.936896</t>
+          <t>-33.3673016, -70.6960216</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-32.84176, -70.93690</t>
+          <t>-33.36730, -70.69602</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>01:29:11</t>
+          <t>73:44:11</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.27</v>
+        <v>7.13</v>
       </c>
       <c r="M108" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N108" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/07/15 20:07:32</t>
+          <t>2026/07/20 02:39:25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-33.38955, -70.6736383</t>
+          <t>-33.367076, -70.696346</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-33.38955, -70.67364</t>
+          <t>-33.36708, -70.69635</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/15 20:50:24</t>
+          <t>2026/07/21 21:39:00</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-33.476245, -70.6983</t>
+          <t>-33.367076, -70.696346</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69830</t>
+          <t>-33.36708, -70.69635</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:42:52</t>
+          <t>42:59:35</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>13.57</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,116 +6799,116 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/07/15 20:51:39</t>
+          <t>2026/07/20 13:53:06</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-33.4761616, -70.698455</t>
+          <t>-33.3599783, -70.8071533</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69845</t>
+          <t>-33.35998, -70.80715</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/17 10:16:04</t>
+          <t>2026/07/20 16:06:45</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-33.3621016, -70.67012</t>
+          <t>-32.7432333, -70.7329216</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-33.36210, -70.67012</t>
+          <t>-32.74323, -70.73292</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>37:24:25</t>
+          <t>02:13:39</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>18.78</v>
+        <v>89.72</v>
       </c>
       <c r="M110" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="N110" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/07/15 21:21:52</t>
+          <t>2026/07/20 13:58:00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-33.4406216, -70.6302316</t>
+          <t>-33.087305, -71.362325</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-33.44062, -70.63023</t>
+          <t>-33.08731, -71.36232</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/15 21:40:14</t>
+          <t>2026/07/21 21:52:20</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-33.43623, -70.6295066</t>
+          <t>-33.0871283, -71.3622183</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-33.43623, -70.62951</t>
+          <t>-33.08713, -71.36222</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:18:22</t>
+          <t>31:54:20</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.74</v>
+        <v>0.02</v>
       </c>
       <c r="M111" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,53 +6917,53 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/07/15 21:32:18</t>
+          <t>2026/07/20 14:29:28</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-32.841741, -70.936882</t>
+          <t>-32.8330833, -70.5958083</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-32.84174, -70.93688</t>
+          <t>-32.83308, -70.59581</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/16 11:02:40</t>
+          <t>2026/07/20 15:11:02</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-32.840636, -70.958522</t>
+          <t>-32.8666599, -70.624135</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-32.84064, -70.95852</t>
+          <t>-32.86666, -70.62413</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>13:30:22</t>
+          <t>00:41:34</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.86</v>
+        <v>6.72</v>
       </c>
       <c r="M112" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="N112" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6976,53 +6976,53 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/07/15 21:41:29</t>
+          <t>2026/07/20 15:12:17</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.4364349, -70.6291566</t>
+          <t>-32.8667333, -70.6243433</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.43643, -70.62916</t>
+          <t>-32.86673, -70.62434</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/17 13:33:27</t>
+          <t>2026/07/20 15:36:34</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.428385, -70.6207366</t>
+          <t>-32.87687, -70.609585</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.42838, -70.62074</t>
+          <t>-32.87687, -70.60958</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>39:51:58</t>
+          <t>00:24:17</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.5</v>
+        <v>4.21</v>
       </c>
       <c r="M113" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N113" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -7035,53 +7035,53 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/07/17 16:21:04</t>
+          <t>2026/07/20 15:37:31</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.3671066, -70.6958466</t>
+          <t>-32.8765083, -70.609945</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.36711, -70.69585</t>
+          <t>-32.87651, -70.60994</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/17 16:50:18</t>
+          <t>2026/07/20 16:47:10</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.368485, -70.6971799</t>
+          <t>-32.8793933, -70.6088766</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.36848, -70.69718</t>
+          <t>-32.87939, -70.60888</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:29:14</t>
+          <t>01:09:39</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.24</v>
+        <v>0.9</v>
       </c>
       <c r="M114" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -7094,53 +7094,53 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/07/17 16:51:20</t>
+          <t>2026/07/20 16:07:02</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.3665833, -70.6954649</t>
+          <t>-32.7433483, -70.73267</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.36658, -70.69546</t>
+          <t>-32.74335, -70.73267</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/17 17:48:13</t>
+          <t>2026/07/20 16:17:37</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.4358716, -70.6300966</t>
+          <t>-32.7431966, -70.7296633</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.43587, -70.63010</t>
+          <t>-32.74320, -70.72966</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:56:53</t>
+          <t>00:10:35</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>13.29</v>
+        <v>0.36</v>
       </c>
       <c r="M115" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="N115" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -7153,57 +7153,57 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/07/17 17:49:25</t>
+          <t>2026/07/20 16:17:45</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-33.43628, -70.629375</t>
+          <t>-32.7432399, -70.7296166</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-33.43628, -70.62937</t>
+          <t>-32.74324, -70.72962</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/19 15:13:00</t>
+          <t>2026/07/20 17:05:10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-33.4296566, -70.6486349</t>
+          <t>-32.7443383, -70.7300983</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-33.42966, -70.64863</t>
+          <t>-32.74434, -70.73010</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>45:23:35</t>
+          <t>00:47:25</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4.21</v>
+        <v>0.25</v>
       </c>
       <c r="M116" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="N116" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,234 +7212,234 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/07/18 10:37:00</t>
+          <t>2026/07/20 16:48:01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-33.55173, -70.8447033</t>
+          <t>-32.8792216, -70.6088016</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-33.55173, -70.84470</t>
+          <t>-32.87922, -70.60880</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/07/18 11:41:27</t>
+          <t>2026/07/20 20:16:06</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-33.3671116, -70.6954666</t>
+          <t>-32.8792416, -70.6089033</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-33.36711, -70.69547</t>
+          <t>-32.87924, -70.60890</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>01:04:27</t>
+          <t>03:28:05</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>35.8</v>
+        <v>13.91</v>
       </c>
       <c r="M117" t="n">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="N117" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/07/18 11:42:39</t>
+          <t>2026/07/20 17:05:47</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-33.3671433, -70.6958149</t>
+          <t>-32.7432966, -70.7327783</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-33.36714, -70.69581</t>
+          <t>-32.74330, -70.73278</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/07/20 23:42:39</t>
+          <t>2026/07/20 19:38:49</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-33.3671433, -70.6958149</t>
+          <t>-32.7431749, -70.72968</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-33.36714, -70.69581</t>
+          <t>-32.74317, -70.72968</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>60:00:00</t>
+          <t>02:33:02</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/07/20 02:39:25</t>
+          <t>2026/07/20 19:40:04</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-33.367076, -70.696346</t>
+          <t>-32.7431333, -70.72971</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-33.36708, -70.69635</t>
+          <t>-32.74313, -70.72971</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/07/20 23:39:23</t>
+          <t>2026/07/21 08:28:24</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.367076, -70.696346</t>
+          <t>-33.3599449, -70.8069633</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.36708, -70.69635</t>
+          <t>-33.35994, -70.80696</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>20:59:58</t>
+          <t>12:48:20</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>90.17</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/07/20 13:58:00</t>
+          <t>2026/07/20 20:16:20</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.087305, -71.362325</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.08731, -71.36232</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/07/20 23:28:49</t>
+          <t>2026/07/21 08:15:52</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.0872533, -71.36223</t>
+          <t>-32.88247, -70.6115716</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.08725, -71.36223</t>
+          <t>-32.88247, -70.61157</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>09:30:49</t>
+          <t>11:59:32</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.01</v>
+        <v>15.17</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,37 +7448,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/07/20 14:02:11</t>
+          <t>2026/07/20 22:53:35</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8870866</t>
+          <t>-32.838364, -70.955511</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88709</t>
+          <t>-32.83836, -70.95551</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/20 22:02:11</t>
+          <t>2026/07/21 21:51:23</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8870866</t>
+          <t>-32.838364, -70.955511</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88709</t>
+          <t>-32.83836, -70.95551</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>22:57:48</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -7494,70 +7494,70 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/07/20 16:17:45</t>
+          <t>2026/07/21 13:28:05</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.7432399, -70.7296166</t>
+          <t>-33.3673033, -70.695955</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.74324, -70.72962</t>
+          <t>-33.36730, -70.69595</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/20 17:05:10</t>
+          <t>2026/07/21 21:29:02</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.7443383, -70.7300983</t>
+          <t>-33.3673033, -70.695955</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.74434, -70.73010</t>
+          <t>-33.36730, -70.69595</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:47:25</t>
+          <t>08:00:57</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,37 +7566,37 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/07/20 16:30:53</t>
+          <t>2026/07/21 15:11:26</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-33.4761683, -70.6984416</t>
+          <t>-32.797595, -70.8870683</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69844</t>
+          <t>-32.79760, -70.88707</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/20 22:31:00</t>
+          <t>2026/07/21 21:11:26</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-33.4761683, -70.6984416</t>
+          <t>-32.797595, -70.8870683</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69844</t>
+          <t>-32.79760, -70.88707</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>06:00:07</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -7612,11 +7612,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,37 +7625,37 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/07/20 16:56:39</t>
+          <t>2026/07/21 18:55:38</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-33.482176, -70.764889</t>
+          <t>-32.7430433, -70.7297816</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76489</t>
+          <t>-32.74304, -70.72978</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/20 23:00:03</t>
+          <t>2026/07/21 20:55:38</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-33.482176, -70.764889</t>
+          <t>-32.7430433, -70.7297816</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76489</t>
+          <t>-32.74304, -70.72978</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>06:03:24</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -7671,70 +7671,70 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/07/20 17:05:47</t>
+          <t>2026/07/21 19:09:20</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-32.7432966, -70.7327783</t>
+          <t>-33.4361516, -70.6295333</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-32.74330, -70.73278</t>
+          <t>-33.43615, -70.62953</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/20 19:38:49</t>
+          <t>2026/07/21 21:09:20</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-32.7431749, -70.72968</t>
+          <t>-33.4361516, -70.6295333</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-32.74317, -70.72968</t>
+          <t>-33.43615, -70.62953</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>02:33:02</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,164 +7743,46 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/07/20 19:40:04</t>
+          <t>2026/07/21 20:16:24</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-32.7431333, -70.72971</t>
+          <t>-32.841737, -70.936815</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-32.74313, -70.72971</t>
+          <t>-32.84174, -70.93681</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/20 23:40:29</t>
+          <t>2026/07/21 22:19:28</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-32.743045, -70.7297683</t>
+          <t>-32.841737, -70.936815</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-32.74305, -70.72977</t>
+          <t>-32.84174, -70.93681</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>04:00:25</t>
+          <t>02:03:04</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>9</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026/07/20 20:16:20</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2026/07/20 22:16:20</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>5</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026/07/20 20:35:17</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-33.4371483, -70.6294466</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-33.43715, -70.62945</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2026/07/20 22:36:07</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-33.43715, -70.629445</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-33.43715, -70.62945</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>02:00:50</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7952,16 +7834,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1187.64</v>
+        <v>1015.51</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -7971,13 +7853,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>339.69</v>
+        <v>331.67</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>140</v>
@@ -7990,10 +7872,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>410.86</v>
+        <v>347.93</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8009,16 +7891,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>592.24</v>
+        <v>600.12</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -8047,7 +7929,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -8180,16 +8062,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>691.37</v>
+        <v>672.64</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -8199,7 +8081,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235.14</v>
+        <v>224.71</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -8218,10 +8100,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77.44</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -8256,13 +8138,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
         <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
@@ -8275,16 +8157,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>535.0599999999999</v>
+        <v>272.36</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -8294,10 +8176,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>466.87</v>
+        <v>532.1799999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/21 22:01:21</t>
+          <t>2026/07/21 23:01:39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>165:59:44</t>
+          <t>167:00:02</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/21 22:11:23</t>
+          <t>2026/07/21 23:11:21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>165:59:55</t>
+          <t>166:59:53</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/21 22:13:39</t>
+          <t>2026/07/21 23:13:15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>166:00:18</t>
+          <t>166:59:54</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/21 22:24:37</t>
+          <t>2026/07/21 23:24:09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>165:58:25</t>
+          <t>166:57:57</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/21 21:31:51</t>
+          <t>2026/07/21 23:32:03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>165:00:30</t>
+          <t>167:00:42</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/21 21:34:57</t>
+          <t>2026/07/21 23:34:53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>164:59:53</t>
+          <t>166:59:49</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/21 21:56:10</t>
+          <t>2026/07/21 23:56:10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>164:59:59</t>
+          <t>166:59:59</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/21 21:57:22</t>
+          <t>2026/07/21 23:57:20</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>164:59:36</t>
+          <t>166:59:34</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/21 21:39:00</t>
+          <t>2026/07/21 23:41:19</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>42:59:35</t>
+          <t>45:01:54</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/21 21:52:20</t>
+          <t>2026/07/21 23:52:20</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>31:54:20</t>
+          <t>33:54:20</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/07/21 21:51:23</t>
+          <t>2026/07/21 23:51:23</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>22:57:48</t>
+          <t>24:57:48</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/07/21 21:29:02</t>
+          <t>2026/07/21 23:29:02</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>08:00:57</t>
+          <t>10:00:57</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/07/21 21:11:26</t>
+          <t>2026/07/21 23:11:26</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/07/21 20:55:38</t>
+          <t>2026/07/21 22:55:38</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/07/21 21:09:20</t>
+          <t>2026/07/21 23:09:20</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/07/21 22:19:28</t>
+          <t>2026/07/21 23:19:28</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>02:03:04</t>
+          <t>03:03:04</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7783,6 +7783,124 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>16</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026/07/21 20:54:58</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-33.4761583, -70.698465</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-33.47616, -70.69846</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026/07/21 22:54:58</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-33.4761583, -70.698465</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-33.47616, -70.69846</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>7</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026/07/21 21:46:46</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-32.8792099, -70.6088216</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-32.87921, -70.60882</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026/07/21 23:46:46</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-32.8792099, -70.6088216</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-32.87921, -70.60882</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8068,7 +8186,7 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>120</v>
@@ -8157,13 +8275,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>272.36</v>
+        <v>272.35</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>138</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/15 04:00:00   Hasta : 2026/07/22 03:59:59</t>
+          <t>Desde : 2026/07/16 04:00:00   Hasta : 2026/07/23 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/07/15 00:01:37</t>
+          <t>2026/07/16 00:01:52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/07/21 23:01:39</t>
+          <t>2026/07/22 22:01:28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-34.345929, -71.125846</t>
+          <t>-34.345908, -71.125861</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.34593, -71.12585</t>
+          <t>-34.34591, -71.12586</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>167:00:02</t>
+          <t>165:59:36</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,47 +604,47 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/07/15 00:03:55</t>
+          <t>2026/07/16 00:07:57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.4761049, -70.6985133</t>
+          <t>-32.838366, -70.955481</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69851</t>
+          <t>-32.83837, -70.95548</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/07/15 09:20:02</t>
+          <t>2026/07/16 14:53:29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.4762616, -70.6983149</t>
+          <t>-32.840584, -70.99572</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69831</t>
+          <t>-32.84058, -70.99572</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>09:16:07</t>
+          <t>14:45:32</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.03</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/07/15 00:11:28</t>
+          <t>2026/07/16 00:11:39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -678,38 +678,38 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/07/21 23:11:21</t>
+          <t>2026/07/22 01:13:47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.205371, -70.677398</t>
+          <t>-34.205224, -70.677378</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67740</t>
+          <t>-34.20522, -70.67738</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>166:59:53</t>
+          <t>145:02:08</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/07/15 00:13:21</t>
+          <t>2026/07/16 00:12:55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.360017, -70.807084</t>
+          <t>-33.360083, -70.807058</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80708</t>
+          <t>-33.36008, -70.80706</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/07/21 23:13:15</t>
+          <t>2026/07/19 11:57:32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.360034, -70.807056</t>
+          <t>-33.360197, -70.807434</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80706</t>
+          <t>-33.36020, -70.80743</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>166:59:54</t>
+          <t>83:44:37</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,41 +781,41 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/07/15 00:26:12</t>
+          <t>2026/07/16 00:13:20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.87625, -71.127289</t>
+          <t>-33.360017, -70.807084</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.87625, -71.12729</t>
+          <t>-33.36002, -70.80708</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/07/21 23:24:09</t>
+          <t>2026/07/22 22:13:38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.876573, -71.127266</t>
+          <t>-33.360025, -70.807068</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.87657, -71.12727</t>
+          <t>-33.36003, -70.80707</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:57:57</t>
+          <t>166:00:18</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/07/15 00:26:27</t>
+          <t>2026/07/16 00:24:22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.3601, -70.807159</t>
+          <t>-33.0872466, -71.362245</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80716</t>
+          <t>-33.08725, -71.36225</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/07/15 09:10:23</t>
+          <t>2026/07/18 11:34:09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.360117, -70.806631</t>
+          <t>-33.0873266, -71.3622566</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.36012, -70.80663</t>
+          <t>-33.08733, -71.36226</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>08:43:56</t>
+          <t>59:09:47</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -899,41 +899,41 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/07/15 00:31:21</t>
+          <t>2026/07/16 00:27:02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.899781, -71.42949</t>
+          <t>-34.87625, -71.127289</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.89978, -71.42949</t>
+          <t>-34.87625, -71.12729</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/07/21 23:32:03</t>
+          <t>2026/07/22 22:23:11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.899813, -71.429474</t>
+          <t>-34.876409, -71.127162</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.89981, -71.42947</t>
+          <t>-34.87641, -71.12716</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>167:00:42</t>
+          <t>165:56:09</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/07/15 00:33:04</t>
+          <t>2026/07/16 00:31:38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-33.0872416, -71.3622349</t>
+          <t>-33.899781, -71.42949</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-33.08724, -71.36223</t>
+          <t>-33.89978, -71.42949</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/07/15 08:27:37</t>
+          <t>2026/07/22 22:31:39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.0872683, -71.3623066</t>
+          <t>-33.899866, -71.42943</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36231</t>
+          <t>-33.89987, -71.42943</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>07:54:33</t>
+          <t>166:00:01</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>0.02</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>VOLKSWAGEN AMAROK KPDV-13</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/07/15 00:35:04</t>
+          <t>2026/07/16 00:35:22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-34.579616, -70.961324</t>
+          <t>-32.841741, -70.936882</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-34.57962, -70.96132</t>
+          <t>-32.84174, -70.93688</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/07/21 23:34:53</t>
+          <t>2026/07/16 11:02:40</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-34.57967, -70.96146</t>
+          <t>-32.840636, -70.958522</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.57967, -70.96146</t>
+          <t>-32.84064, -70.95852</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>166:59:49</t>
+          <t>10:27:18</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,58 +1071,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/07/15 00:41:32</t>
+          <t>2026/07/16 00:35:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.365999, -70.696202</t>
+          <t>-34.579616, -70.961324</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.36600, -70.69620</t>
+          <t>-34.57962, -70.96132</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/07/20 01:41:36</t>
+          <t>2026/07/22 21:34:38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.367076, -70.696346</t>
+          <t>-34.579707, -70.961419</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.36708, -70.69635</t>
+          <t>-34.57971, -70.96142</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>121:00:04</t>
+          <t>164:59:15</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/07/15 00:43:26</t>
+          <t>2026/07/16 00:39:25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-32.8792233, -70.6087466</t>
+          <t>-33.365999, -70.696202</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60875</t>
+          <t>-33.36600, -70.69620</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/07/15 09:00:26</t>
+          <t>2026/07/20 01:41:36</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.36727, -70.6965783</t>
+          <t>-33.367076, -70.696346</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36727, -70.69658</t>
+          <t>-33.36708, -70.69635</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>08:17:00</t>
+          <t>97:02:11</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>72.78</v>
+        <v>0.14</v>
       </c>
       <c r="M14" t="n">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1194,53 +1194,53 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/07/15 00:48:19</t>
+          <t>2026/07/16 00:56:09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-32.838363, -70.95554</t>
+          <t>-33.4761616, -70.698455</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95554</t>
+          <t>-33.47616, -70.69845</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/07/15 08:50:12</t>
+          <t>2026/07/17 10:16:04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-32.838373, -70.955507</t>
+          <t>-33.3621016, -70.67012</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95551</t>
+          <t>-33.36210, -70.67012</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08:01:53</t>
+          <t>33:19:55</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>18.78</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN AMAROK KPDV-13</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,58 +1248,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/07/15 00:51:39</t>
+          <t>2026/07/16 00:56:11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.482178, -70.764895</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76489</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/07/15 08:54:52</t>
+          <t>2026/07/22 21:56:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.359961, -70.806992</t>
+          <t>-33.367368, -70.696671</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80699</t>
+          <t>-33.36737, -70.69667</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>08:03:13</t>
+          <t>164:59:59</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>22.72</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,41 +1312,41 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/07/15 00:56:11</t>
+          <t>2026/07/16 00:59:14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.042558, -70.6817</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.04256, -70.68170</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/07/21 23:56:10</t>
+          <t>2026/07/22 21:57:38</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.367368, -70.696671</t>
+          <t>-34.042545, -70.681829</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69667</t>
+          <t>-34.04254, -70.68183</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>166:59:59</t>
+          <t>164:58:24</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/07/15 00:57:46</t>
+          <t>2026/07/16 01:02:21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-34.042558, -70.6817</t>
+          <t>-33.3672816, -70.69573</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-34.04256, -70.68170</t>
+          <t>-33.36728, -70.69573</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/07/21 23:57:20</t>
+          <t>2026/07/18 09:59:20</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-34.042665, -70.681704</t>
+          <t>-33.4640433, -70.6511716</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68170</t>
+          <t>-33.46404, -70.65117</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>166:59:34</t>
+          <t>56:56:59</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.04</v>
+        <v>16.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,53 +1430,53 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/07/15 01:02:21</t>
+          <t>2026/07/16 01:12:02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t